--- a/pattern_signals.xlsx
+++ b/pattern_signals.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Signals"/>
+    <sheet sheetId="1" name="Signals" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="200">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -443,42 +443,219 @@
   </si>
   <si>
     <t>2026-02-19 15:43</t>
+  </si>
+  <si>
+    <t>NSE:ADANIENSOL-EQ_BEAR_1771479900_1771560000</t>
+  </si>
+  <si>
+    <t>NSE:ADANIENSOL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 09:30</t>
+  </si>
+  <si>
+    <t>2026-02-20 09:45</t>
+  </si>
+  <si>
+    <t>NSE:ADANIENT-EQ_BEAR_1771475400_1771572600</t>
+  </si>
+  <si>
+    <t>NSE:ADANIENT-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 13:00</t>
+  </si>
+  <si>
+    <t>2026-02-20 13:20</t>
+  </si>
+  <si>
+    <t>NSE:AMBER-EQ_BEAR_1771489800_1771570800</t>
+  </si>
+  <si>
+    <t>NSE:AMBER-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 12:30</t>
+  </si>
+  <si>
+    <t>NSE:KFINTECH-EQ_BEAR_1771559100_1771571700</t>
+  </si>
+  <si>
+    <t>NSE:KFINTECH-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 09:15</t>
+  </si>
+  <si>
+    <t>2026-02-20 12:45</t>
+  </si>
+  <si>
+    <t>NSE:PHOENIXLTD-EQ_BEAR_1771473600_1771559100</t>
+  </si>
+  <si>
+    <t>NSE:PHOENIXLTD-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 13:21</t>
+  </si>
+  <si>
+    <t>NSE:UNITDSPR-EQ_BEAR_1771481700_1771561800</t>
+  </si>
+  <si>
+    <t>NSE:UNITDSPR-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 10:00</t>
+  </si>
+  <si>
+    <t>NSE:APLAPOLLO-EQ_BEAR_1771472700_1771573500</t>
+  </si>
+  <si>
+    <t>NSE:APLAPOLLO-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 13:15</t>
+  </si>
+  <si>
+    <t>2026-02-20 13:30</t>
+  </si>
+  <si>
+    <t>NSE:JUBLFOOD-EQ_BULL_1771571700_1771573500</t>
+  </si>
+  <si>
+    <t>NSE:JUBLFOOD-EQ</t>
+  </si>
+  <si>
+    <t>NSE:TIINDIA-EQ_BULL_1771475400_1771573500</t>
+  </si>
+  <si>
+    <t>NSE:TIINDIA-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 13:31</t>
+  </si>
+  <si>
+    <t>NSE:NTPC-EQ_BULL_1771565400_1771574400</t>
+  </si>
+  <si>
+    <t>2026-02-20 11:00</t>
+  </si>
+  <si>
+    <t>2026-02-20 13:48</t>
+  </si>
+  <si>
+    <t>NSE:BLUESTARCO-EQ_BEAR_1771481700_1771579800</t>
+  </si>
+  <si>
+    <t>2026-02-20 15:00</t>
+  </si>
+  <si>
+    <t>2026-02-20 15:16</t>
+  </si>
+  <si>
+    <t>NSE:INFY-EQ_BEAR_1771482600_1771579800</t>
+  </si>
+  <si>
+    <t>NSE:INFY-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-19 12:00</t>
+  </si>
+  <si>
+    <t>NSE:MANKIND-EQ_BEAR_1771482600_1771579800</t>
+  </si>
+  <si>
+    <t>NSE:MANKIND-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 15:17</t>
+  </si>
+  <si>
+    <t>NSE:ULTRACEMCO-EQ_BEAR_1771479900_1771579800</t>
+  </si>
+  <si>
+    <t>NSE:BRITANNIA-EQ_BEAR_1771488000_1771580700</t>
+  </si>
+  <si>
+    <t>NSE:BRITANNIA-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 15:15</t>
+  </si>
+  <si>
+    <t>2026-02-20 15:30</t>
+  </si>
+  <si>
+    <t>NSE:KEI-EQ_BULL_1771563600_1771580700</t>
+  </si>
+  <si>
+    <t>NSE:KEI-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 10:30</t>
+  </si>
+  <si>
+    <t>NSE:MFSL-EQ_BULL_1771564500_1771580700</t>
+  </si>
+  <si>
+    <t>NSE:MFSL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 10:45</t>
+  </si>
+  <si>
+    <t>NSE:TORNTPHARM-EQ_BULL_1771567200_1771580700</t>
+  </si>
+  <si>
+    <t>NSE:TORNTPHARM-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 11:30</t>
+  </si>
+  <si>
+    <t>2026-02-20 15:31</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;₹&quot;#,##0.00"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FFffffff"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color rgb="FFffffff"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
       <family val="2"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -500,8 +677,18 @@
         <fgColor rgb="FFfce4d6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -524,51 +711,67 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -862,26 +1065,23 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N46"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N64"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="9" width="30.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="9" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="9" width="20.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="9" width="22.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="10" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="9" width="22.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="10" width="20.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="10" width="20.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="10" width="22.005" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="9" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="9" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="9" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="9" width="16.005" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="9" width="22.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="30.005" customWidth="1"/>
+    <col min="2" max="2" width="14.005" customWidth="1"/>
+    <col min="3" max="3" width="20.005" customWidth="1"/>
+    <col min="4" max="4" width="22.005" customWidth="1"/>
+    <col min="5" max="5" width="18.005" customWidth="1"/>
+    <col min="6" max="6" width="22.005" customWidth="1"/>
+    <col min="7" max="8" width="20.005" customWidth="1"/>
+    <col min="9" max="9" width="22.005" customWidth="1"/>
+    <col min="10" max="12" width="18.005" customWidth="1"/>
+    <col min="13" max="13" width="16.005" customWidth="1"/>
+    <col min="14" max="14" width="22.005" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="24">
+    <row r="1" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -915,7 +1115,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row r="2" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -949,7 +1149,7 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row r="3" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
@@ -983,7 +1183,7 @@
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row r="4" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
@@ -1017,7 +1217,7 @@
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row r="5" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>22</v>
       </c>
@@ -1051,7 +1251,7 @@
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row r="6" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>26</v>
       </c>
@@ -1085,7 +1285,7 @@
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row r="7" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>29</v>
       </c>
@@ -1119,7 +1319,7 @@
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row r="8" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>32</v>
       </c>
@@ -1153,7 +1353,7 @@
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row r="9" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>36</v>
       </c>
@@ -1187,7 +1387,7 @@
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row r="10" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
@@ -1221,7 +1421,7 @@
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row r="11" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>44</v>
       </c>
@@ -1255,7 +1455,7 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row r="12" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>47</v>
       </c>
@@ -1289,7 +1489,7 @@
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row r="13" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>50</v>
       </c>
@@ -1323,7 +1523,7 @@
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row r="14" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>55</v>
       </c>
@@ -1357,7 +1557,7 @@
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row r="15" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>58</v>
       </c>
@@ -1391,7 +1591,7 @@
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row r="16" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>61</v>
       </c>
@@ -1425,7 +1625,7 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row r="17" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>64</v>
       </c>
@@ -1459,7 +1659,7 @@
       <c r="M17" s="5"/>
       <c r="N17" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row r="18" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>66</v>
       </c>
@@ -1493,7 +1693,7 @@
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row r="19" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>70</v>
       </c>
@@ -1527,7 +1727,7 @@
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row r="20" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>73</v>
       </c>
@@ -1561,7 +1761,7 @@
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row r="21" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>77</v>
       </c>
@@ -1595,7 +1795,7 @@
       <c r="M21" s="5"/>
       <c r="N21" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row r="22" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>79</v>
       </c>
@@ -1629,7 +1829,7 @@
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row r="23" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>82</v>
       </c>
@@ -1663,7 +1863,7 @@
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row r="24" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>85</v>
       </c>
@@ -1697,7 +1897,7 @@
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row r="25" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>87</v>
       </c>
@@ -1731,7 +1931,7 @@
       <c r="M25" s="5"/>
       <c r="N25" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row r="26" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>90</v>
       </c>
@@ -1765,7 +1965,7 @@
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row r="27" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>94</v>
       </c>
@@ -1799,7 +1999,7 @@
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row r="28" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>97</v>
       </c>
@@ -1833,7 +2033,7 @@
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row r="29" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>98</v>
       </c>
@@ -1867,7 +2067,7 @@
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row r="30" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>101</v>
       </c>
@@ -1901,7 +2101,7 @@
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+    <row r="31" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>104</v>
       </c>
@@ -1935,7 +2135,7 @@
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+    <row r="32" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>107</v>
       </c>
@@ -1969,7 +2169,7 @@
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+    <row r="33" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>111</v>
       </c>
@@ -2003,7 +2203,7 @@
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+    <row r="34" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>114</v>
       </c>
@@ -2037,7 +2237,7 @@
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+    <row r="35" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>117</v>
       </c>
@@ -2071,7 +2271,7 @@
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+    <row r="36" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>119</v>
       </c>
@@ -2105,7 +2305,7 @@
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+    <row r="37" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>120</v>
       </c>
@@ -2139,7 +2339,7 @@
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+    <row r="38" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>122</v>
       </c>
@@ -2173,7 +2373,7 @@
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+    <row r="39" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>124</v>
       </c>
@@ -2207,7 +2407,7 @@
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
+    <row r="40" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>126</v>
       </c>
@@ -2241,7 +2441,7 @@
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
+    <row r="41" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>128</v>
       </c>
@@ -2275,7 +2475,7 @@
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
+    <row r="42" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>130</v>
       </c>
@@ -2309,7 +2509,7 @@
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
+    <row r="43" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>134</v>
       </c>
@@ -2343,7 +2543,7 @@
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
+    <row r="44" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>136</v>
       </c>
@@ -2377,7 +2577,7 @@
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
+    <row r="45" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>137</v>
       </c>
@@ -2411,7 +2611,7 @@
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
+    <row r="46" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>139</v>
       </c>
@@ -2447,6 +2647,654 @@
         <v>142</v>
       </c>
     </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="E47" s="10">
+        <v>1014.2</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="G47" s="10">
+        <v>1000.65</v>
+      </c>
+      <c r="H47" s="10">
+        <v>989.15</v>
+      </c>
+      <c r="I47" s="10">
+        <v>990.8</v>
+      </c>
+      <c r="J47" s="9"/>
+      <c r="K47" s="9"/>
+      <c r="L47" s="9"/>
+      <c r="M47" s="9"/>
+      <c r="N47" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="E48" s="10">
+        <v>2193.3</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="G48" s="10">
+        <v>2165.4</v>
+      </c>
+      <c r="H48" s="10">
+        <v>2156.5</v>
+      </c>
+      <c r="I48" s="10">
+        <v>2159.4</v>
+      </c>
+      <c r="J48" s="9"/>
+      <c r="K48" s="9"/>
+      <c r="L48" s="9"/>
+      <c r="M48" s="9"/>
+      <c r="N48" s="9" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E49" s="10">
+        <v>7759</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="G49" s="10">
+        <v>7675.5</v>
+      </c>
+      <c r="H49" s="10">
+        <v>7647</v>
+      </c>
+      <c r="I49" s="10">
+        <v>7652</v>
+      </c>
+      <c r="J49" s="9"/>
+      <c r="K49" s="9"/>
+      <c r="L49" s="9"/>
+      <c r="M49" s="9"/>
+      <c r="N49" s="9" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="E50" s="10">
+        <v>1019</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="G50" s="10">
+        <v>1018</v>
+      </c>
+      <c r="H50" s="10">
+        <v>1013.3</v>
+      </c>
+      <c r="I50" s="10">
+        <v>1013.9</v>
+      </c>
+      <c r="J50" s="9"/>
+      <c r="K50" s="9"/>
+      <c r="L50" s="9"/>
+      <c r="M50" s="9"/>
+      <c r="N50" s="9" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A51" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E51" s="10">
+        <v>1753.3</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="G51" s="10">
+        <v>1746.1</v>
+      </c>
+      <c r="H51" s="10">
+        <v>1721.7</v>
+      </c>
+      <c r="I51" s="10">
+        <v>1725.9</v>
+      </c>
+      <c r="J51" s="9"/>
+      <c r="K51" s="9"/>
+      <c r="L51" s="9"/>
+      <c r="M51" s="9"/>
+      <c r="N51" s="9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A52" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E52" s="10">
+        <v>1409.9</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G52" s="10">
+        <v>1393.3</v>
+      </c>
+      <c r="H52" s="10">
+        <v>1383.9</v>
+      </c>
+      <c r="I52" s="10">
+        <v>1384.1</v>
+      </c>
+      <c r="J52" s="9"/>
+      <c r="K52" s="9"/>
+      <c r="L52" s="9"/>
+      <c r="M52" s="9"/>
+      <c r="N52" s="9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A53" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E53" s="10">
+        <v>2223.2</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="G53" s="10">
+        <v>2203.5</v>
+      </c>
+      <c r="H53" s="10">
+        <v>2183.6</v>
+      </c>
+      <c r="I53" s="10">
+        <v>2189</v>
+      </c>
+      <c r="J53" s="9"/>
+      <c r="K53" s="9"/>
+      <c r="L53" s="9"/>
+      <c r="M53" s="9"/>
+      <c r="N53" s="9" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A54" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="E54" s="12">
+        <v>534.55</v>
+      </c>
+      <c r="F54" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="G54" s="12">
+        <v>539.45</v>
+      </c>
+      <c r="H54" s="12">
+        <v>532.15</v>
+      </c>
+      <c r="I54" s="12">
+        <v>538.85</v>
+      </c>
+      <c r="J54" s="11"/>
+      <c r="K54" s="11"/>
+      <c r="L54" s="11"/>
+      <c r="M54" s="11"/>
+      <c r="N54" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A55" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E55" s="12">
+        <v>2502</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="G55" s="12">
+        <v>2558</v>
+      </c>
+      <c r="H55" s="12">
+        <v>2537.7</v>
+      </c>
+      <c r="I55" s="12">
+        <v>2554.8</v>
+      </c>
+      <c r="J55" s="11"/>
+      <c r="K55" s="11"/>
+      <c r="L55" s="11"/>
+      <c r="M55" s="11"/>
+      <c r="N55" s="11" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A56" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="E56" s="12">
+        <v>369.85</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="G56" s="12">
+        <v>372.35</v>
+      </c>
+      <c r="H56" s="12">
+        <v>370.75</v>
+      </c>
+      <c r="I56" s="12">
+        <v>372.3</v>
+      </c>
+      <c r="J56" s="11"/>
+      <c r="K56" s="11"/>
+      <c r="L56" s="11"/>
+      <c r="M56" s="11"/>
+      <c r="N56" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A57" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E57" s="10">
+        <v>1982.4</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="G57" s="10">
+        <v>1976</v>
+      </c>
+      <c r="H57" s="10">
+        <v>1965.6</v>
+      </c>
+      <c r="I57" s="10">
+        <v>1966.6</v>
+      </c>
+      <c r="J57" s="9"/>
+      <c r="K57" s="9"/>
+      <c r="L57" s="9"/>
+      <c r="M57" s="9"/>
+      <c r="N57" s="9" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A58" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="E58" s="10">
+        <v>1381.8</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="G58" s="10">
+        <v>1358.2</v>
+      </c>
+      <c r="H58" s="10">
+        <v>1351.2</v>
+      </c>
+      <c r="I58" s="10">
+        <v>1352.8</v>
+      </c>
+      <c r="J58" s="9"/>
+      <c r="K58" s="9"/>
+      <c r="L58" s="9"/>
+      <c r="M58" s="9"/>
+      <c r="N58" s="9" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A59" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="E59" s="10">
+        <v>2061.1</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="G59" s="10">
+        <v>2041.8</v>
+      </c>
+      <c r="H59" s="10">
+        <v>2026.6</v>
+      </c>
+      <c r="I59" s="10">
+        <v>2028</v>
+      </c>
+      <c r="J59" s="9"/>
+      <c r="K59" s="9"/>
+      <c r="L59" s="9"/>
+      <c r="M59" s="9"/>
+      <c r="N59" s="9" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A60" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="E60" s="10">
+        <v>12907</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="G60" s="10">
+        <v>12812</v>
+      </c>
+      <c r="H60" s="10">
+        <v>12739</v>
+      </c>
+      <c r="I60" s="10">
+        <v>12766</v>
+      </c>
+      <c r="J60" s="9"/>
+      <c r="K60" s="9"/>
+      <c r="L60" s="9"/>
+      <c r="M60" s="9"/>
+      <c r="N60" s="9" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A61" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E61" s="10">
+        <v>6101</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="G61" s="10">
+        <v>6119</v>
+      </c>
+      <c r="H61" s="10">
+        <v>6086</v>
+      </c>
+      <c r="I61" s="10">
+        <v>6088</v>
+      </c>
+      <c r="J61" s="9"/>
+      <c r="K61" s="9"/>
+      <c r="L61" s="9"/>
+      <c r="M61" s="9"/>
+      <c r="N61" s="9" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A62" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="E62" s="12">
+        <v>4613.7</v>
+      </c>
+      <c r="F62" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="G62" s="12">
+        <v>4785</v>
+      </c>
+      <c r="H62" s="12">
+        <v>4741.9</v>
+      </c>
+      <c r="I62" s="12">
+        <v>4782.6</v>
+      </c>
+      <c r="J62" s="11"/>
+      <c r="K62" s="11"/>
+      <c r="L62" s="11"/>
+      <c r="M62" s="11"/>
+      <c r="N62" s="11" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A63" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="E63" s="12">
+        <v>1847.7</v>
+      </c>
+      <c r="F63" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="G63" s="12">
+        <v>1851.9</v>
+      </c>
+      <c r="H63" s="12">
+        <v>1842.2</v>
+      </c>
+      <c r="I63" s="12">
+        <v>1850</v>
+      </c>
+      <c r="J63" s="11"/>
+      <c r="K63" s="11"/>
+      <c r="L63" s="11"/>
+      <c r="M63" s="11"/>
+      <c r="N63" s="11" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A64" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E64" s="12">
+        <v>4232.5</v>
+      </c>
+      <c r="F64" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="G64" s="12">
+        <v>4245</v>
+      </c>
+      <c r="H64" s="12">
+        <v>4212</v>
+      </c>
+      <c r="I64" s="12">
+        <v>4245</v>
+      </c>
+      <c r="J64" s="11"/>
+      <c r="K64" s="11"/>
+      <c r="L64" s="11"/>
+      <c r="M64" s="11"/>
+      <c r="N64" s="11" t="s">
+        <v>199</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pattern_signals.xlsx
+++ b/pattern_signals.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84CDBBBF-5C37-4DAC-8948-6EA944FD2CAB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Signals" state="visible" r:id="rId4"/>
+    <sheet name="Signals" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="431">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -614,48 +615,741 @@
   </si>
   <si>
     <t>2026-02-20 15:31</t>
+  </si>
+  <si>
+    <t>NSE:DIXON-EQ_BEAR_1771320600_1771565400</t>
+  </si>
+  <si>
+    <t>NSE:DIXON-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-17 15:00</t>
+  </si>
+  <si>
+    <t>2026-02-21 13:54</t>
+  </si>
+  <si>
+    <t>NSE:HCLTECH-EQ_BEAR_1771317900_1771559100</t>
+  </si>
+  <si>
+    <t>NSE:HCLTECH-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-17 14:15</t>
+  </si>
+  <si>
+    <t>NSE:HDFCBANK-EQ_BEAR_1771320600_1771572600</t>
+  </si>
+  <si>
+    <t>NSE:HDFCBANK-EQ</t>
+  </si>
+  <si>
+    <t>NSE:HDFCLIFE-EQ_BULL_1771229700_1771494300</t>
+  </si>
+  <si>
+    <t>NSE:HDFCLIFE-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-16 13:45</t>
+  </si>
+  <si>
+    <t>NSE:KALYANKJIL-EQ_BEAR_1771307100_1771475400</t>
+  </si>
+  <si>
+    <t>NSE:KALYANKJIL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-17 11:15</t>
+  </si>
+  <si>
+    <t>2026-02-21 13:55</t>
+  </si>
+  <si>
+    <t>NSE:ASHOKLEY-EQ_BULL_1771570800_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:ASHOKLEY-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 09:15</t>
+  </si>
+  <si>
+    <t>NSE:AUROPHARMA-EQ_BEAR_1771560000_1771826400</t>
+  </si>
+  <si>
+    <t>NSE:AUROPHARMA-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 11:30</t>
+  </si>
+  <si>
+    <t>NSE:AXISBANK-EQ_BULL_1771564500_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:AXISBANK-EQ</t>
+  </si>
+  <si>
+    <t>NSE:BEL-EQ_BEAR_1771571700_1771821900</t>
+  </si>
+  <si>
+    <t>NSE:BEL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 10:15</t>
+  </si>
+  <si>
+    <t>NSE:HUDCO-EQ_BEAR_1771577100_1771821900</t>
+  </si>
+  <si>
+    <t>NSE:HUDCO-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 14:15</t>
+  </si>
+  <si>
+    <t>NSE:KEI-EQ_BULL_1771563600_1771819200</t>
+  </si>
+  <si>
+    <t>2026-02-23 09:30</t>
+  </si>
+  <si>
+    <t>NSE:LTF-EQ_BULL_1771565400_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:LTF-EQ</t>
+  </si>
+  <si>
+    <t>NSE:LAURUSLABS-EQ_BEAR_1771560000_1771821900</t>
+  </si>
+  <si>
+    <t>NSE:LAURUSLABS-EQ</t>
+  </si>
+  <si>
+    <t>NSE:LICI-EQ_BULL_1771819200_1771824600</t>
+  </si>
+  <si>
+    <t>2026-02-23 11:00</t>
+  </si>
+  <si>
+    <t>NSE:NESTLEIND-EQ_BULL_1771566300_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:NESTLEIND-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 11:15</t>
+  </si>
+  <si>
+    <t>NSE:POLYCAB-EQ_BULL_1771571700_1771828200</t>
+  </si>
+  <si>
+    <t>NSE:POLYCAB-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 12:00</t>
+  </si>
+  <si>
+    <t>2026-02-23 12:15</t>
+  </si>
+  <si>
+    <t>NSE:TATAPOWER-EQ_BULL_1771577100_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:TATAPOWER-EQ</t>
+  </si>
+  <si>
+    <t>NSE:FEDERALBNK-EQ_BULL_1771561800_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:FEDERALBNK-EQ</t>
+  </si>
+  <si>
+    <t>NSE:ICICIBANK-EQ_BEAR_1771826400_1771829100</t>
+  </si>
+  <si>
+    <t>NSE:ICICIBANK-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 12:30</t>
+  </si>
+  <si>
+    <t>NSE:BAJFINANCE-EQ_BULL_1771561800_1771830000</t>
+  </si>
+  <si>
+    <t>NSE:BAJFINANCE-EQ</t>
+  </si>
+  <si>
+    <t>NSE:POWERGRID-EQ_BULL_1771569000_1771830000</t>
+  </si>
+  <si>
+    <t>NSE:POWERGRID-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 12:00</t>
+  </si>
+  <si>
+    <t>NSE:SUNPHARMA-EQ_BULL_1771566300_1771832700</t>
+  </si>
+  <si>
+    <t>2026-02-23 13:15</t>
+  </si>
+  <si>
+    <t>NSE:SAIL-EQ_BEAR_1771821000_1771835400</t>
+  </si>
+  <si>
+    <t>2026-02-23 10:00</t>
+  </si>
+  <si>
+    <t>2026-02-23 14:00</t>
+  </si>
+  <si>
+    <t>NSE:DELHIVERY-EQ_BULL_1771819200_1771838100</t>
+  </si>
+  <si>
+    <t>NSE:DELHIVERY-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 14:45</t>
+  </si>
+  <si>
+    <t>2026-02-23 15:00</t>
+  </si>
+  <si>
+    <t>NSE:MARICO-EQ_BULL_1771563600_1771838100</t>
+  </si>
+  <si>
+    <t>NSE:MARICO-EQ</t>
+  </si>
+  <si>
+    <t>NSE:PIIND-EQ_BULL_1771825500_1771838100</t>
+  </si>
+  <si>
+    <t>NSE:PIIND-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 11:15</t>
+  </si>
+  <si>
+    <t>NSE:SYNGENE-EQ_BULL_1771567200_1771838100</t>
+  </si>
+  <si>
+    <t>NSE:SYNGENE-EQ</t>
+  </si>
+  <si>
+    <t>NSE:APOLLOHOSP-EQ_BULL_1771576200_1771839000</t>
+  </si>
+  <si>
+    <t>NSE:APOLLOHOSP-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 14:00</t>
+  </si>
+  <si>
+    <t>2026-02-23 15:15</t>
+  </si>
+  <si>
+    <t>NSE:DABUR-EQ_BULL_1771828200_1771839000</t>
+  </si>
+  <si>
+    <t>NSE:BPCL-EQ_BULL_1771826400_1771839900</t>
+  </si>
+  <si>
+    <t>NSE:BPCL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:RVNL-EQ_BULL_1771570800_1771839900</t>
+  </si>
+  <si>
+    <t>NSE:RVNL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:TORNTPHARM-EQ_BULL_1771567200_1771839900</t>
+  </si>
+  <si>
+    <t>₹207.88</t>
+  </si>
+  <si>
+    <t>₹211.13</t>
+  </si>
+  <si>
+    <t>₹208.96</t>
+  </si>
+  <si>
+    <t>₹210.79</t>
+  </si>
+  <si>
+    <t>₹1,370.70</t>
+  </si>
+  <si>
+    <t>₹1,397.60</t>
+  </si>
+  <si>
+    <t>₹1,380.20</t>
+  </si>
+  <si>
+    <t>₹1,396.50</t>
+  </si>
+  <si>
+    <t>NSE:BAJFINANCE-EQ_BULL_1771561800_1771818300</t>
+  </si>
+  <si>
+    <t>₹1,015.65</t>
+  </si>
+  <si>
+    <t>₹1,040.00</t>
+  </si>
+  <si>
+    <t>₹1,031.95</t>
+  </si>
+  <si>
+    <t>₹1,037.20</t>
+  </si>
+  <si>
+    <t>NSE:BANKINDIA-EQ_BULL_1771560000_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:BANKINDIA-EQ</t>
+  </si>
+  <si>
+    <t>₹171.91</t>
+  </si>
+  <si>
+    <t>₹174.38</t>
+  </si>
+  <si>
+    <t>₹171.83</t>
+  </si>
+  <si>
+    <t>₹174.23</t>
+  </si>
+  <si>
+    <t>NSE:POWERINDIA-EQ_BULL_1771560900_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:POWERINDIA-EQ</t>
+  </si>
+  <si>
+    <t>₹23,424.00</t>
+  </si>
+  <si>
+    <t>₹24,170.00</t>
+  </si>
+  <si>
+    <t>₹23,827.00</t>
+  </si>
+  <si>
+    <t>NSE:JINDALSTEL-EQ_BULL_1771560900_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:JINDALSTEL-EQ</t>
+  </si>
+  <si>
+    <t>₹1,218.60</t>
+  </si>
+  <si>
+    <t>₹1,230.00</t>
+  </si>
+  <si>
+    <t>₹1,219.10</t>
+  </si>
+  <si>
+    <t>₹1,223.70</t>
+  </si>
+  <si>
+    <t>NSE:JSWENERGY-EQ_BULL_1771568100_1771818300</t>
+  </si>
+  <si>
+    <t>2026-02-20 11:45</t>
+  </si>
+  <si>
+    <t>₹490.35</t>
+  </si>
+  <si>
+    <t>₹498.95</t>
+  </si>
+  <si>
+    <t>₹492.05</t>
+  </si>
+  <si>
+    <t>₹495.95</t>
+  </si>
+  <si>
+    <t>₹297.20</t>
+  </si>
+  <si>
+    <t>₹303.00</t>
+  </si>
+  <si>
+    <t>₹298.40</t>
+  </si>
+  <si>
+    <t>₹301.95</t>
+  </si>
+  <si>
+    <t>₹1,295.40</t>
+  </si>
+  <si>
+    <t>₹1,311.20</t>
+  </si>
+  <si>
+    <t>₹1,295.50</t>
+  </si>
+  <si>
+    <t>₹1,309.70</t>
+  </si>
+  <si>
+    <t>NSE:RVNL-EQ_BULL_1771570800_1771818300</t>
+  </si>
+  <si>
+    <t>₹312.95</t>
+  </si>
+  <si>
+    <t>₹313.90</t>
+  </si>
+  <si>
+    <t>₹310.00</t>
+  </si>
+  <si>
+    <t>₹313.15</t>
+  </si>
+  <si>
+    <t>NSE:SBILIFE-EQ_BULL_1771561800_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:SBILIFE-EQ</t>
+  </si>
+  <si>
+    <t>₹2,060.00</t>
+  </si>
+  <si>
+    <t>₹2,104.90</t>
+  </si>
+  <si>
+    <t>₹2,072.20</t>
+  </si>
+  <si>
+    <t>₹2,104.30</t>
+  </si>
+  <si>
+    <t>₹377.30</t>
+  </si>
+  <si>
+    <t>₹380.45</t>
+  </si>
+  <si>
+    <t>₹376.80</t>
+  </si>
+  <si>
+    <t>₹380.20</t>
+  </si>
+  <si>
+    <t>₹291.20</t>
+  </si>
+  <si>
+    <t>₹295.10</t>
+  </si>
+  <si>
+    <t>₹288.00</t>
+  </si>
+  <si>
+    <t>₹294.50</t>
+  </si>
+  <si>
+    <t>NSE:FORTIS-EQ_BULL_1771567200_1771819200</t>
+  </si>
+  <si>
+    <t>NSE:FORTIS-EQ</t>
+  </si>
+  <si>
+    <t>₹920.10</t>
+  </si>
+  <si>
+    <t>₹932.15</t>
+  </si>
+  <si>
+    <t>₹921.75</t>
+  </si>
+  <si>
+    <t>₹930.00</t>
+  </si>
+  <si>
+    <t>₹4,613.70</t>
+  </si>
+  <si>
+    <t>₹4,836.50</t>
+  </si>
+  <si>
+    <t>₹4,786.50</t>
+  </si>
+  <si>
+    <t>₹4,834.00</t>
+  </si>
+  <si>
+    <t>₹443.15</t>
+  </si>
+  <si>
+    <t>₹441.25</t>
+  </si>
+  <si>
+    <t>₹439.05</t>
+  </si>
+  <si>
+    <t>₹439.55</t>
+  </si>
+  <si>
+    <t>₹195.00</t>
+  </si>
+  <si>
+    <t>₹196.20</t>
+  </si>
+  <si>
+    <t>₹195.50</t>
+  </si>
+  <si>
+    <t>₹1,025.00</t>
+  </si>
+  <si>
+    <t>₹1,025.50</t>
+  </si>
+  <si>
+    <t>₹1,022.30</t>
+  </si>
+  <si>
+    <t>₹1,022.80</t>
+  </si>
+  <si>
+    <t>₹882.20</t>
+  </si>
+  <si>
+    <t>₹884.95</t>
+  </si>
+  <si>
+    <t>₹879.15</t>
+  </si>
+  <si>
+    <t>₹884.70</t>
+  </si>
+  <si>
+    <t>₹1,172.10</t>
+  </si>
+  <si>
+    <t>₹1,160.40</t>
+  </si>
+  <si>
+    <t>₹1,154.60</t>
+  </si>
+  <si>
+    <t>₹7,803.00</t>
+  </si>
+  <si>
+    <t>₹7,984.00</t>
+  </si>
+  <si>
+    <t>₹7,912.00</t>
+  </si>
+  <si>
+    <t>₹7,955.50</t>
+  </si>
+  <si>
+    <t>₹1,401.10</t>
+  </si>
+  <si>
+    <t>₹1,402.80</t>
+  </si>
+  <si>
+    <t>₹1,399.10</t>
+  </si>
+  <si>
+    <t>₹1,399.50</t>
+  </si>
+  <si>
+    <t>₹1,046.00</t>
+  </si>
+  <si>
+    <t>₹1,037.00</t>
+  </si>
+  <si>
+    <t>₹1,041.05</t>
+  </si>
+  <si>
+    <t>₹300.10</t>
+  </si>
+  <si>
+    <t>₹303.90</t>
+  </si>
+  <si>
+    <t>₹302.45</t>
+  </si>
+  <si>
+    <t>₹303.85</t>
+  </si>
+  <si>
+    <t>₹1,720.80</t>
+  </si>
+  <si>
+    <t>₹1,730.30</t>
+  </si>
+  <si>
+    <t>₹1,725.00</t>
+  </si>
+  <si>
+    <t>₹1,730.00</t>
+  </si>
+  <si>
+    <t>₹158.20</t>
+  </si>
+  <si>
+    <t>₹156.75</t>
+  </si>
+  <si>
+    <t>₹156.05</t>
+  </si>
+  <si>
+    <t>₹156.11</t>
+  </si>
+  <si>
+    <t>₹432.70</t>
+  </si>
+  <si>
+    <t>₹434.20</t>
+  </si>
+  <si>
+    <t>₹431.70</t>
+  </si>
+  <si>
+    <t>₹433.65</t>
+  </si>
+  <si>
+    <t>₹3,065.10</t>
+  </si>
+  <si>
+    <t>₹3,135.50</t>
+  </si>
+  <si>
+    <t>₹3,093.20</t>
+  </si>
+  <si>
+    <t>₹3,123.00</t>
+  </si>
+  <si>
+    <t>₹787.85</t>
+  </si>
+  <si>
+    <t>₹799.90</t>
+  </si>
+  <si>
+    <t>₹795.95</t>
+  </si>
+  <si>
+    <t>₹440.35</t>
+  </si>
+  <si>
+    <t>₹447.70</t>
+  </si>
+  <si>
+    <t>₹442.55</t>
+  </si>
+  <si>
+    <t>₹447.05</t>
+  </si>
+  <si>
+    <t>₹512.60</t>
+  </si>
+  <si>
+    <t>₹514.50</t>
+  </si>
+  <si>
+    <t>₹512.05</t>
+  </si>
+  <si>
+    <t>₹513.10</t>
+  </si>
+  <si>
+    <t>₹7,622.50</t>
+  </si>
+  <si>
+    <t>₹7,697.50</t>
+  </si>
+  <si>
+    <t>₹7,669.00</t>
+  </si>
+  <si>
+    <t>₹7,691.50</t>
+  </si>
+  <si>
+    <t>₹374.40</t>
+  </si>
+  <si>
+    <t>₹373.90</t>
+  </si>
+  <si>
+    <t>₹371.70</t>
+  </si>
+  <si>
+    <t>₹373.50</t>
+  </si>
+  <si>
+    <t>₹320.90</t>
+  </si>
+  <si>
+    <t>₹318.10</t>
+  </si>
+  <si>
+    <t>₹320.15</t>
+  </si>
+  <si>
+    <t>₹4,232.50</t>
+  </si>
+  <si>
+    <t>₹4,325.00</t>
+  </si>
+  <si>
+    <t>₹4,300.00</t>
+  </si>
+  <si>
+    <t>₹4,318.50</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;#,##0.00"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFffffff"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="10"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="10"/>
-      <name val="Arial"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -664,17 +1358,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1f3864"/>
+        <fgColor rgb="FF1F3864"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe2efda"/>
+        <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFfce4d6"/>
+        <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -687,8 +1381,18 @@
         <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -698,16 +1402,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFbfbfbf"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="FFbfbfbf"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="FFbfbfbf"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFbfbfbf"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
       <diagonal/>
     </border>
@@ -726,11 +1430,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -760,6 +1479,18 @@
     <xf numFmtId="164" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -782,10 +1513,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -823,71 +1554,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -915,7 +1646,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -938,11 +1669,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -951,13 +1682,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -967,7 +1698,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -976,7 +1707,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -985,7 +1716,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -993,10 +1724,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -1061,27 +1792,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N64"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N104"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.005" customWidth="1"/>
-    <col min="2" max="2" width="14.005" customWidth="1"/>
-    <col min="3" max="3" width="20.005" customWidth="1"/>
-    <col min="4" max="4" width="22.005" customWidth="1"/>
-    <col min="5" max="5" width="18.005" customWidth="1"/>
-    <col min="6" max="6" width="22.005" customWidth="1"/>
-    <col min="7" max="8" width="20.005" customWidth="1"/>
-    <col min="9" max="9" width="22.005" customWidth="1"/>
-    <col min="10" max="12" width="18.005" customWidth="1"/>
-    <col min="13" max="13" width="16.005" customWidth="1"/>
-    <col min="14" max="14" width="22.005" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="10" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="16" customWidth="1"/>
+    <col min="14" max="14" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1115,7 +1846,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -1149,7 +1880,7 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
     </row>
-    <row r="3" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
@@ -1183,7 +1914,7 @@
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
     </row>
-    <row r="4" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
@@ -1203,13 +1934,13 @@
         <v>21</v>
       </c>
       <c r="G4" s="4">
-        <v>73.18</v>
+        <v>73.180000000000007</v>
       </c>
       <c r="H4" s="4">
-        <v>71.4</v>
+        <v>71.400000000000006</v>
       </c>
       <c r="I4" s="4">
-        <v>72.79</v>
+        <v>72.790000000000006</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
@@ -1217,7 +1948,7 @@
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
     </row>
-    <row r="5" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>22</v>
       </c>
@@ -1251,7 +1982,7 @@
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
     </row>
-    <row r="6" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>26</v>
       </c>
@@ -1285,7 +2016,7 @@
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
     </row>
-    <row r="7" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>29</v>
       </c>
@@ -1319,7 +2050,7 @@
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
     </row>
-    <row r="8" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>32</v>
       </c>
@@ -1353,7 +2084,7 @@
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
     </row>
-    <row r="9" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>36</v>
       </c>
@@ -1367,19 +2098,19 @@
         <v>38</v>
       </c>
       <c r="E9" s="4">
-        <v>1148.9</v>
+        <v>1148.9000000000001</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G9" s="4">
-        <v>1168.6</v>
+        <v>1168.5999999999999</v>
       </c>
       <c r="H9" s="4">
-        <v>1162.9</v>
+        <v>1162.9000000000001</v>
       </c>
       <c r="I9" s="4">
-        <v>1167.9</v>
+        <v>1167.9000000000001</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -1387,7 +2118,7 @@
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
     </row>
-    <row r="10" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
@@ -1421,7 +2152,7 @@
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
     </row>
-    <row r="11" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>44</v>
       </c>
@@ -1455,7 +2186,7 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
     </row>
-    <row r="12" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>47</v>
       </c>
@@ -1489,7 +2220,7 @@
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
     </row>
-    <row r="13" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>50</v>
       </c>
@@ -1523,7 +2254,7 @@
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
     </row>
-    <row r="14" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>55</v>
       </c>
@@ -1557,7 +2288,7 @@
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
     </row>
-    <row r="15" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>58</v>
       </c>
@@ -1577,7 +2308,7 @@
         <v>54</v>
       </c>
       <c r="G15" s="6">
-        <v>515.8</v>
+        <v>515.79999999999995</v>
       </c>
       <c r="H15" s="6">
         <v>506.7</v>
@@ -1591,7 +2322,7 @@
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
     </row>
-    <row r="16" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>61</v>
       </c>
@@ -1614,7 +2345,7 @@
         <v>627.85</v>
       </c>
       <c r="H16" s="4">
-        <v>619.3</v>
+        <v>619.29999999999995</v>
       </c>
       <c r="I16" s="4">
         <v>626.6</v>
@@ -1625,7 +2356,7 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
     </row>
-    <row r="17" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>64</v>
       </c>
@@ -1659,7 +2390,7 @@
       <c r="M17" s="5"/>
       <c r="N17" s="5"/>
     </row>
-    <row r="18" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>66</v>
       </c>
@@ -1693,7 +2424,7 @@
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
     </row>
-    <row r="19" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>70</v>
       </c>
@@ -1727,7 +2458,7 @@
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
     </row>
-    <row r="20" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>73</v>
       </c>
@@ -1761,7 +2492,7 @@
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
     </row>
-    <row r="21" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>77</v>
       </c>
@@ -1795,7 +2526,7 @@
       <c r="M21" s="5"/>
       <c r="N21" s="5"/>
     </row>
-    <row r="22" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>79</v>
       </c>
@@ -1829,7 +2560,7 @@
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
     </row>
-    <row r="23" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>82</v>
       </c>
@@ -1863,7 +2594,7 @@
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
     </row>
-    <row r="24" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>85</v>
       </c>
@@ -1897,7 +2628,7 @@
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
     </row>
-    <row r="25" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>87</v>
       </c>
@@ -1931,7 +2662,7 @@
       <c r="M25" s="5"/>
       <c r="N25" s="5"/>
     </row>
-    <row r="26" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>90</v>
       </c>
@@ -1951,10 +2682,10 @@
         <v>93</v>
       </c>
       <c r="G26" s="6">
-        <v>1198.4</v>
+        <v>1198.4000000000001</v>
       </c>
       <c r="H26" s="6">
-        <v>1194.4</v>
+        <v>1194.4000000000001</v>
       </c>
       <c r="I26" s="6">
         <v>1196.3</v>
@@ -1965,7 +2696,7 @@
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
     </row>
-    <row r="27" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>94</v>
       </c>
@@ -1979,7 +2710,7 @@
         <v>96</v>
       </c>
       <c r="E27" s="6">
-        <v>4203.4</v>
+        <v>4203.3999999999996</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>69</v>
@@ -1988,7 +2719,7 @@
         <v>4164.3</v>
       </c>
       <c r="H27" s="6">
-        <v>4134.9</v>
+        <v>4134.8999999999996</v>
       </c>
       <c r="I27" s="6">
         <v>4135.7</v>
@@ -1999,7 +2730,7 @@
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
     </row>
-    <row r="28" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>97</v>
       </c>
@@ -2033,7 +2764,7 @@
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
     </row>
-    <row r="29" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>98</v>
       </c>
@@ -2067,7 +2798,7 @@
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
     </row>
-    <row r="30" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>101</v>
       </c>
@@ -2101,7 +2832,7 @@
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
     </row>
-    <row r="31" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>104</v>
       </c>
@@ -2135,7 +2866,7 @@
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
     </row>
-    <row r="32" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>107</v>
       </c>
@@ -2169,7 +2900,7 @@
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
     </row>
-    <row r="33" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>111</v>
       </c>
@@ -2203,7 +2934,7 @@
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
     </row>
-    <row r="34" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>114</v>
       </c>
@@ -2237,7 +2968,7 @@
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
     </row>
-    <row r="35" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>117</v>
       </c>
@@ -2271,7 +3002,7 @@
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
     </row>
-    <row r="36" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>119</v>
       </c>
@@ -2305,7 +3036,7 @@
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
     </row>
-    <row r="37" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>120</v>
       </c>
@@ -2339,7 +3070,7 @@
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
     </row>
-    <row r="38" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>122</v>
       </c>
@@ -2365,7 +3096,7 @@
         <v>606.25</v>
       </c>
       <c r="I38" s="6">
-        <v>606.7</v>
+        <v>606.70000000000005</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
@@ -2373,7 +3104,7 @@
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
     </row>
-    <row r="39" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>124</v>
       </c>
@@ -2407,7 +3138,7 @@
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
     </row>
-    <row r="40" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>126</v>
       </c>
@@ -2441,7 +3172,7 @@
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
     </row>
-    <row r="41" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>128</v>
       </c>
@@ -2467,7 +3198,7 @@
         <v>1053.5</v>
       </c>
       <c r="I41" s="6">
-        <v>1053.9</v>
+        <v>1053.9000000000001</v>
       </c>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
@@ -2475,7 +3206,7 @@
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
     </row>
-    <row r="42" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>130</v>
       </c>
@@ -2509,7 +3240,7 @@
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
     </row>
-    <row r="43" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>134</v>
       </c>
@@ -2543,7 +3274,7 @@
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
     </row>
-    <row r="44" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>136</v>
       </c>
@@ -2577,7 +3308,7 @@
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
     </row>
-    <row r="45" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>137</v>
       </c>
@@ -2611,7 +3342,7 @@
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
     </row>
-    <row r="46" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>139</v>
       </c>
@@ -2697,7 +3428,7 @@
         <v>81</v>
       </c>
       <c r="E48" s="10">
-        <v>2193.3</v>
+        <v>2193.3000000000002</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>149</v>
@@ -2877,7 +3608,7 @@
         <v>54</v>
       </c>
       <c r="E53" s="10">
-        <v>2223.2</v>
+        <v>2223.1999999999998</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>166</v>
@@ -2913,13 +3644,13 @@
         <v>157</v>
       </c>
       <c r="E54" s="12">
-        <v>534.55</v>
+        <v>534.54999999999995</v>
       </c>
       <c r="F54" s="11" t="s">
         <v>166</v>
       </c>
       <c r="G54" s="12">
-        <v>539.45</v>
+        <v>539.45000000000005</v>
       </c>
       <c r="H54" s="12">
         <v>532.15</v>
@@ -2958,10 +3689,10 @@
         <v>2558</v>
       </c>
       <c r="H55" s="12">
-        <v>2537.7</v>
+        <v>2537.6999999999998</v>
       </c>
       <c r="I55" s="12">
-        <v>2554.8</v>
+        <v>2554.8000000000002</v>
       </c>
       <c r="J55" s="11"/>
       <c r="K55" s="11"/>
@@ -3210,10 +3941,10 @@
         <v>4785</v>
       </c>
       <c r="H62" s="12">
-        <v>4741.9</v>
+        <v>4741.8999999999996</v>
       </c>
       <c r="I62" s="12">
-        <v>4782.6</v>
+        <v>4782.6000000000004</v>
       </c>
       <c r="J62" s="11"/>
       <c r="K62" s="11"/>
@@ -3295,6 +4026,1201 @@
         <v>199</v>
       </c>
     </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A65" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="E65" s="10">
+        <v>11644</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G65" s="10">
+        <v>11152</v>
+      </c>
+      <c r="H65" s="10">
+        <v>11074</v>
+      </c>
+      <c r="I65" s="10">
+        <v>11081</v>
+      </c>
+      <c r="J65" s="9"/>
+      <c r="K65" s="9"/>
+      <c r="L65" s="9"/>
+      <c r="M65" s="9"/>
+      <c r="N65" s="9" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A66" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="E66" s="10">
+        <v>1477.9</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="G66" s="10">
+        <v>1447.5</v>
+      </c>
+      <c r="H66" s="10">
+        <v>1431</v>
+      </c>
+      <c r="I66" s="10">
+        <v>1433.8</v>
+      </c>
+      <c r="J66" s="9"/>
+      <c r="K66" s="9"/>
+      <c r="L66" s="9"/>
+      <c r="M66" s="9"/>
+      <c r="N66" s="9" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A67" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="E67" s="10">
+        <v>925.7</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="G67" s="10">
+        <v>911.9</v>
+      </c>
+      <c r="H67" s="10">
+        <v>908.4</v>
+      </c>
+      <c r="I67" s="10">
+        <v>909.4</v>
+      </c>
+      <c r="J67" s="9"/>
+      <c r="K67" s="9"/>
+      <c r="L67" s="9"/>
+      <c r="M67" s="9"/>
+      <c r="N67" s="9" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A68" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="B68" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="E68" s="12">
+        <v>702.95</v>
+      </c>
+      <c r="F68" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="G68" s="12">
+        <v>734.85</v>
+      </c>
+      <c r="H68" s="12">
+        <v>731.2</v>
+      </c>
+      <c r="I68" s="12">
+        <v>734.45</v>
+      </c>
+      <c r="J68" s="11"/>
+      <c r="K68" s="11"/>
+      <c r="L68" s="11"/>
+      <c r="M68" s="11"/>
+      <c r="N68" s="11" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E69" s="10">
+        <v>422.6</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="G69" s="10">
+        <v>414</v>
+      </c>
+      <c r="H69" s="10">
+        <v>412.05</v>
+      </c>
+      <c r="I69" s="10">
+        <v>412.15</v>
+      </c>
+      <c r="J69" s="9"/>
+      <c r="K69" s="9"/>
+      <c r="L69" s="9"/>
+      <c r="M69" s="9"/>
+      <c r="N69" s="9" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="B70" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="C70" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D70" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="E70" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="F70" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="G70" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="H70" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="I70" s="14" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="B71" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="C71" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D71" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="E71" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="F71" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="G71" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="H71" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="I71" s="14" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="B72" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="C72" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D72" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="E72" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="F72" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="G72" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="H72" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="I72" s="14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="B73" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="C73" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D73" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="E73" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="F73" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="G73" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="H73" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="I73" s="14" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="B74" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="C74" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D74" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="E74" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="F74" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="G74" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="H74" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="I74" s="14" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="B75" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="C75" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D75" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="E75" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="F75" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="G75" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="H75" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="I75" s="14" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="B76" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C76" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D76" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="E76" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="F76" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="G76" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="H76" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="I76" s="14" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="B77" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="C77" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D77" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="E77" s="14" t="s">
+        <v>319</v>
+      </c>
+      <c r="F77" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="G77" s="14" t="s">
+        <v>320</v>
+      </c>
+      <c r="H77" s="14" t="s">
+        <v>321</v>
+      </c>
+      <c r="I77" s="14" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="B78" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="C78" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D78" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="E78" s="14" t="s">
+        <v>323</v>
+      </c>
+      <c r="F78" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="G78" s="14" t="s">
+        <v>324</v>
+      </c>
+      <c r="H78" s="14" t="s">
+        <v>325</v>
+      </c>
+      <c r="I78" s="14" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="B79" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="C79" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D79" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="E79" s="14" t="s">
+        <v>328</v>
+      </c>
+      <c r="F79" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="G79" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="H79" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="I79" s="14" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="B80" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="C80" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D80" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="E80" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="F80" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="G80" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="H80" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="I80" s="14" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="B81" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="C81" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="E81" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="F81" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="G81" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="H81" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="I81" s="14" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="B82" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="C82" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D82" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="E82" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="F82" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="G82" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="H82" s="14" t="s">
+        <v>344</v>
+      </c>
+      <c r="I82" s="14" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="B83" s="14" t="s">
+        <v>347</v>
+      </c>
+      <c r="C83" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D83" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="E83" s="14" t="s">
+        <v>348</v>
+      </c>
+      <c r="F83" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="G83" s="14" t="s">
+        <v>349</v>
+      </c>
+      <c r="H83" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="I83" s="14" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="B84" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="C84" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D84" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="E84" s="14" t="s">
+        <v>352</v>
+      </c>
+      <c r="F84" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="G84" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="H84" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="I84" s="14" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="B85" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="C85" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D85" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="E85" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="F85" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="G85" s="16" t="s">
+        <v>357</v>
+      </c>
+      <c r="H85" s="16" t="s">
+        <v>358</v>
+      </c>
+      <c r="I85" s="16" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="B86" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="C86" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D86" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="E86" s="16" t="s">
+        <v>360</v>
+      </c>
+      <c r="F86" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="G86" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="H86" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="I86" s="16" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="B87" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="C87" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D87" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="E87" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="F87" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="G87" s="16" t="s">
+        <v>364</v>
+      </c>
+      <c r="H87" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="I87" s="16" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="B88" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C88" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D88" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="E88" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="F88" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="G88" s="14" t="s">
+        <v>368</v>
+      </c>
+      <c r="H88" s="14" t="s">
+        <v>369</v>
+      </c>
+      <c r="I88" s="14" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="B89" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="C89" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D89" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="E89" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="F89" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="G89" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="H89" s="16" t="s">
+        <v>373</v>
+      </c>
+      <c r="I89" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="B90" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="C90" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D90" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="E90" s="14" t="s">
+        <v>374</v>
+      </c>
+      <c r="F90" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="G90" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="H90" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="I90" s="14" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="B91" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="C91" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D91" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="E91" s="16" t="s">
+        <v>378</v>
+      </c>
+      <c r="F91" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="G91" s="16" t="s">
+        <v>379</v>
+      </c>
+      <c r="H91" s="16" t="s">
+        <v>380</v>
+      </c>
+      <c r="I91" s="16" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="B92" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="C92" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D92" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="E92" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="F92" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="G92" s="14" t="s">
+        <v>382</v>
+      </c>
+      <c r="H92" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="I92" s="14" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="B93" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="C93" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D93" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="E93" s="14" t="s">
+        <v>385</v>
+      </c>
+      <c r="F93" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="G93" s="14" t="s">
+        <v>386</v>
+      </c>
+      <c r="H93" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="I93" s="14" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="B94" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C94" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D94" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="E94" s="14" t="s">
+        <v>389</v>
+      </c>
+      <c r="F94" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="G94" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="H94" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="I94" s="14" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="B95" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="C95" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D95" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="E95" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="F95" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="G95" s="16" t="s">
+        <v>394</v>
+      </c>
+      <c r="H95" s="16" t="s">
+        <v>395</v>
+      </c>
+      <c r="I95" s="16" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="B96" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="C96" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D96" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="E96" s="14" t="s">
+        <v>397</v>
+      </c>
+      <c r="F96" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="G96" s="14" t="s">
+        <v>398</v>
+      </c>
+      <c r="H96" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="I96" s="14" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="B97" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="C97" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D97" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="E97" s="14" t="s">
+        <v>401</v>
+      </c>
+      <c r="F97" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="G97" s="14" t="s">
+        <v>402</v>
+      </c>
+      <c r="H97" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="I97" s="14" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="B98" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="C98" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D98" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="E98" s="14" t="s">
+        <v>405</v>
+      </c>
+      <c r="F98" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="G98" s="14" t="s">
+        <v>406</v>
+      </c>
+      <c r="H98" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="I98" s="14" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="B99" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="C99" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D99" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="E99" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="F99" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="G99" s="14" t="s">
+        <v>409</v>
+      </c>
+      <c r="H99" s="14" t="s">
+        <v>410</v>
+      </c>
+      <c r="I99" s="14" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="B100" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C100" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D100" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="E100" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="F100" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="G100" s="14" t="s">
+        <v>413</v>
+      </c>
+      <c r="H100" s="14" t="s">
+        <v>414</v>
+      </c>
+      <c r="I100" s="14" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="B101" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="C101" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D101" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="E101" s="14" t="s">
+        <v>416</v>
+      </c>
+      <c r="F101" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="G101" s="14" t="s">
+        <v>417</v>
+      </c>
+      <c r="H101" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="I101" s="14" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="B102" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="C102" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D102" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="E102" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="F102" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="G102" s="14" t="s">
+        <v>421</v>
+      </c>
+      <c r="H102" s="14" t="s">
+        <v>422</v>
+      </c>
+      <c r="I102" s="14" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="B103" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="C103" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D103" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="E103" s="14" t="s">
+        <v>328</v>
+      </c>
+      <c r="F103" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="G103" s="14" t="s">
+        <v>424</v>
+      </c>
+      <c r="H103" s="14" t="s">
+        <v>425</v>
+      </c>
+      <c r="I103" s="14" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="B104" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="C104" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D104" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="E104" s="14" t="s">
+        <v>427</v>
+      </c>
+      <c r="F104" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="G104" s="14" t="s">
+        <v>428</v>
+      </c>
+      <c r="H104" s="14" t="s">
+        <v>429</v>
+      </c>
+      <c r="I104" s="14" t="s">
+        <v>430</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pattern_signals.xlsx
+++ b/pattern_signals.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84CDBBBF-5C37-4DAC-8948-6EA944FD2CAB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505"/>
   </bookViews>
   <sheets>
-    <sheet name="Signals" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Signals" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="508">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -671,73 +670,364 @@
     <t>NSE:ASHOKLEY-EQ</t>
   </si>
   <si>
+    <t>₹207.88</t>
+  </si>
+  <si>
     <t>2026-02-23 09:15</t>
   </si>
   <si>
+    <t>₹211.13</t>
+  </si>
+  <si>
+    <t>₹208.96</t>
+  </si>
+  <si>
+    <t>₹210.79</t>
+  </si>
+  <si>
+    <t>NSE:AXISBANK-EQ_BULL_1771564500_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:AXISBANK-EQ</t>
+  </si>
+  <si>
+    <t>₹1,370.70</t>
+  </si>
+  <si>
+    <t>₹1,397.60</t>
+  </si>
+  <si>
+    <t>₹1,380.20</t>
+  </si>
+  <si>
+    <t>₹1,396.50</t>
+  </si>
+  <si>
+    <t>NSE:BAJFINANCE-EQ_BULL_1771561800_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:BAJFINANCE-EQ</t>
+  </si>
+  <si>
+    <t>₹1,015.65</t>
+  </si>
+  <si>
+    <t>₹1,040.00</t>
+  </si>
+  <si>
+    <t>₹1,031.95</t>
+  </si>
+  <si>
+    <t>₹1,037.20</t>
+  </si>
+  <si>
+    <t>NSE:BANKINDIA-EQ_BULL_1771560000_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:BANKINDIA-EQ</t>
+  </si>
+  <si>
+    <t>₹171.91</t>
+  </si>
+  <si>
+    <t>₹174.38</t>
+  </si>
+  <si>
+    <t>₹171.83</t>
+  </si>
+  <si>
+    <t>₹174.23</t>
+  </si>
+  <si>
+    <t>NSE:POWERINDIA-EQ_BULL_1771560900_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:POWERINDIA-EQ</t>
+  </si>
+  <si>
+    <t>₹23,424.00</t>
+  </si>
+  <si>
+    <t>₹24,170.00</t>
+  </si>
+  <si>
+    <t>₹23,827.00</t>
+  </si>
+  <si>
+    <t>NSE:JINDALSTEL-EQ_BULL_1771560900_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:JINDALSTEL-EQ</t>
+  </si>
+  <si>
+    <t>₹1,218.60</t>
+  </si>
+  <si>
+    <t>₹1,230.00</t>
+  </si>
+  <si>
+    <t>₹1,219.10</t>
+  </si>
+  <si>
+    <t>₹1,223.70</t>
+  </si>
+  <si>
+    <t>NSE:JSWENERGY-EQ_BULL_1771568100_1771818300</t>
+  </si>
+  <si>
+    <t>2026-02-20 11:45</t>
+  </si>
+  <si>
+    <t>₹490.35</t>
+  </si>
+  <si>
+    <t>₹498.95</t>
+  </si>
+  <si>
+    <t>₹492.05</t>
+  </si>
+  <si>
+    <t>₹495.95</t>
+  </si>
+  <si>
+    <t>NSE:LTF-EQ_BULL_1771565400_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:LTF-EQ</t>
+  </si>
+  <si>
+    <t>₹297.20</t>
+  </si>
+  <si>
+    <t>₹303.00</t>
+  </si>
+  <si>
+    <t>₹298.40</t>
+  </si>
+  <si>
+    <t>₹301.95</t>
+  </si>
+  <si>
+    <t>NSE:NESTLEIND-EQ_BULL_1771566300_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:NESTLEIND-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 11:15</t>
+  </si>
+  <si>
+    <t>₹1,295.40</t>
+  </si>
+  <si>
+    <t>₹1,311.20</t>
+  </si>
+  <si>
+    <t>₹1,295.50</t>
+  </si>
+  <si>
+    <t>₹1,309.70</t>
+  </si>
+  <si>
+    <t>NSE:RVNL-EQ_BULL_1771570800_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:RVNL-EQ</t>
+  </si>
+  <si>
+    <t>₹312.95</t>
+  </si>
+  <si>
+    <t>₹313.90</t>
+  </si>
+  <si>
+    <t>₹310.00</t>
+  </si>
+  <si>
+    <t>₹313.15</t>
+  </si>
+  <si>
+    <t>NSE:SBILIFE-EQ_BULL_1771561800_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:SBILIFE-EQ</t>
+  </si>
+  <si>
+    <t>₹2,060.00</t>
+  </si>
+  <si>
+    <t>₹2,104.90</t>
+  </si>
+  <si>
+    <t>₹2,072.20</t>
+  </si>
+  <si>
+    <t>₹2,104.30</t>
+  </si>
+  <si>
+    <t>NSE:TATAPOWER-EQ_BULL_1771577100_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:TATAPOWER-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-20 14:15</t>
+  </si>
+  <si>
+    <t>₹377.30</t>
+  </si>
+  <si>
+    <t>₹380.45</t>
+  </si>
+  <si>
+    <t>₹376.80</t>
+  </si>
+  <si>
+    <t>₹380.20</t>
+  </si>
+  <si>
+    <t>NSE:FEDERALBNK-EQ_BULL_1771561800_1771818300</t>
+  </si>
+  <si>
+    <t>NSE:FEDERALBNK-EQ</t>
+  </si>
+  <si>
+    <t>₹291.20</t>
+  </si>
+  <si>
+    <t>₹295.10</t>
+  </si>
+  <si>
+    <t>₹288.00</t>
+  </si>
+  <si>
+    <t>₹294.50</t>
+  </si>
+  <si>
+    <t>NSE:FORTIS-EQ_BULL_1771567200_1771819200</t>
+  </si>
+  <si>
+    <t>NSE:FORTIS-EQ</t>
+  </si>
+  <si>
+    <t>₹920.10</t>
+  </si>
+  <si>
+    <t>2026-02-23 09:30</t>
+  </si>
+  <si>
+    <t>₹932.15</t>
+  </si>
+  <si>
+    <t>₹921.75</t>
+  </si>
+  <si>
+    <t>₹930.00</t>
+  </si>
+  <si>
+    <t>NSE:KEI-EQ_BULL_1771563600_1771819200</t>
+  </si>
+  <si>
+    <t>₹4,613.70</t>
+  </si>
+  <si>
+    <t>₹4,836.50</t>
+  </si>
+  <si>
+    <t>₹4,786.50</t>
+  </si>
+  <si>
+    <t>₹4,834.00</t>
+  </si>
+  <si>
+    <t>NSE:BEL-EQ_BEAR_1771571700_1771821900</t>
+  </si>
+  <si>
+    <t>NSE:BEL-EQ</t>
+  </si>
+  <si>
+    <t>₹443.15</t>
+  </si>
+  <si>
+    <t>2026-02-23 10:15</t>
+  </si>
+  <si>
+    <t>₹441.25</t>
+  </si>
+  <si>
+    <t>₹439.05</t>
+  </si>
+  <si>
+    <t>₹439.55</t>
+  </si>
+  <si>
+    <t>NSE:HUDCO-EQ_BEAR_1771577100_1771821900</t>
+  </si>
+  <si>
+    <t>NSE:HUDCO-EQ</t>
+  </si>
+  <si>
+    <t>₹195.00</t>
+  </si>
+  <si>
+    <t>₹196.20</t>
+  </si>
+  <si>
+    <t>₹195.50</t>
+  </si>
+  <si>
+    <t>NSE:LAURUSLABS-EQ_BEAR_1771560000_1771821900</t>
+  </si>
+  <si>
+    <t>NSE:LAURUSLABS-EQ</t>
+  </si>
+  <si>
+    <t>₹1,025.00</t>
+  </si>
+  <si>
+    <t>₹1,025.50</t>
+  </si>
+  <si>
+    <t>₹1,022.30</t>
+  </si>
+  <si>
+    <t>₹1,022.80</t>
+  </si>
+  <si>
+    <t>NSE:LICI-EQ_BULL_1771819200_1771824600</t>
+  </si>
+  <si>
+    <t>₹882.20</t>
+  </si>
+  <si>
+    <t>2026-02-23 11:00</t>
+  </si>
+  <si>
+    <t>₹884.95</t>
+  </si>
+  <si>
+    <t>₹879.15</t>
+  </si>
+  <si>
+    <t>₹884.70</t>
+  </si>
+  <si>
     <t>NSE:AUROPHARMA-EQ_BEAR_1771560000_1771826400</t>
   </si>
   <si>
     <t>NSE:AUROPHARMA-EQ</t>
   </si>
   <si>
+    <t>₹1,172.10</t>
+  </si>
+  <si>
     <t>2026-02-23 11:30</t>
   </si>
   <si>
-    <t>NSE:AXISBANK-EQ_BULL_1771564500_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:AXISBANK-EQ</t>
-  </si>
-  <si>
-    <t>NSE:BEL-EQ_BEAR_1771571700_1771821900</t>
-  </si>
-  <si>
-    <t>NSE:BEL-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-23 10:15</t>
-  </si>
-  <si>
-    <t>NSE:HUDCO-EQ_BEAR_1771577100_1771821900</t>
-  </si>
-  <si>
-    <t>NSE:HUDCO-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-20 14:15</t>
-  </si>
-  <si>
-    <t>NSE:KEI-EQ_BULL_1771563600_1771819200</t>
-  </si>
-  <si>
-    <t>2026-02-23 09:30</t>
-  </si>
-  <si>
-    <t>NSE:LTF-EQ_BULL_1771565400_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:LTF-EQ</t>
-  </si>
-  <si>
-    <t>NSE:LAURUSLABS-EQ_BEAR_1771560000_1771821900</t>
-  </si>
-  <si>
-    <t>NSE:LAURUSLABS-EQ</t>
-  </si>
-  <si>
-    <t>NSE:LICI-EQ_BULL_1771819200_1771824600</t>
-  </si>
-  <si>
-    <t>2026-02-23 11:00</t>
-  </si>
-  <si>
-    <t>NSE:NESTLEIND-EQ_BULL_1771566300_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:NESTLEIND-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-20 11:15</t>
+    <t>₹1,160.40</t>
+  </si>
+  <si>
+    <t>₹1,154.60</t>
   </si>
   <si>
     <t>NSE:POLYCAB-EQ_BULL_1771571700_1771828200</t>
@@ -746,37 +1036,55 @@
     <t>NSE:POLYCAB-EQ</t>
   </si>
   <si>
+    <t>₹7,803.00</t>
+  </si>
+  <si>
     <t>2026-02-23 12:00</t>
   </si>
   <si>
+    <t>₹7,984.00</t>
+  </si>
+  <si>
+    <t>₹7,912.00</t>
+  </si>
+  <si>
+    <t>₹7,955.50</t>
+  </si>
+  <si>
+    <t>NSE:ICICIBANK-EQ_BEAR_1771826400_1771829100</t>
+  </si>
+  <si>
+    <t>NSE:ICICIBANK-EQ</t>
+  </si>
+  <si>
+    <t>₹1,401.10</t>
+  </si>
+  <si>
     <t>2026-02-23 12:15</t>
   </si>
   <si>
-    <t>NSE:TATAPOWER-EQ_BULL_1771577100_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:TATAPOWER-EQ</t>
-  </si>
-  <si>
-    <t>NSE:FEDERALBNK-EQ_BULL_1771561800_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:FEDERALBNK-EQ</t>
-  </si>
-  <si>
-    <t>NSE:ICICIBANK-EQ_BEAR_1771826400_1771829100</t>
-  </si>
-  <si>
-    <t>NSE:ICICIBANK-EQ</t>
+    <t>₹1,402.80</t>
+  </si>
+  <si>
+    <t>₹1,399.10</t>
+  </si>
+  <si>
+    <t>₹1,399.50</t>
+  </si>
+  <si>
+    <t>NSE:BAJFINANCE-EQ_BULL_1771561800_1771830000</t>
   </si>
   <si>
     <t>2026-02-23 12:30</t>
   </si>
   <si>
-    <t>NSE:BAJFINANCE-EQ_BULL_1771561800_1771830000</t>
-  </si>
-  <si>
-    <t>NSE:BAJFINANCE-EQ</t>
+    <t>₹1,046.00</t>
+  </si>
+  <si>
+    <t>₹1,037.00</t>
+  </si>
+  <si>
+    <t>₹1,041.05</t>
   </si>
   <si>
     <t>NSE:POWERGRID-EQ_BULL_1771569000_1771830000</t>
@@ -788,52 +1096,148 @@
     <t>2026-02-20 12:00</t>
   </si>
   <si>
+    <t>₹300.10</t>
+  </si>
+  <si>
+    <t>₹303.90</t>
+  </si>
+  <si>
+    <t>₹302.45</t>
+  </si>
+  <si>
+    <t>₹303.85</t>
+  </si>
+  <si>
     <t>NSE:SUNPHARMA-EQ_BULL_1771566300_1771832700</t>
   </si>
   <si>
+    <t>₹1,720.80</t>
+  </si>
+  <si>
     <t>2026-02-23 13:15</t>
   </si>
   <si>
+    <t>₹1,730.30</t>
+  </si>
+  <si>
+    <t>₹1,725.00</t>
+  </si>
+  <si>
+    <t>₹1,730.00</t>
+  </si>
+  <si>
     <t>NSE:SAIL-EQ_BEAR_1771821000_1771835400</t>
   </si>
   <si>
     <t>2026-02-23 10:00</t>
   </si>
   <si>
+    <t>₹158.20</t>
+  </si>
+  <si>
     <t>2026-02-23 14:00</t>
   </si>
   <si>
+    <t>₹156.75</t>
+  </si>
+  <si>
+    <t>₹156.05</t>
+  </si>
+  <si>
+    <t>₹156.11</t>
+  </si>
+  <si>
     <t>NSE:DELHIVERY-EQ_BULL_1771819200_1771838100</t>
   </si>
   <si>
     <t>NSE:DELHIVERY-EQ</t>
   </si>
   <si>
+    <t>₹432.70</t>
+  </si>
+  <si>
     <t>2026-02-23 14:45</t>
   </si>
   <si>
+    <t>₹434.20</t>
+  </si>
+  <si>
+    <t>₹431.70</t>
+  </si>
+  <si>
+    <t>₹433.65</t>
+  </si>
+  <si>
+    <t>NSE:PIIND-EQ_BULL_1771825500_1771838100</t>
+  </si>
+  <si>
+    <t>NSE:PIIND-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 11:15</t>
+  </si>
+  <si>
+    <t>₹3,065.10</t>
+  </si>
+  <si>
+    <t>₹3,135.50</t>
+  </si>
+  <si>
+    <t>₹3,093.20</t>
+  </si>
+  <si>
+    <t>₹3,123.00</t>
+  </si>
+  <si>
+    <t>NSE:MARICO-EQ_BULL_1771563600_1771838100</t>
+  </si>
+  <si>
+    <t>NSE:MARICO-EQ</t>
+  </si>
+  <si>
+    <t>₹787.85</t>
+  </si>
+  <si>
+    <t>₹799.90</t>
+  </si>
+  <si>
+    <t>₹795.95</t>
+  </si>
+  <si>
+    <t>NSE:SYNGENE-EQ_BULL_1771567200_1771838100</t>
+  </si>
+  <si>
+    <t>NSE:SYNGENE-EQ</t>
+  </si>
+  <si>
+    <t>₹440.35</t>
+  </si>
+  <si>
+    <t>₹447.70</t>
+  </si>
+  <si>
+    <t>₹442.55</t>
+  </si>
+  <si>
+    <t>₹447.05</t>
+  </si>
+  <si>
+    <t>NSE:DABUR-EQ_BULL_1771828200_1771839000</t>
+  </si>
+  <si>
+    <t>₹512.60</t>
+  </si>
+  <si>
     <t>2026-02-23 15:00</t>
   </si>
   <si>
-    <t>NSE:MARICO-EQ_BULL_1771563600_1771838100</t>
-  </si>
-  <si>
-    <t>NSE:MARICO-EQ</t>
-  </si>
-  <si>
-    <t>NSE:PIIND-EQ_BULL_1771825500_1771838100</t>
-  </si>
-  <si>
-    <t>NSE:PIIND-EQ</t>
-  </si>
-  <si>
-    <t>2026-02-23 11:15</t>
-  </si>
-  <si>
-    <t>NSE:SYNGENE-EQ_BULL_1771567200_1771838100</t>
-  </si>
-  <si>
-    <t>NSE:SYNGENE-EQ</t>
+    <t>₹514.50</t>
+  </si>
+  <si>
+    <t>₹512.05</t>
+  </si>
+  <si>
+    <t>₹513.10</t>
   </si>
   <si>
     <t>NSE:APOLLOHOSP-EQ_BULL_1771576200_1771839000</t>
@@ -845,459 +1249,54 @@
     <t>2026-02-20 14:00</t>
   </si>
   <si>
+    <t>₹7,622.50</t>
+  </si>
+  <si>
+    <t>₹7,697.50</t>
+  </si>
+  <si>
+    <t>₹7,669.00</t>
+  </si>
+  <si>
+    <t>₹7,691.50</t>
+  </si>
+  <si>
+    <t>NSE:BPCL-EQ_BULL_1771826400_1771839900</t>
+  </si>
+  <si>
+    <t>NSE:BPCL-EQ</t>
+  </si>
+  <si>
+    <t>₹374.40</t>
+  </si>
+  <si>
     <t>2026-02-23 15:15</t>
   </si>
   <si>
-    <t>NSE:DABUR-EQ_BULL_1771828200_1771839000</t>
-  </si>
-  <si>
-    <t>NSE:BPCL-EQ_BULL_1771826400_1771839900</t>
-  </si>
-  <si>
-    <t>NSE:BPCL-EQ</t>
+    <t>₹373.90</t>
+  </si>
+  <si>
+    <t>₹371.70</t>
+  </si>
+  <si>
+    <t>₹373.50</t>
   </si>
   <si>
     <t>NSE:RVNL-EQ_BULL_1771570800_1771839900</t>
   </si>
   <si>
-    <t>NSE:RVNL-EQ</t>
+    <t>₹320.90</t>
+  </si>
+  <si>
+    <t>₹318.10</t>
+  </si>
+  <si>
+    <t>₹320.15</t>
   </si>
   <si>
     <t>NSE:TORNTPHARM-EQ_BULL_1771567200_1771839900</t>
   </si>
   <si>
-    <t>₹207.88</t>
-  </si>
-  <si>
-    <t>₹211.13</t>
-  </si>
-  <si>
-    <t>₹208.96</t>
-  </si>
-  <si>
-    <t>₹210.79</t>
-  </si>
-  <si>
-    <t>₹1,370.70</t>
-  </si>
-  <si>
-    <t>₹1,397.60</t>
-  </si>
-  <si>
-    <t>₹1,380.20</t>
-  </si>
-  <si>
-    <t>₹1,396.50</t>
-  </si>
-  <si>
-    <t>NSE:BAJFINANCE-EQ_BULL_1771561800_1771818300</t>
-  </si>
-  <si>
-    <t>₹1,015.65</t>
-  </si>
-  <si>
-    <t>₹1,040.00</t>
-  </si>
-  <si>
-    <t>₹1,031.95</t>
-  </si>
-  <si>
-    <t>₹1,037.20</t>
-  </si>
-  <si>
-    <t>NSE:BANKINDIA-EQ_BULL_1771560000_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:BANKINDIA-EQ</t>
-  </si>
-  <si>
-    <t>₹171.91</t>
-  </si>
-  <si>
-    <t>₹174.38</t>
-  </si>
-  <si>
-    <t>₹171.83</t>
-  </si>
-  <si>
-    <t>₹174.23</t>
-  </si>
-  <si>
-    <t>NSE:POWERINDIA-EQ_BULL_1771560900_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:POWERINDIA-EQ</t>
-  </si>
-  <si>
-    <t>₹23,424.00</t>
-  </si>
-  <si>
-    <t>₹24,170.00</t>
-  </si>
-  <si>
-    <t>₹23,827.00</t>
-  </si>
-  <si>
-    <t>NSE:JINDALSTEL-EQ_BULL_1771560900_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:JINDALSTEL-EQ</t>
-  </si>
-  <si>
-    <t>₹1,218.60</t>
-  </si>
-  <si>
-    <t>₹1,230.00</t>
-  </si>
-  <si>
-    <t>₹1,219.10</t>
-  </si>
-  <si>
-    <t>₹1,223.70</t>
-  </si>
-  <si>
-    <t>NSE:JSWENERGY-EQ_BULL_1771568100_1771818300</t>
-  </si>
-  <si>
-    <t>2026-02-20 11:45</t>
-  </si>
-  <si>
-    <t>₹490.35</t>
-  </si>
-  <si>
-    <t>₹498.95</t>
-  </si>
-  <si>
-    <t>₹492.05</t>
-  </si>
-  <si>
-    <t>₹495.95</t>
-  </si>
-  <si>
-    <t>₹297.20</t>
-  </si>
-  <si>
-    <t>₹303.00</t>
-  </si>
-  <si>
-    <t>₹298.40</t>
-  </si>
-  <si>
-    <t>₹301.95</t>
-  </si>
-  <si>
-    <t>₹1,295.40</t>
-  </si>
-  <si>
-    <t>₹1,311.20</t>
-  </si>
-  <si>
-    <t>₹1,295.50</t>
-  </si>
-  <si>
-    <t>₹1,309.70</t>
-  </si>
-  <si>
-    <t>NSE:RVNL-EQ_BULL_1771570800_1771818300</t>
-  </si>
-  <si>
-    <t>₹312.95</t>
-  </si>
-  <si>
-    <t>₹313.90</t>
-  </si>
-  <si>
-    <t>₹310.00</t>
-  </si>
-  <si>
-    <t>₹313.15</t>
-  </si>
-  <si>
-    <t>NSE:SBILIFE-EQ_BULL_1771561800_1771818300</t>
-  </si>
-  <si>
-    <t>NSE:SBILIFE-EQ</t>
-  </si>
-  <si>
-    <t>₹2,060.00</t>
-  </si>
-  <si>
-    <t>₹2,104.90</t>
-  </si>
-  <si>
-    <t>₹2,072.20</t>
-  </si>
-  <si>
-    <t>₹2,104.30</t>
-  </si>
-  <si>
-    <t>₹377.30</t>
-  </si>
-  <si>
-    <t>₹380.45</t>
-  </si>
-  <si>
-    <t>₹376.80</t>
-  </si>
-  <si>
-    <t>₹380.20</t>
-  </si>
-  <si>
-    <t>₹291.20</t>
-  </si>
-  <si>
-    <t>₹295.10</t>
-  </si>
-  <si>
-    <t>₹288.00</t>
-  </si>
-  <si>
-    <t>₹294.50</t>
-  </si>
-  <si>
-    <t>NSE:FORTIS-EQ_BULL_1771567200_1771819200</t>
-  </si>
-  <si>
-    <t>NSE:FORTIS-EQ</t>
-  </si>
-  <si>
-    <t>₹920.10</t>
-  </si>
-  <si>
-    <t>₹932.15</t>
-  </si>
-  <si>
-    <t>₹921.75</t>
-  </si>
-  <si>
-    <t>₹930.00</t>
-  </si>
-  <si>
-    <t>₹4,613.70</t>
-  </si>
-  <si>
-    <t>₹4,836.50</t>
-  </si>
-  <si>
-    <t>₹4,786.50</t>
-  </si>
-  <si>
-    <t>₹4,834.00</t>
-  </si>
-  <si>
-    <t>₹443.15</t>
-  </si>
-  <si>
-    <t>₹441.25</t>
-  </si>
-  <si>
-    <t>₹439.05</t>
-  </si>
-  <si>
-    <t>₹439.55</t>
-  </si>
-  <si>
-    <t>₹195.00</t>
-  </si>
-  <si>
-    <t>₹196.20</t>
-  </si>
-  <si>
-    <t>₹195.50</t>
-  </si>
-  <si>
-    <t>₹1,025.00</t>
-  </si>
-  <si>
-    <t>₹1,025.50</t>
-  </si>
-  <si>
-    <t>₹1,022.30</t>
-  </si>
-  <si>
-    <t>₹1,022.80</t>
-  </si>
-  <si>
-    <t>₹882.20</t>
-  </si>
-  <si>
-    <t>₹884.95</t>
-  </si>
-  <si>
-    <t>₹879.15</t>
-  </si>
-  <si>
-    <t>₹884.70</t>
-  </si>
-  <si>
-    <t>₹1,172.10</t>
-  </si>
-  <si>
-    <t>₹1,160.40</t>
-  </si>
-  <si>
-    <t>₹1,154.60</t>
-  </si>
-  <si>
-    <t>₹7,803.00</t>
-  </si>
-  <si>
-    <t>₹7,984.00</t>
-  </si>
-  <si>
-    <t>₹7,912.00</t>
-  </si>
-  <si>
-    <t>₹7,955.50</t>
-  </si>
-  <si>
-    <t>₹1,401.10</t>
-  </si>
-  <si>
-    <t>₹1,402.80</t>
-  </si>
-  <si>
-    <t>₹1,399.10</t>
-  </si>
-  <si>
-    <t>₹1,399.50</t>
-  </si>
-  <si>
-    <t>₹1,046.00</t>
-  </si>
-  <si>
-    <t>₹1,037.00</t>
-  </si>
-  <si>
-    <t>₹1,041.05</t>
-  </si>
-  <si>
-    <t>₹300.10</t>
-  </si>
-  <si>
-    <t>₹303.90</t>
-  </si>
-  <si>
-    <t>₹302.45</t>
-  </si>
-  <si>
-    <t>₹303.85</t>
-  </si>
-  <si>
-    <t>₹1,720.80</t>
-  </si>
-  <si>
-    <t>₹1,730.30</t>
-  </si>
-  <si>
-    <t>₹1,725.00</t>
-  </si>
-  <si>
-    <t>₹1,730.00</t>
-  </si>
-  <si>
-    <t>₹158.20</t>
-  </si>
-  <si>
-    <t>₹156.75</t>
-  </si>
-  <si>
-    <t>₹156.05</t>
-  </si>
-  <si>
-    <t>₹156.11</t>
-  </si>
-  <si>
-    <t>₹432.70</t>
-  </si>
-  <si>
-    <t>₹434.20</t>
-  </si>
-  <si>
-    <t>₹431.70</t>
-  </si>
-  <si>
-    <t>₹433.65</t>
-  </si>
-  <si>
-    <t>₹3,065.10</t>
-  </si>
-  <si>
-    <t>₹3,135.50</t>
-  </si>
-  <si>
-    <t>₹3,093.20</t>
-  </si>
-  <si>
-    <t>₹3,123.00</t>
-  </si>
-  <si>
-    <t>₹787.85</t>
-  </si>
-  <si>
-    <t>₹799.90</t>
-  </si>
-  <si>
-    <t>₹795.95</t>
-  </si>
-  <si>
-    <t>₹440.35</t>
-  </si>
-  <si>
-    <t>₹447.70</t>
-  </si>
-  <si>
-    <t>₹442.55</t>
-  </si>
-  <si>
-    <t>₹447.05</t>
-  </si>
-  <si>
-    <t>₹512.60</t>
-  </si>
-  <si>
-    <t>₹514.50</t>
-  </si>
-  <si>
-    <t>₹512.05</t>
-  </si>
-  <si>
-    <t>₹513.10</t>
-  </si>
-  <si>
-    <t>₹7,622.50</t>
-  </si>
-  <si>
-    <t>₹7,697.50</t>
-  </si>
-  <si>
-    <t>₹7,669.00</t>
-  </si>
-  <si>
-    <t>₹7,691.50</t>
-  </si>
-  <si>
-    <t>₹374.40</t>
-  </si>
-  <si>
-    <t>₹373.90</t>
-  </si>
-  <si>
-    <t>₹371.70</t>
-  </si>
-  <si>
-    <t>₹373.50</t>
-  </si>
-  <si>
-    <t>₹320.90</t>
-  </si>
-  <si>
-    <t>₹318.10</t>
-  </si>
-  <si>
-    <t>₹320.15</t>
-  </si>
-  <si>
     <t>₹4,232.50</t>
   </si>
   <si>
@@ -1308,48 +1307,279 @@
   </si>
   <si>
     <t>₹4,318.50</t>
+  </si>
+  <si>
+    <t>NSE:ABCAPITAL-EQ_BEAR_1771828200_1771904700</t>
+  </si>
+  <si>
+    <t>NSE:ABCAPITAL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-24 09:15</t>
+  </si>
+  <si>
+    <t>2026-02-24 09:31</t>
+  </si>
+  <si>
+    <t>NSE:BDL-EQ_BEAR_1771822800_1771904700</t>
+  </si>
+  <si>
+    <t>NSE:BDL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 10:30</t>
+  </si>
+  <si>
+    <t>NSE:DIVISLAB-EQ_BEAR_1771834500_1771904700</t>
+  </si>
+  <si>
+    <t>2026-02-23 13:45</t>
+  </si>
+  <si>
+    <t>NSE:ITC-EQ_BEAR_1771821000_1771904700</t>
+  </si>
+  <si>
+    <t>NSE:ITC-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IOC-EQ_BULL_1771825500_1771904700</t>
+  </si>
+  <si>
+    <t>NSE:IOC-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-24 09:32</t>
+  </si>
+  <si>
+    <t>NSE:OIL-EQ_BULL_1771834500_1771904700</t>
+  </si>
+  <si>
+    <t>NSE:OIL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:SBICARD-EQ_BEAR_1771832700_1771904700</t>
+  </si>
+  <si>
+    <t>NSE:SBICARD-EQ</t>
+  </si>
+  <si>
+    <t>NSE:GODREJCP-EQ_BULL_1771819200_1771911000</t>
+  </si>
+  <si>
+    <t>2026-02-24 11:00</t>
+  </si>
+  <si>
+    <t>2026-02-24 11:15</t>
+  </si>
+  <si>
+    <t>NSE:PATANJALI-EQ_BEAR_1771836300_1771913700</t>
+  </si>
+  <si>
+    <t>NSE:PATANJALI-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 14:15</t>
+  </si>
+  <si>
+    <t>2026-02-24 11:45</t>
+  </si>
+  <si>
+    <t>2026-02-24 12:01</t>
+  </si>
+  <si>
+    <t>NSE:POLICYBZR-EQ_BEAR_1771836300_1771914600</t>
+  </si>
+  <si>
+    <t>NSE:POLICYBZR-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-24 12:00</t>
+  </si>
+  <si>
+    <t>2026-02-24 12:15</t>
+  </si>
+  <si>
+    <t>NSE:IREDA-EQ_BEAR_1771818300_1771915500</t>
+  </si>
+  <si>
+    <t>2026-02-24 12:30</t>
+  </si>
+  <si>
+    <t>NSE:SHREECEM-EQ_BEAR_1771830900_1771917300</t>
+  </si>
+  <si>
+    <t>NSE:SHREECEM-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-23 12:45</t>
+  </si>
+  <si>
+    <t>2026-02-24 12:45</t>
+  </si>
+  <si>
+    <t>2026-02-24 13:01</t>
+  </si>
+  <si>
+    <t>NSE:SAIL-EQ_BEAR_1771821000_1771917300</t>
+  </si>
+  <si>
+    <t>NSE:IGL-EQ_BULL_1771907400_1771918200</t>
+  </si>
+  <si>
+    <t>2026-02-24 10:00</t>
+  </si>
+  <si>
+    <t>2026-02-24 13:00</t>
+  </si>
+  <si>
+    <t>2026-02-24 13:15</t>
+  </si>
+  <si>
+    <t>NSE:BAJAJ-AUTO-EQ_BEAR_1771904700_1771920000</t>
+  </si>
+  <si>
+    <t>2026-02-24 13:30</t>
+  </si>
+  <si>
+    <t>2026-02-24 13:45</t>
+  </si>
+  <si>
+    <t>NSE:GLENMARK-EQ_BULL_1771910100_1771920900</t>
+  </si>
+  <si>
+    <t>NSE:GLENMARK-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-24 10:45</t>
+  </si>
+  <si>
+    <t>2026-02-24 14:00</t>
+  </si>
+  <si>
+    <t>NSE:TATACONSUM-EQ_BULL_1771819200_1771920900</t>
+  </si>
+  <si>
+    <t>2026-02-24 14:01</t>
+  </si>
+  <si>
+    <t>NSE:JSWENERGY-EQ_BEAR_1771838100_1771922700</t>
+  </si>
+  <si>
+    <t>2026-02-24 14:15</t>
+  </si>
+  <si>
+    <t>2026-02-24 14:31</t>
+  </si>
+  <si>
+    <t>NSE:HDFCBANK-EQ_BEAR_1771911000_1771923600</t>
+  </si>
+  <si>
+    <t>2026-02-24 14:30</t>
+  </si>
+  <si>
+    <t>2026-02-24 14:45</t>
+  </si>
+  <si>
+    <t>NSE:ICICIBANK-EQ_BEAR_1771826400_1771923600</t>
+  </si>
+  <si>
+    <t>NSE:ASTRAL-EQ_BULL_1771910100_1771924500</t>
+  </si>
+  <si>
+    <t>NSE:ASTRAL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-24 15:00</t>
+  </si>
+  <si>
+    <t>NSE:JINDALSTEL-EQ_BULL_1771921800_1771924500</t>
+  </si>
+  <si>
+    <t>NSE:JSWSTEEL-EQ_BULL_1771913700_1771924500</t>
+  </si>
+  <si>
+    <t>NSE:JSWSTEEL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-24 15:01</t>
+  </si>
+  <si>
+    <t>NSE:LICHSGFIN-EQ_BULL_1771907400_1771924500</t>
+  </si>
+  <si>
+    <t>NSE:LICHSGFIN-EQ</t>
+  </si>
+  <si>
+    <t>NSE:VEDL-EQ_BULL_1771907400_1771924500</t>
+  </si>
+  <si>
+    <t>NSE:VEDL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:BRITANNIA-EQ_BULL_1771909200_1771925400</t>
+  </si>
+  <si>
+    <t>2026-02-24 10:30</t>
+  </si>
+  <si>
+    <t>2026-02-24 15:15</t>
+  </si>
+  <si>
+    <t>NSE:DELHIVERY-EQ_BULL_1771918200_1771925400</t>
+  </si>
+  <si>
+    <t>NSE:ADANIPORTS-EQ_BULL_1771821900_1771926300</t>
+  </si>
+  <si>
+    <t>2026-02-24 15:30</t>
+  </si>
+  <si>
+    <t>NSE:AMBER-EQ_BULL_1771908300_1771926300</t>
+  </si>
+  <si>
+    <t>2026-02-24 10:15</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;#,##0.00"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="10"/>
-      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1373,16 +1603,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
@@ -1392,27 +1612,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1475,20 +1680,20 @@
     <xf numFmtId="4" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1792,12 +1997,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N104"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N133"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1812,7 +2017,7 @@
     <col min="14" max="14" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1846,7 +2051,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -1880,7 +2085,7 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
     </row>
-    <row r="3" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
@@ -1914,7 +2119,7 @@
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
     </row>
-    <row r="4" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
@@ -1934,13 +2139,13 @@
         <v>21</v>
       </c>
       <c r="G4" s="4">
-        <v>73.180000000000007</v>
+        <v>73.18</v>
       </c>
       <c r="H4" s="4">
-        <v>71.400000000000006</v>
+        <v>71.4</v>
       </c>
       <c r="I4" s="4">
-        <v>72.790000000000006</v>
+        <v>72.79</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
@@ -1948,7 +2153,7 @@
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
     </row>
-    <row r="5" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>22</v>
       </c>
@@ -1982,7 +2187,7 @@
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
     </row>
-    <row r="6" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>26</v>
       </c>
@@ -2016,7 +2221,7 @@
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
     </row>
-    <row r="7" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>29</v>
       </c>
@@ -2050,7 +2255,7 @@
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
     </row>
-    <row r="8" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>32</v>
       </c>
@@ -2084,7 +2289,7 @@
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
     </row>
-    <row r="9" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>36</v>
       </c>
@@ -2098,19 +2303,19 @@
         <v>38</v>
       </c>
       <c r="E9" s="4">
-        <v>1148.9000000000001</v>
+        <v>1148.9</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G9" s="4">
-        <v>1168.5999999999999</v>
+        <v>1168.6</v>
       </c>
       <c r="H9" s="4">
-        <v>1162.9000000000001</v>
+        <v>1162.9</v>
       </c>
       <c r="I9" s="4">
-        <v>1167.9000000000001</v>
+        <v>1167.9</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -2118,7 +2323,7 @@
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
     </row>
-    <row r="10" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
@@ -2152,7 +2357,7 @@
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
     </row>
-    <row r="11" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>44</v>
       </c>
@@ -2186,7 +2391,7 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
     </row>
-    <row r="12" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>47</v>
       </c>
@@ -2220,7 +2425,7 @@
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
     </row>
-    <row r="13" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>50</v>
       </c>
@@ -2254,7 +2459,7 @@
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
     </row>
-    <row r="14" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>55</v>
       </c>
@@ -2288,7 +2493,7 @@
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
     </row>
-    <row r="15" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>58</v>
       </c>
@@ -2308,7 +2513,7 @@
         <v>54</v>
       </c>
       <c r="G15" s="6">
-        <v>515.79999999999995</v>
+        <v>515.8</v>
       </c>
       <c r="H15" s="6">
         <v>506.7</v>
@@ -2322,7 +2527,7 @@
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
     </row>
-    <row r="16" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>61</v>
       </c>
@@ -2345,7 +2550,7 @@
         <v>627.85</v>
       </c>
       <c r="H16" s="4">
-        <v>619.29999999999995</v>
+        <v>619.3</v>
       </c>
       <c r="I16" s="4">
         <v>626.6</v>
@@ -2356,7 +2561,7 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
     </row>
-    <row r="17" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>64</v>
       </c>
@@ -2390,7 +2595,7 @@
       <c r="M17" s="5"/>
       <c r="N17" s="5"/>
     </row>
-    <row r="18" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>66</v>
       </c>
@@ -2424,7 +2629,7 @@
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
     </row>
-    <row r="19" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>70</v>
       </c>
@@ -2458,7 +2663,7 @@
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
     </row>
-    <row r="20" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>73</v>
       </c>
@@ -2492,7 +2697,7 @@
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
     </row>
-    <row r="21" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>77</v>
       </c>
@@ -2526,7 +2731,7 @@
       <c r="M21" s="5"/>
       <c r="N21" s="5"/>
     </row>
-    <row r="22" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>79</v>
       </c>
@@ -2560,7 +2765,7 @@
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
     </row>
-    <row r="23" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>82</v>
       </c>
@@ -2594,7 +2799,7 @@
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
     </row>
-    <row r="24" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>85</v>
       </c>
@@ -2628,7 +2833,7 @@
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
     </row>
-    <row r="25" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>87</v>
       </c>
@@ -2662,7 +2867,7 @@
       <c r="M25" s="5"/>
       <c r="N25" s="5"/>
     </row>
-    <row r="26" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>90</v>
       </c>
@@ -2682,10 +2887,10 @@
         <v>93</v>
       </c>
       <c r="G26" s="6">
-        <v>1198.4000000000001</v>
+        <v>1198.4</v>
       </c>
       <c r="H26" s="6">
-        <v>1194.4000000000001</v>
+        <v>1194.4</v>
       </c>
       <c r="I26" s="6">
         <v>1196.3</v>
@@ -2696,7 +2901,7 @@
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
     </row>
-    <row r="27" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>94</v>
       </c>
@@ -2710,7 +2915,7 @@
         <v>96</v>
       </c>
       <c r="E27" s="6">
-        <v>4203.3999999999996</v>
+        <v>4203.4</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>69</v>
@@ -2719,7 +2924,7 @@
         <v>4164.3</v>
       </c>
       <c r="H27" s="6">
-        <v>4134.8999999999996</v>
+        <v>4134.9</v>
       </c>
       <c r="I27" s="6">
         <v>4135.7</v>
@@ -2730,7 +2935,7 @@
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
     </row>
-    <row r="28" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>97</v>
       </c>
@@ -2764,7 +2969,7 @@
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
     </row>
-    <row r="29" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>98</v>
       </c>
@@ -2798,7 +3003,7 @@
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
     </row>
-    <row r="30" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>101</v>
       </c>
@@ -2832,7 +3037,7 @@
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
     </row>
-    <row r="31" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>104</v>
       </c>
@@ -2866,7 +3071,7 @@
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
     </row>
-    <row r="32" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>107</v>
       </c>
@@ -2900,7 +3105,7 @@
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
     </row>
-    <row r="33" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>111</v>
       </c>
@@ -2934,7 +3139,7 @@
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
     </row>
-    <row r="34" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>114</v>
       </c>
@@ -2968,7 +3173,7 @@
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
     </row>
-    <row r="35" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>117</v>
       </c>
@@ -3002,7 +3207,7 @@
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
     </row>
-    <row r="36" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>119</v>
       </c>
@@ -3036,7 +3241,7 @@
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
     </row>
-    <row r="37" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>120</v>
       </c>
@@ -3070,7 +3275,7 @@
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
     </row>
-    <row r="38" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>122</v>
       </c>
@@ -3096,7 +3301,7 @@
         <v>606.25</v>
       </c>
       <c r="I38" s="6">
-        <v>606.70000000000005</v>
+        <v>606.7</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
@@ -3104,7 +3309,7 @@
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
     </row>
-    <row r="39" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>124</v>
       </c>
@@ -3138,7 +3343,7 @@
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
     </row>
-    <row r="40" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>126</v>
       </c>
@@ -3172,7 +3377,7 @@
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
     </row>
-    <row r="41" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>128</v>
       </c>
@@ -3198,7 +3403,7 @@
         <v>1053.5</v>
       </c>
       <c r="I41" s="6">
-        <v>1053.9000000000001</v>
+        <v>1053.9</v>
       </c>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
@@ -3206,7 +3411,7 @@
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
     </row>
-    <row r="42" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>130</v>
       </c>
@@ -3240,7 +3445,7 @@
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
     </row>
-    <row r="43" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>134</v>
       </c>
@@ -3274,7 +3479,7 @@
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
     </row>
-    <row r="44" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>136</v>
       </c>
@@ -3308,7 +3513,7 @@
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
     </row>
-    <row r="45" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>137</v>
       </c>
@@ -3342,7 +3547,7 @@
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
     </row>
-    <row r="46" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>139</v>
       </c>
@@ -3428,7 +3633,7 @@
         <v>81</v>
       </c>
       <c r="E48" s="10">
-        <v>2193.3000000000002</v>
+        <v>2193.3</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>149</v>
@@ -3608,7 +3813,7 @@
         <v>54</v>
       </c>
       <c r="E53" s="10">
-        <v>2223.1999999999998</v>
+        <v>2223.2</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>166</v>
@@ -3644,13 +3849,13 @@
         <v>157</v>
       </c>
       <c r="E54" s="12">
-        <v>534.54999999999995</v>
+        <v>534.55</v>
       </c>
       <c r="F54" s="11" t="s">
         <v>166</v>
       </c>
       <c r="G54" s="12">
-        <v>539.45000000000005</v>
+        <v>539.45</v>
       </c>
       <c r="H54" s="12">
         <v>532.15</v>
@@ -3689,10 +3894,10 @@
         <v>2558</v>
       </c>
       <c r="H55" s="12">
-        <v>2537.6999999999998</v>
+        <v>2537.7</v>
       </c>
       <c r="I55" s="12">
-        <v>2554.8000000000002</v>
+        <v>2554.8</v>
       </c>
       <c r="J55" s="11"/>
       <c r="K55" s="11"/>
@@ -3941,10 +4146,10 @@
         <v>4785</v>
       </c>
       <c r="H62" s="12">
-        <v>4741.8999999999996</v>
+        <v>4741.9</v>
       </c>
       <c r="I62" s="12">
-        <v>4782.6000000000004</v>
+        <v>4782.6</v>
       </c>
       <c r="J62" s="11"/>
       <c r="K62" s="11"/>
@@ -4206,7 +4411,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="13" t="s">
         <v>216</v>
       </c>
@@ -4220,27 +4425,27 @@
         <v>153</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>283</v>
+        <v>218</v>
       </c>
       <c r="F70" s="14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G70" s="14" t="s">
-        <v>284</v>
+        <v>220</v>
       </c>
       <c r="H70" s="14" t="s">
-        <v>285</v>
+        <v>221</v>
       </c>
       <c r="I70" s="14" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C71" s="14" t="s">
         <v>11</v>
@@ -4249,27 +4454,27 @@
         <v>195</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>287</v>
+        <v>225</v>
       </c>
       <c r="F71" s="14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G71" s="14" t="s">
-        <v>288</v>
+        <v>226</v>
       </c>
       <c r="H71" s="14" t="s">
-        <v>289</v>
+        <v>227</v>
       </c>
       <c r="I71" s="14" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="13" t="s">
-        <v>291</v>
+        <v>229</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="C72" s="14" t="s">
         <v>11</v>
@@ -4278,27 +4483,27 @@
         <v>163</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>292</v>
+        <v>231</v>
       </c>
       <c r="F72" s="14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G72" s="14" t="s">
-        <v>293</v>
+        <v>232</v>
       </c>
       <c r="H72" s="14" t="s">
-        <v>294</v>
+        <v>233</v>
       </c>
       <c r="I72" s="14" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="13" t="s">
-        <v>296</v>
+        <v>235</v>
       </c>
       <c r="B73" s="14" t="s">
-        <v>297</v>
+        <v>236</v>
       </c>
       <c r="C73" s="14" t="s">
         <v>11</v>
@@ -4307,27 +4512,27 @@
         <v>145</v>
       </c>
       <c r="E73" s="14" t="s">
-        <v>298</v>
+        <v>237</v>
       </c>
       <c r="F73" s="14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G73" s="14" t="s">
-        <v>299</v>
+        <v>238</v>
       </c>
       <c r="H73" s="14" t="s">
-        <v>300</v>
+        <v>239</v>
       </c>
       <c r="I73" s="14" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="13" t="s">
-        <v>302</v>
+        <v>241</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>303</v>
+        <v>242</v>
       </c>
       <c r="C74" s="14" t="s">
         <v>11</v>
@@ -4336,27 +4541,27 @@
         <v>146</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>304</v>
+        <v>243</v>
       </c>
       <c r="F74" s="14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G74" s="14" t="s">
-        <v>305</v>
+        <v>244</v>
       </c>
       <c r="H74" s="14" t="s">
-        <v>306</v>
+        <v>245</v>
       </c>
       <c r="I74" s="14" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="13" t="s">
-        <v>307</v>
+        <v>246</v>
       </c>
       <c r="B75" s="14" t="s">
-        <v>308</v>
+        <v>247</v>
       </c>
       <c r="C75" s="14" t="s">
         <v>11</v>
@@ -4365,24 +4570,24 @@
         <v>146</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>309</v>
+        <v>248</v>
       </c>
       <c r="F75" s="14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G75" s="14" t="s">
-        <v>310</v>
+        <v>249</v>
       </c>
       <c r="H75" s="14" t="s">
-        <v>311</v>
+        <v>250</v>
       </c>
       <c r="I75" s="14" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="13" t="s">
-        <v>313</v>
+        <v>252</v>
       </c>
       <c r="B76" s="14" t="s">
         <v>115</v>
@@ -4391,30 +4596,30 @@
         <v>11</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>314</v>
+        <v>253</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>315</v>
+        <v>254</v>
       </c>
       <c r="F76" s="14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G76" s="14" t="s">
-        <v>316</v>
+        <v>255</v>
       </c>
       <c r="H76" s="14" t="s">
-        <v>317</v>
+        <v>256</v>
       </c>
       <c r="I76" s="14" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="13" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="B77" s="14" t="s">
-        <v>233</v>
+        <v>259</v>
       </c>
       <c r="C77" s="14" t="s">
         <v>11</v>
@@ -4423,56 +4628,56 @@
         <v>174</v>
       </c>
       <c r="E77" s="14" t="s">
-        <v>319</v>
+        <v>260</v>
       </c>
       <c r="F77" s="14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G77" s="14" t="s">
-        <v>320</v>
+        <v>261</v>
       </c>
       <c r="H77" s="14" t="s">
-        <v>321</v>
+        <v>262</v>
       </c>
       <c r="I77" s="14" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="13" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="B78" s="14" t="s">
-        <v>239</v>
+        <v>265</v>
       </c>
       <c r="C78" s="14" t="s">
         <v>11</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>240</v>
+        <v>266</v>
       </c>
       <c r="E78" s="14" t="s">
-        <v>323</v>
+        <v>267</v>
       </c>
       <c r="F78" s="14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G78" s="14" t="s">
-        <v>324</v>
+        <v>268</v>
       </c>
       <c r="H78" s="14" t="s">
-        <v>325</v>
+        <v>269</v>
       </c>
       <c r="I78" s="14" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="13" t="s">
-        <v>327</v>
+        <v>271</v>
       </c>
       <c r="B79" s="14" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="C79" s="14" t="s">
         <v>11</v>
@@ -4481,27 +4686,27 @@
         <v>153</v>
       </c>
       <c r="E79" s="14" t="s">
-        <v>328</v>
+        <v>273</v>
       </c>
       <c r="F79" s="14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G79" s="14" t="s">
-        <v>329</v>
+        <v>274</v>
       </c>
       <c r="H79" s="14" t="s">
-        <v>330</v>
+        <v>275</v>
       </c>
       <c r="I79" s="14" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="13" t="s">
-        <v>332</v>
+        <v>277</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>333</v>
+        <v>278</v>
       </c>
       <c r="C80" s="14" t="s">
         <v>11</v>
@@ -4510,56 +4715,56 @@
         <v>163</v>
       </c>
       <c r="E80" s="14" t="s">
-        <v>334</v>
+        <v>279</v>
       </c>
       <c r="F80" s="14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G80" s="14" t="s">
-        <v>335</v>
+        <v>280</v>
       </c>
       <c r="H80" s="14" t="s">
-        <v>336</v>
+        <v>281</v>
       </c>
       <c r="I80" s="14" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
-        <v>245</v>
+        <v>283</v>
       </c>
       <c r="B81" s="14" t="s">
-        <v>246</v>
+        <v>284</v>
       </c>
       <c r="C81" s="14" t="s">
         <v>11</v>
       </c>
       <c r="D81" s="14" t="s">
-        <v>229</v>
+        <v>285</v>
       </c>
       <c r="E81" s="14" t="s">
-        <v>338</v>
+        <v>286</v>
       </c>
       <c r="F81" s="14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G81" s="14" t="s">
-        <v>339</v>
+        <v>287</v>
       </c>
       <c r="H81" s="14" t="s">
-        <v>340</v>
+        <v>288</v>
       </c>
       <c r="I81" s="14" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="13" t="s">
-        <v>247</v>
+        <v>290</v>
       </c>
       <c r="B82" s="14" t="s">
-        <v>248</v>
+        <v>291</v>
       </c>
       <c r="C82" s="14" t="s">
         <v>11</v>
@@ -4568,27 +4773,27 @@
         <v>163</v>
       </c>
       <c r="E82" s="14" t="s">
-        <v>342</v>
+        <v>292</v>
       </c>
       <c r="F82" s="14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G82" s="14" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
       <c r="H82" s="14" t="s">
-        <v>344</v>
+        <v>294</v>
       </c>
       <c r="I82" s="14" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="13" t="s">
-        <v>346</v>
+        <v>296</v>
       </c>
       <c r="B83" s="14" t="s">
-        <v>347</v>
+        <v>297</v>
       </c>
       <c r="C83" s="14" t="s">
         <v>11</v>
@@ -4597,24 +4802,24 @@
         <v>198</v>
       </c>
       <c r="E83" s="14" t="s">
-        <v>348</v>
+        <v>298</v>
       </c>
       <c r="F83" s="14" t="s">
-        <v>231</v>
+        <v>299</v>
       </c>
       <c r="G83" s="14" t="s">
-        <v>349</v>
+        <v>300</v>
       </c>
       <c r="H83" s="14" t="s">
-        <v>350</v>
+        <v>301</v>
       </c>
       <c r="I83" s="14" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="13" t="s">
-        <v>230</v>
+        <v>303</v>
       </c>
       <c r="B84" s="14" t="s">
         <v>191</v>
@@ -4626,27 +4831,27 @@
         <v>192</v>
       </c>
       <c r="E84" s="14" t="s">
-        <v>352</v>
+        <v>304</v>
       </c>
       <c r="F84" s="14" t="s">
-        <v>231</v>
+        <v>299</v>
       </c>
       <c r="G84" s="14" t="s">
-        <v>353</v>
+        <v>305</v>
       </c>
       <c r="H84" s="14" t="s">
-        <v>354</v>
+        <v>306</v>
       </c>
       <c r="I84" s="14" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="15" t="s">
-        <v>224</v>
+        <v>308</v>
       </c>
       <c r="B85" s="16" t="s">
-        <v>225</v>
+        <v>309</v>
       </c>
       <c r="C85" s="16" t="s">
         <v>52</v>
@@ -4655,56 +4860,56 @@
         <v>157</v>
       </c>
       <c r="E85" s="16" t="s">
-        <v>356</v>
+        <v>310</v>
       </c>
       <c r="F85" s="16" t="s">
-        <v>226</v>
+        <v>311</v>
       </c>
       <c r="G85" s="16" t="s">
-        <v>357</v>
+        <v>312</v>
       </c>
       <c r="H85" s="16" t="s">
-        <v>358</v>
+        <v>313</v>
       </c>
       <c r="I85" s="16" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="15" t="s">
-        <v>227</v>
+        <v>315</v>
       </c>
       <c r="B86" s="16" t="s">
-        <v>228</v>
+        <v>316</v>
       </c>
       <c r="C86" s="16" t="s">
         <v>52</v>
       </c>
       <c r="D86" s="16" t="s">
-        <v>229</v>
+        <v>285</v>
       </c>
       <c r="E86" s="16" t="s">
-        <v>360</v>
+        <v>317</v>
       </c>
       <c r="F86" s="16" t="s">
-        <v>226</v>
+        <v>311</v>
       </c>
       <c r="G86" s="16" t="s">
-        <v>361</v>
+        <v>318</v>
       </c>
       <c r="H86" s="16" t="s">
-        <v>362</v>
+        <v>319</v>
       </c>
       <c r="I86" s="16" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="15" t="s">
-        <v>234</v>
+        <v>320</v>
       </c>
       <c r="B87" s="16" t="s">
-        <v>235</v>
+        <v>321</v>
       </c>
       <c r="C87" s="16" t="s">
         <v>52</v>
@@ -4713,24 +4918,24 @@
         <v>145</v>
       </c>
       <c r="E87" s="16" t="s">
-        <v>363</v>
+        <v>322</v>
       </c>
       <c r="F87" s="16" t="s">
-        <v>226</v>
+        <v>311</v>
       </c>
       <c r="G87" s="16" t="s">
-        <v>364</v>
+        <v>323</v>
       </c>
       <c r="H87" s="16" t="s">
-        <v>365</v>
+        <v>324</v>
       </c>
       <c r="I87" s="16" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="13" t="s">
-        <v>236</v>
+        <v>326</v>
       </c>
       <c r="B88" s="14" t="s">
         <v>27</v>
@@ -4739,30 +4944,30 @@
         <v>11</v>
       </c>
       <c r="D88" s="14" t="s">
-        <v>231</v>
+        <v>299</v>
       </c>
       <c r="E88" s="14" t="s">
-        <v>367</v>
+        <v>327</v>
       </c>
       <c r="F88" s="14" t="s">
-        <v>237</v>
+        <v>328</v>
       </c>
       <c r="G88" s="14" t="s">
-        <v>368</v>
+        <v>329</v>
       </c>
       <c r="H88" s="14" t="s">
-        <v>369</v>
+        <v>330</v>
       </c>
       <c r="I88" s="14" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="89" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="15" t="s">
-        <v>219</v>
+        <v>332</v>
       </c>
       <c r="B89" s="16" t="s">
-        <v>220</v>
+        <v>333</v>
       </c>
       <c r="C89" s="16" t="s">
         <v>52</v>
@@ -4771,27 +4976,27 @@
         <v>145</v>
       </c>
       <c r="E89" s="16" t="s">
-        <v>371</v>
+        <v>334</v>
       </c>
       <c r="F89" s="16" t="s">
-        <v>221</v>
+        <v>335</v>
       </c>
       <c r="G89" s="16" t="s">
-        <v>372</v>
+        <v>336</v>
       </c>
       <c r="H89" s="16" t="s">
-        <v>373</v>
+        <v>337</v>
       </c>
       <c r="I89" s="16" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="13" t="s">
-        <v>241</v>
+        <v>338</v>
       </c>
       <c r="B90" s="14" t="s">
-        <v>242</v>
+        <v>339</v>
       </c>
       <c r="C90" s="14" t="s">
         <v>11</v>
@@ -4800,56 +5005,56 @@
         <v>157</v>
       </c>
       <c r="E90" s="14" t="s">
-        <v>374</v>
+        <v>340</v>
       </c>
       <c r="F90" s="14" t="s">
-        <v>243</v>
+        <v>341</v>
       </c>
       <c r="G90" s="14" t="s">
-        <v>375</v>
+        <v>342</v>
       </c>
       <c r="H90" s="14" t="s">
-        <v>376</v>
+        <v>343</v>
       </c>
       <c r="I90" s="14" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="15" t="s">
-        <v>249</v>
+        <v>345</v>
       </c>
       <c r="B91" s="16" t="s">
-        <v>250</v>
+        <v>346</v>
       </c>
       <c r="C91" s="16" t="s">
         <v>52</v>
       </c>
       <c r="D91" s="16" t="s">
-        <v>221</v>
+        <v>335</v>
       </c>
       <c r="E91" s="16" t="s">
-        <v>378</v>
+        <v>347</v>
       </c>
       <c r="F91" s="16" t="s">
-        <v>244</v>
+        <v>348</v>
       </c>
       <c r="G91" s="16" t="s">
-        <v>379</v>
+        <v>349</v>
       </c>
       <c r="H91" s="16" t="s">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="I91" s="16" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="13" t="s">
-        <v>252</v>
+        <v>352</v>
       </c>
       <c r="B92" s="14" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="C92" s="14" t="s">
         <v>11</v>
@@ -4858,53 +5063,53 @@
         <v>163</v>
       </c>
       <c r="E92" s="14" t="s">
-        <v>292</v>
+        <v>231</v>
       </c>
       <c r="F92" s="14" t="s">
-        <v>251</v>
+        <v>353</v>
       </c>
       <c r="G92" s="14" t="s">
-        <v>382</v>
+        <v>354</v>
       </c>
       <c r="H92" s="14" t="s">
-        <v>383</v>
+        <v>355</v>
       </c>
       <c r="I92" s="14" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="13" t="s">
-        <v>254</v>
+        <v>357</v>
       </c>
       <c r="B93" s="14" t="s">
-        <v>255</v>
+        <v>358</v>
       </c>
       <c r="C93" s="14" t="s">
         <v>11</v>
       </c>
       <c r="D93" s="14" t="s">
-        <v>256</v>
+        <v>359</v>
       </c>
       <c r="E93" s="14" t="s">
-        <v>385</v>
+        <v>360</v>
       </c>
       <c r="F93" s="14" t="s">
-        <v>251</v>
+        <v>353</v>
       </c>
       <c r="G93" s="14" t="s">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="H93" s="14" t="s">
-        <v>387</v>
+        <v>362</v>
       </c>
       <c r="I93" s="14" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="13" t="s">
-        <v>257</v>
+        <v>364</v>
       </c>
       <c r="B94" s="14" t="s">
         <v>33</v>
@@ -4913,27 +5118,27 @@
         <v>11</v>
       </c>
       <c r="D94" s="14" t="s">
-        <v>240</v>
+        <v>266</v>
       </c>
       <c r="E94" s="14" t="s">
-        <v>389</v>
+        <v>365</v>
       </c>
       <c r="F94" s="14" t="s">
-        <v>258</v>
+        <v>366</v>
       </c>
       <c r="G94" s="14" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
       <c r="H94" s="14" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="I94" s="14" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="15" t="s">
-        <v>259</v>
+        <v>370</v>
       </c>
       <c r="B95" s="16" t="s">
         <v>131</v>
@@ -4942,88 +5147,88 @@
         <v>52</v>
       </c>
       <c r="D95" s="16" t="s">
-        <v>260</v>
+        <v>371</v>
       </c>
       <c r="E95" s="16" t="s">
-        <v>393</v>
+        <v>372</v>
       </c>
       <c r="F95" s="16" t="s">
-        <v>261</v>
+        <v>373</v>
       </c>
       <c r="G95" s="16" t="s">
-        <v>394</v>
+        <v>374</v>
       </c>
       <c r="H95" s="16" t="s">
-        <v>395</v>
+        <v>375</v>
       </c>
       <c r="I95" s="16" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="96" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="13" t="s">
-        <v>262</v>
+        <v>377</v>
       </c>
       <c r="B96" s="14" t="s">
-        <v>263</v>
+        <v>378</v>
       </c>
       <c r="C96" s="14" t="s">
         <v>11</v>
       </c>
       <c r="D96" s="14" t="s">
-        <v>231</v>
+        <v>299</v>
       </c>
       <c r="E96" s="14" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="F96" s="14" t="s">
-        <v>264</v>
+        <v>380</v>
       </c>
       <c r="G96" s="14" t="s">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="H96" s="14" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="I96" s="14" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="13" t="s">
-        <v>268</v>
+        <v>384</v>
       </c>
       <c r="B97" s="14" t="s">
-        <v>269</v>
+        <v>385</v>
       </c>
       <c r="C97" s="14" t="s">
         <v>11</v>
       </c>
       <c r="D97" s="14" t="s">
-        <v>270</v>
+        <v>386</v>
       </c>
       <c r="E97" s="14" t="s">
-        <v>401</v>
+        <v>387</v>
       </c>
       <c r="F97" s="14" t="s">
-        <v>264</v>
+        <v>380</v>
       </c>
       <c r="G97" s="14" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="H97" s="14" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="I97" s="14" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="98" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="13" t="s">
-        <v>266</v>
+        <v>391</v>
       </c>
       <c r="B98" s="14" t="s">
-        <v>267</v>
+        <v>392</v>
       </c>
       <c r="C98" s="14" t="s">
         <v>11</v>
@@ -5032,27 +5237,27 @@
         <v>192</v>
       </c>
       <c r="E98" s="14" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="F98" s="14" t="s">
-        <v>264</v>
+        <v>380</v>
       </c>
       <c r="G98" s="14" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="H98" s="14" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="I98" s="14" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="99" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="13" t="s">
-        <v>271</v>
+        <v>396</v>
       </c>
       <c r="B99" s="14" t="s">
-        <v>272</v>
+        <v>397</v>
       </c>
       <c r="C99" s="14" t="s">
         <v>11</v>
@@ -5061,24 +5266,24 @@
         <v>198</v>
       </c>
       <c r="E99" s="14" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="F99" s="14" t="s">
-        <v>264</v>
+        <v>380</v>
       </c>
       <c r="G99" s="14" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="H99" s="14" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="I99" s="14" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="100" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
-        <v>277</v>
+        <v>402</v>
       </c>
       <c r="B100" s="14" t="s">
         <v>86</v>
@@ -5087,88 +5292,88 @@
         <v>11</v>
       </c>
       <c r="D100" s="14" t="s">
-        <v>243</v>
+        <v>341</v>
       </c>
       <c r="E100" s="14" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="F100" s="14" t="s">
-        <v>265</v>
+        <v>404</v>
       </c>
       <c r="G100" s="14" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="H100" s="14" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="I100" s="14" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="101" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="13" t="s">
-        <v>273</v>
+        <v>408</v>
       </c>
       <c r="B101" s="14" t="s">
-        <v>274</v>
+        <v>409</v>
       </c>
       <c r="C101" s="14" t="s">
         <v>11</v>
       </c>
       <c r="D101" s="14" t="s">
-        <v>275</v>
+        <v>410</v>
       </c>
       <c r="E101" s="14" t="s">
+        <v>411</v>
+      </c>
+      <c r="F101" s="14" t="s">
+        <v>404</v>
+      </c>
+      <c r="G101" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="H101" s="14" t="s">
+        <v>413</v>
+      </c>
+      <c r="I101" s="14" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="102" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" s="13" t="s">
+        <v>415</v>
+      </c>
+      <c r="B102" s="14" t="s">
         <v>416</v>
-      </c>
-      <c r="F101" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="G101" s="14" t="s">
-        <v>417</v>
-      </c>
-      <c r="H101" s="14" t="s">
-        <v>418</v>
-      </c>
-      <c r="I101" s="14" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="13" t="s">
-        <v>278</v>
-      </c>
-      <c r="B102" s="14" t="s">
-        <v>279</v>
       </c>
       <c r="C102" s="14" t="s">
         <v>11</v>
       </c>
       <c r="D102" s="14" t="s">
-        <v>221</v>
+        <v>335</v>
       </c>
       <c r="E102" s="14" t="s">
+        <v>417</v>
+      </c>
+      <c r="F102" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="G102" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="H102" s="14" t="s">
         <v>420</v>
       </c>
-      <c r="F102" s="14" t="s">
-        <v>276</v>
-      </c>
-      <c r="G102" s="14" t="s">
+      <c r="I102" s="14" t="s">
         <v>421</v>
       </c>
-      <c r="H102" s="14" t="s">
+    </row>
+    <row r="103" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" s="13" t="s">
         <v>422</v>
       </c>
-      <c r="I102" s="14" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="13" t="s">
-        <v>280</v>
-      </c>
       <c r="B103" s="14" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="C103" s="14" t="s">
         <v>11</v>
@@ -5177,24 +5382,24 @@
         <v>153</v>
       </c>
       <c r="E103" s="14" t="s">
-        <v>328</v>
+        <v>273</v>
       </c>
       <c r="F103" s="14" t="s">
-        <v>276</v>
+        <v>418</v>
       </c>
       <c r="G103" s="14" t="s">
+        <v>423</v>
+      </c>
+      <c r="H103" s="14" t="s">
         <v>424</v>
       </c>
-      <c r="H103" s="14" t="s">
+      <c r="I103" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="I103" s="14" t="s">
+    </row>
+    <row r="104" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="13" t="s">
         <v>426</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="13" t="s">
-        <v>282</v>
       </c>
       <c r="B104" s="14" t="s">
         <v>197</v>
@@ -5209,7 +5414,7 @@
         <v>427</v>
       </c>
       <c r="F104" s="14" t="s">
-        <v>276</v>
+        <v>418</v>
       </c>
       <c r="G104" s="14" t="s">
         <v>428</v>
@@ -5219,6 +5424,1050 @@
       </c>
       <c r="I104" s="14" t="s">
         <v>430</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A105" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="B105" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="C105" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D105" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="E105" s="10">
+        <v>346.35</v>
+      </c>
+      <c r="F105" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="G105" s="10">
+        <v>345</v>
+      </c>
+      <c r="H105" s="10">
+        <v>341.65</v>
+      </c>
+      <c r="I105" s="10">
+        <v>342.7</v>
+      </c>
+      <c r="J105" s="9"/>
+      <c r="K105" s="9"/>
+      <c r="L105" s="9"/>
+      <c r="M105" s="9"/>
+      <c r="N105" s="9" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A106" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="B106" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="C106" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D106" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="E106" s="10">
+        <v>1268.7</v>
+      </c>
+      <c r="F106" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="G106" s="10">
+        <v>1269</v>
+      </c>
+      <c r="H106" s="10">
+        <v>1248.3</v>
+      </c>
+      <c r="I106" s="10">
+        <v>1249.7</v>
+      </c>
+      <c r="J106" s="9"/>
+      <c r="K106" s="9"/>
+      <c r="L106" s="9"/>
+      <c r="M106" s="9"/>
+      <c r="N106" s="9" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A107" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="B107" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C107" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D107" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="E107" s="10">
+        <v>6272</v>
+      </c>
+      <c r="F107" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="G107" s="10">
+        <v>6287</v>
+      </c>
+      <c r="H107" s="10">
+        <v>6230</v>
+      </c>
+      <c r="I107" s="10">
+        <v>6239</v>
+      </c>
+      <c r="J107" s="9"/>
+      <c r="K107" s="9"/>
+      <c r="L107" s="9"/>
+      <c r="M107" s="9"/>
+      <c r="N107" s="9" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A108" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="B108" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="C108" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="E108" s="10">
+        <v>325.8</v>
+      </c>
+      <c r="F108" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="G108" s="10">
+        <v>325.4</v>
+      </c>
+      <c r="H108" s="10">
+        <v>322.65</v>
+      </c>
+      <c r="I108" s="10">
+        <v>323</v>
+      </c>
+      <c r="J108" s="9"/>
+      <c r="K108" s="9"/>
+      <c r="L108" s="9"/>
+      <c r="M108" s="9"/>
+      <c r="N108" s="9" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A109" s="11" t="s">
+        <v>442</v>
+      </c>
+      <c r="B109" s="11" t="s">
+        <v>443</v>
+      </c>
+      <c r="C109" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D109" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="E109" s="12">
+        <v>176.21</v>
+      </c>
+      <c r="F109" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="G109" s="12">
+        <v>178.67</v>
+      </c>
+      <c r="H109" s="12">
+        <v>176.51</v>
+      </c>
+      <c r="I109" s="12">
+        <v>178.15</v>
+      </c>
+      <c r="J109" s="11"/>
+      <c r="K109" s="11"/>
+      <c r="L109" s="11"/>
+      <c r="M109" s="11"/>
+      <c r="N109" s="11" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A110" s="11" t="s">
+        <v>445</v>
+      </c>
+      <c r="B110" s="11" t="s">
+        <v>446</v>
+      </c>
+      <c r="C110" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D110" s="11" t="s">
+        <v>439</v>
+      </c>
+      <c r="E110" s="12">
+        <v>472.5</v>
+      </c>
+      <c r="F110" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="G110" s="12">
+        <v>478.8</v>
+      </c>
+      <c r="H110" s="12">
+        <v>473.5</v>
+      </c>
+      <c r="I110" s="12">
+        <v>476.4</v>
+      </c>
+      <c r="J110" s="11"/>
+      <c r="K110" s="11"/>
+      <c r="L110" s="11"/>
+      <c r="M110" s="11"/>
+      <c r="N110" s="11" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A111" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="B111" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="C111" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D111" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="E111" s="10">
+        <v>785.6</v>
+      </c>
+      <c r="F111" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="G111" s="10">
+        <v>778</v>
+      </c>
+      <c r="H111" s="10">
+        <v>769.55</v>
+      </c>
+      <c r="I111" s="10">
+        <v>770.1</v>
+      </c>
+      <c r="J111" s="9"/>
+      <c r="K111" s="9"/>
+      <c r="L111" s="9"/>
+      <c r="M111" s="9"/>
+      <c r="N111" s="9" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A112" s="11" t="s">
+        <v>449</v>
+      </c>
+      <c r="B112" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C112" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D112" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="E112" s="12">
+        <v>1208.7</v>
+      </c>
+      <c r="F112" s="11" t="s">
+        <v>450</v>
+      </c>
+      <c r="G112" s="12">
+        <v>1229.2</v>
+      </c>
+      <c r="H112" s="12">
+        <v>1222.3</v>
+      </c>
+      <c r="I112" s="12">
+        <v>1228.8</v>
+      </c>
+      <c r="J112" s="11"/>
+      <c r="K112" s="11"/>
+      <c r="L112" s="11"/>
+      <c r="M112" s="11"/>
+      <c r="N112" s="11" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A113" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="B113" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="C113" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D113" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="E113" s="10">
+        <v>526.7</v>
+      </c>
+      <c r="F113" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="G113" s="10">
+        <v>529.7</v>
+      </c>
+      <c r="H113" s="10">
+        <v>526</v>
+      </c>
+      <c r="I113" s="10">
+        <v>526.85</v>
+      </c>
+      <c r="J113" s="9"/>
+      <c r="K113" s="9"/>
+      <c r="L113" s="9"/>
+      <c r="M113" s="9"/>
+      <c r="N113" s="9" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A114" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="B114" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="C114" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D114" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="E114" s="10">
+        <v>1493.5</v>
+      </c>
+      <c r="F114" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="G114" s="10">
+        <v>1491</v>
+      </c>
+      <c r="H114" s="10">
+        <v>1485.9</v>
+      </c>
+      <c r="I114" s="10">
+        <v>1487.1</v>
+      </c>
+      <c r="J114" s="9"/>
+      <c r="K114" s="9"/>
+      <c r="L114" s="9"/>
+      <c r="M114" s="9"/>
+      <c r="N114" s="9" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A115" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="B115" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C115" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D115" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="E115" s="10">
+        <v>127.29</v>
+      </c>
+      <c r="F115" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="G115" s="10">
+        <v>126.41</v>
+      </c>
+      <c r="H115" s="10">
+        <v>125.9</v>
+      </c>
+      <c r="I115" s="10">
+        <v>125.95</v>
+      </c>
+      <c r="J115" s="9"/>
+      <c r="K115" s="9"/>
+      <c r="L115" s="9"/>
+      <c r="M115" s="9"/>
+      <c r="N115" s="9" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A116" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="B116" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="C116" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D116" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="E116" s="10">
+        <v>26410</v>
+      </c>
+      <c r="F116" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="G116" s="10">
+        <v>26505</v>
+      </c>
+      <c r="H116" s="10">
+        <v>26390</v>
+      </c>
+      <c r="I116" s="10">
+        <v>26395</v>
+      </c>
+      <c r="J116" s="9"/>
+      <c r="K116" s="9"/>
+      <c r="L116" s="9"/>
+      <c r="M116" s="9"/>
+      <c r="N116" s="9" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A117" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="B117" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C117" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D117" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="E117" s="10">
+        <v>158.2</v>
+      </c>
+      <c r="F117" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="G117" s="10">
+        <v>156.1</v>
+      </c>
+      <c r="H117" s="10">
+        <v>154.89</v>
+      </c>
+      <c r="I117" s="10">
+        <v>155.09</v>
+      </c>
+      <c r="J117" s="9"/>
+      <c r="K117" s="9"/>
+      <c r="L117" s="9"/>
+      <c r="M117" s="9"/>
+      <c r="N117" s="9" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A118" s="11" t="s">
+        <v>469</v>
+      </c>
+      <c r="B118" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C118" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D118" s="11" t="s">
+        <v>470</v>
+      </c>
+      <c r="E118" s="12">
+        <v>170.37</v>
+      </c>
+      <c r="F118" s="11" t="s">
+        <v>471</v>
+      </c>
+      <c r="G118" s="12">
+        <v>171.45</v>
+      </c>
+      <c r="H118" s="12">
+        <v>170.13</v>
+      </c>
+      <c r="I118" s="12">
+        <v>170.92</v>
+      </c>
+      <c r="J118" s="11"/>
+      <c r="K118" s="11"/>
+      <c r="L118" s="11"/>
+      <c r="M118" s="11"/>
+      <c r="N118" s="11" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A119" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="B119" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C119" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D119" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="E119" s="10">
+        <v>9747</v>
+      </c>
+      <c r="F119" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="G119" s="10">
+        <v>9810</v>
+      </c>
+      <c r="H119" s="10">
+        <v>9769.5</v>
+      </c>
+      <c r="I119" s="10">
+        <v>9784.5</v>
+      </c>
+      <c r="J119" s="9"/>
+      <c r="K119" s="9"/>
+      <c r="L119" s="9"/>
+      <c r="M119" s="9"/>
+      <c r="N119" s="9" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A120" s="11" t="s">
+        <v>476</v>
+      </c>
+      <c r="B120" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="C120" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D120" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="E120" s="12">
+        <v>2039.5</v>
+      </c>
+      <c r="F120" s="11" t="s">
+        <v>475</v>
+      </c>
+      <c r="G120" s="12">
+        <v>2049.3</v>
+      </c>
+      <c r="H120" s="12">
+        <v>2039</v>
+      </c>
+      <c r="I120" s="12">
+        <v>2048.4</v>
+      </c>
+      <c r="J120" s="11"/>
+      <c r="K120" s="11"/>
+      <c r="L120" s="11"/>
+      <c r="M120" s="11"/>
+      <c r="N120" s="11" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A121" s="11" t="s">
+        <v>480</v>
+      </c>
+      <c r="B121" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C121" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D121" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="E121" s="12">
+        <v>1170.7</v>
+      </c>
+      <c r="F121" s="11" t="s">
+        <v>475</v>
+      </c>
+      <c r="G121" s="12">
+        <v>1177.1</v>
+      </c>
+      <c r="H121" s="12">
+        <v>1171</v>
+      </c>
+      <c r="I121" s="12">
+        <v>1176.4</v>
+      </c>
+      <c r="J121" s="11"/>
+      <c r="K121" s="11"/>
+      <c r="L121" s="11"/>
+      <c r="M121" s="11"/>
+      <c r="N121" s="11" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A122" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="B122" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C122" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D122" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="E122" s="10">
+        <v>487</v>
+      </c>
+      <c r="F122" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="G122" s="10">
+        <v>482.35</v>
+      </c>
+      <c r="H122" s="10">
+        <v>480.55</v>
+      </c>
+      <c r="I122" s="10">
+        <v>480.7</v>
+      </c>
+      <c r="J122" s="9"/>
+      <c r="K122" s="9"/>
+      <c r="L122" s="9"/>
+      <c r="M122" s="9"/>
+      <c r="N122" s="9" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A123" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="B123" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C123" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D123" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="E123" s="10">
+        <v>920</v>
+      </c>
+      <c r="F123" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="G123" s="10">
+        <v>914.25</v>
+      </c>
+      <c r="H123" s="10">
+        <v>912.15</v>
+      </c>
+      <c r="I123" s="10">
+        <v>912.4</v>
+      </c>
+      <c r="J123" s="9"/>
+      <c r="K123" s="9"/>
+      <c r="L123" s="9"/>
+      <c r="M123" s="9"/>
+      <c r="N123" s="9" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A124" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="B124" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="C124" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D124" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="E124" s="10">
+        <v>1401.1</v>
+      </c>
+      <c r="F124" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="G124" s="10">
+        <v>1388.1</v>
+      </c>
+      <c r="H124" s="10">
+        <v>1384.4</v>
+      </c>
+      <c r="I124" s="10">
+        <v>1384.4</v>
+      </c>
+      <c r="J124" s="9"/>
+      <c r="K124" s="9"/>
+      <c r="L124" s="9"/>
+      <c r="M124" s="9"/>
+      <c r="N124" s="9" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A125" s="11" t="s">
+        <v>489</v>
+      </c>
+      <c r="B125" s="11" t="s">
+        <v>490</v>
+      </c>
+      <c r="C125" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D125" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="E125" s="12">
+        <v>1642.4</v>
+      </c>
+      <c r="F125" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="G125" s="12">
+        <v>1659.8</v>
+      </c>
+      <c r="H125" s="12">
+        <v>1650.1</v>
+      </c>
+      <c r="I125" s="12">
+        <v>1658</v>
+      </c>
+      <c r="J125" s="11"/>
+      <c r="K125" s="11"/>
+      <c r="L125" s="11"/>
+      <c r="M125" s="11"/>
+      <c r="N125" s="11" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A126" s="11" t="s">
+        <v>492</v>
+      </c>
+      <c r="B126" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="C126" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D126" s="11" t="s">
+        <v>479</v>
+      </c>
+      <c r="E126" s="12">
+        <v>1225.5</v>
+      </c>
+      <c r="F126" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="G126" s="12">
+        <v>1238.4</v>
+      </c>
+      <c r="H126" s="12">
+        <v>1226.6</v>
+      </c>
+      <c r="I126" s="12">
+        <v>1235</v>
+      </c>
+      <c r="J126" s="11"/>
+      <c r="K126" s="11"/>
+      <c r="L126" s="11"/>
+      <c r="M126" s="11"/>
+      <c r="N126" s="11" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A127" s="11" t="s">
+        <v>493</v>
+      </c>
+      <c r="B127" s="11" t="s">
+        <v>494</v>
+      </c>
+      <c r="C127" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D127" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="E127" s="12">
+        <v>1244.3</v>
+      </c>
+      <c r="F127" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="G127" s="12">
+        <v>1256</v>
+      </c>
+      <c r="H127" s="12">
+        <v>1249.5</v>
+      </c>
+      <c r="I127" s="12">
+        <v>1256</v>
+      </c>
+      <c r="J127" s="11"/>
+      <c r="K127" s="11"/>
+      <c r="L127" s="11"/>
+      <c r="M127" s="11"/>
+      <c r="N127" s="11" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A128" s="11" t="s">
+        <v>496</v>
+      </c>
+      <c r="B128" s="11" t="s">
+        <v>497</v>
+      </c>
+      <c r="C128" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D128" s="11" t="s">
+        <v>470</v>
+      </c>
+      <c r="E128" s="12">
+        <v>526.2</v>
+      </c>
+      <c r="F128" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="G128" s="12">
+        <v>531.45</v>
+      </c>
+      <c r="H128" s="12">
+        <v>528.1</v>
+      </c>
+      <c r="I128" s="12">
+        <v>531.05</v>
+      </c>
+      <c r="J128" s="11"/>
+      <c r="K128" s="11"/>
+      <c r="L128" s="11"/>
+      <c r="M128" s="11"/>
+      <c r="N128" s="11" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A129" s="11" t="s">
+        <v>498</v>
+      </c>
+      <c r="B129" s="11" t="s">
+        <v>499</v>
+      </c>
+      <c r="C129" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D129" s="11" t="s">
+        <v>470</v>
+      </c>
+      <c r="E129" s="12">
+        <v>687</v>
+      </c>
+      <c r="F129" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="G129" s="12">
+        <v>693.5</v>
+      </c>
+      <c r="H129" s="12">
+        <v>689.1</v>
+      </c>
+      <c r="I129" s="12">
+        <v>692.9</v>
+      </c>
+      <c r="J129" s="11"/>
+      <c r="K129" s="11"/>
+      <c r="L129" s="11"/>
+      <c r="M129" s="11"/>
+      <c r="N129" s="11" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A130" s="11" t="s">
+        <v>500</v>
+      </c>
+      <c r="B130" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="C130" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D130" s="11" t="s">
+        <v>501</v>
+      </c>
+      <c r="E130" s="12">
+        <v>6126</v>
+      </c>
+      <c r="F130" s="11" t="s">
+        <v>491</v>
+      </c>
+      <c r="G130" s="12">
+        <v>6173</v>
+      </c>
+      <c r="H130" s="12">
+        <v>6143</v>
+      </c>
+      <c r="I130" s="12">
+        <v>6167</v>
+      </c>
+      <c r="J130" s="11"/>
+      <c r="K130" s="11"/>
+      <c r="L130" s="11"/>
+      <c r="M130" s="11"/>
+      <c r="N130" s="11" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A131" s="11" t="s">
+        <v>503</v>
+      </c>
+      <c r="B131" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="C131" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D131" s="11" t="s">
+        <v>471</v>
+      </c>
+      <c r="E131" s="12">
+        <v>433</v>
+      </c>
+      <c r="F131" s="11" t="s">
+        <v>491</v>
+      </c>
+      <c r="G131" s="12">
+        <v>437.35</v>
+      </c>
+      <c r="H131" s="12">
+        <v>433.9</v>
+      </c>
+      <c r="I131" s="12">
+        <v>436.2</v>
+      </c>
+      <c r="J131" s="11"/>
+      <c r="K131" s="11"/>
+      <c r="L131" s="11"/>
+      <c r="M131" s="11"/>
+      <c r="N131" s="11" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A132" s="11" t="s">
+        <v>504</v>
+      </c>
+      <c r="B132" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C132" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D132" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="E132" s="12">
+        <v>1552.6</v>
+      </c>
+      <c r="F132" s="11" t="s">
+        <v>502</v>
+      </c>
+      <c r="G132" s="12">
+        <v>1564</v>
+      </c>
+      <c r="H132" s="12">
+        <v>1553.6</v>
+      </c>
+      <c r="I132" s="12">
+        <v>1561.9</v>
+      </c>
+      <c r="J132" s="11"/>
+      <c r="K132" s="11"/>
+      <c r="L132" s="11"/>
+      <c r="M132" s="11"/>
+      <c r="N132" s="11" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A133" s="11" t="s">
+        <v>506</v>
+      </c>
+      <c r="B133" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="C133" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D133" s="11" t="s">
+        <v>507</v>
+      </c>
+      <c r="E133" s="12">
+        <v>7836.5</v>
+      </c>
+      <c r="F133" s="11" t="s">
+        <v>502</v>
+      </c>
+      <c r="G133" s="12">
+        <v>8011</v>
+      </c>
+      <c r="H133" s="12">
+        <v>7886.5</v>
+      </c>
+      <c r="I133" s="12">
+        <v>7980</v>
+      </c>
+      <c r="J133" s="11"/>
+      <c r="K133" s="11"/>
+      <c r="L133" s="11"/>
+      <c r="M133" s="11"/>
+      <c r="N133" s="11" t="s">
+        <v>505</v>
       </c>
     </row>
   </sheetData>

--- a/pattern_signals.xlsx
+++ b/pattern_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="577">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -1538,6 +1538,213 @@
   </si>
   <si>
     <t>2026-02-24 10:15</t>
+  </si>
+  <si>
+    <t>NSE:JINDALSTEL-EQ_BULL_1771921800_1771991100</t>
+  </si>
+  <si>
+    <t>2026-02-25 09:15</t>
+  </si>
+  <si>
+    <t>2026-02-25 09:30</t>
+  </si>
+  <si>
+    <t>NSE:JSWSTEEL-EQ_BULL_1771913700_1771991100</t>
+  </si>
+  <si>
+    <t>NSE:PETRONET-EQ_BULL_1771925400_1771991100</t>
+  </si>
+  <si>
+    <t>NSE:PETRONET-EQ</t>
+  </si>
+  <si>
+    <t>NSE:PFC-EQ_BULL_1771912800_1771991100</t>
+  </si>
+  <si>
+    <t>NSE:PFC-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-24 11:30</t>
+  </si>
+  <si>
+    <t>2026-02-25 09:31</t>
+  </si>
+  <si>
+    <t>NSE:TATASTEEL-EQ_BULL_1771905600_1771991100</t>
+  </si>
+  <si>
+    <t>NSE:TATASTEEL-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-24 09:30</t>
+  </si>
+  <si>
+    <t>NSE:VEDL-EQ_BULL_1771907400_1771992900</t>
+  </si>
+  <si>
+    <t>2026-02-25 09:45</t>
+  </si>
+  <si>
+    <t>2026-02-25 10:01</t>
+  </si>
+  <si>
+    <t>NSE:HEROMOTOCO-EQ_BULL_1771992000_1771999200</t>
+  </si>
+  <si>
+    <t>NSE:HEROMOTOCO-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-25 11:30</t>
+  </si>
+  <si>
+    <t>2026-02-25 11:45</t>
+  </si>
+  <si>
+    <t>NSE:HINDZINC-EQ_BULL_1771921800_1771999200</t>
+  </si>
+  <si>
+    <t>NSE:HINDZINC-EQ</t>
+  </si>
+  <si>
+    <t>NSE:LAURUSLABS-EQ_BULL_1771923600_1771999200</t>
+  </si>
+  <si>
+    <t>2026-02-25 11:46</t>
+  </si>
+  <si>
+    <t>NSE:IRCTC-EQ_BEAR_1771906500_1772001900</t>
+  </si>
+  <si>
+    <t>2026-02-24 09:45</t>
+  </si>
+  <si>
+    <t>2026-02-25 12:15</t>
+  </si>
+  <si>
+    <t>2026-02-25 12:30</t>
+  </si>
+  <si>
+    <t>NSE:PIDILITIND-EQ_BULL_1771907400_1772001900</t>
+  </si>
+  <si>
+    <t>2026-02-25 12:31</t>
+  </si>
+  <si>
+    <t>NSE:PAYTM-EQ_BEAR_1771905600_1772002800</t>
+  </si>
+  <si>
+    <t>NSE:PAYTM-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-25 12:46</t>
+  </si>
+  <si>
+    <t>NSE:CONCOR-EQ_BEAR_1771904700_1772003700</t>
+  </si>
+  <si>
+    <t>2026-02-25 12:45</t>
+  </si>
+  <si>
+    <t>2026-02-25 13:00</t>
+  </si>
+  <si>
+    <t>NSE:360ONE-EQ_BULL_1771994700_1772004600</t>
+  </si>
+  <si>
+    <t>NSE:360ONE-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-25 10:15</t>
+  </si>
+  <si>
+    <t>2026-02-25 13:15</t>
+  </si>
+  <si>
+    <t>NSE:ASIANPAINT-EQ_BEAR_1771911000_1772005500</t>
+  </si>
+  <si>
+    <t>NSE:ASIANPAINT-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-25 13:30</t>
+  </si>
+  <si>
+    <t>NSE:SAMMAANCAP-EQ_BULL_1771991100_1772007300</t>
+  </si>
+  <si>
+    <t>NSE:SAMMAANCAP-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-25 13:45</t>
+  </si>
+  <si>
+    <t>2026-02-25 14:01</t>
+  </si>
+  <si>
+    <t>NSE:MANKIND-EQ_BULL_1771991100_1772008200</t>
+  </si>
+  <si>
+    <t>2026-02-25 14:00</t>
+  </si>
+  <si>
+    <t>2026-02-25 14:16</t>
+  </si>
+  <si>
+    <t>NSE:BPCL-EQ_BULL_1771925400_1772009100</t>
+  </si>
+  <si>
+    <t>2026-02-25 14:15</t>
+  </si>
+  <si>
+    <t>2026-02-25 14:30</t>
+  </si>
+  <si>
+    <t>NSE:UNOMINDA-EQ_BULL_1771997400_1772009100</t>
+  </si>
+  <si>
+    <t>NSE:UNOMINDA-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-25 11:00</t>
+  </si>
+  <si>
+    <t>2026-02-25 14:31</t>
+  </si>
+  <si>
+    <t>NSE:AUROPHARMA-EQ_BULL_1771992900_1772010000</t>
+  </si>
+  <si>
+    <t>2026-02-25 14:45</t>
+  </si>
+  <si>
+    <t>NSE:ASTRAL-EQ_BULL_1771910100_1772011800</t>
+  </si>
+  <si>
+    <t>2026-02-25 15:00</t>
+  </si>
+  <si>
+    <t>2026-02-25 15:15</t>
+  </si>
+  <si>
+    <t>NSE:GLENMARK-EQ_BULL_1771910100_1772011800</t>
+  </si>
+  <si>
+    <t>NSE:IIFL-EQ_BULL_1771995600_1772011800</t>
+  </si>
+  <si>
+    <t>2026-02-25 10:30</t>
+  </si>
+  <si>
+    <t>NSE:PGEL-EQ_BULL_1771997400_1772011800</t>
+  </si>
+  <si>
+    <t>2026-02-25 15:16</t>
+  </si>
+  <si>
+    <t>NSE:SONACOMS-EQ_BULL_1771995600_1772011800</t>
+  </si>
+  <si>
+    <t>NSE:SONACOMS-EQ</t>
   </si>
 </sst>
 </file>
@@ -2001,7 +2208,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N133"/>
+  <dimension ref="A1:N158"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -6470,6 +6677,906 @@
         <v>505</v>
       </c>
     </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A134" s="11" t="s">
+        <v>508</v>
+      </c>
+      <c r="B134" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="C134" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D134" s="11" t="s">
+        <v>479</v>
+      </c>
+      <c r="E134" s="12">
+        <v>1225.5</v>
+      </c>
+      <c r="F134" s="11" t="s">
+        <v>509</v>
+      </c>
+      <c r="G134" s="12">
+        <v>1249.9</v>
+      </c>
+      <c r="H134" s="12">
+        <v>1237.7</v>
+      </c>
+      <c r="I134" s="12">
+        <v>1245.9</v>
+      </c>
+      <c r="J134" s="11"/>
+      <c r="K134" s="11"/>
+      <c r="L134" s="11"/>
+      <c r="M134" s="11"/>
+      <c r="N134" s="11" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A135" s="11" t="s">
+        <v>511</v>
+      </c>
+      <c r="B135" s="11" t="s">
+        <v>494</v>
+      </c>
+      <c r="C135" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D135" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="E135" s="12">
+        <v>1244.3</v>
+      </c>
+      <c r="F135" s="11" t="s">
+        <v>509</v>
+      </c>
+      <c r="G135" s="12">
+        <v>1270.1</v>
+      </c>
+      <c r="H135" s="12">
+        <v>1257.3</v>
+      </c>
+      <c r="I135" s="12">
+        <v>1269.8</v>
+      </c>
+      <c r="J135" s="11"/>
+      <c r="K135" s="11"/>
+      <c r="L135" s="11"/>
+      <c r="M135" s="11"/>
+      <c r="N135" s="11" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A136" s="11" t="s">
+        <v>512</v>
+      </c>
+      <c r="B136" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="C136" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D136" s="11" t="s">
+        <v>491</v>
+      </c>
+      <c r="E136" s="12">
+        <v>308.05</v>
+      </c>
+      <c r="F136" s="11" t="s">
+        <v>509</v>
+      </c>
+      <c r="G136" s="12">
+        <v>312.75</v>
+      </c>
+      <c r="H136" s="12">
+        <v>307.65</v>
+      </c>
+      <c r="I136" s="12">
+        <v>311.6</v>
+      </c>
+      <c r="J136" s="11"/>
+      <c r="K136" s="11"/>
+      <c r="L136" s="11"/>
+      <c r="M136" s="11"/>
+      <c r="N136" s="11" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A137" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="B137" s="11" t="s">
+        <v>515</v>
+      </c>
+      <c r="C137" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D137" s="11" t="s">
+        <v>516</v>
+      </c>
+      <c r="E137" s="12">
+        <v>418</v>
+      </c>
+      <c r="F137" s="11" t="s">
+        <v>509</v>
+      </c>
+      <c r="G137" s="12">
+        <v>425.25</v>
+      </c>
+      <c r="H137" s="12">
+        <v>419.65</v>
+      </c>
+      <c r="I137" s="12">
+        <v>422.7</v>
+      </c>
+      <c r="J137" s="11"/>
+      <c r="K137" s="11"/>
+      <c r="L137" s="11"/>
+      <c r="M137" s="11"/>
+      <c r="N137" s="11" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A138" s="11" t="s">
+        <v>518</v>
+      </c>
+      <c r="B138" s="11" t="s">
+        <v>519</v>
+      </c>
+      <c r="C138" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D138" s="11" t="s">
+        <v>520</v>
+      </c>
+      <c r="E138" s="12">
+        <v>208.5</v>
+      </c>
+      <c r="F138" s="11" t="s">
+        <v>509</v>
+      </c>
+      <c r="G138" s="12">
+        <v>212.1</v>
+      </c>
+      <c r="H138" s="12">
+        <v>209.4</v>
+      </c>
+      <c r="I138" s="12">
+        <v>212.05</v>
+      </c>
+      <c r="J138" s="11"/>
+      <c r="K138" s="11"/>
+      <c r="L138" s="11"/>
+      <c r="M138" s="11"/>
+      <c r="N138" s="11" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A139" s="11" t="s">
+        <v>521</v>
+      </c>
+      <c r="B139" s="11" t="s">
+        <v>499</v>
+      </c>
+      <c r="C139" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D139" s="11" t="s">
+        <v>470</v>
+      </c>
+      <c r="E139" s="12">
+        <v>687</v>
+      </c>
+      <c r="F139" s="11" t="s">
+        <v>522</v>
+      </c>
+      <c r="G139" s="12">
+        <v>722.9</v>
+      </c>
+      <c r="H139" s="12">
+        <v>713.8</v>
+      </c>
+      <c r="I139" s="12">
+        <v>722.55</v>
+      </c>
+      <c r="J139" s="11"/>
+      <c r="K139" s="11"/>
+      <c r="L139" s="11"/>
+      <c r="M139" s="11"/>
+      <c r="N139" s="11" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A140" s="11" t="s">
+        <v>524</v>
+      </c>
+      <c r="B140" s="11" t="s">
+        <v>525</v>
+      </c>
+      <c r="C140" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D140" s="11" t="s">
+        <v>510</v>
+      </c>
+      <c r="E140" s="12">
+        <v>5588.5</v>
+      </c>
+      <c r="F140" s="11" t="s">
+        <v>526</v>
+      </c>
+      <c r="G140" s="12">
+        <v>5827.5</v>
+      </c>
+      <c r="H140" s="12">
+        <v>5758.5</v>
+      </c>
+      <c r="I140" s="12">
+        <v>5822</v>
+      </c>
+      <c r="J140" s="11"/>
+      <c r="K140" s="11"/>
+      <c r="L140" s="11"/>
+      <c r="M140" s="11"/>
+      <c r="N140" s="11" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A141" s="11" t="s">
+        <v>528</v>
+      </c>
+      <c r="B141" s="11" t="s">
+        <v>529</v>
+      </c>
+      <c r="C141" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D141" s="11" t="s">
+        <v>479</v>
+      </c>
+      <c r="E141" s="12">
+        <v>594.2</v>
+      </c>
+      <c r="F141" s="11" t="s">
+        <v>526</v>
+      </c>
+      <c r="G141" s="12">
+        <v>621.3</v>
+      </c>
+      <c r="H141" s="12">
+        <v>616.4</v>
+      </c>
+      <c r="I141" s="12">
+        <v>619.55</v>
+      </c>
+      <c r="J141" s="11"/>
+      <c r="K141" s="11"/>
+      <c r="L141" s="11"/>
+      <c r="M141" s="11"/>
+      <c r="N141" s="11" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A142" s="11" t="s">
+        <v>530</v>
+      </c>
+      <c r="B142" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="C142" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D142" s="11" t="s">
+        <v>486</v>
+      </c>
+      <c r="E142" s="12">
+        <v>1024</v>
+      </c>
+      <c r="F142" s="11" t="s">
+        <v>526</v>
+      </c>
+      <c r="G142" s="12">
+        <v>1061</v>
+      </c>
+      <c r="H142" s="12">
+        <v>1052</v>
+      </c>
+      <c r="I142" s="12">
+        <v>1061</v>
+      </c>
+      <c r="J142" s="11"/>
+      <c r="K142" s="11"/>
+      <c r="L142" s="11"/>
+      <c r="M142" s="11"/>
+      <c r="N142" s="11" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A143" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="B143" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C143" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D143" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="E143" s="10">
+        <v>633.7</v>
+      </c>
+      <c r="F143" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="G143" s="10">
+        <v>612.45</v>
+      </c>
+      <c r="H143" s="10">
+        <v>607.75</v>
+      </c>
+      <c r="I143" s="10">
+        <v>609.4</v>
+      </c>
+      <c r="J143" s="9"/>
+      <c r="K143" s="9"/>
+      <c r="L143" s="9"/>
+      <c r="M143" s="9"/>
+      <c r="N143" s="9" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A144" s="11" t="s">
+        <v>536</v>
+      </c>
+      <c r="B144" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C144" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D144" s="11" t="s">
+        <v>470</v>
+      </c>
+      <c r="E144" s="12">
+        <v>1479.5</v>
+      </c>
+      <c r="F144" s="11" t="s">
+        <v>534</v>
+      </c>
+      <c r="G144" s="12">
+        <v>1501.2</v>
+      </c>
+      <c r="H144" s="12">
+        <v>1495.4</v>
+      </c>
+      <c r="I144" s="12">
+        <v>1501.1</v>
+      </c>
+      <c r="J144" s="11"/>
+      <c r="K144" s="11"/>
+      <c r="L144" s="11"/>
+      <c r="M144" s="11"/>
+      <c r="N144" s="11" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A145" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="B145" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="C145" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D145" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="E145" s="10">
+        <v>1135.2</v>
+      </c>
+      <c r="F145" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="G145" s="10">
+        <v>1135.6</v>
+      </c>
+      <c r="H145" s="10">
+        <v>1126.2</v>
+      </c>
+      <c r="I145" s="10">
+        <v>1127.4</v>
+      </c>
+      <c r="J145" s="9"/>
+      <c r="K145" s="9"/>
+      <c r="L145" s="9"/>
+      <c r="M145" s="9"/>
+      <c r="N145" s="9" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A146" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="B146" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C146" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D146" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="E146" s="10">
+        <v>502.95</v>
+      </c>
+      <c r="F146" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="G146" s="10">
+        <v>501.05</v>
+      </c>
+      <c r="H146" s="10">
+        <v>499.25</v>
+      </c>
+      <c r="I146" s="10">
+        <v>499.25</v>
+      </c>
+      <c r="J146" s="9"/>
+      <c r="K146" s="9"/>
+      <c r="L146" s="9"/>
+      <c r="M146" s="9"/>
+      <c r="N146" s="9" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A147" s="11" t="s">
+        <v>544</v>
+      </c>
+      <c r="B147" s="11" t="s">
+        <v>545</v>
+      </c>
+      <c r="C147" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D147" s="11" t="s">
+        <v>546</v>
+      </c>
+      <c r="E147" s="12">
+        <v>1125.6</v>
+      </c>
+      <c r="F147" s="11" t="s">
+        <v>543</v>
+      </c>
+      <c r="G147" s="12">
+        <v>1130.9</v>
+      </c>
+      <c r="H147" s="12">
+        <v>1122.7</v>
+      </c>
+      <c r="I147" s="12">
+        <v>1130</v>
+      </c>
+      <c r="J147" s="11"/>
+      <c r="K147" s="11"/>
+      <c r="L147" s="11"/>
+      <c r="M147" s="11"/>
+      <c r="N147" s="11" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A148" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="B148" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="C148" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D148" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="E148" s="10">
+        <v>2418.3</v>
+      </c>
+      <c r="F148" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="G148" s="10">
+        <v>2408.4</v>
+      </c>
+      <c r="H148" s="10">
+        <v>2400</v>
+      </c>
+      <c r="I148" s="10">
+        <v>2401.2</v>
+      </c>
+      <c r="J148" s="9"/>
+      <c r="K148" s="9"/>
+      <c r="L148" s="9"/>
+      <c r="M148" s="9"/>
+      <c r="N148" s="9" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A149" s="11" t="s">
+        <v>551</v>
+      </c>
+      <c r="B149" s="11" t="s">
+        <v>552</v>
+      </c>
+      <c r="C149" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D149" s="11" t="s">
+        <v>509</v>
+      </c>
+      <c r="E149" s="12">
+        <v>154.59</v>
+      </c>
+      <c r="F149" s="11" t="s">
+        <v>553</v>
+      </c>
+      <c r="G149" s="12">
+        <v>161.4</v>
+      </c>
+      <c r="H149" s="12">
+        <v>158.78</v>
+      </c>
+      <c r="I149" s="12">
+        <v>161.17</v>
+      </c>
+      <c r="J149" s="11"/>
+      <c r="K149" s="11"/>
+      <c r="L149" s="11"/>
+      <c r="M149" s="11"/>
+      <c r="N149" s="11" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A150" s="11" t="s">
+        <v>555</v>
+      </c>
+      <c r="B150" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="C150" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D150" s="11" t="s">
+        <v>509</v>
+      </c>
+      <c r="E150" s="12">
+        <v>2062.2</v>
+      </c>
+      <c r="F150" s="11" t="s">
+        <v>556</v>
+      </c>
+      <c r="G150" s="12">
+        <v>2128</v>
+      </c>
+      <c r="H150" s="12">
+        <v>2115.5</v>
+      </c>
+      <c r="I150" s="12">
+        <v>2125</v>
+      </c>
+      <c r="J150" s="11"/>
+      <c r="K150" s="11"/>
+      <c r="L150" s="11"/>
+      <c r="M150" s="11"/>
+      <c r="N150" s="11" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A151" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="B151" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="C151" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D151" s="11" t="s">
+        <v>491</v>
+      </c>
+      <c r="E151" s="12">
+        <v>375</v>
+      </c>
+      <c r="F151" s="11" t="s">
+        <v>559</v>
+      </c>
+      <c r="G151" s="12">
+        <v>379.15</v>
+      </c>
+      <c r="H151" s="12">
+        <v>377.2</v>
+      </c>
+      <c r="I151" s="12">
+        <v>378.7</v>
+      </c>
+      <c r="J151" s="11"/>
+      <c r="K151" s="11"/>
+      <c r="L151" s="11"/>
+      <c r="M151" s="11"/>
+      <c r="N151" s="11" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A152" s="11" t="s">
+        <v>561</v>
+      </c>
+      <c r="B152" s="11" t="s">
+        <v>562</v>
+      </c>
+      <c r="C152" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D152" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="E152" s="12">
+        <v>1208.1</v>
+      </c>
+      <c r="F152" s="11" t="s">
+        <v>559</v>
+      </c>
+      <c r="G152" s="12">
+        <v>1215</v>
+      </c>
+      <c r="H152" s="12">
+        <v>1207.5</v>
+      </c>
+      <c r="I152" s="12">
+        <v>1213.8</v>
+      </c>
+      <c r="J152" s="11"/>
+      <c r="K152" s="11"/>
+      <c r="L152" s="11"/>
+      <c r="M152" s="11"/>
+      <c r="N152" s="11" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A153" s="11" t="s">
+        <v>565</v>
+      </c>
+      <c r="B153" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="C153" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D153" s="11" t="s">
+        <v>522</v>
+      </c>
+      <c r="E153" s="12">
+        <v>1176.2</v>
+      </c>
+      <c r="F153" s="11" t="s">
+        <v>560</v>
+      </c>
+      <c r="G153" s="12">
+        <v>1213.8</v>
+      </c>
+      <c r="H153" s="12">
+        <v>1203.3</v>
+      </c>
+      <c r="I153" s="12">
+        <v>1208</v>
+      </c>
+      <c r="J153" s="11"/>
+      <c r="K153" s="11"/>
+      <c r="L153" s="11"/>
+      <c r="M153" s="11"/>
+      <c r="N153" s="11" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A154" s="11" t="s">
+        <v>567</v>
+      </c>
+      <c r="B154" s="11" t="s">
+        <v>490</v>
+      </c>
+      <c r="C154" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D154" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="E154" s="12">
+        <v>1642.4</v>
+      </c>
+      <c r="F154" s="11" t="s">
+        <v>568</v>
+      </c>
+      <c r="G154" s="12">
+        <v>1687.5</v>
+      </c>
+      <c r="H154" s="12">
+        <v>1677.5</v>
+      </c>
+      <c r="I154" s="12">
+        <v>1685.9</v>
+      </c>
+      <c r="J154" s="11"/>
+      <c r="K154" s="11"/>
+      <c r="L154" s="11"/>
+      <c r="M154" s="11"/>
+      <c r="N154" s="11" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A155" s="11" t="s">
+        <v>570</v>
+      </c>
+      <c r="B155" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="C155" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D155" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="E155" s="12">
+        <v>2039.5</v>
+      </c>
+      <c r="F155" s="11" t="s">
+        <v>568</v>
+      </c>
+      <c r="G155" s="12">
+        <v>2088.9</v>
+      </c>
+      <c r="H155" s="12">
+        <v>2079.2</v>
+      </c>
+      <c r="I155" s="12">
+        <v>2086.7</v>
+      </c>
+      <c r="J155" s="11"/>
+      <c r="K155" s="11"/>
+      <c r="L155" s="11"/>
+      <c r="M155" s="11"/>
+      <c r="N155" s="11" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A156" s="11" t="s">
+        <v>571</v>
+      </c>
+      <c r="B156" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C156" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D156" s="11" t="s">
+        <v>572</v>
+      </c>
+      <c r="E156" s="12">
+        <v>505.7</v>
+      </c>
+      <c r="F156" s="11" t="s">
+        <v>568</v>
+      </c>
+      <c r="G156" s="12">
+        <v>510.4</v>
+      </c>
+      <c r="H156" s="12">
+        <v>506.3</v>
+      </c>
+      <c r="I156" s="12">
+        <v>509.4</v>
+      </c>
+      <c r="J156" s="11"/>
+      <c r="K156" s="11"/>
+      <c r="L156" s="11"/>
+      <c r="M156" s="11"/>
+      <c r="N156" s="11" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A157" s="11" t="s">
+        <v>573</v>
+      </c>
+      <c r="B157" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C157" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D157" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="E157" s="12">
+        <v>624.05</v>
+      </c>
+      <c r="F157" s="11" t="s">
+        <v>568</v>
+      </c>
+      <c r="G157" s="12">
+        <v>624.1</v>
+      </c>
+      <c r="H157" s="12">
+        <v>618.45</v>
+      </c>
+      <c r="I157" s="12">
+        <v>624</v>
+      </c>
+      <c r="J157" s="11"/>
+      <c r="K157" s="11"/>
+      <c r="L157" s="11"/>
+      <c r="M157" s="11"/>
+      <c r="N157" s="11" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A158" s="11" t="s">
+        <v>575</v>
+      </c>
+      <c r="B158" s="11" t="s">
+        <v>576</v>
+      </c>
+      <c r="C158" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D158" s="11" t="s">
+        <v>572</v>
+      </c>
+      <c r="E158" s="12">
+        <v>538</v>
+      </c>
+      <c r="F158" s="11" t="s">
+        <v>568</v>
+      </c>
+      <c r="G158" s="12">
+        <v>542.7</v>
+      </c>
+      <c r="H158" s="12">
+        <v>540.05</v>
+      </c>
+      <c r="I158" s="12">
+        <v>541.25</v>
+      </c>
+      <c r="J158" s="11"/>
+      <c r="K158" s="11"/>
+      <c r="L158" s="11"/>
+      <c r="M158" s="11"/>
+      <c r="N158" s="11" t="s">
+        <v>574</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pattern_signals.xlsx
+++ b/pattern_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="580">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -1745,6 +1745,15 @@
   </si>
   <si>
     <t>NSE:SONACOMS-EQ</t>
+  </si>
+  <si>
+    <t>NSE:HINDZINC-EQ_BULL_1771921800_1772012700</t>
+  </si>
+  <si>
+    <t>2026-02-25 16:43</t>
+  </si>
+  <si>
+    <t>NSE:MANKIND-EQ_BULL_1771991100_1772011800</t>
   </si>
 </sst>
 </file>
@@ -2208,7 +2217,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N158"/>
+  <dimension ref="A1:N160"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -7577,6 +7586,78 @@
         <v>574</v>
       </c>
     </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A159" s="11" t="s">
+        <v>577</v>
+      </c>
+      <c r="B159" s="11" t="s">
+        <v>529</v>
+      </c>
+      <c r="C159" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D159" s="11" t="s">
+        <v>479</v>
+      </c>
+      <c r="E159" s="12">
+        <v>594.2</v>
+      </c>
+      <c r="F159" s="11" t="s">
+        <v>569</v>
+      </c>
+      <c r="G159" s="12">
+        <v>620.5</v>
+      </c>
+      <c r="H159" s="12">
+        <v>616.25</v>
+      </c>
+      <c r="I159" s="12">
+        <v>620</v>
+      </c>
+      <c r="J159" s="11"/>
+      <c r="K159" s="11"/>
+      <c r="L159" s="11"/>
+      <c r="M159" s="11"/>
+      <c r="N159" s="11" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A160" s="11" t="s">
+        <v>579</v>
+      </c>
+      <c r="B160" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="C160" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D160" s="11" t="s">
+        <v>509</v>
+      </c>
+      <c r="E160" s="12">
+        <v>2062.2</v>
+      </c>
+      <c r="F160" s="11" t="s">
+        <v>568</v>
+      </c>
+      <c r="G160" s="12">
+        <v>2164.5</v>
+      </c>
+      <c r="H160" s="12">
+        <v>2139</v>
+      </c>
+      <c r="I160" s="12">
+        <v>2159.3</v>
+      </c>
+      <c r="J160" s="11"/>
+      <c r="K160" s="11"/>
+      <c r="L160" s="11"/>
+      <c r="M160" s="11"/>
+      <c r="N160" s="11" t="s">
+        <v>578</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pattern_signals.xlsx
+++ b/pattern_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="652">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -1754,6 +1754,222 @@
   </si>
   <si>
     <t>NSE:MANKIND-EQ_BULL_1771991100_1772011800</t>
+  </si>
+  <si>
+    <t>NSE:APLAPOLLO-EQ_BULL_1771999200_1772077500</t>
+  </si>
+  <si>
+    <t>2026-02-26 09:15</t>
+  </si>
+  <si>
+    <t>2026-02-26 09:30</t>
+  </si>
+  <si>
+    <t>NSE:AUBANK-EQ_BEAR_1772003700_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:AUBANK-EQ</t>
+  </si>
+  <si>
+    <t>NSE:DIVISLAB-EQ_BULL_1771995600_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:FORTIS-EQ_BULL_1771993800_1772077500</t>
+  </si>
+  <si>
+    <t>2026-02-25 10:00</t>
+  </si>
+  <si>
+    <t>NSE:GAIL-EQ_BULL_1771991100_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:GAIL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IEX-EQ_BULL_1771992000_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:INDUSINDBK-EQ_BULL_1771991100_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:INDUSINDBK-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-26 09:31</t>
+  </si>
+  <si>
+    <t>NSE:KAYNES-EQ_BULL_1771996500_1772077500</t>
+  </si>
+  <si>
+    <t>2026-02-25 10:45</t>
+  </si>
+  <si>
+    <t>NSE:NCC-EQ_BULL_1771995600_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:NCC-EQ</t>
+  </si>
+  <si>
+    <t>NSE:PNBHOUSING-EQ_BULL_1771997400_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:PNBHOUSING-EQ</t>
+  </si>
+  <si>
+    <t>NSE:SHRIRAMFIN-EQ_BULL_1771994700_1772077500</t>
+  </si>
+  <si>
+    <t>NSE:BSE-EQ_BULL_1772010000_1772078400</t>
+  </si>
+  <si>
+    <t>NSE:BSE-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-26 09:45</t>
+  </si>
+  <si>
+    <t>NSE:PGEL-EQ_BULL_1771997400_1772078400</t>
+  </si>
+  <si>
+    <t>2026-02-26 09:46</t>
+  </si>
+  <si>
+    <t>NSE:CIPLA-EQ_BULL_1771996500_1772079300</t>
+  </si>
+  <si>
+    <t>2026-02-26 10:00</t>
+  </si>
+  <si>
+    <t>NSE:JSWENERGY-EQ_BULL_1771993800_1772079300</t>
+  </si>
+  <si>
+    <t>NSE:SOLARINDS-EQ_BULL_1771994700_1772081100</t>
+  </si>
+  <si>
+    <t>2026-02-26 10:15</t>
+  </si>
+  <si>
+    <t>2026-02-26 10:31</t>
+  </si>
+  <si>
+    <t>NSE:TMPV-EQ_BULL_1771997400_1772081100</t>
+  </si>
+  <si>
+    <t>NSE:TATAPOWER-EQ_BULL_1771992000_1772082000</t>
+  </si>
+  <si>
+    <t>2026-02-26 10:30</t>
+  </si>
+  <si>
+    <t>2026-02-26 10:46</t>
+  </si>
+  <si>
+    <t>NSE:BAJAJFINSV-EQ_BEAR_1772007300_1772086500</t>
+  </si>
+  <si>
+    <t>NSE:BAJAJFINSV-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-26 11:45</t>
+  </si>
+  <si>
+    <t>2026-02-26 12:00</t>
+  </si>
+  <si>
+    <t>NSE:MAXHEALTH-EQ_BULL_1772009100_1772086500</t>
+  </si>
+  <si>
+    <t>NSE:MAXHEALTH-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-26 12:01</t>
+  </si>
+  <si>
+    <t>NSE:BAJFINANCE-EQ_BEAR_1772002800_1772090100</t>
+  </si>
+  <si>
+    <t>2026-02-26 12:45</t>
+  </si>
+  <si>
+    <t>2026-02-26 13:00</t>
+  </si>
+  <si>
+    <t>NSE:MARUTI-EQ_BULL_1772077500_1772091900</t>
+  </si>
+  <si>
+    <t>NSE:MARUTI-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-26 13:15</t>
+  </si>
+  <si>
+    <t>2026-02-26 13:30</t>
+  </si>
+  <si>
+    <t>NSE:KOTAKBANK-EQ_BEAR_1771993800_1772092800</t>
+  </si>
+  <si>
+    <t>NSE:KOTAKBANK-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-26 13:46</t>
+  </si>
+  <si>
+    <t>NSE:BEL-EQ_BULL_1772012700_1772096400</t>
+  </si>
+  <si>
+    <t>2026-02-26 14:30</t>
+  </si>
+  <si>
+    <t>2026-02-26 15:19</t>
+  </si>
+  <si>
+    <t>NSE:INDUSINDBK-EQ_BULL_1771991100_1772098200</t>
+  </si>
+  <si>
+    <t>2026-02-26 15:00</t>
+  </si>
+  <si>
+    <t>2026-02-26 15:20</t>
+  </si>
+  <si>
+    <t>NSE:MANKIND-EQ_BULL_1771991100_1772098200</t>
+  </si>
+  <si>
+    <t>NSE:MOTHERSON-EQ_BULL_1771991100_1772098200</t>
+  </si>
+  <si>
+    <t>NSE:MOTHERSON-EQ</t>
+  </si>
+  <si>
+    <t>NSE:SONACOMS-EQ_BULL_1771995600_1772098200</t>
+  </si>
+  <si>
+    <t>NSE:TMPV-EQ_BULL_1771997400_1772098200</t>
+  </si>
+  <si>
+    <t>NSE:OFSS-EQ_BULL_1772078400_1772099100</t>
+  </si>
+  <si>
+    <t>NSE:OFSS-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-26 15:15</t>
+  </si>
+  <si>
+    <t>2026-02-26 15:32</t>
+  </si>
+  <si>
+    <t>NSE:PNB-EQ_BEAR_1772092800_1772099100</t>
+  </si>
+  <si>
+    <t>NSE:PNB-EQ</t>
+  </si>
+  <si>
+    <t>NSE:TVSMOTOR-EQ_BULL_1771994700_1772099100</t>
+  </si>
+  <si>
+    <t>NSE:TVSMOTOR-EQ</t>
   </si>
 </sst>
 </file>
@@ -2217,7 +2433,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N160"/>
+  <dimension ref="A1:N192"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -7658,6 +7874,1158 @@
         <v>578</v>
       </c>
     </row>
+    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A161" s="11" t="s">
+        <v>580</v>
+      </c>
+      <c r="B161" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="C161" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D161" s="11" t="s">
+        <v>526</v>
+      </c>
+      <c r="E161" s="12">
+        <v>2216.2</v>
+      </c>
+      <c r="F161" s="11" t="s">
+        <v>581</v>
+      </c>
+      <c r="G161" s="12">
+        <v>2247.7</v>
+      </c>
+      <c r="H161" s="12">
+        <v>2234.3</v>
+      </c>
+      <c r="I161" s="12">
+        <v>2242.4</v>
+      </c>
+      <c r="J161" s="11"/>
+      <c r="K161" s="11"/>
+      <c r="L161" s="11"/>
+      <c r="M161" s="11"/>
+      <c r="N161" s="11" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A162" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="B162" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="C162" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D162" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="E162" s="10">
+        <v>986.25</v>
+      </c>
+      <c r="F162" s="9" t="s">
+        <v>581</v>
+      </c>
+      <c r="G162" s="10">
+        <v>982.9</v>
+      </c>
+      <c r="H162" s="10">
+        <v>973</v>
+      </c>
+      <c r="I162" s="10">
+        <v>976.45</v>
+      </c>
+      <c r="J162" s="9"/>
+      <c r="K162" s="9"/>
+      <c r="L162" s="9"/>
+      <c r="M162" s="9"/>
+      <c r="N162" s="9" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A163" s="11" t="s">
+        <v>585</v>
+      </c>
+      <c r="B163" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C163" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D163" s="11" t="s">
+        <v>572</v>
+      </c>
+      <c r="E163" s="12">
+        <v>6349</v>
+      </c>
+      <c r="F163" s="11" t="s">
+        <v>581</v>
+      </c>
+      <c r="G163" s="12">
+        <v>6468</v>
+      </c>
+      <c r="H163" s="12">
+        <v>6420</v>
+      </c>
+      <c r="I163" s="12">
+        <v>6466</v>
+      </c>
+      <c r="J163" s="11"/>
+      <c r="K163" s="11"/>
+      <c r="L163" s="11"/>
+      <c r="M163" s="11"/>
+      <c r="N163" s="11" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A164" s="11" t="s">
+        <v>586</v>
+      </c>
+      <c r="B164" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="C164" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D164" s="11" t="s">
+        <v>587</v>
+      </c>
+      <c r="E164" s="12">
+        <v>924.3</v>
+      </c>
+      <c r="F164" s="11" t="s">
+        <v>581</v>
+      </c>
+      <c r="G164" s="12">
+        <v>948</v>
+      </c>
+      <c r="H164" s="12">
+        <v>935.15</v>
+      </c>
+      <c r="I164" s="12">
+        <v>947.55</v>
+      </c>
+      <c r="J164" s="11"/>
+      <c r="K164" s="11"/>
+      <c r="L164" s="11"/>
+      <c r="M164" s="11"/>
+      <c r="N164" s="11" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A165" s="11" t="s">
+        <v>588</v>
+      </c>
+      <c r="B165" s="11" t="s">
+        <v>589</v>
+      </c>
+      <c r="C165" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D165" s="11" t="s">
+        <v>509</v>
+      </c>
+      <c r="E165" s="12">
+        <v>169.44</v>
+      </c>
+      <c r="F165" s="11" t="s">
+        <v>581</v>
+      </c>
+      <c r="G165" s="12">
+        <v>171.2</v>
+      </c>
+      <c r="H165" s="12">
+        <v>170.3</v>
+      </c>
+      <c r="I165" s="12">
+        <v>170.66</v>
+      </c>
+      <c r="J165" s="11"/>
+      <c r="K165" s="11"/>
+      <c r="L165" s="11"/>
+      <c r="M165" s="11"/>
+      <c r="N165" s="11" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A166" s="11" t="s">
+        <v>590</v>
+      </c>
+      <c r="B166" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C166" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D166" s="11" t="s">
+        <v>510</v>
+      </c>
+      <c r="E166" s="12">
+        <v>126.57</v>
+      </c>
+      <c r="F166" s="11" t="s">
+        <v>581</v>
+      </c>
+      <c r="G166" s="12">
+        <v>130.7</v>
+      </c>
+      <c r="H166" s="12">
+        <v>128.61</v>
+      </c>
+      <c r="I166" s="12">
+        <v>129.65</v>
+      </c>
+      <c r="J166" s="11"/>
+      <c r="K166" s="11"/>
+      <c r="L166" s="11"/>
+      <c r="M166" s="11"/>
+      <c r="N166" s="11" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A167" s="11" t="s">
+        <v>591</v>
+      </c>
+      <c r="B167" s="11" t="s">
+        <v>592</v>
+      </c>
+      <c r="C167" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D167" s="11" t="s">
+        <v>509</v>
+      </c>
+      <c r="E167" s="12">
+        <v>934.5</v>
+      </c>
+      <c r="F167" s="11" t="s">
+        <v>581</v>
+      </c>
+      <c r="G167" s="12">
+        <v>946.8</v>
+      </c>
+      <c r="H167" s="12">
+        <v>936.3</v>
+      </c>
+      <c r="I167" s="12">
+        <v>945.95</v>
+      </c>
+      <c r="J167" s="11"/>
+      <c r="K167" s="11"/>
+      <c r="L167" s="11"/>
+      <c r="M167" s="11"/>
+      <c r="N167" s="11" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A168" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="B168" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C168" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D168" s="11" t="s">
+        <v>595</v>
+      </c>
+      <c r="E168" s="12">
+        <v>3927.4</v>
+      </c>
+      <c r="F168" s="11" t="s">
+        <v>581</v>
+      </c>
+      <c r="G168" s="12">
+        <v>3987.9</v>
+      </c>
+      <c r="H168" s="12">
+        <v>3916</v>
+      </c>
+      <c r="I168" s="12">
+        <v>3966.1</v>
+      </c>
+      <c r="J168" s="11"/>
+      <c r="K168" s="11"/>
+      <c r="L168" s="11"/>
+      <c r="M168" s="11"/>
+      <c r="N168" s="11" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A169" s="11" t="s">
+        <v>596</v>
+      </c>
+      <c r="B169" s="11" t="s">
+        <v>597</v>
+      </c>
+      <c r="C169" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D169" s="11" t="s">
+        <v>572</v>
+      </c>
+      <c r="E169" s="12">
+        <v>150.11</v>
+      </c>
+      <c r="F169" s="11" t="s">
+        <v>581</v>
+      </c>
+      <c r="G169" s="12">
+        <v>154.34</v>
+      </c>
+      <c r="H169" s="12">
+        <v>151.22</v>
+      </c>
+      <c r="I169" s="12">
+        <v>153.52</v>
+      </c>
+      <c r="J169" s="11"/>
+      <c r="K169" s="11"/>
+      <c r="L169" s="11"/>
+      <c r="M169" s="11"/>
+      <c r="N169" s="11" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A170" s="11" t="s">
+        <v>598</v>
+      </c>
+      <c r="B170" s="11" t="s">
+        <v>599</v>
+      </c>
+      <c r="C170" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D170" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="E170" s="12">
+        <v>854.05</v>
+      </c>
+      <c r="F170" s="11" t="s">
+        <v>581</v>
+      </c>
+      <c r="G170" s="12">
+        <v>869.15</v>
+      </c>
+      <c r="H170" s="12">
+        <v>836.05</v>
+      </c>
+      <c r="I170" s="12">
+        <v>855</v>
+      </c>
+      <c r="J170" s="11"/>
+      <c r="K170" s="11"/>
+      <c r="L170" s="11"/>
+      <c r="M170" s="11"/>
+      <c r="N170" s="11" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A171" s="11" t="s">
+        <v>600</v>
+      </c>
+      <c r="B171" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C171" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D171" s="11" t="s">
+        <v>546</v>
+      </c>
+      <c r="E171" s="12">
+        <v>1078.4</v>
+      </c>
+      <c r="F171" s="11" t="s">
+        <v>581</v>
+      </c>
+      <c r="G171" s="12">
+        <v>1105</v>
+      </c>
+      <c r="H171" s="12">
+        <v>1087</v>
+      </c>
+      <c r="I171" s="12">
+        <v>1099.3</v>
+      </c>
+      <c r="J171" s="11"/>
+      <c r="K171" s="11"/>
+      <c r="L171" s="11"/>
+      <c r="M171" s="11"/>
+      <c r="N171" s="11" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A172" s="11" t="s">
+        <v>601</v>
+      </c>
+      <c r="B172" s="11" t="s">
+        <v>602</v>
+      </c>
+      <c r="C172" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D172" s="11" t="s">
+        <v>560</v>
+      </c>
+      <c r="E172" s="12">
+        <v>2771.7</v>
+      </c>
+      <c r="F172" s="11" t="s">
+        <v>582</v>
+      </c>
+      <c r="G172" s="12">
+        <v>2793.6</v>
+      </c>
+      <c r="H172" s="12">
+        <v>2770</v>
+      </c>
+      <c r="I172" s="12">
+        <v>2791.2</v>
+      </c>
+      <c r="J172" s="11"/>
+      <c r="K172" s="11"/>
+      <c r="L172" s="11"/>
+      <c r="M172" s="11"/>
+      <c r="N172" s="11" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A173" s="11" t="s">
+        <v>604</v>
+      </c>
+      <c r="B173" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C173" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D173" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="E173" s="12">
+        <v>624.05</v>
+      </c>
+      <c r="F173" s="11" t="s">
+        <v>582</v>
+      </c>
+      <c r="G173" s="12">
+        <v>630.75</v>
+      </c>
+      <c r="H173" s="12">
+        <v>620.5</v>
+      </c>
+      <c r="I173" s="12">
+        <v>628.55</v>
+      </c>
+      <c r="J173" s="11"/>
+      <c r="K173" s="11"/>
+      <c r="L173" s="11"/>
+      <c r="M173" s="11"/>
+      <c r="N173" s="11" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A174" s="11" t="s">
+        <v>606</v>
+      </c>
+      <c r="B174" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C174" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D174" s="11" t="s">
+        <v>595</v>
+      </c>
+      <c r="E174" s="12">
+        <v>1341.5</v>
+      </c>
+      <c r="F174" s="11" t="s">
+        <v>603</v>
+      </c>
+      <c r="G174" s="12">
+        <v>1364.6</v>
+      </c>
+      <c r="H174" s="12">
+        <v>1353.1</v>
+      </c>
+      <c r="I174" s="12">
+        <v>1363.9</v>
+      </c>
+      <c r="J174" s="11"/>
+      <c r="K174" s="11"/>
+      <c r="L174" s="11"/>
+      <c r="M174" s="11"/>
+      <c r="N174" s="11" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A175" s="11" t="s">
+        <v>608</v>
+      </c>
+      <c r="B175" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C175" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D175" s="11" t="s">
+        <v>587</v>
+      </c>
+      <c r="E175" s="12">
+        <v>489.95</v>
+      </c>
+      <c r="F175" s="11" t="s">
+        <v>603</v>
+      </c>
+      <c r="G175" s="12">
+        <v>500.35</v>
+      </c>
+      <c r="H175" s="12">
+        <v>493.9</v>
+      </c>
+      <c r="I175" s="12">
+        <v>500.3</v>
+      </c>
+      <c r="J175" s="11"/>
+      <c r="K175" s="11"/>
+      <c r="L175" s="11"/>
+      <c r="M175" s="11"/>
+      <c r="N175" s="11" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A176" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="B176" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C176" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D176" s="11" t="s">
+        <v>546</v>
+      </c>
+      <c r="E176" s="12">
+        <v>13405</v>
+      </c>
+      <c r="F176" s="11" t="s">
+        <v>610</v>
+      </c>
+      <c r="G176" s="12">
+        <v>13770</v>
+      </c>
+      <c r="H176" s="12">
+        <v>13554</v>
+      </c>
+      <c r="I176" s="12">
+        <v>13741</v>
+      </c>
+      <c r="J176" s="11"/>
+      <c r="K176" s="11"/>
+      <c r="L176" s="11"/>
+      <c r="M176" s="11"/>
+      <c r="N176" s="11" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A177" s="11" t="s">
+        <v>612</v>
+      </c>
+      <c r="B177" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="C177" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D177" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="E177" s="12">
+        <v>382.5</v>
+      </c>
+      <c r="F177" s="11" t="s">
+        <v>610</v>
+      </c>
+      <c r="G177" s="12">
+        <v>390.45</v>
+      </c>
+      <c r="H177" s="12">
+        <v>386.6</v>
+      </c>
+      <c r="I177" s="12">
+        <v>389.65</v>
+      </c>
+      <c r="J177" s="11"/>
+      <c r="K177" s="11"/>
+      <c r="L177" s="11"/>
+      <c r="M177" s="11"/>
+      <c r="N177" s="11" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A178" s="11" t="s">
+        <v>613</v>
+      </c>
+      <c r="B178" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="C178" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D178" s="11" t="s">
+        <v>510</v>
+      </c>
+      <c r="E178" s="12">
+        <v>380.2</v>
+      </c>
+      <c r="F178" s="11" t="s">
+        <v>614</v>
+      </c>
+      <c r="G178" s="12">
+        <v>385.4</v>
+      </c>
+      <c r="H178" s="12">
+        <v>381.45</v>
+      </c>
+      <c r="I178" s="12">
+        <v>383.3</v>
+      </c>
+      <c r="J178" s="11"/>
+      <c r="K178" s="11"/>
+      <c r="L178" s="11"/>
+      <c r="M178" s="11"/>
+      <c r="N178" s="11" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A179" s="9" t="s">
+        <v>616</v>
+      </c>
+      <c r="B179" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="C179" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D179" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="E179" s="10">
+        <v>2048.4</v>
+      </c>
+      <c r="F179" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="G179" s="10">
+        <v>2054.9</v>
+      </c>
+      <c r="H179" s="10">
+        <v>2047.1</v>
+      </c>
+      <c r="I179" s="10">
+        <v>2050.4</v>
+      </c>
+      <c r="J179" s="9"/>
+      <c r="K179" s="9"/>
+      <c r="L179" s="9"/>
+      <c r="M179" s="9"/>
+      <c r="N179" s="9" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A180" s="11" t="s">
+        <v>620</v>
+      </c>
+      <c r="B180" s="11" t="s">
+        <v>621</v>
+      </c>
+      <c r="C180" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D180" s="11" t="s">
+        <v>559</v>
+      </c>
+      <c r="E180" s="12">
+        <v>1085.55</v>
+      </c>
+      <c r="F180" s="11" t="s">
+        <v>618</v>
+      </c>
+      <c r="G180" s="12">
+        <v>1100.05</v>
+      </c>
+      <c r="H180" s="12">
+        <v>1089</v>
+      </c>
+      <c r="I180" s="12">
+        <v>1100.05</v>
+      </c>
+      <c r="J180" s="11"/>
+      <c r="K180" s="11"/>
+      <c r="L180" s="11"/>
+      <c r="M180" s="11"/>
+      <c r="N180" s="11" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A181" s="9" t="s">
+        <v>623</v>
+      </c>
+      <c r="B181" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="C181" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D181" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="E181" s="10">
+        <v>1018.25</v>
+      </c>
+      <c r="F181" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="G181" s="10">
+        <v>1020.15</v>
+      </c>
+      <c r="H181" s="10">
+        <v>1012.15</v>
+      </c>
+      <c r="I181" s="10">
+        <v>1015.1</v>
+      </c>
+      <c r="J181" s="9"/>
+      <c r="K181" s="9"/>
+      <c r="L181" s="9"/>
+      <c r="M181" s="9"/>
+      <c r="N181" s="9" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A182" s="11" t="s">
+        <v>626</v>
+      </c>
+      <c r="B182" s="11" t="s">
+        <v>627</v>
+      </c>
+      <c r="C182" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D182" s="11" t="s">
+        <v>581</v>
+      </c>
+      <c r="E182" s="12">
+        <v>15134</v>
+      </c>
+      <c r="F182" s="11" t="s">
+        <v>628</v>
+      </c>
+      <c r="G182" s="12">
+        <v>15208</v>
+      </c>
+      <c r="H182" s="12">
+        <v>15150</v>
+      </c>
+      <c r="I182" s="12">
+        <v>15195</v>
+      </c>
+      <c r="J182" s="11"/>
+      <c r="K182" s="11"/>
+      <c r="L182" s="11"/>
+      <c r="M182" s="11"/>
+      <c r="N182" s="11" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A183" s="9" t="s">
+        <v>630</v>
+      </c>
+      <c r="B183" s="9" t="s">
+        <v>631</v>
+      </c>
+      <c r="C183" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D183" s="9" t="s">
+        <v>587</v>
+      </c>
+      <c r="E183" s="10">
+        <v>427.5</v>
+      </c>
+      <c r="F183" s="9" t="s">
+        <v>629</v>
+      </c>
+      <c r="G183" s="10">
+        <v>424.6</v>
+      </c>
+      <c r="H183" s="10">
+        <v>423</v>
+      </c>
+      <c r="I183" s="10">
+        <v>423.15</v>
+      </c>
+      <c r="J183" s="9"/>
+      <c r="K183" s="9"/>
+      <c r="L183" s="9"/>
+      <c r="M183" s="9"/>
+      <c r="N183" s="9" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A184" s="11" t="s">
+        <v>633</v>
+      </c>
+      <c r="B184" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="C184" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D184" s="11" t="s">
+        <v>569</v>
+      </c>
+      <c r="E184" s="12">
+        <v>439.5</v>
+      </c>
+      <c r="F184" s="11" t="s">
+        <v>634</v>
+      </c>
+      <c r="G184" s="12">
+        <v>447.35</v>
+      </c>
+      <c r="H184" s="12">
+        <v>445.4</v>
+      </c>
+      <c r="I184" s="12">
+        <v>447.3</v>
+      </c>
+      <c r="J184" s="11"/>
+      <c r="K184" s="11"/>
+      <c r="L184" s="11"/>
+      <c r="M184" s="11"/>
+      <c r="N184" s="11" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A185" s="11" t="s">
+        <v>636</v>
+      </c>
+      <c r="B185" s="11" t="s">
+        <v>592</v>
+      </c>
+      <c r="C185" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D185" s="11" t="s">
+        <v>509</v>
+      </c>
+      <c r="E185" s="12">
+        <v>934.5</v>
+      </c>
+      <c r="F185" s="11" t="s">
+        <v>637</v>
+      </c>
+      <c r="G185" s="12">
+        <v>964.9</v>
+      </c>
+      <c r="H185" s="12">
+        <v>957.25</v>
+      </c>
+      <c r="I185" s="12">
+        <v>963.65</v>
+      </c>
+      <c r="J185" s="11"/>
+      <c r="K185" s="11"/>
+      <c r="L185" s="11"/>
+      <c r="M185" s="11"/>
+      <c r="N185" s="11" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A186" s="11" t="s">
+        <v>639</v>
+      </c>
+      <c r="B186" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="C186" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D186" s="11" t="s">
+        <v>509</v>
+      </c>
+      <c r="E186" s="12">
+        <v>2062.2</v>
+      </c>
+      <c r="F186" s="11" t="s">
+        <v>637</v>
+      </c>
+      <c r="G186" s="12">
+        <v>2284</v>
+      </c>
+      <c r="H186" s="12">
+        <v>2271</v>
+      </c>
+      <c r="I186" s="12">
+        <v>2282.5</v>
+      </c>
+      <c r="J186" s="11"/>
+      <c r="K186" s="11"/>
+      <c r="L186" s="11"/>
+      <c r="M186" s="11"/>
+      <c r="N186" s="11" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A187" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="B187" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="C187" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D187" s="11" t="s">
+        <v>509</v>
+      </c>
+      <c r="E187" s="12">
+        <v>133.52</v>
+      </c>
+      <c r="F187" s="11" t="s">
+        <v>637</v>
+      </c>
+      <c r="G187" s="12">
+        <v>135.65</v>
+      </c>
+      <c r="H187" s="12">
+        <v>134.95</v>
+      </c>
+      <c r="I187" s="12">
+        <v>135.35</v>
+      </c>
+      <c r="J187" s="11"/>
+      <c r="K187" s="11"/>
+      <c r="L187" s="11"/>
+      <c r="M187" s="11"/>
+      <c r="N187" s="11" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A188" s="11" t="s">
+        <v>642</v>
+      </c>
+      <c r="B188" s="11" t="s">
+        <v>576</v>
+      </c>
+      <c r="C188" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D188" s="11" t="s">
+        <v>572</v>
+      </c>
+      <c r="E188" s="12">
+        <v>538</v>
+      </c>
+      <c r="F188" s="11" t="s">
+        <v>637</v>
+      </c>
+      <c r="G188" s="12">
+        <v>546</v>
+      </c>
+      <c r="H188" s="12">
+        <v>543.15</v>
+      </c>
+      <c r="I188" s="12">
+        <v>545.3</v>
+      </c>
+      <c r="J188" s="11"/>
+      <c r="K188" s="11"/>
+      <c r="L188" s="11"/>
+      <c r="M188" s="11"/>
+      <c r="N188" s="11" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A189" s="11" t="s">
+        <v>643</v>
+      </c>
+      <c r="B189" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="C189" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D189" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="E189" s="12">
+        <v>382.5</v>
+      </c>
+      <c r="F189" s="11" t="s">
+        <v>637</v>
+      </c>
+      <c r="G189" s="12">
+        <v>391.8</v>
+      </c>
+      <c r="H189" s="12">
+        <v>388.9</v>
+      </c>
+      <c r="I189" s="12">
+        <v>391.65</v>
+      </c>
+      <c r="J189" s="11"/>
+      <c r="K189" s="11"/>
+      <c r="L189" s="11"/>
+      <c r="M189" s="11"/>
+      <c r="N189" s="11" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A190" s="11" t="s">
+        <v>644</v>
+      </c>
+      <c r="B190" s="11" t="s">
+        <v>645</v>
+      </c>
+      <c r="C190" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D190" s="11" t="s">
+        <v>582</v>
+      </c>
+      <c r="E190" s="12">
+        <v>6760</v>
+      </c>
+      <c r="F190" s="11" t="s">
+        <v>646</v>
+      </c>
+      <c r="G190" s="12">
+        <v>6880</v>
+      </c>
+      <c r="H190" s="12">
+        <v>6840.5</v>
+      </c>
+      <c r="I190" s="12">
+        <v>6870</v>
+      </c>
+      <c r="J190" s="11"/>
+      <c r="K190" s="11"/>
+      <c r="L190" s="11"/>
+      <c r="M190" s="11"/>
+      <c r="N190" s="11" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A191" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="B191" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="C191" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D191" s="9" t="s">
+        <v>629</v>
+      </c>
+      <c r="E191" s="10">
+        <v>130</v>
+      </c>
+      <c r="F191" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="G191" s="10">
+        <v>130.72</v>
+      </c>
+      <c r="H191" s="10">
+        <v>130.13</v>
+      </c>
+      <c r="I191" s="10">
+        <v>130.14</v>
+      </c>
+      <c r="J191" s="9"/>
+      <c r="K191" s="9"/>
+      <c r="L191" s="9"/>
+      <c r="M191" s="9"/>
+      <c r="N191" s="9" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A192" s="11" t="s">
+        <v>650</v>
+      </c>
+      <c r="B192" s="11" t="s">
+        <v>651</v>
+      </c>
+      <c r="C192" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D192" s="11" t="s">
+        <v>546</v>
+      </c>
+      <c r="E192" s="12">
+        <v>3876.6</v>
+      </c>
+      <c r="F192" s="11" t="s">
+        <v>646</v>
+      </c>
+      <c r="G192" s="12">
+        <v>3970</v>
+      </c>
+      <c r="H192" s="12">
+        <v>3951.8</v>
+      </c>
+      <c r="I192" s="12">
+        <v>3959.9</v>
+      </c>
+      <c r="J192" s="11"/>
+      <c r="K192" s="11"/>
+      <c r="L192" s="11"/>
+      <c r="M192" s="11"/>
+      <c r="N192" s="11" t="s">
+        <v>647</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pattern_signals.xlsx
+++ b/pattern_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1336" uniqueCount="702">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -1970,6 +1970,156 @@
   </si>
   <si>
     <t>NSE:TVSMOTOR-EQ</t>
+  </si>
+  <si>
+    <t>NSE:ABCAPITAL-EQ_BEAR_1772165700_1772184600</t>
+  </si>
+  <si>
+    <t>2026-02-27 09:45</t>
+  </si>
+  <si>
+    <t>2026-02-27 15:00</t>
+  </si>
+  <si>
+    <t>2026-02-28 13:18</t>
+  </si>
+  <si>
+    <t>NSE:BIOCON-EQ_BEAR_1772167500_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:BIOCON-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-27 10:15</t>
+  </si>
+  <si>
+    <t>NSE:EXIDEIND-EQ_BEAR_1772163900_1772184600</t>
+  </si>
+  <si>
+    <t>2026-02-27 09:15</t>
+  </si>
+  <si>
+    <t>NSE:GODREJCP-EQ_BEAR_1772165700_1772176500</t>
+  </si>
+  <si>
+    <t>2026-02-27 12:45</t>
+  </si>
+  <si>
+    <t>NSE:HDFCAMC-EQ_BEAR_1772164800_1772169300</t>
+  </si>
+  <si>
+    <t>NSE:HDFCAMC-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-27 09:30</t>
+  </si>
+  <si>
+    <t>2026-02-27 10:45</t>
+  </si>
+  <si>
+    <t>2026-02-28 13:19</t>
+  </si>
+  <si>
+    <t>NSE:HINDUNILVR-EQ_BEAR_1772166600_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:HINDUNILVR-EQ</t>
+  </si>
+  <si>
+    <t>2026-02-27 10:00</t>
+  </si>
+  <si>
+    <t>NSE:ICICIGI-EQ_BEAR_1772164800_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:ICICIGI-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IEX-EQ_BEAR_1772172000_1772185500</t>
+  </si>
+  <si>
+    <t>2026-02-27 11:30</t>
+  </si>
+  <si>
+    <t>2026-02-27 15:15</t>
+  </si>
+  <si>
+    <t>NSE:JSWENERGY-EQ_BEAR_1772167500_1772185500</t>
+  </si>
+  <si>
+    <t>NSE:KAYNES-EQ_BEAR_1772165700_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:PFC-EQ_BEAR_1772168400_1772184600</t>
+  </si>
+  <si>
+    <t>2026-02-27 10:30</t>
+  </si>
+  <si>
+    <t>2026-02-28 13:22</t>
+  </si>
+  <si>
+    <t>NSE:SONACOMS-EQ_BEAR_1772169300_1772185500</t>
+  </si>
+  <si>
+    <t>NSE:UNOMINDA-EQ_BEAR_1772170200_1772181000</t>
+  </si>
+  <si>
+    <t>2026-02-27 11:00</t>
+  </si>
+  <si>
+    <t>2026-02-27 14:00</t>
+  </si>
+  <si>
+    <t>NSE:VBL-EQ_BEAR_1772170200_1772184600</t>
+  </si>
+  <si>
+    <t>NSE:AXISBANK-EQ_BEAR_1772164800_1772424000</t>
+  </si>
+  <si>
+    <t>2026-03-02 09:30</t>
+  </si>
+  <si>
+    <t>2026-03-02 11:17</t>
+  </si>
+  <si>
+    <t>NSE:DRREDDY-EQ_BEAR_1772167500_1772425800</t>
+  </si>
+  <si>
+    <t>NSE:DRREDDY-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-02 10:00</t>
+  </si>
+  <si>
+    <t>2026-03-02 11:18</t>
+  </si>
+  <si>
+    <t>NSE:ICICIPRULI-EQ_BEAR_1772167500_1772423100</t>
+  </si>
+  <si>
+    <t>NSE:ICICIPRULI-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-02 09:15</t>
+  </si>
+  <si>
+    <t>NSE:NESTLEIND-EQ_BEAR_1772163900_1772425800</t>
+  </si>
+  <si>
+    <t>NSE:IEX-EQ_BEAR_1772172000_1772432100</t>
+  </si>
+  <si>
+    <t>2026-03-02 11:45</t>
+  </si>
+  <si>
+    <t>2026-03-02 12:02</t>
+  </si>
+  <si>
+    <t>NSE:M&amp;M-EQ_BEAR_1772164800_1772432100</t>
+  </si>
+  <si>
+    <t>NSE:M&amp;M-EQ</t>
   </si>
 </sst>
 </file>
@@ -2433,7 +2583,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N192"/>
+  <dimension ref="A1:N212"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -9026,6 +9176,726 @@
         <v>647</v>
       </c>
     </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A193" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="B193" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="C193" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D193" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="E193" s="10">
+        <v>344.45</v>
+      </c>
+      <c r="F193" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="G193" s="10">
+        <v>347.25</v>
+      </c>
+      <c r="H193" s="10">
+        <v>338.2</v>
+      </c>
+      <c r="I193" s="10">
+        <v>344.9</v>
+      </c>
+      <c r="J193" s="9"/>
+      <c r="K193" s="9"/>
+      <c r="L193" s="9"/>
+      <c r="M193" s="9"/>
+      <c r="N193" s="9" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A194" s="9" t="s">
+        <v>656</v>
+      </c>
+      <c r="B194" s="9" t="s">
+        <v>657</v>
+      </c>
+      <c r="C194" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D194" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="E194" s="10">
+        <v>390.8</v>
+      </c>
+      <c r="F194" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="G194" s="10">
+        <v>391.7</v>
+      </c>
+      <c r="H194" s="10">
+        <v>388.8</v>
+      </c>
+      <c r="I194" s="10">
+        <v>389.8</v>
+      </c>
+      <c r="J194" s="9"/>
+      <c r="K194" s="9"/>
+      <c r="L194" s="9"/>
+      <c r="M194" s="9"/>
+      <c r="N194" s="9" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A195" s="9" t="s">
+        <v>659</v>
+      </c>
+      <c r="B195" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C195" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D195" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="E195" s="10">
+        <v>337.15</v>
+      </c>
+      <c r="F195" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="G195" s="10">
+        <v>337.2</v>
+      </c>
+      <c r="H195" s="10">
+        <v>333.5</v>
+      </c>
+      <c r="I195" s="10">
+        <v>334</v>
+      </c>
+      <c r="J195" s="9"/>
+      <c r="K195" s="9"/>
+      <c r="L195" s="9"/>
+      <c r="M195" s="9"/>
+      <c r="N195" s="9" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A196" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="B196" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C196" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D196" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="E196" s="10">
+        <v>1216.4</v>
+      </c>
+      <c r="F196" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="G196" s="10">
+        <v>1228.4</v>
+      </c>
+      <c r="H196" s="10">
+        <v>1220.3</v>
+      </c>
+      <c r="I196" s="10">
+        <v>1220.9</v>
+      </c>
+      <c r="J196" s="9"/>
+      <c r="K196" s="9"/>
+      <c r="L196" s="9"/>
+      <c r="M196" s="9"/>
+      <c r="N196" s="9" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A197" s="9" t="s">
+        <v>663</v>
+      </c>
+      <c r="B197" s="9" t="s">
+        <v>664</v>
+      </c>
+      <c r="C197" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D197" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="E197" s="10">
+        <v>2727.8</v>
+      </c>
+      <c r="F197" s="9" t="s">
+        <v>666</v>
+      </c>
+      <c r="G197" s="10">
+        <v>2731</v>
+      </c>
+      <c r="H197" s="10">
+        <v>2717</v>
+      </c>
+      <c r="I197" s="10">
+        <v>2718.6</v>
+      </c>
+      <c r="J197" s="9"/>
+      <c r="K197" s="9"/>
+      <c r="L197" s="9"/>
+      <c r="M197" s="9"/>
+      <c r="N197" s="9" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A198" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="B198" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="C198" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D198" s="9" t="s">
+        <v>670</v>
+      </c>
+      <c r="E198" s="10">
+        <v>2343.3</v>
+      </c>
+      <c r="F198" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="G198" s="10">
+        <v>2349.3</v>
+      </c>
+      <c r="H198" s="10">
+        <v>2330.6</v>
+      </c>
+      <c r="I198" s="10">
+        <v>2339.5</v>
+      </c>
+      <c r="J198" s="9"/>
+      <c r="K198" s="9"/>
+      <c r="L198" s="9"/>
+      <c r="M198" s="9"/>
+      <c r="N198" s="9" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A199" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="B199" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="C199" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D199" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="E199" s="10">
+        <v>1927.3</v>
+      </c>
+      <c r="F199" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="G199" s="10">
+        <v>1914</v>
+      </c>
+      <c r="H199" s="10">
+        <v>1894.6</v>
+      </c>
+      <c r="I199" s="10">
+        <v>1898</v>
+      </c>
+      <c r="J199" s="9"/>
+      <c r="K199" s="9"/>
+      <c r="L199" s="9"/>
+      <c r="M199" s="9"/>
+      <c r="N199" s="9" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A200" s="9" t="s">
+        <v>673</v>
+      </c>
+      <c r="B200" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C200" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D200" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="E200" s="10">
+        <v>126.5</v>
+      </c>
+      <c r="F200" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="G200" s="10">
+        <v>125.75</v>
+      </c>
+      <c r="H200" s="10">
+        <v>125.07</v>
+      </c>
+      <c r="I200" s="10">
+        <v>125.16</v>
+      </c>
+      <c r="J200" s="9"/>
+      <c r="K200" s="9"/>
+      <c r="L200" s="9"/>
+      <c r="M200" s="9"/>
+      <c r="N200" s="9" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A201" s="9" t="s">
+        <v>676</v>
+      </c>
+      <c r="B201" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C201" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D201" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="E201" s="10">
+        <v>491.8</v>
+      </c>
+      <c r="F201" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="G201" s="10">
+        <v>488.55</v>
+      </c>
+      <c r="H201" s="10">
+        <v>484.35</v>
+      </c>
+      <c r="I201" s="10">
+        <v>485.55</v>
+      </c>
+      <c r="J201" s="9"/>
+      <c r="K201" s="9"/>
+      <c r="L201" s="9"/>
+      <c r="M201" s="9"/>
+      <c r="N201" s="9" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A202" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="B202" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C202" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D202" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="E202" s="10">
+        <v>3863.7</v>
+      </c>
+      <c r="F202" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="G202" s="10">
+        <v>3904</v>
+      </c>
+      <c r="H202" s="10">
+        <v>3841</v>
+      </c>
+      <c r="I202" s="10">
+        <v>3848.6</v>
+      </c>
+      <c r="J202" s="9"/>
+      <c r="K202" s="9"/>
+      <c r="L202" s="9"/>
+      <c r="M202" s="9"/>
+      <c r="N202" s="9" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A203" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="B203" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="C203" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D203" s="9" t="s">
+        <v>679</v>
+      </c>
+      <c r="E203" s="10">
+        <v>417.7</v>
+      </c>
+      <c r="F203" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="G203" s="10">
+        <v>418.75</v>
+      </c>
+      <c r="H203" s="10">
+        <v>413.3</v>
+      </c>
+      <c r="I203" s="10">
+        <v>414.05</v>
+      </c>
+      <c r="J203" s="9"/>
+      <c r="K203" s="9"/>
+      <c r="L203" s="9"/>
+      <c r="M203" s="9"/>
+      <c r="N203" s="9" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A204" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="B204" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="C204" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D204" s="9" t="s">
+        <v>666</v>
+      </c>
+      <c r="E204" s="10">
+        <v>536</v>
+      </c>
+      <c r="F204" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="G204" s="10">
+        <v>536.2</v>
+      </c>
+      <c r="H204" s="10">
+        <v>532.05</v>
+      </c>
+      <c r="I204" s="10">
+        <v>533.25</v>
+      </c>
+      <c r="J204" s="9"/>
+      <c r="K204" s="9"/>
+      <c r="L204" s="9"/>
+      <c r="M204" s="9"/>
+      <c r="N204" s="9" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A205" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="B205" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="C205" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D205" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="E205" s="10">
+        <v>1204.3</v>
+      </c>
+      <c r="F205" s="9" t="s">
+        <v>684</v>
+      </c>
+      <c r="G205" s="10">
+        <v>1205.8</v>
+      </c>
+      <c r="H205" s="10">
+        <v>1201.1</v>
+      </c>
+      <c r="I205" s="10">
+        <v>1201.1</v>
+      </c>
+      <c r="J205" s="9"/>
+      <c r="K205" s="9"/>
+      <c r="L205" s="9"/>
+      <c r="M205" s="9"/>
+      <c r="N205" s="9" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A206" s="9" t="s">
+        <v>685</v>
+      </c>
+      <c r="B206" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C206" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D206" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="E206" s="10">
+        <v>456.7</v>
+      </c>
+      <c r="F206" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="G206" s="10">
+        <v>455.55</v>
+      </c>
+      <c r="H206" s="10">
+        <v>450</v>
+      </c>
+      <c r="I206" s="10">
+        <v>451</v>
+      </c>
+      <c r="J206" s="9"/>
+      <c r="K206" s="9"/>
+      <c r="L206" s="9"/>
+      <c r="M206" s="9"/>
+      <c r="N206" s="9" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A207" s="9" t="s">
+        <v>686</v>
+      </c>
+      <c r="B207" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="C207" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D207" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="E207" s="10">
+        <v>1387.9</v>
+      </c>
+      <c r="F207" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="G207" s="10">
+        <v>1373.1</v>
+      </c>
+      <c r="H207" s="10">
+        <v>1365.5</v>
+      </c>
+      <c r="I207" s="10">
+        <v>1366.2</v>
+      </c>
+      <c r="J207" s="9"/>
+      <c r="K207" s="9"/>
+      <c r="L207" s="9"/>
+      <c r="M207" s="9"/>
+      <c r="N207" s="9" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A208" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="B208" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="C208" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D208" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="E208" s="10">
+        <v>1293.5</v>
+      </c>
+      <c r="F208" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="G208" s="10">
+        <v>1278.8</v>
+      </c>
+      <c r="H208" s="10">
+        <v>1274</v>
+      </c>
+      <c r="I208" s="10">
+        <v>1276.6</v>
+      </c>
+      <c r="J208" s="9"/>
+      <c r="K208" s="9"/>
+      <c r="L208" s="9"/>
+      <c r="M208" s="9"/>
+      <c r="N208" s="9" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A209" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="B209" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="C209" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D209" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="E209" s="10">
+        <v>659</v>
+      </c>
+      <c r="F209" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="G209" s="10">
+        <v>654</v>
+      </c>
+      <c r="H209" s="10">
+        <v>646.35</v>
+      </c>
+      <c r="I209" s="10">
+        <v>647.35</v>
+      </c>
+      <c r="J209" s="9"/>
+      <c r="K209" s="9"/>
+      <c r="L209" s="9"/>
+      <c r="M209" s="9"/>
+      <c r="N209" s="9" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A210" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="B210" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="C210" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D210" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="E210" s="10">
+        <v>1302</v>
+      </c>
+      <c r="F210" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="G210" s="10">
+        <v>1280</v>
+      </c>
+      <c r="H210" s="10">
+        <v>1275.1</v>
+      </c>
+      <c r="I210" s="10">
+        <v>1276</v>
+      </c>
+      <c r="J210" s="9"/>
+      <c r="K210" s="9"/>
+      <c r="L210" s="9"/>
+      <c r="M210" s="9"/>
+      <c r="N210" s="9" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="211" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A211" s="9" t="s">
+        <v>697</v>
+      </c>
+      <c r="B211" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C211" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D211" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="E211" s="10">
+        <v>126.5</v>
+      </c>
+      <c r="F211" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="G211" s="10">
+        <v>122.43</v>
+      </c>
+      <c r="H211" s="10">
+        <v>121.51</v>
+      </c>
+      <c r="I211" s="10">
+        <v>121.51</v>
+      </c>
+      <c r="J211" s="9"/>
+      <c r="K211" s="9"/>
+      <c r="L211" s="9"/>
+      <c r="M211" s="9"/>
+      <c r="N211" s="9" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="212" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A212" s="9" t="s">
+        <v>700</v>
+      </c>
+      <c r="B212" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="C212" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D212" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="E212" s="10">
+        <v>3447</v>
+      </c>
+      <c r="F212" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="G212" s="10">
+        <v>3306.1</v>
+      </c>
+      <c r="H212" s="10">
+        <v>3283.4</v>
+      </c>
+      <c r="I212" s="10">
+        <v>3285.9</v>
+      </c>
+      <c r="J212" s="9"/>
+      <c r="K212" s="9"/>
+      <c r="L212" s="9"/>
+      <c r="M212" s="9"/>
+      <c r="N212" s="9" t="s">
+        <v>699</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pattern_signals.xlsx
+++ b/pattern_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1336" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1462" uniqueCount="747">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -2120,6 +2120,141 @@
   </si>
   <si>
     <t>NSE:M&amp;M-EQ</t>
+  </si>
+  <si>
+    <t>NSE:AUROPHARMA-EQ_BEAR_1772430300_1772595900</t>
+  </si>
+  <si>
+    <t>2026-03-02 11:15</t>
+  </si>
+  <si>
+    <t>2026-03-04 09:15</t>
+  </si>
+  <si>
+    <t>2026-03-04 11:44</t>
+  </si>
+  <si>
+    <t>NSE:BHARATFORG-EQ_BEAR_1772431200_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:BHARATFORG-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-02 11:30</t>
+  </si>
+  <si>
+    <t>NSE:COLPAL-EQ_BEAR_1772423100_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:COLPAL-EQ</t>
+  </si>
+  <si>
+    <t>NSE:IDFCFIRSTB-EQ_BEAR_1772423100_1772601300</t>
+  </si>
+  <si>
+    <t>2026-03-04 10:45</t>
+  </si>
+  <si>
+    <t>2026-03-04 11:45</t>
+  </si>
+  <si>
+    <t>NSE:INDIANB-EQ_BEAR_1772426700_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:INDIANB-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-02 10:15</t>
+  </si>
+  <si>
+    <t>NSE:IGL-EQ_BEAR_1772423100_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:JSWSTEEL-EQ_BEAR_1772423100_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:KALYANKJIL-EQ_BEAR_1772423100_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:MAXHEALTH-EQ_BEAR_1772423100_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:NCC-EQ_BEAR_1772423100_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:NTPC-EQ_BEAR_1772423100_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:PGEL-EQ_BEAR_1772423100_1772595900</t>
+  </si>
+  <si>
+    <t>NSE:DIXON-EQ_BEAR_1772423100_1772604900</t>
+  </si>
+  <si>
+    <t>2026-03-04 12:01</t>
+  </si>
+  <si>
+    <t>NSE:CUMMINSIND-EQ_BEAR_1772423100_1772605800</t>
+  </si>
+  <si>
+    <t>NSE:CUMMINSIND-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-04 12:00</t>
+  </si>
+  <si>
+    <t>2026-03-04 12:17</t>
+  </si>
+  <si>
+    <t>NSE:SOLARINDS-EQ_BULL_1772424900_1772609400</t>
+  </si>
+  <si>
+    <t>2026-03-02 09:45</t>
+  </si>
+  <si>
+    <t>2026-03-04 13:00</t>
+  </si>
+  <si>
+    <t>2026-03-04 13:16</t>
+  </si>
+  <si>
+    <t>NSE:NATIONALUM-EQ_BULL_1772424900_1772615700</t>
+  </si>
+  <si>
+    <t>NSE:NATIONALUM-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-04 14:45</t>
+  </si>
+  <si>
+    <t>2026-03-04 15:00</t>
+  </si>
+  <si>
+    <t>NSE:DIVISLAB-EQ_BEAR_1772424000_1772617500</t>
+  </si>
+  <si>
+    <t>2026-03-04 15:15</t>
+  </si>
+  <si>
+    <t>2026-03-04 15:43</t>
+  </si>
+  <si>
+    <t>NSE:PIDILITIND-EQ_BEAR_1772423100_1772616600</t>
+  </si>
+  <si>
+    <t>NSE:DABUR-EQ_BEAR_1772423100_1772616600</t>
+  </si>
+  <si>
+    <t>NSE:BHEL-EQ_BEAR_1772427600_1772616600</t>
+  </si>
+  <si>
+    <t>NSE:BHEL-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-02 10:30</t>
+  </si>
+  <si>
+    <t>NSE:ASTRAL-EQ_BEAR_1772423100_1772616600</t>
   </si>
 </sst>
 </file>
@@ -2583,7 +2718,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N212"/>
+  <dimension ref="A1:N233"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -9896,6 +10031,762 @@
         <v>699</v>
       </c>
     </row>
+    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A213" s="9" t="s">
+        <v>702</v>
+      </c>
+      <c r="B213" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="C213" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D213" s="9" t="s">
+        <v>703</v>
+      </c>
+      <c r="E213" s="10">
+        <v>1200.8</v>
+      </c>
+      <c r="F213" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="G213" s="10">
+        <v>1202.9</v>
+      </c>
+      <c r="H213" s="10">
+        <v>1183.4</v>
+      </c>
+      <c r="I213" s="10">
+        <v>1188.3</v>
+      </c>
+      <c r="J213" s="9"/>
+      <c r="K213" s="9"/>
+      <c r="L213" s="9"/>
+      <c r="M213" s="9"/>
+      <c r="N213" s="9" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="214" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A214" s="9" t="s">
+        <v>706</v>
+      </c>
+      <c r="B214" s="9" t="s">
+        <v>707</v>
+      </c>
+      <c r="C214" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D214" s="9" t="s">
+        <v>708</v>
+      </c>
+      <c r="E214" s="10">
+        <v>1874.8</v>
+      </c>
+      <c r="F214" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="G214" s="10">
+        <v>1870</v>
+      </c>
+      <c r="H214" s="10">
+        <v>1833</v>
+      </c>
+      <c r="I214" s="10">
+        <v>1841.4</v>
+      </c>
+      <c r="J214" s="9"/>
+      <c r="K214" s="9"/>
+      <c r="L214" s="9"/>
+      <c r="M214" s="9"/>
+      <c r="N214" s="9" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="215" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A215" s="9" t="s">
+        <v>709</v>
+      </c>
+      <c r="B215" s="9" t="s">
+        <v>710</v>
+      </c>
+      <c r="C215" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D215" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="E215" s="10">
+        <v>2228.9</v>
+      </c>
+      <c r="F215" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="G215" s="10">
+        <v>2203.6</v>
+      </c>
+      <c r="H215" s="10">
+        <v>2185.4</v>
+      </c>
+      <c r="I215" s="10">
+        <v>2192.8</v>
+      </c>
+      <c r="J215" s="9"/>
+      <c r="K215" s="9"/>
+      <c r="L215" s="9"/>
+      <c r="M215" s="9"/>
+      <c r="N215" s="9" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A216" s="9" t="s">
+        <v>711</v>
+      </c>
+      <c r="B216" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C216" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D216" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="E216" s="10">
+        <v>73.16</v>
+      </c>
+      <c r="F216" s="9" t="s">
+        <v>712</v>
+      </c>
+      <c r="G216" s="10">
+        <v>70.31</v>
+      </c>
+      <c r="H216" s="10">
+        <v>70.02</v>
+      </c>
+      <c r="I216" s="10">
+        <v>70.1</v>
+      </c>
+      <c r="J216" s="9"/>
+      <c r="K216" s="9"/>
+      <c r="L216" s="9"/>
+      <c r="M216" s="9"/>
+      <c r="N216" s="9" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A217" s="9" t="s">
+        <v>714</v>
+      </c>
+      <c r="B217" s="9" t="s">
+        <v>715</v>
+      </c>
+      <c r="C217" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D217" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="E217" s="10">
+        <v>974.85</v>
+      </c>
+      <c r="F217" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="G217" s="10">
+        <v>961.35</v>
+      </c>
+      <c r="H217" s="10">
+        <v>947.1</v>
+      </c>
+      <c r="I217" s="10">
+        <v>949.25</v>
+      </c>
+      <c r="J217" s="9"/>
+      <c r="K217" s="9"/>
+      <c r="L217" s="9"/>
+      <c r="M217" s="9"/>
+      <c r="N217" s="9" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A218" s="9" t="s">
+        <v>717</v>
+      </c>
+      <c r="B218" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C218" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D218" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="E218" s="10">
+        <v>166.61</v>
+      </c>
+      <c r="F218" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="G218" s="10">
+        <v>165.26</v>
+      </c>
+      <c r="H218" s="10">
+        <v>162.03</v>
+      </c>
+      <c r="I218" s="10">
+        <v>162.38</v>
+      </c>
+      <c r="J218" s="9"/>
+      <c r="K218" s="9"/>
+      <c r="L218" s="9"/>
+      <c r="M218" s="9"/>
+      <c r="N218" s="9" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A219" s="9" t="s">
+        <v>718</v>
+      </c>
+      <c r="B219" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="C219" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D219" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="E219" s="10">
+        <v>1260.8</v>
+      </c>
+      <c r="F219" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="G219" s="10">
+        <v>1253.9</v>
+      </c>
+      <c r="H219" s="10">
+        <v>1215.3</v>
+      </c>
+      <c r="I219" s="10">
+        <v>1217</v>
+      </c>
+      <c r="J219" s="9"/>
+      <c r="K219" s="9"/>
+      <c r="L219" s="9"/>
+      <c r="M219" s="9"/>
+      <c r="N219" s="9" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A220" s="9" t="s">
+        <v>719</v>
+      </c>
+      <c r="B220" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C220" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D220" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="E220" s="10">
+        <v>402.45</v>
+      </c>
+      <c r="F220" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="G220" s="10">
+        <v>396.3</v>
+      </c>
+      <c r="H220" s="10">
+        <v>390.05</v>
+      </c>
+      <c r="I220" s="10">
+        <v>392.55</v>
+      </c>
+      <c r="J220" s="9"/>
+      <c r="K220" s="9"/>
+      <c r="L220" s="9"/>
+      <c r="M220" s="9"/>
+      <c r="N220" s="9" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="221" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A221" s="9" t="s">
+        <v>720</v>
+      </c>
+      <c r="B221" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="C221" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D221" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="E221" s="10">
+        <v>1074.2</v>
+      </c>
+      <c r="F221" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="G221" s="10">
+        <v>1067.8</v>
+      </c>
+      <c r="H221" s="10">
+        <v>1047</v>
+      </c>
+      <c r="I221" s="10">
+        <v>1050.6</v>
+      </c>
+      <c r="J221" s="9"/>
+      <c r="K221" s="9"/>
+      <c r="L221" s="9"/>
+      <c r="M221" s="9"/>
+      <c r="N221" s="9" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="222" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A222" s="9" t="s">
+        <v>721</v>
+      </c>
+      <c r="B222" s="9" t="s">
+        <v>597</v>
+      </c>
+      <c r="C222" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D222" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="E222" s="10">
+        <v>147.19</v>
+      </c>
+      <c r="F222" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="G222" s="10">
+        <v>147.09</v>
+      </c>
+      <c r="H222" s="10">
+        <v>145</v>
+      </c>
+      <c r="I222" s="10">
+        <v>145.4</v>
+      </c>
+      <c r="J222" s="9"/>
+      <c r="K222" s="9"/>
+      <c r="L222" s="9"/>
+      <c r="M222" s="9"/>
+      <c r="N222" s="9" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A223" s="9" t="s">
+        <v>722</v>
+      </c>
+      <c r="B223" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="C223" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D223" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="E223" s="10">
+        <v>377.25</v>
+      </c>
+      <c r="F223" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="G223" s="10">
+        <v>373.85</v>
+      </c>
+      <c r="H223" s="10">
+        <v>366.6</v>
+      </c>
+      <c r="I223" s="10">
+        <v>366.9</v>
+      </c>
+      <c r="J223" s="9"/>
+      <c r="K223" s="9"/>
+      <c r="L223" s="9"/>
+      <c r="M223" s="9"/>
+      <c r="N223" s="9" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A224" s="9" t="s">
+        <v>723</v>
+      </c>
+      <c r="B224" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C224" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D224" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="E224" s="10">
+        <v>611.45</v>
+      </c>
+      <c r="F224" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="G224" s="10">
+        <v>606.95</v>
+      </c>
+      <c r="H224" s="10">
+        <v>590.5</v>
+      </c>
+      <c r="I224" s="10">
+        <v>591.7</v>
+      </c>
+      <c r="J224" s="9"/>
+      <c r="K224" s="9"/>
+      <c r="L224" s="9"/>
+      <c r="M224" s="9"/>
+      <c r="N224" s="9" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="225" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A225" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="B225" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="C225" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D225" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="E225" s="10">
+        <v>10395</v>
+      </c>
+      <c r="F225" s="9" t="s">
+        <v>713</v>
+      </c>
+      <c r="G225" s="10">
+        <v>9827</v>
+      </c>
+      <c r="H225" s="10">
+        <v>9792</v>
+      </c>
+      <c r="I225" s="10">
+        <v>9797</v>
+      </c>
+      <c r="J225" s="9"/>
+      <c r="K225" s="9"/>
+      <c r="L225" s="9"/>
+      <c r="M225" s="9"/>
+      <c r="N225" s="9" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="226" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A226" s="9" t="s">
+        <v>726</v>
+      </c>
+      <c r="B226" s="9" t="s">
+        <v>727</v>
+      </c>
+      <c r="C226" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D226" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="E226" s="10">
+        <v>4855.3</v>
+      </c>
+      <c r="F226" s="9" t="s">
+        <v>728</v>
+      </c>
+      <c r="G226" s="10">
+        <v>4662.9</v>
+      </c>
+      <c r="H226" s="10">
+        <v>4646.6</v>
+      </c>
+      <c r="I226" s="10">
+        <v>4650.6</v>
+      </c>
+      <c r="J226" s="9"/>
+      <c r="K226" s="9"/>
+      <c r="L226" s="9"/>
+      <c r="M226" s="9"/>
+      <c r="N226" s="9" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="227" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A227" s="11" t="s">
+        <v>730</v>
+      </c>
+      <c r="B227" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C227" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D227" s="11" t="s">
+        <v>731</v>
+      </c>
+      <c r="E227" s="12">
+        <v>13916</v>
+      </c>
+      <c r="F227" s="11" t="s">
+        <v>732</v>
+      </c>
+      <c r="G227" s="12">
+        <v>14499</v>
+      </c>
+      <c r="H227" s="12">
+        <v>14393</v>
+      </c>
+      <c r="I227" s="12">
+        <v>14455</v>
+      </c>
+      <c r="J227" s="11"/>
+      <c r="K227" s="11"/>
+      <c r="L227" s="11"/>
+      <c r="M227" s="11"/>
+      <c r="N227" s="11" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="228" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A228" s="11" t="s">
+        <v>734</v>
+      </c>
+      <c r="B228" s="11" t="s">
+        <v>735</v>
+      </c>
+      <c r="C228" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D228" s="11" t="s">
+        <v>731</v>
+      </c>
+      <c r="E228" s="12">
+        <v>362.5</v>
+      </c>
+      <c r="F228" s="11" t="s">
+        <v>736</v>
+      </c>
+      <c r="G228" s="12">
+        <v>377.3</v>
+      </c>
+      <c r="H228" s="12">
+        <v>371.4</v>
+      </c>
+      <c r="I228" s="12">
+        <v>375.95</v>
+      </c>
+      <c r="J228" s="11"/>
+      <c r="K228" s="11"/>
+      <c r="L228" s="11"/>
+      <c r="M228" s="11"/>
+      <c r="N228" s="11" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="229" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A229" s="9" t="s">
+        <v>738</v>
+      </c>
+      <c r="B229" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C229" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D229" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="E229" s="10">
+        <v>6347</v>
+      </c>
+      <c r="F229" s="9" t="s">
+        <v>739</v>
+      </c>
+      <c r="G229" s="10">
+        <v>6317.5</v>
+      </c>
+      <c r="H229" s="10">
+        <v>6281.5</v>
+      </c>
+      <c r="I229" s="10">
+        <v>6281.5</v>
+      </c>
+      <c r="J229" s="9"/>
+      <c r="K229" s="9"/>
+      <c r="L229" s="9"/>
+      <c r="M229" s="9"/>
+      <c r="N229" s="9" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="230" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A230" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="B230" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C230" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D230" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="E230" s="10">
+        <v>1464.1</v>
+      </c>
+      <c r="F230" s="9" t="s">
+        <v>737</v>
+      </c>
+      <c r="G230" s="10">
+        <v>1444</v>
+      </c>
+      <c r="H230" s="10">
+        <v>1436.5</v>
+      </c>
+      <c r="I230" s="10">
+        <v>1436.9</v>
+      </c>
+      <c r="J230" s="9"/>
+      <c r="K230" s="9"/>
+      <c r="L230" s="9"/>
+      <c r="M230" s="9"/>
+      <c r="N230" s="9" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="231" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A231" s="9" t="s">
+        <v>742</v>
+      </c>
+      <c r="B231" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C231" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D231" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="E231" s="10">
+        <v>510.5</v>
+      </c>
+      <c r="F231" s="9" t="s">
+        <v>737</v>
+      </c>
+      <c r="G231" s="10">
+        <v>490.8</v>
+      </c>
+      <c r="H231" s="10">
+        <v>486.65</v>
+      </c>
+      <c r="I231" s="10">
+        <v>487.15</v>
+      </c>
+      <c r="J231" s="9"/>
+      <c r="K231" s="9"/>
+      <c r="L231" s="9"/>
+      <c r="M231" s="9"/>
+      <c r="N231" s="9" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="232" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A232" s="9" t="s">
+        <v>743</v>
+      </c>
+      <c r="B232" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="C232" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D232" s="9" t="s">
+        <v>745</v>
+      </c>
+      <c r="E232" s="10">
+        <v>261.55</v>
+      </c>
+      <c r="F232" s="9" t="s">
+        <v>737</v>
+      </c>
+      <c r="G232" s="10">
+        <v>249.5</v>
+      </c>
+      <c r="H232" s="10">
+        <v>247.25</v>
+      </c>
+      <c r="I232" s="10">
+        <v>247.45</v>
+      </c>
+      <c r="J232" s="9"/>
+      <c r="K232" s="9"/>
+      <c r="L232" s="9"/>
+      <c r="M232" s="9"/>
+      <c r="N232" s="9" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="233" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A233" s="9" t="s">
+        <v>746</v>
+      </c>
+      <c r="B233" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="C233" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D233" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="E233" s="10">
+        <v>1641.9</v>
+      </c>
+      <c r="F233" s="9" t="s">
+        <v>737</v>
+      </c>
+      <c r="G233" s="10">
+        <v>1656.3</v>
+      </c>
+      <c r="H233" s="10">
+        <v>1645</v>
+      </c>
+      <c r="I233" s="10">
+        <v>1647.7</v>
+      </c>
+      <c r="J233" s="9"/>
+      <c r="K233" s="9"/>
+      <c r="L233" s="9"/>
+      <c r="M233" s="9"/>
+      <c r="N233" s="9" t="s">
+        <v>740</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pattern_signals.xlsx
+++ b/pattern_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1462" uniqueCount="747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="750">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -2255,6 +2255,15 @@
   </si>
   <si>
     <t>NSE:ASTRAL-EQ_BEAR_1772423100_1772616600</t>
+  </si>
+  <si>
+    <t>NSE:IGL-EQ_BEAR_1772423100_1772617500</t>
+  </si>
+  <si>
+    <t>2026-03-04 16:43</t>
+  </si>
+  <si>
+    <t>NSE:SOLARINDS-EQ_BULL_1772424900_1772617500</t>
   </si>
 </sst>
 </file>
@@ -2718,7 +2727,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N233"/>
+  <dimension ref="A1:N235"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -10787,6 +10796,78 @@
         <v>740</v>
       </c>
     </row>
+    <row r="234" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A234" s="9" t="s">
+        <v>747</v>
+      </c>
+      <c r="B234" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C234" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D234" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="E234" s="10">
+        <v>166.61</v>
+      </c>
+      <c r="F234" s="9" t="s">
+        <v>739</v>
+      </c>
+      <c r="G234" s="10">
+        <v>157.7</v>
+      </c>
+      <c r="H234" s="10">
+        <v>156.8</v>
+      </c>
+      <c r="I234" s="10">
+        <v>157.18</v>
+      </c>
+      <c r="J234" s="9"/>
+      <c r="K234" s="9"/>
+      <c r="L234" s="9"/>
+      <c r="M234" s="9"/>
+      <c r="N234" s="9" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="235" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A235" s="11" t="s">
+        <v>749</v>
+      </c>
+      <c r="B235" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C235" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D235" s="11" t="s">
+        <v>731</v>
+      </c>
+      <c r="E235" s="12">
+        <v>13916</v>
+      </c>
+      <c r="F235" s="11" t="s">
+        <v>739</v>
+      </c>
+      <c r="G235" s="12">
+        <v>14599</v>
+      </c>
+      <c r="H235" s="12">
+        <v>14500</v>
+      </c>
+      <c r="I235" s="12">
+        <v>14598</v>
+      </c>
+      <c r="J235" s="11"/>
+      <c r="K235" s="11"/>
+      <c r="L235" s="11"/>
+      <c r="M235" s="11"/>
+      <c r="N235" s="11" t="s">
+        <v>748</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pattern_signals.xlsx
+++ b/pattern_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="774">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -2264,6 +2264,78 @@
   </si>
   <si>
     <t>NSE:SOLARINDS-EQ_BULL_1772424900_1772617500</t>
+  </si>
+  <si>
+    <t>NSE:COALINDIA-EQ_BULL_1772598600_1772682300</t>
+  </si>
+  <si>
+    <t>2026-03-04 10:00</t>
+  </si>
+  <si>
+    <t>2026-03-05 09:15</t>
+  </si>
+  <si>
+    <t>2026-03-05 09:30</t>
+  </si>
+  <si>
+    <t>NSE:LUPIN-EQ_BULL_1772615700_1772682300</t>
+  </si>
+  <si>
+    <t>NSE:LUPIN-EQ</t>
+  </si>
+  <si>
+    <t>NSE:MAZDOCK-EQ_BULL_1772686800_1772693100</t>
+  </si>
+  <si>
+    <t>NSE:MAZDOCK-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-05 10:30</t>
+  </si>
+  <si>
+    <t>2026-03-05 12:15</t>
+  </si>
+  <si>
+    <t>2026-03-05 12:30</t>
+  </si>
+  <si>
+    <t>NSE:BANDHANBNK-EQ_BULL_1772685900_1772701200</t>
+  </si>
+  <si>
+    <t>NSE:BANDHANBNK-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-05 10:15</t>
+  </si>
+  <si>
+    <t>2026-03-05 14:30</t>
+  </si>
+  <si>
+    <t>2026-03-05 14:45</t>
+  </si>
+  <si>
+    <t>NSE:RELIANCE-EQ_BULL_1772689500_1772701200</t>
+  </si>
+  <si>
+    <t>2026-03-05 11:15</t>
+  </si>
+  <si>
+    <t>NSE:HINDZINC-EQ_BEAR_1772595900_1772702100</t>
+  </si>
+  <si>
+    <t>2026-03-05 15:00</t>
+  </si>
+  <si>
+    <t>NSE:NTPC-EQ_BULL_1772691300_1772702100</t>
+  </si>
+  <si>
+    <t>2026-03-05 11:45</t>
+  </si>
+  <si>
+    <t>NSE:OFSS-EQ_BEAR_1772686800_1772703000</t>
+  </si>
+  <si>
+    <t>2026-03-05 15:15</t>
   </si>
 </sst>
 </file>
@@ -2727,7 +2799,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N235"/>
+  <dimension ref="A1:N243"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -10868,6 +10940,294 @@
         <v>748</v>
       </c>
     </row>
+    <row r="236" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A236" s="11" t="s">
+        <v>750</v>
+      </c>
+      <c r="B236" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C236" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D236" s="11" t="s">
+        <v>751</v>
+      </c>
+      <c r="E236" s="12">
+        <v>437.15</v>
+      </c>
+      <c r="F236" s="11" t="s">
+        <v>752</v>
+      </c>
+      <c r="G236" s="12">
+        <v>452.4</v>
+      </c>
+      <c r="H236" s="12">
+        <v>440</v>
+      </c>
+      <c r="I236" s="12">
+        <v>451.05</v>
+      </c>
+      <c r="J236" s="11"/>
+      <c r="K236" s="11"/>
+      <c r="L236" s="11"/>
+      <c r="M236" s="11"/>
+      <c r="N236" s="11" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="237" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A237" s="11" t="s">
+        <v>754</v>
+      </c>
+      <c r="B237" s="11" t="s">
+        <v>755</v>
+      </c>
+      <c r="C237" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D237" s="11" t="s">
+        <v>736</v>
+      </c>
+      <c r="E237" s="12">
+        <v>2309.9</v>
+      </c>
+      <c r="F237" s="11" t="s">
+        <v>752</v>
+      </c>
+      <c r="G237" s="12">
+        <v>2352.3</v>
+      </c>
+      <c r="H237" s="12">
+        <v>2310</v>
+      </c>
+      <c r="I237" s="12">
+        <v>2348</v>
+      </c>
+      <c r="J237" s="11"/>
+      <c r="K237" s="11"/>
+      <c r="L237" s="11"/>
+      <c r="M237" s="11"/>
+      <c r="N237" s="11" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="238" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A238" s="11" t="s">
+        <v>756</v>
+      </c>
+      <c r="B238" s="11" t="s">
+        <v>757</v>
+      </c>
+      <c r="C238" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D238" s="11" t="s">
+        <v>758</v>
+      </c>
+      <c r="E238" s="12">
+        <v>2276.7</v>
+      </c>
+      <c r="F238" s="11" t="s">
+        <v>759</v>
+      </c>
+      <c r="G238" s="12">
+        <v>2318</v>
+      </c>
+      <c r="H238" s="12">
+        <v>2280.4</v>
+      </c>
+      <c r="I238" s="12">
+        <v>2313.1</v>
+      </c>
+      <c r="J238" s="11"/>
+      <c r="K238" s="11"/>
+      <c r="L238" s="11"/>
+      <c r="M238" s="11"/>
+      <c r="N238" s="11" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="239" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A239" s="11" t="s">
+        <v>761</v>
+      </c>
+      <c r="B239" s="11" t="s">
+        <v>762</v>
+      </c>
+      <c r="C239" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D239" s="11" t="s">
+        <v>763</v>
+      </c>
+      <c r="E239" s="12">
+        <v>180.98</v>
+      </c>
+      <c r="F239" s="11" t="s">
+        <v>764</v>
+      </c>
+      <c r="G239" s="12">
+        <v>184.98</v>
+      </c>
+      <c r="H239" s="12">
+        <v>182.15</v>
+      </c>
+      <c r="I239" s="12">
+        <v>184.62</v>
+      </c>
+      <c r="J239" s="11"/>
+      <c r="K239" s="11"/>
+      <c r="L239" s="11"/>
+      <c r="M239" s="11"/>
+      <c r="N239" s="11" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="240" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A240" s="11" t="s">
+        <v>766</v>
+      </c>
+      <c r="B240" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C240" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D240" s="11" t="s">
+        <v>767</v>
+      </c>
+      <c r="E240" s="12">
+        <v>1380.9</v>
+      </c>
+      <c r="F240" s="11" t="s">
+        <v>764</v>
+      </c>
+      <c r="G240" s="12">
+        <v>1392.8</v>
+      </c>
+      <c r="H240" s="12">
+        <v>1378.1</v>
+      </c>
+      <c r="I240" s="12">
+        <v>1389.7</v>
+      </c>
+      <c r="J240" s="11"/>
+      <c r="K240" s="11"/>
+      <c r="L240" s="11"/>
+      <c r="M240" s="11"/>
+      <c r="N240" s="11" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="241" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A241" s="9" t="s">
+        <v>768</v>
+      </c>
+      <c r="B241" s="9" t="s">
+        <v>529</v>
+      </c>
+      <c r="C241" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D241" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="E241" s="10">
+        <v>596</v>
+      </c>
+      <c r="F241" s="9" t="s">
+        <v>765</v>
+      </c>
+      <c r="G241" s="10">
+        <v>598.25</v>
+      </c>
+      <c r="H241" s="10">
+        <v>593.3</v>
+      </c>
+      <c r="I241" s="10">
+        <v>593.65</v>
+      </c>
+      <c r="J241" s="9"/>
+      <c r="K241" s="9"/>
+      <c r="L241" s="9"/>
+      <c r="M241" s="9"/>
+      <c r="N241" s="9" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="242" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A242" s="11" t="s">
+        <v>770</v>
+      </c>
+      <c r="B242" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C242" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D242" s="11" t="s">
+        <v>771</v>
+      </c>
+      <c r="E242" s="12">
+        <v>375.95</v>
+      </c>
+      <c r="F242" s="11" t="s">
+        <v>765</v>
+      </c>
+      <c r="G242" s="12">
+        <v>379.8</v>
+      </c>
+      <c r="H242" s="12">
+        <v>376.2</v>
+      </c>
+      <c r="I242" s="12">
+        <v>379.6</v>
+      </c>
+      <c r="J242" s="11"/>
+      <c r="K242" s="11"/>
+      <c r="L242" s="11"/>
+      <c r="M242" s="11"/>
+      <c r="N242" s="11" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="243" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A243" s="9" t="s">
+        <v>772</v>
+      </c>
+      <c r="B243" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="C243" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D243" s="9" t="s">
+        <v>758</v>
+      </c>
+      <c r="E243" s="10">
+        <v>6788</v>
+      </c>
+      <c r="F243" s="9" t="s">
+        <v>769</v>
+      </c>
+      <c r="G243" s="10">
+        <v>6825</v>
+      </c>
+      <c r="H243" s="10">
+        <v>6764</v>
+      </c>
+      <c r="I243" s="10">
+        <v>6768.5</v>
+      </c>
+      <c r="J243" s="9"/>
+      <c r="K243" s="9"/>
+      <c r="L243" s="9"/>
+      <c r="M243" s="9"/>
+      <c r="N243" s="9" t="s">
+        <v>773</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pattern_signals.xlsx
+++ b/pattern_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="774">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1594" uniqueCount="792">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -2336,6 +2336,60 @@
   </si>
   <si>
     <t>2026-03-05 15:15</t>
+  </si>
+  <si>
+    <t>NSE:AUBANK-EQ_BULL_1772689500_1772768700</t>
+  </si>
+  <si>
+    <t>2026-03-06 09:15</t>
+  </si>
+  <si>
+    <t>2026-03-06 09:30</t>
+  </si>
+  <si>
+    <t>NSE:AUROPHARMA-EQ_BULL_1772685900_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:BSE-EQ_BULL_1772686800_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:BDL-EQ_BULL_1772683200_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:BEL-EQ_BULL_1772684100_1772768700</t>
+  </si>
+  <si>
+    <t>2026-03-05 09:45</t>
+  </si>
+  <si>
+    <t>NSE:GLENMARK-EQ_BULL_1772700300_1772768700</t>
+  </si>
+  <si>
+    <t>2026-03-05 14:15</t>
+  </si>
+  <si>
+    <t>NSE:POWERINDIA-EQ_BULL_1772688600_1772768700</t>
+  </si>
+  <si>
+    <t>2026-03-05 11:00</t>
+  </si>
+  <si>
+    <t>2026-03-06 09:31</t>
+  </si>
+  <si>
+    <t>NSE:MAZDOCK-EQ_BULL_1772686800_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:POLYCAB-EQ_BULL_1772702100_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:PFC-EQ_BULL_1772693100_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:RELIANCE-EQ_BULL_1772689500_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:TATAPOWER-EQ_BULL_1772688600_1772768700</t>
   </si>
 </sst>
 </file>
@@ -2799,7 +2853,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N243"/>
+  <dimension ref="A1:N255"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -11228,6 +11282,438 @@
         <v>773</v>
       </c>
     </row>
+    <row r="244" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A244" s="11" t="s">
+        <v>774</v>
+      </c>
+      <c r="B244" s="11" t="s">
+        <v>584</v>
+      </c>
+      <c r="C244" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D244" s="11" t="s">
+        <v>767</v>
+      </c>
+      <c r="E244" s="12">
+        <v>965.7</v>
+      </c>
+      <c r="F244" s="11" t="s">
+        <v>775</v>
+      </c>
+      <c r="G244" s="12">
+        <v>980.15</v>
+      </c>
+      <c r="H244" s="12">
+        <v>965.7</v>
+      </c>
+      <c r="I244" s="12">
+        <v>977.9</v>
+      </c>
+      <c r="J244" s="11"/>
+      <c r="K244" s="11"/>
+      <c r="L244" s="11"/>
+      <c r="M244" s="11"/>
+      <c r="N244" s="11" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="245" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A245" s="11" t="s">
+        <v>777</v>
+      </c>
+      <c r="B245" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="C245" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D245" s="11" t="s">
+        <v>763</v>
+      </c>
+      <c r="E245" s="12">
+        <v>1212.5</v>
+      </c>
+      <c r="F245" s="11" t="s">
+        <v>775</v>
+      </c>
+      <c r="G245" s="12">
+        <v>1235</v>
+      </c>
+      <c r="H245" s="12">
+        <v>1220.3</v>
+      </c>
+      <c r="I245" s="12">
+        <v>1233.1</v>
+      </c>
+      <c r="J245" s="11"/>
+      <c r="K245" s="11"/>
+      <c r="L245" s="11"/>
+      <c r="M245" s="11"/>
+      <c r="N245" s="11" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="246" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A246" s="11" t="s">
+        <v>778</v>
+      </c>
+      <c r="B246" s="11" t="s">
+        <v>602</v>
+      </c>
+      <c r="C246" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D246" s="11" t="s">
+        <v>758</v>
+      </c>
+      <c r="E246" s="12">
+        <v>2731.5</v>
+      </c>
+      <c r="F246" s="11" t="s">
+        <v>775</v>
+      </c>
+      <c r="G246" s="12">
+        <v>2789</v>
+      </c>
+      <c r="H246" s="12">
+        <v>2736.4</v>
+      </c>
+      <c r="I246" s="12">
+        <v>2781.8</v>
+      </c>
+      <c r="J246" s="11"/>
+      <c r="K246" s="11"/>
+      <c r="L246" s="11"/>
+      <c r="M246" s="11"/>
+      <c r="N246" s="11" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="247" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A247" s="11" t="s">
+        <v>779</v>
+      </c>
+      <c r="B247" s="11" t="s">
+        <v>436</v>
+      </c>
+      <c r="C247" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D247" s="11" t="s">
+        <v>753</v>
+      </c>
+      <c r="E247" s="12">
+        <v>1283.6</v>
+      </c>
+      <c r="F247" s="11" t="s">
+        <v>775</v>
+      </c>
+      <c r="G247" s="12">
+        <v>1327.9</v>
+      </c>
+      <c r="H247" s="12">
+        <v>1276.1</v>
+      </c>
+      <c r="I247" s="12">
+        <v>1324.6</v>
+      </c>
+      <c r="J247" s="11"/>
+      <c r="K247" s="11"/>
+      <c r="L247" s="11"/>
+      <c r="M247" s="11"/>
+      <c r="N247" s="11" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="248" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A248" s="11" t="s">
+        <v>780</v>
+      </c>
+      <c r="B248" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="C248" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D248" s="11" t="s">
+        <v>781</v>
+      </c>
+      <c r="E248" s="12">
+        <v>454.9</v>
+      </c>
+      <c r="F248" s="11" t="s">
+        <v>775</v>
+      </c>
+      <c r="G248" s="12">
+        <v>469.7</v>
+      </c>
+      <c r="H248" s="12">
+        <v>460.35</v>
+      </c>
+      <c r="I248" s="12">
+        <v>468.65</v>
+      </c>
+      <c r="J248" s="11"/>
+      <c r="K248" s="11"/>
+      <c r="L248" s="11"/>
+      <c r="M248" s="11"/>
+      <c r="N248" s="11" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="249" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A249" s="11" t="s">
+        <v>782</v>
+      </c>
+      <c r="B249" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="C249" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D249" s="11" t="s">
+        <v>783</v>
+      </c>
+      <c r="E249" s="12">
+        <v>2094.2</v>
+      </c>
+      <c r="F249" s="11" t="s">
+        <v>775</v>
+      </c>
+      <c r="G249" s="12">
+        <v>2135.5</v>
+      </c>
+      <c r="H249" s="12">
+        <v>2094.4</v>
+      </c>
+      <c r="I249" s="12">
+        <v>2131.5</v>
+      </c>
+      <c r="J249" s="11"/>
+      <c r="K249" s="11"/>
+      <c r="L249" s="11"/>
+      <c r="M249" s="11"/>
+      <c r="N249" s="11" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="250" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A250" s="11" t="s">
+        <v>784</v>
+      </c>
+      <c r="B250" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="C250" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D250" s="11" t="s">
+        <v>785</v>
+      </c>
+      <c r="E250" s="12">
+        <v>25300</v>
+      </c>
+      <c r="F250" s="11" t="s">
+        <v>775</v>
+      </c>
+      <c r="G250" s="12">
+        <v>25720</v>
+      </c>
+      <c r="H250" s="12">
+        <v>25320</v>
+      </c>
+      <c r="I250" s="12">
+        <v>25650</v>
+      </c>
+      <c r="J250" s="11"/>
+      <c r="K250" s="11"/>
+      <c r="L250" s="11"/>
+      <c r="M250" s="11"/>
+      <c r="N250" s="11" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="251" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A251" s="11" t="s">
+        <v>787</v>
+      </c>
+      <c r="B251" s="11" t="s">
+        <v>757</v>
+      </c>
+      <c r="C251" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D251" s="11" t="s">
+        <v>758</v>
+      </c>
+      <c r="E251" s="12">
+        <v>2276.7</v>
+      </c>
+      <c r="F251" s="11" t="s">
+        <v>775</v>
+      </c>
+      <c r="G251" s="12">
+        <v>2476</v>
+      </c>
+      <c r="H251" s="12">
+        <v>2370.1</v>
+      </c>
+      <c r="I251" s="12">
+        <v>2457.7</v>
+      </c>
+      <c r="J251" s="11"/>
+      <c r="K251" s="11"/>
+      <c r="L251" s="11"/>
+      <c r="M251" s="11"/>
+      <c r="N251" s="11" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="252" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A252" s="11" t="s">
+        <v>788</v>
+      </c>
+      <c r="B252" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="C252" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D252" s="11" t="s">
+        <v>765</v>
+      </c>
+      <c r="E252" s="12">
+        <v>8566.5</v>
+      </c>
+      <c r="F252" s="11" t="s">
+        <v>775</v>
+      </c>
+      <c r="G252" s="12">
+        <v>8628</v>
+      </c>
+      <c r="H252" s="12">
+        <v>8480</v>
+      </c>
+      <c r="I252" s="12">
+        <v>8621</v>
+      </c>
+      <c r="J252" s="11"/>
+      <c r="K252" s="11"/>
+      <c r="L252" s="11"/>
+      <c r="M252" s="11"/>
+      <c r="N252" s="11" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="253" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A253" s="11" t="s">
+        <v>789</v>
+      </c>
+      <c r="B253" s="11" t="s">
+        <v>515</v>
+      </c>
+      <c r="C253" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D253" s="11" t="s">
+        <v>759</v>
+      </c>
+      <c r="E253" s="12">
+        <v>409.65</v>
+      </c>
+      <c r="F253" s="11" t="s">
+        <v>775</v>
+      </c>
+      <c r="G253" s="12">
+        <v>422.45</v>
+      </c>
+      <c r="H253" s="12">
+        <v>412.2</v>
+      </c>
+      <c r="I253" s="12">
+        <v>421.75</v>
+      </c>
+      <c r="J253" s="11"/>
+      <c r="K253" s="11"/>
+      <c r="L253" s="11"/>
+      <c r="M253" s="11"/>
+      <c r="N253" s="11" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="254" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A254" s="11" t="s">
+        <v>790</v>
+      </c>
+      <c r="B254" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C254" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D254" s="11" t="s">
+        <v>767</v>
+      </c>
+      <c r="E254" s="12">
+        <v>1380.9</v>
+      </c>
+      <c r="F254" s="11" t="s">
+        <v>775</v>
+      </c>
+      <c r="G254" s="12">
+        <v>1415.7</v>
+      </c>
+      <c r="H254" s="12">
+        <v>1390.3</v>
+      </c>
+      <c r="I254" s="12">
+        <v>1414.6</v>
+      </c>
+      <c r="J254" s="11"/>
+      <c r="K254" s="11"/>
+      <c r="L254" s="11"/>
+      <c r="M254" s="11"/>
+      <c r="N254" s="11" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="255" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A255" s="11" t="s">
+        <v>791</v>
+      </c>
+      <c r="B255" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="C255" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D255" s="11" t="s">
+        <v>785</v>
+      </c>
+      <c r="E255" s="12">
+        <v>374.45</v>
+      </c>
+      <c r="F255" s="11" t="s">
+        <v>775</v>
+      </c>
+      <c r="G255" s="12">
+        <v>382.25</v>
+      </c>
+      <c r="H255" s="12">
+        <v>373.1</v>
+      </c>
+      <c r="I255" s="12">
+        <v>382.1</v>
+      </c>
+      <c r="J255" s="11"/>
+      <c r="K255" s="11"/>
+      <c r="L255" s="11"/>
+      <c r="M255" s="11"/>
+      <c r="N255" s="11" t="s">
+        <v>786</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pattern_signals.xlsx
+++ b/pattern_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1594" uniqueCount="792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1600" uniqueCount="794">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -2390,6 +2390,12 @@
   </si>
   <si>
     <t>NSE:TATAPOWER-EQ_BULL_1772688600_1772768700</t>
+  </si>
+  <si>
+    <t>NSE:SOLARINDS-EQ_BULL_1772424900_1772768700</t>
+  </si>
+  <si>
+    <t>2026-03-06 12:59</t>
   </si>
 </sst>
 </file>
@@ -2853,7 +2859,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N255"/>
+  <dimension ref="A1:N256"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -11714,6 +11720,42 @@
         <v>786</v>
       </c>
     </row>
+    <row r="256" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A256" s="11" t="s">
+        <v>792</v>
+      </c>
+      <c r="B256" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C256" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D256" s="11" t="s">
+        <v>731</v>
+      </c>
+      <c r="E256" s="12">
+        <v>13916</v>
+      </c>
+      <c r="F256" s="11" t="s">
+        <v>775</v>
+      </c>
+      <c r="G256" s="12">
+        <v>15153</v>
+      </c>
+      <c r="H256" s="12">
+        <v>14671</v>
+      </c>
+      <c r="I256" s="12">
+        <v>15142</v>
+      </c>
+      <c r="J256" s="11"/>
+      <c r="K256" s="11"/>
+      <c r="L256" s="11"/>
+      <c r="M256" s="11"/>
+      <c r="N256" s="11" t="s">
+        <v>793</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pattern_signals.xlsx
+++ b/pattern_signals.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PIS\Desktop\Project\new\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B3425CB-C7B3-4930-AB47-8823AB64D99D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505"/>
   </bookViews>
   <sheets>
-    <sheet name="Signals" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Signals" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1732" uniqueCount="853">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1786" uniqueCount="881">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -2579,41 +2573,125 @@
   </si>
   <si>
     <t>2026-03-05 12:15</t>
+  </si>
+  <si>
+    <t>NSE:KALYANKJIL-EQ_BEAR_1772775000_1773027900</t>
+  </si>
+  <si>
+    <t>2026-03-06 11:00</t>
+  </si>
+  <si>
+    <t>2026-03-09 09:15</t>
+  </si>
+  <si>
+    <t>2026-03-09 09:30</t>
+  </si>
+  <si>
+    <t>NSE:NUVAMA-EQ_BEAR_1772784900_1773027900</t>
+  </si>
+  <si>
+    <t>NSE:NUVAMA-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-06 13:45</t>
+  </si>
+  <si>
+    <t>NSE:TATATECH-EQ_BEAR_1772788500_1773027900</t>
+  </si>
+  <si>
+    <t>NSE:TATATECH-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-06 14:45</t>
+  </si>
+  <si>
+    <t>2026-03-09 09:31</t>
+  </si>
+  <si>
+    <t>NSE:MANKIND-EQ_BEAR_1772771400_1773029700</t>
+  </si>
+  <si>
+    <t>2026-03-09 09:45</t>
+  </si>
+  <si>
+    <t>2026-03-09 10:00</t>
+  </si>
+  <si>
+    <t>NSE:AMBER-EQ_BEAR_1773028800_1773037800</t>
+  </si>
+  <si>
+    <t>2026-03-09 12:00</t>
+  </si>
+  <si>
+    <t>2026-03-09 12:15</t>
+  </si>
+  <si>
+    <t>NSE:HAVELLS-EQ_BEAR_1772788500_1773038700</t>
+  </si>
+  <si>
+    <t>2026-03-09 12:30</t>
+  </si>
+  <si>
+    <t>NSE:BANDHANBNK-EQ_BEAR_1773027900_1773041400</t>
+  </si>
+  <si>
+    <t>NSE:BANDHANBNK-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-09 13:00</t>
+  </si>
+  <si>
+    <t>2026-03-09 13:15</t>
+  </si>
+  <si>
+    <t>NSE:GRASIM-EQ_BEAR_1772789400_1773049500</t>
+  </si>
+  <si>
+    <t>NSE:GRASIM-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-09 15:15</t>
+  </si>
+  <si>
+    <t>2026-03-09 15:30</t>
+  </si>
+  <si>
+    <t>NSE:MARICO-EQ_BEAR_1773027900_1773049500</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;#,##0.00"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="10"/>
-      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2695,7 +2773,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2736,7 +2814,6 @@
     <xf numFmtId="4" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2746,18 +2823,16 @@
     <xf numFmtId="4" fontId="3" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -3053,27 +3128,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N278"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N287"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22" style="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18" style="19" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22" style="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="20" style="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22" style="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="18" style="18" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16" style="18" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22" style="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="10" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="16" customWidth="1"/>
+    <col min="14" max="14" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3107,7 +3182,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -3141,7 +3216,7 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
     </row>
-    <row r="3" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
@@ -3175,7 +3250,7 @@
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
     </row>
-    <row r="4" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
@@ -3195,13 +3270,13 @@
         <v>21</v>
       </c>
       <c r="G4" s="4">
-        <v>73.180000000000007</v>
+        <v>73.18</v>
       </c>
       <c r="H4" s="4">
-        <v>71.400000000000006</v>
+        <v>71.4</v>
       </c>
       <c r="I4" s="4">
-        <v>72.790000000000006</v>
+        <v>72.79</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
@@ -3209,7 +3284,7 @@
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
     </row>
-    <row r="5" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>22</v>
       </c>
@@ -3243,7 +3318,7 @@
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
     </row>
-    <row r="6" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>26</v>
       </c>
@@ -3277,7 +3352,7 @@
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
     </row>
-    <row r="7" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>29</v>
       </c>
@@ -3311,7 +3386,7 @@
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
     </row>
-    <row r="8" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>32</v>
       </c>
@@ -3345,7 +3420,7 @@
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
     </row>
-    <row r="9" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>36</v>
       </c>
@@ -3359,19 +3434,19 @@
         <v>38</v>
       </c>
       <c r="E9" s="4">
-        <v>1148.9000000000001</v>
+        <v>1148.9</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>39</v>
       </c>
       <c r="G9" s="4">
-        <v>1168.5999999999999</v>
+        <v>1168.6</v>
       </c>
       <c r="H9" s="4">
-        <v>1162.9000000000001</v>
+        <v>1162.9</v>
       </c>
       <c r="I9" s="4">
-        <v>1167.9000000000001</v>
+        <v>1167.9</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -3379,7 +3454,7 @@
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
     </row>
-    <row r="10" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
@@ -3413,7 +3488,7 @@
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
     </row>
-    <row r="11" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>44</v>
       </c>
@@ -3447,7 +3522,7 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
     </row>
-    <row r="12" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>47</v>
       </c>
@@ -3481,7 +3556,7 @@
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
     </row>
-    <row r="13" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>50</v>
       </c>
@@ -3515,7 +3590,7 @@
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
     </row>
-    <row r="14" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>55</v>
       </c>
@@ -3549,7 +3624,7 @@
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
     </row>
-    <row r="15" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>58</v>
       </c>
@@ -3569,7 +3644,7 @@
         <v>54</v>
       </c>
       <c r="G15" s="6">
-        <v>515.79999999999995</v>
+        <v>515.8</v>
       </c>
       <c r="H15" s="6">
         <v>506.7</v>
@@ -3583,7 +3658,7 @@
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
     </row>
-    <row r="16" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>61</v>
       </c>
@@ -3606,7 +3681,7 @@
         <v>627.85</v>
       </c>
       <c r="H16" s="4">
-        <v>619.29999999999995</v>
+        <v>619.3</v>
       </c>
       <c r="I16" s="4">
         <v>626.6</v>
@@ -3617,7 +3692,7 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
     </row>
-    <row r="17" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>64</v>
       </c>
@@ -3651,7 +3726,7 @@
       <c r="M17" s="5"/>
       <c r="N17" s="5"/>
     </row>
-    <row r="18" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>66</v>
       </c>
@@ -3685,7 +3760,7 @@
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
     </row>
-    <row r="19" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>70</v>
       </c>
@@ -3719,7 +3794,7 @@
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
     </row>
-    <row r="20" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>73</v>
       </c>
@@ -3753,7 +3828,7 @@
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
     </row>
-    <row r="21" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>77</v>
       </c>
@@ -3787,7 +3862,7 @@
       <c r="M21" s="5"/>
       <c r="N21" s="5"/>
     </row>
-    <row r="22" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>79</v>
       </c>
@@ -3821,7 +3896,7 @@
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
     </row>
-    <row r="23" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>82</v>
       </c>
@@ -3855,7 +3930,7 @@
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
     </row>
-    <row r="24" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>85</v>
       </c>
@@ -3889,7 +3964,7 @@
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
     </row>
-    <row r="25" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>87</v>
       </c>
@@ -3923,7 +3998,7 @@
       <c r="M25" s="5"/>
       <c r="N25" s="5"/>
     </row>
-    <row r="26" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>90</v>
       </c>
@@ -3943,10 +4018,10 @@
         <v>93</v>
       </c>
       <c r="G26" s="6">
-        <v>1198.4000000000001</v>
+        <v>1198.4</v>
       </c>
       <c r="H26" s="6">
-        <v>1194.4000000000001</v>
+        <v>1194.4</v>
       </c>
       <c r="I26" s="6">
         <v>1196.3</v>
@@ -3957,7 +4032,7 @@
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
     </row>
-    <row r="27" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>94</v>
       </c>
@@ -3971,7 +4046,7 @@
         <v>96</v>
       </c>
       <c r="E27" s="6">
-        <v>4203.3999999999996</v>
+        <v>4203.4</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>69</v>
@@ -3980,7 +4055,7 @@
         <v>4164.3</v>
       </c>
       <c r="H27" s="6">
-        <v>4134.8999999999996</v>
+        <v>4134.9</v>
       </c>
       <c r="I27" s="6">
         <v>4135.7</v>
@@ -3991,7 +4066,7 @@
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
     </row>
-    <row r="28" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>97</v>
       </c>
@@ -4025,7 +4100,7 @@
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
     </row>
-    <row r="29" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>98</v>
       </c>
@@ -4059,7 +4134,7 @@
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
     </row>
-    <row r="30" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>101</v>
       </c>
@@ -4093,7 +4168,7 @@
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
     </row>
-    <row r="31" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>104</v>
       </c>
@@ -4127,7 +4202,7 @@
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
     </row>
-    <row r="32" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>107</v>
       </c>
@@ -4161,7 +4236,7 @@
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
     </row>
-    <row r="33" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>111</v>
       </c>
@@ -4195,7 +4270,7 @@
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
     </row>
-    <row r="34" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>114</v>
       </c>
@@ -4229,7 +4304,7 @@
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
     </row>
-    <row r="35" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>117</v>
       </c>
@@ -4263,7 +4338,7 @@
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
     </row>
-    <row r="36" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>119</v>
       </c>
@@ -4297,7 +4372,7 @@
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
     </row>
-    <row r="37" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>120</v>
       </c>
@@ -4331,7 +4406,7 @@
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
     </row>
-    <row r="38" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>122</v>
       </c>
@@ -4357,7 +4432,7 @@
         <v>606.25</v>
       </c>
       <c r="I38" s="6">
-        <v>606.70000000000005</v>
+        <v>606.7</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
@@ -4365,7 +4440,7 @@
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
     </row>
-    <row r="39" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>124</v>
       </c>
@@ -4399,7 +4474,7 @@
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
     </row>
-    <row r="40" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>126</v>
       </c>
@@ -4433,7 +4508,7 @@
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
     </row>
-    <row r="41" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>128</v>
       </c>
@@ -4459,7 +4534,7 @@
         <v>1053.5</v>
       </c>
       <c r="I41" s="6">
-        <v>1053.9000000000001</v>
+        <v>1053.9</v>
       </c>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
@@ -4467,7 +4542,7 @@
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
     </row>
-    <row r="42" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>130</v>
       </c>
@@ -4501,7 +4576,7 @@
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
     </row>
-    <row r="43" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>134</v>
       </c>
@@ -4535,7 +4610,7 @@
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
     </row>
-    <row r="44" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>136</v>
       </c>
@@ -4569,7 +4644,7 @@
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
     </row>
-    <row r="45" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>137</v>
       </c>
@@ -4603,7 +4678,7 @@
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
     </row>
-    <row r="46" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>139</v>
       </c>
@@ -4639,7 +4714,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>143</v>
       </c>
@@ -4675,7 +4750,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
         <v>147</v>
       </c>
@@ -4689,7 +4764,7 @@
         <v>81</v>
       </c>
       <c r="E48" s="8">
-        <v>2193.3000000000002</v>
+        <v>2193.3</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>149</v>
@@ -4711,7 +4786,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
         <v>151</v>
       </c>
@@ -4747,7 +4822,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="50" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>154</v>
       </c>
@@ -4783,7 +4858,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
         <v>158</v>
       </c>
@@ -4819,7 +4894,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
         <v>161</v>
       </c>
@@ -4855,7 +4930,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
         <v>164</v>
       </c>
@@ -4869,7 +4944,7 @@
         <v>54</v>
       </c>
       <c r="E53" s="8">
-        <v>2223.1999999999998</v>
+        <v>2223.2</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>166</v>
@@ -4891,7 +4966,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>168</v>
       </c>
@@ -4905,13 +4980,13 @@
         <v>157</v>
       </c>
       <c r="E54" s="10">
-        <v>534.54999999999995</v>
+        <v>534.55</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>166</v>
       </c>
       <c r="G54" s="10">
-        <v>539.45000000000005</v>
+        <v>539.45</v>
       </c>
       <c r="H54" s="10">
         <v>532.15</v>
@@ -4927,7 +5002,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
         <v>170</v>
       </c>
@@ -4950,10 +5025,10 @@
         <v>2558</v>
       </c>
       <c r="H55" s="10">
-        <v>2537.6999999999998</v>
+        <v>2537.7</v>
       </c>
       <c r="I55" s="10">
-        <v>2554.8000000000002</v>
+        <v>2554.8</v>
       </c>
       <c r="J55" s="9"/>
       <c r="K55" s="9"/>
@@ -4963,7 +5038,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="9" t="s">
         <v>173</v>
       </c>
@@ -4999,7 +5074,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
         <v>176</v>
       </c>
@@ -5035,7 +5110,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="58" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
         <v>179</v>
       </c>
@@ -5071,7 +5146,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
         <v>182</v>
       </c>
@@ -5107,7 +5182,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
         <v>185</v>
       </c>
@@ -5143,7 +5218,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
         <v>186</v>
       </c>
@@ -5179,7 +5254,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="9" t="s">
         <v>190</v>
       </c>
@@ -5202,10 +5277,10 @@
         <v>4785</v>
       </c>
       <c r="H62" s="10">
-        <v>4741.8999999999996</v>
+        <v>4741.9</v>
       </c>
       <c r="I62" s="10">
-        <v>4782.6000000000004</v>
+        <v>4782.6</v>
       </c>
       <c r="J62" s="9"/>
       <c r="K62" s="9"/>
@@ -5215,7 +5290,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="9" t="s">
         <v>193</v>
       </c>
@@ -5251,7 +5326,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="64" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="9" t="s">
         <v>196</v>
       </c>
@@ -5287,7 +5362,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
         <v>200</v>
       </c>
@@ -5323,7 +5398,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="66" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
         <v>204</v>
       </c>
@@ -5359,7 +5434,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
         <v>207</v>
       </c>
@@ -5395,7 +5470,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="68" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="s">
         <v>209</v>
       </c>
@@ -5431,7 +5506,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
         <v>212</v>
       </c>
@@ -5467,7 +5542,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="11" t="s">
         <v>216</v>
       </c>
@@ -5495,13 +5570,8 @@
       <c r="I70" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="J70" s="14"/>
-      <c r="K70" s="14"/>
-      <c r="L70" s="14"/>
-      <c r="M70" s="14"/>
-      <c r="N70" s="14"/>
-    </row>
-    <row r="71" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="11" t="s">
         <v>223</v>
       </c>
@@ -5529,13 +5599,8 @@
       <c r="I71" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="J71" s="14"/>
-      <c r="K71" s="14"/>
-      <c r="L71" s="14"/>
-      <c r="M71" s="14"/>
-      <c r="N71" s="14"/>
-    </row>
-    <row r="72" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="11" t="s">
         <v>229</v>
       </c>
@@ -5563,13 +5628,8 @@
       <c r="I72" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="J72" s="14"/>
-      <c r="K72" s="14"/>
-      <c r="L72" s="14"/>
-      <c r="M72" s="14"/>
-      <c r="N72" s="14"/>
-    </row>
-    <row r="73" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="11" t="s">
         <v>235</v>
       </c>
@@ -5597,13 +5657,8 @@
       <c r="I73" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="J73" s="14"/>
-      <c r="K73" s="14"/>
-      <c r="L73" s="14"/>
-      <c r="M73" s="14"/>
-      <c r="N73" s="14"/>
-    </row>
-    <row r="74" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="11" t="s">
         <v>241</v>
       </c>
@@ -5631,13 +5686,8 @@
       <c r="I74" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="J74" s="14"/>
-      <c r="K74" s="14"/>
-      <c r="L74" s="14"/>
-      <c r="M74" s="14"/>
-      <c r="N74" s="14"/>
-    </row>
-    <row r="75" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="11" t="s">
         <v>246</v>
       </c>
@@ -5665,13 +5715,8 @@
       <c r="I75" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="J75" s="14"/>
-      <c r="K75" s="14"/>
-      <c r="L75" s="14"/>
-      <c r="M75" s="14"/>
-      <c r="N75" s="14"/>
-    </row>
-    <row r="76" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="11" t="s">
         <v>252</v>
       </c>
@@ -5699,13 +5744,8 @@
       <c r="I76" s="13" t="s">
         <v>257</v>
       </c>
-      <c r="J76" s="14"/>
-      <c r="K76" s="14"/>
-      <c r="L76" s="14"/>
-      <c r="M76" s="14"/>
-      <c r="N76" s="14"/>
-    </row>
-    <row r="77" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="11" t="s">
         <v>258</v>
       </c>
@@ -5733,13 +5773,8 @@
       <c r="I77" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="J77" s="14"/>
-      <c r="K77" s="14"/>
-      <c r="L77" s="14"/>
-      <c r="M77" s="14"/>
-      <c r="N77" s="14"/>
-    </row>
-    <row r="78" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="11" t="s">
         <v>264</v>
       </c>
@@ -5767,13 +5802,8 @@
       <c r="I78" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="J78" s="14"/>
-      <c r="K78" s="14"/>
-      <c r="L78" s="14"/>
-      <c r="M78" s="14"/>
-      <c r="N78" s="14"/>
-    </row>
-    <row r="79" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="11" t="s">
         <v>271</v>
       </c>
@@ -5801,13 +5831,8 @@
       <c r="I79" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="J79" s="14"/>
-      <c r="K79" s="14"/>
-      <c r="L79" s="14"/>
-      <c r="M79" s="14"/>
-      <c r="N79" s="14"/>
-    </row>
-    <row r="80" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="11" t="s">
         <v>277</v>
       </c>
@@ -5835,13 +5860,8 @@
       <c r="I80" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="J80" s="14"/>
-      <c r="K80" s="14"/>
-      <c r="L80" s="14"/>
-      <c r="M80" s="14"/>
-      <c r="N80" s="14"/>
-    </row>
-    <row r="81" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="11" t="s">
         <v>283</v>
       </c>
@@ -5869,13 +5889,8 @@
       <c r="I81" s="13" t="s">
         <v>289</v>
       </c>
-      <c r="J81" s="14"/>
-      <c r="K81" s="14"/>
-      <c r="L81" s="14"/>
-      <c r="M81" s="14"/>
-      <c r="N81" s="14"/>
-    </row>
-    <row r="82" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="82" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="11" t="s">
         <v>290</v>
       </c>
@@ -5903,13 +5918,8 @@
       <c r="I82" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="J82" s="14"/>
-      <c r="K82" s="14"/>
-      <c r="L82" s="14"/>
-      <c r="M82" s="14"/>
-      <c r="N82" s="14"/>
-    </row>
-    <row r="83" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="11" t="s">
         <v>296</v>
       </c>
@@ -5937,13 +5947,8 @@
       <c r="I83" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="J83" s="14"/>
-      <c r="K83" s="14"/>
-      <c r="L83" s="14"/>
-      <c r="M83" s="14"/>
-      <c r="N83" s="14"/>
-    </row>
-    <row r="84" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="11" t="s">
         <v>303</v>
       </c>
@@ -5971,115 +5976,95 @@
       <c r="I84" s="13" t="s">
         <v>307</v>
       </c>
-      <c r="J84" s="14"/>
-      <c r="K84" s="14"/>
-      <c r="L84" s="14"/>
-      <c r="M84" s="14"/>
-      <c r="N84" s="14"/>
-    </row>
-    <row r="85" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="15" t="s">
+    </row>
+    <row r="85" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="14" t="s">
         <v>308</v>
       </c>
-      <c r="B85" s="16" t="s">
+      <c r="B85" s="15" t="s">
         <v>309</v>
       </c>
-      <c r="C85" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D85" s="16" t="s">
+      <c r="C85" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D85" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="E85" s="17" t="s">
+      <c r="E85" s="16" t="s">
         <v>310</v>
       </c>
-      <c r="F85" s="16" t="s">
+      <c r="F85" s="15" t="s">
         <v>311</v>
       </c>
-      <c r="G85" s="17" t="s">
+      <c r="G85" s="16" t="s">
         <v>312</v>
       </c>
-      <c r="H85" s="17" t="s">
+      <c r="H85" s="16" t="s">
         <v>313</v>
       </c>
-      <c r="I85" s="17" t="s">
+      <c r="I85" s="16" t="s">
         <v>314</v>
       </c>
-      <c r="J85" s="14"/>
-      <c r="K85" s="14"/>
-      <c r="L85" s="14"/>
-      <c r="M85" s="14"/>
-      <c r="N85" s="14"/>
-    </row>
-    <row r="86" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="15" t="s">
+    </row>
+    <row r="86" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B86" s="16" t="s">
+      <c r="B86" s="15" t="s">
         <v>316</v>
       </c>
-      <c r="C86" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D86" s="16" t="s">
+      <c r="C86" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D86" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="E86" s="17" t="s">
+      <c r="E86" s="16" t="s">
         <v>317</v>
       </c>
-      <c r="F86" s="16" t="s">
+      <c r="F86" s="15" t="s">
         <v>311</v>
       </c>
-      <c r="G86" s="17" t="s">
+      <c r="G86" s="16" t="s">
         <v>318</v>
       </c>
-      <c r="H86" s="17" t="s">
+      <c r="H86" s="16" t="s">
         <v>319</v>
       </c>
-      <c r="I86" s="17" t="s">
+      <c r="I86" s="16" t="s">
         <v>319</v>
       </c>
-      <c r="J86" s="14"/>
-      <c r="K86" s="14"/>
-      <c r="L86" s="14"/>
-      <c r="M86" s="14"/>
-      <c r="N86" s="14"/>
-    </row>
-    <row r="87" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="15" t="s">
+    </row>
+    <row r="87" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="B87" s="16" t="s">
+      <c r="B87" s="15" t="s">
         <v>321</v>
       </c>
-      <c r="C87" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D87" s="16" t="s">
+      <c r="C87" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D87" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="E87" s="17" t="s">
+      <c r="E87" s="16" t="s">
         <v>322</v>
       </c>
-      <c r="F87" s="16" t="s">
+      <c r="F87" s="15" t="s">
         <v>311</v>
       </c>
-      <c r="G87" s="17" t="s">
+      <c r="G87" s="16" t="s">
         <v>323</v>
       </c>
-      <c r="H87" s="17" t="s">
+      <c r="H87" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="I87" s="17" t="s">
+      <c r="I87" s="16" t="s">
         <v>325</v>
       </c>
-      <c r="J87" s="14"/>
-      <c r="K87" s="14"/>
-      <c r="L87" s="14"/>
-      <c r="M87" s="14"/>
-      <c r="N87" s="14"/>
-    </row>
-    <row r="88" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="11" t="s">
         <v>326</v>
       </c>
@@ -6107,47 +6092,37 @@
       <c r="I88" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="J88" s="14"/>
-      <c r="K88" s="14"/>
-      <c r="L88" s="14"/>
-      <c r="M88" s="14"/>
-      <c r="N88" s="14"/>
-    </row>
-    <row r="89" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="15" t="s">
+    </row>
+    <row r="89" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="B89" s="16" t="s">
+      <c r="B89" s="15" t="s">
         <v>333</v>
       </c>
-      <c r="C89" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D89" s="16" t="s">
+      <c r="C89" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D89" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="E89" s="17" t="s">
+      <c r="E89" s="16" t="s">
         <v>334</v>
       </c>
-      <c r="F89" s="16" t="s">
+      <c r="F89" s="15" t="s">
         <v>335</v>
       </c>
-      <c r="G89" s="17" t="s">
+      <c r="G89" s="16" t="s">
         <v>336</v>
       </c>
-      <c r="H89" s="17" t="s">
+      <c r="H89" s="16" t="s">
         <v>337</v>
       </c>
-      <c r="I89" s="17" t="s">
+      <c r="I89" s="16" t="s">
         <v>337</v>
       </c>
-      <c r="J89" s="14"/>
-      <c r="K89" s="14"/>
-      <c r="L89" s="14"/>
-      <c r="M89" s="14"/>
-      <c r="N89" s="14"/>
-    </row>
-    <row r="90" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="90" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="11" t="s">
         <v>338</v>
       </c>
@@ -6175,47 +6150,37 @@
       <c r="I90" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="J90" s="14"/>
-      <c r="K90" s="14"/>
-      <c r="L90" s="14"/>
-      <c r="M90" s="14"/>
-      <c r="N90" s="14"/>
-    </row>
-    <row r="91" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="15" t="s">
+    </row>
+    <row r="91" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="14" t="s">
         <v>345</v>
       </c>
-      <c r="B91" s="16" t="s">
+      <c r="B91" s="15" t="s">
         <v>346</v>
       </c>
-      <c r="C91" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D91" s="16" t="s">
+      <c r="C91" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D91" s="15" t="s">
         <v>335</v>
       </c>
-      <c r="E91" s="17" t="s">
+      <c r="E91" s="16" t="s">
         <v>347</v>
       </c>
-      <c r="F91" s="16" t="s">
+      <c r="F91" s="15" t="s">
         <v>348</v>
       </c>
-      <c r="G91" s="17" t="s">
+      <c r="G91" s="16" t="s">
         <v>349</v>
       </c>
-      <c r="H91" s="17" t="s">
+      <c r="H91" s="16" t="s">
         <v>350</v>
       </c>
-      <c r="I91" s="17" t="s">
+      <c r="I91" s="16" t="s">
         <v>351</v>
       </c>
-      <c r="J91" s="14"/>
-      <c r="K91" s="14"/>
-      <c r="L91" s="14"/>
-      <c r="M91" s="14"/>
-      <c r="N91" s="14"/>
-    </row>
-    <row r="92" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="92" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="11" t="s">
         <v>352</v>
       </c>
@@ -6243,13 +6208,8 @@
       <c r="I92" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="J92" s="14"/>
-      <c r="K92" s="14"/>
-      <c r="L92" s="14"/>
-      <c r="M92" s="14"/>
-      <c r="N92" s="14"/>
-    </row>
-    <row r="93" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="93" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="11" t="s">
         <v>357</v>
       </c>
@@ -6277,13 +6237,8 @@
       <c r="I93" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="J93" s="14"/>
-      <c r="K93" s="14"/>
-      <c r="L93" s="14"/>
-      <c r="M93" s="14"/>
-      <c r="N93" s="14"/>
-    </row>
-    <row r="94" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="94" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="11" t="s">
         <v>364</v>
       </c>
@@ -6311,47 +6266,37 @@
       <c r="I94" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="J94" s="14"/>
-      <c r="K94" s="14"/>
-      <c r="L94" s="14"/>
-      <c r="M94" s="14"/>
-      <c r="N94" s="14"/>
-    </row>
-    <row r="95" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="15" t="s">
+    </row>
+    <row r="95" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="14" t="s">
         <v>370</v>
       </c>
-      <c r="B95" s="16" t="s">
+      <c r="B95" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="C95" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D95" s="16" t="s">
+      <c r="C95" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D95" s="15" t="s">
         <v>371</v>
       </c>
-      <c r="E95" s="17" t="s">
+      <c r="E95" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="F95" s="16" t="s">
+      <c r="F95" s="15" t="s">
         <v>373</v>
       </c>
-      <c r="G95" s="17" t="s">
+      <c r="G95" s="16" t="s">
         <v>374</v>
       </c>
-      <c r="H95" s="17" t="s">
+      <c r="H95" s="16" t="s">
         <v>375</v>
       </c>
-      <c r="I95" s="17" t="s">
+      <c r="I95" s="16" t="s">
         <v>376</v>
       </c>
-      <c r="J95" s="14"/>
-      <c r="K95" s="14"/>
-      <c r="L95" s="14"/>
-      <c r="M95" s="14"/>
-      <c r="N95" s="14"/>
-    </row>
-    <row r="96" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="96" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="11" t="s">
         <v>377</v>
       </c>
@@ -6379,13 +6324,8 @@
       <c r="I96" s="13" t="s">
         <v>383</v>
       </c>
-      <c r="J96" s="14"/>
-      <c r="K96" s="14"/>
-      <c r="L96" s="14"/>
-      <c r="M96" s="14"/>
-      <c r="N96" s="14"/>
-    </row>
-    <row r="97" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="11" t="s">
         <v>384</v>
       </c>
@@ -6413,13 +6353,8 @@
       <c r="I97" s="13" t="s">
         <v>390</v>
       </c>
-      <c r="J97" s="14"/>
-      <c r="K97" s="14"/>
-      <c r="L97" s="14"/>
-      <c r="M97" s="14"/>
-      <c r="N97" s="14"/>
-    </row>
-    <row r="98" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="98" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="11" t="s">
         <v>391</v>
       </c>
@@ -6447,13 +6382,8 @@
       <c r="I98" s="13" t="s">
         <v>394</v>
       </c>
-      <c r="J98" s="14"/>
-      <c r="K98" s="14"/>
-      <c r="L98" s="14"/>
-      <c r="M98" s="14"/>
-      <c r="N98" s="14"/>
-    </row>
-    <row r="99" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="99" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="11" t="s">
         <v>396</v>
       </c>
@@ -6481,13 +6411,8 @@
       <c r="I99" s="13" t="s">
         <v>401</v>
       </c>
-      <c r="J99" s="14"/>
-      <c r="K99" s="14"/>
-      <c r="L99" s="14"/>
-      <c r="M99" s="14"/>
-      <c r="N99" s="14"/>
-    </row>
-    <row r="100" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="11" t="s">
         <v>402</v>
       </c>
@@ -6515,13 +6440,8 @@
       <c r="I100" s="13" t="s">
         <v>407</v>
       </c>
-      <c r="J100" s="14"/>
-      <c r="K100" s="14"/>
-      <c r="L100" s="14"/>
-      <c r="M100" s="14"/>
-      <c r="N100" s="14"/>
-    </row>
-    <row r="101" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="101" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="11" t="s">
         <v>408</v>
       </c>
@@ -6549,13 +6469,8 @@
       <c r="I101" s="13" t="s">
         <v>414</v>
       </c>
-      <c r="J101" s="14"/>
-      <c r="K101" s="14"/>
-      <c r="L101" s="14"/>
-      <c r="M101" s="14"/>
-      <c r="N101" s="14"/>
-    </row>
-    <row r="102" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="11" t="s">
         <v>415</v>
       </c>
@@ -6583,13 +6498,8 @@
       <c r="I102" s="13" t="s">
         <v>421</v>
       </c>
-      <c r="J102" s="14"/>
-      <c r="K102" s="14"/>
-      <c r="L102" s="14"/>
-      <c r="M102" s="14"/>
-      <c r="N102" s="14"/>
-    </row>
-    <row r="103" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="103" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="11" t="s">
         <v>422</v>
       </c>
@@ -6617,13 +6527,8 @@
       <c r="I103" s="13" t="s">
         <v>425</v>
       </c>
-      <c r="J103" s="14"/>
-      <c r="K103" s="14"/>
-      <c r="L103" s="14"/>
-      <c r="M103" s="14"/>
-      <c r="N103" s="14"/>
-    </row>
-    <row r="104" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="11" t="s">
         <v>426</v>
       </c>
@@ -6651,13 +6556,8 @@
       <c r="I104" s="13" t="s">
         <v>430</v>
       </c>
-      <c r="J104" s="14"/>
-      <c r="K104" s="14"/>
-      <c r="L104" s="14"/>
-      <c r="M104" s="14"/>
-      <c r="N104" s="14"/>
-    </row>
-    <row r="105" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
         <v>431</v>
       </c>
@@ -6693,7 +6593,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="106" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
         <v>435</v>
       </c>
@@ -6729,7 +6629,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="107" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
         <v>438</v>
       </c>
@@ -6765,7 +6665,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="108" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
         <v>440</v>
       </c>
@@ -6785,10 +6685,10 @@
         <v>433</v>
       </c>
       <c r="G108" s="8">
-        <v>325.39999999999998</v>
+        <v>325.4</v>
       </c>
       <c r="H108" s="8">
-        <v>322.64999999999998</v>
+        <v>322.65</v>
       </c>
       <c r="I108" s="8">
         <v>323</v>
@@ -6801,7 +6701,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="109" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" s="9" t="s">
         <v>442</v>
       </c>
@@ -6837,7 +6737,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="110" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" s="9" t="s">
         <v>445</v>
       </c>
@@ -6873,7 +6773,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="111" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
         <v>447</v>
       </c>
@@ -6909,7 +6809,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="112" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" s="9" t="s">
         <v>449</v>
       </c>
@@ -6945,7 +6845,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="113" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
         <v>452</v>
       </c>
@@ -6959,13 +6859,13 @@
         <v>454</v>
       </c>
       <c r="E113" s="8">
-        <v>526.70000000000005</v>
+        <v>526.7</v>
       </c>
       <c r="F113" s="7" t="s">
         <v>455</v>
       </c>
       <c r="G113" s="8">
-        <v>529.70000000000005</v>
+        <v>529.7</v>
       </c>
       <c r="H113" s="8">
         <v>526</v>
@@ -6981,7 +6881,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="114" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
         <v>457</v>
       </c>
@@ -7017,7 +6917,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="115" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
         <v>461</v>
       </c>
@@ -7053,7 +6953,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="116" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
         <v>463</v>
       </c>
@@ -7089,7 +6989,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="117" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
         <v>468</v>
       </c>
@@ -7103,7 +7003,7 @@
         <v>371</v>
       </c>
       <c r="E117" s="8">
-        <v>158.19999999999999</v>
+        <v>158.2</v>
       </c>
       <c r="F117" s="7" t="s">
         <v>466</v>
@@ -7112,7 +7012,7 @@
         <v>156.1</v>
       </c>
       <c r="H117" s="8">
-        <v>154.88999999999999</v>
+        <v>154.89</v>
       </c>
       <c r="I117" s="8">
         <v>155.09</v>
@@ -7125,7 +7025,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="118" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" s="9" t="s">
         <v>469</v>
       </c>
@@ -7161,7 +7061,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="119" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
         <v>473</v>
       </c>
@@ -7197,7 +7097,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="120" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" s="9" t="s">
         <v>476</v>
       </c>
@@ -7217,7 +7117,7 @@
         <v>475</v>
       </c>
       <c r="G120" s="10">
-        <v>2049.3000000000002</v>
+        <v>2049.3</v>
       </c>
       <c r="H120" s="10">
         <v>2039</v>
@@ -7233,7 +7133,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="121" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" s="9" t="s">
         <v>480</v>
       </c>
@@ -7253,13 +7153,13 @@
         <v>475</v>
       </c>
       <c r="G121" s="10">
-        <v>1177.0999999999999</v>
+        <v>1177.1</v>
       </c>
       <c r="H121" s="10">
         <v>1171</v>
       </c>
       <c r="I121" s="10">
-        <v>1176.4000000000001</v>
+        <v>1176.4</v>
       </c>
       <c r="J121" s="9"/>
       <c r="K121" s="9"/>
@@ -7269,7 +7169,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="122" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" s="7" t="s">
         <v>482</v>
       </c>
@@ -7305,7 +7205,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="123" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
         <v>485</v>
       </c>
@@ -7341,7 +7241,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="124" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" s="7" t="s">
         <v>488</v>
       </c>
@@ -7377,7 +7277,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="125" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" s="9" t="s">
         <v>489</v>
       </c>
@@ -7413,7 +7313,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="126" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" s="9" t="s">
         <v>492</v>
       </c>
@@ -7433,10 +7333,10 @@
         <v>487</v>
       </c>
       <c r="G126" s="10">
-        <v>1238.4000000000001</v>
+        <v>1238.4</v>
       </c>
       <c r="H126" s="10">
-        <v>1226.5999999999999</v>
+        <v>1226.6</v>
       </c>
       <c r="I126" s="10">
         <v>1235</v>
@@ -7449,7 +7349,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="127" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A127" s="9" t="s">
         <v>493</v>
       </c>
@@ -7485,7 +7385,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="128" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A128" s="9" t="s">
         <v>496</v>
       </c>
@@ -7499,19 +7399,19 @@
         <v>470</v>
       </c>
       <c r="E128" s="10">
-        <v>526.20000000000005</v>
+        <v>526.2</v>
       </c>
       <c r="F128" s="9" t="s">
         <v>487</v>
       </c>
       <c r="G128" s="10">
-        <v>531.45000000000005</v>
+        <v>531.45</v>
       </c>
       <c r="H128" s="10">
         <v>528.1</v>
       </c>
       <c r="I128" s="10">
-        <v>531.04999999999995</v>
+        <v>531.05</v>
       </c>
       <c r="J128" s="9"/>
       <c r="K128" s="9"/>
@@ -7521,7 +7421,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="129" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" s="9" t="s">
         <v>498</v>
       </c>
@@ -7557,7 +7457,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="130" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A130" s="9" t="s">
         <v>500</v>
       </c>
@@ -7593,7 +7493,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="131" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A131" s="9" t="s">
         <v>503</v>
       </c>
@@ -7629,7 +7529,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="132" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A132" s="9" t="s">
         <v>504</v>
       </c>
@@ -7665,7 +7565,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="133" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A133" s="9" t="s">
         <v>506</v>
       </c>
@@ -7701,7 +7601,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="134" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A134" s="9" t="s">
         <v>508</v>
       </c>
@@ -7721,13 +7621,13 @@
         <v>509</v>
       </c>
       <c r="G134" s="10">
-        <v>1249.9000000000001</v>
+        <v>1249.9</v>
       </c>
       <c r="H134" s="10">
         <v>1237.7</v>
       </c>
       <c r="I134" s="10">
-        <v>1245.9000000000001</v>
+        <v>1245.9</v>
       </c>
       <c r="J134" s="9"/>
       <c r="K134" s="9"/>
@@ -7737,7 +7637,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="135" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A135" s="9" t="s">
         <v>511</v>
       </c>
@@ -7757,7 +7657,7 @@
         <v>509</v>
       </c>
       <c r="G135" s="10">
-        <v>1270.0999999999999</v>
+        <v>1270.1</v>
       </c>
       <c r="H135" s="10">
         <v>1257.3</v>
@@ -7773,7 +7673,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="136" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A136" s="9" t="s">
         <v>512</v>
       </c>
@@ -7796,10 +7696,10 @@
         <v>312.75</v>
       </c>
       <c r="H136" s="10">
-        <v>307.64999999999998</v>
+        <v>307.65</v>
       </c>
       <c r="I136" s="10">
-        <v>311.60000000000002</v>
+        <v>311.6</v>
       </c>
       <c r="J136" s="9"/>
       <c r="K136" s="9"/>
@@ -7809,7 +7709,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="137" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A137" s="9" t="s">
         <v>514</v>
       </c>
@@ -7845,7 +7745,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="138" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A138" s="9" t="s">
         <v>518</v>
       </c>
@@ -7881,7 +7781,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="139" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A139" s="9" t="s">
         <v>521</v>
       </c>
@@ -7917,7 +7817,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="140" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A140" s="9" t="s">
         <v>524</v>
       </c>
@@ -7953,7 +7853,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="141" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A141" s="9" t="s">
         <v>528</v>
       </c>
@@ -7967,19 +7867,19 @@
         <v>479</v>
       </c>
       <c r="E141" s="10">
-        <v>594.20000000000005</v>
+        <v>594.2</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>526</v>
       </c>
       <c r="G141" s="10">
-        <v>621.29999999999995</v>
+        <v>621.3</v>
       </c>
       <c r="H141" s="10">
         <v>616.4</v>
       </c>
       <c r="I141" s="10">
-        <v>619.54999999999995</v>
+        <v>619.55</v>
       </c>
       <c r="J141" s="9"/>
       <c r="K141" s="9"/>
@@ -7989,7 +7889,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="142" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A142" s="9" t="s">
         <v>530</v>
       </c>
@@ -8025,7 +7925,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="143" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
         <v>532</v>
       </c>
@@ -8039,13 +7939,13 @@
         <v>533</v>
       </c>
       <c r="E143" s="8">
-        <v>633.70000000000005</v>
+        <v>633.7</v>
       </c>
       <c r="F143" s="7" t="s">
         <v>534</v>
       </c>
       <c r="G143" s="8">
-        <v>612.45000000000005</v>
+        <v>612.45</v>
       </c>
       <c r="H143" s="8">
         <v>607.75</v>
@@ -8061,7 +7961,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="144" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A144" s="9" t="s">
         <v>536</v>
       </c>
@@ -8097,7 +7997,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="145" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
         <v>538</v>
       </c>
@@ -8117,13 +8017,13 @@
         <v>535</v>
       </c>
       <c r="G145" s="8">
-        <v>1135.5999999999999</v>
+        <v>1135.6</v>
       </c>
       <c r="H145" s="8">
         <v>1126.2</v>
       </c>
       <c r="I145" s="8">
-        <v>1127.4000000000001</v>
+        <v>1127.4</v>
       </c>
       <c r="J145" s="7"/>
       <c r="K145" s="7"/>
@@ -8133,7 +8033,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="146" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A146" s="7" t="s">
         <v>541</v>
       </c>
@@ -8169,7 +8069,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="147" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A147" s="9" t="s">
         <v>544</v>
       </c>
@@ -8183,13 +8083,13 @@
         <v>546</v>
       </c>
       <c r="E147" s="10">
-        <v>1125.5999999999999</v>
+        <v>1125.6</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>543</v>
       </c>
       <c r="G147" s="10">
-        <v>1130.9000000000001</v>
+        <v>1130.9</v>
       </c>
       <c r="H147" s="10">
         <v>1122.7</v>
@@ -8205,7 +8105,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="148" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A148" s="7" t="s">
         <v>548</v>
       </c>
@@ -8219,7 +8119,7 @@
         <v>450</v>
       </c>
       <c r="E148" s="8">
-        <v>2418.3000000000002</v>
+        <v>2418.3</v>
       </c>
       <c r="F148" s="7" t="s">
         <v>547</v>
@@ -8231,7 +8131,7 @@
         <v>2400</v>
       </c>
       <c r="I148" s="8">
-        <v>2401.1999999999998</v>
+        <v>2401.2</v>
       </c>
       <c r="J148" s="7"/>
       <c r="K148" s="7"/>
@@ -8241,7 +8141,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="149" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A149" s="9" t="s">
         <v>551</v>
       </c>
@@ -8267,7 +8167,7 @@
         <v>158.78</v>
       </c>
       <c r="I149" s="10">
-        <v>161.16999999999999</v>
+        <v>161.17</v>
       </c>
       <c r="J149" s="9"/>
       <c r="K149" s="9"/>
@@ -8277,7 +8177,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="150" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150" s="9" t="s">
         <v>555</v>
       </c>
@@ -8291,7 +8191,7 @@
         <v>509</v>
       </c>
       <c r="E150" s="10">
-        <v>2062.1999999999998</v>
+        <v>2062.2</v>
       </c>
       <c r="F150" s="9" t="s">
         <v>556</v>
@@ -8313,7 +8213,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="151" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A151" s="9" t="s">
         <v>558</v>
       </c>
@@ -8349,7 +8249,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="152" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A152" s="9" t="s">
         <v>561</v>
       </c>
@@ -8363,7 +8263,7 @@
         <v>563</v>
       </c>
       <c r="E152" s="10">
-        <v>1208.0999999999999</v>
+        <v>1208.1</v>
       </c>
       <c r="F152" s="9" t="s">
         <v>559</v>
@@ -8385,7 +8285,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="153" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" s="9" t="s">
         <v>565</v>
       </c>
@@ -8421,7 +8321,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="154" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" s="9" t="s">
         <v>567</v>
       </c>
@@ -8457,7 +8357,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="155" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A155" s="9" t="s">
         <v>570</v>
       </c>
@@ -8480,10 +8380,10 @@
         <v>2088.9</v>
       </c>
       <c r="H155" s="10">
-        <v>2079.1999999999998</v>
+        <v>2079.2</v>
       </c>
       <c r="I155" s="10">
-        <v>2086.6999999999998</v>
+        <v>2086.7</v>
       </c>
       <c r="J155" s="9"/>
       <c r="K155" s="9"/>
@@ -8493,7 +8393,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="156" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A156" s="9" t="s">
         <v>571</v>
       </c>
@@ -8529,7 +8429,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="157" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" s="9" t="s">
         <v>573</v>
       </c>
@@ -8543,7 +8443,7 @@
         <v>563</v>
       </c>
       <c r="E157" s="10">
-        <v>624.04999999999995</v>
+        <v>624.05</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>568</v>
@@ -8552,7 +8452,7 @@
         <v>624.1</v>
       </c>
       <c r="H157" s="10">
-        <v>618.45000000000005</v>
+        <v>618.45</v>
       </c>
       <c r="I157" s="10">
         <v>624</v>
@@ -8565,7 +8465,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="158" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A158" s="9" t="s">
         <v>575</v>
       </c>
@@ -8585,10 +8485,10 @@
         <v>568</v>
       </c>
       <c r="G158" s="10">
-        <v>542.70000000000005</v>
+        <v>542.7</v>
       </c>
       <c r="H158" s="10">
-        <v>540.04999999999995</v>
+        <v>540.05</v>
       </c>
       <c r="I158" s="10">
         <v>541.25</v>
@@ -8601,7 +8501,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="159" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A159" s="9" t="s">
         <v>577</v>
       </c>
@@ -8615,7 +8515,7 @@
         <v>479</v>
       </c>
       <c r="E159" s="10">
-        <v>594.20000000000005</v>
+        <v>594.2</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>569</v>
@@ -8637,7 +8537,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="160" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A160" s="9" t="s">
         <v>579</v>
       </c>
@@ -8651,7 +8551,7 @@
         <v>509</v>
       </c>
       <c r="E160" s="10">
-        <v>2062.1999999999998</v>
+        <v>2062.2</v>
       </c>
       <c r="F160" s="9" t="s">
         <v>568</v>
@@ -8663,7 +8563,7 @@
         <v>2139</v>
       </c>
       <c r="I160" s="10">
-        <v>2159.3000000000002</v>
+        <v>2159.3</v>
       </c>
       <c r="J160" s="9"/>
       <c r="K160" s="9"/>
@@ -8673,7 +8573,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="161" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A161" s="9" t="s">
         <v>580</v>
       </c>
@@ -8687,16 +8587,16 @@
         <v>526</v>
       </c>
       <c r="E161" s="10">
-        <v>2216.1999999999998</v>
+        <v>2216.2</v>
       </c>
       <c r="F161" s="9" t="s">
         <v>581</v>
       </c>
       <c r="G161" s="10">
-        <v>2247.6999999999998</v>
+        <v>2247.7</v>
       </c>
       <c r="H161" s="10">
-        <v>2234.3000000000002</v>
+        <v>2234.3</v>
       </c>
       <c r="I161" s="10">
         <v>2242.4</v>
@@ -8709,7 +8609,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="162" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A162" s="7" t="s">
         <v>583</v>
       </c>
@@ -8745,7 +8645,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="163" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A163" s="9" t="s">
         <v>585</v>
       </c>
@@ -8781,7 +8681,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="164" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A164" s="9" t="s">
         <v>586</v>
       </c>
@@ -8817,7 +8717,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="165" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A165" s="9" t="s">
         <v>588</v>
       </c>
@@ -8853,7 +8753,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="166" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A166" s="9" t="s">
         <v>590</v>
       </c>
@@ -8873,10 +8773,10 @@
         <v>581</v>
       </c>
       <c r="G166" s="10">
-        <v>130.69999999999999</v>
+        <v>130.7</v>
       </c>
       <c r="H166" s="10">
-        <v>128.61000000000001</v>
+        <v>128.61</v>
       </c>
       <c r="I166" s="10">
         <v>129.65</v>
@@ -8889,7 +8789,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="167" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A167" s="9" t="s">
         <v>591</v>
       </c>
@@ -8925,7 +8825,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="168" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A168" s="9" t="s">
         <v>594</v>
       </c>
@@ -8961,7 +8861,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="169" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A169" s="9" t="s">
         <v>596</v>
       </c>
@@ -8975,7 +8875,7 @@
         <v>572</v>
       </c>
       <c r="E169" s="10">
-        <v>150.11000000000001</v>
+        <v>150.11</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>581</v>
@@ -8987,7 +8887,7 @@
         <v>151.22</v>
       </c>
       <c r="I169" s="10">
-        <v>153.52000000000001</v>
+        <v>153.52</v>
       </c>
       <c r="J169" s="9"/>
       <c r="K169" s="9"/>
@@ -8997,7 +8897,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="170" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A170" s="9" t="s">
         <v>598</v>
       </c>
@@ -9033,7 +8933,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="171" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A171" s="9" t="s">
         <v>600</v>
       </c>
@@ -9047,7 +8947,7 @@
         <v>546</v>
       </c>
       <c r="E171" s="10">
-        <v>1078.4000000000001</v>
+        <v>1078.4</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>581</v>
@@ -9069,7 +8969,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="172" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A172" s="9" t="s">
         <v>601</v>
       </c>
@@ -9105,7 +9005,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="173" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A173" s="9" t="s">
         <v>604</v>
       </c>
@@ -9119,7 +9019,7 @@
         <v>563</v>
       </c>
       <c r="E173" s="10">
-        <v>624.04999999999995</v>
+        <v>624.05</v>
       </c>
       <c r="F173" s="9" t="s">
         <v>582</v>
@@ -9131,7 +9031,7 @@
         <v>620.5</v>
       </c>
       <c r="I173" s="10">
-        <v>628.54999999999995</v>
+        <v>628.55</v>
       </c>
       <c r="J173" s="9"/>
       <c r="K173" s="9"/>
@@ -9141,7 +9041,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="174" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A174" s="9" t="s">
         <v>606</v>
       </c>
@@ -9177,7 +9077,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="175" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A175" s="9" t="s">
         <v>608</v>
       </c>
@@ -9213,7 +9113,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="176" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A176" s="9" t="s">
         <v>609</v>
       </c>
@@ -9249,7 +9149,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="177" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A177" s="9" t="s">
         <v>612</v>
       </c>
@@ -9285,7 +9185,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="178" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A178" s="9" t="s">
         <v>613</v>
       </c>
@@ -9321,7 +9221,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="179" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
         <v>616</v>
       </c>
@@ -9357,7 +9257,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="180" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A180" s="9" t="s">
         <v>620</v>
       </c>
@@ -9393,7 +9293,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="181" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
         <v>623</v>
       </c>
@@ -9429,7 +9329,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="182" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A182" s="9" t="s">
         <v>626</v>
       </c>
@@ -9465,7 +9365,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="183" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
         <v>630</v>
       </c>
@@ -9501,7 +9401,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="184" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A184" s="9" t="s">
         <v>633</v>
       </c>
@@ -9537,7 +9437,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="185" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A185" s="9" t="s">
         <v>636</v>
       </c>
@@ -9573,7 +9473,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="186" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A186" s="9" t="s">
         <v>639</v>
       </c>
@@ -9587,7 +9487,7 @@
         <v>509</v>
       </c>
       <c r="E186" s="10">
-        <v>2062.1999999999998</v>
+        <v>2062.2</v>
       </c>
       <c r="F186" s="9" t="s">
         <v>637</v>
@@ -9609,7 +9509,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="187" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A187" s="9" t="s">
         <v>640</v>
       </c>
@@ -9623,7 +9523,7 @@
         <v>509</v>
       </c>
       <c r="E187" s="10">
-        <v>133.52000000000001</v>
+        <v>133.52</v>
       </c>
       <c r="F187" s="9" t="s">
         <v>637</v>
@@ -9632,7 +9532,7 @@
         <v>135.65</v>
       </c>
       <c r="H187" s="10">
-        <v>134.94999999999999</v>
+        <v>134.95</v>
       </c>
       <c r="I187" s="10">
         <v>135.35</v>
@@ -9645,7 +9545,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="188" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A188" s="9" t="s">
         <v>642</v>
       </c>
@@ -9671,7 +9571,7 @@
         <v>543.15</v>
       </c>
       <c r="I188" s="10">
-        <v>545.29999999999995</v>
+        <v>545.3</v>
       </c>
       <c r="J188" s="9"/>
       <c r="K188" s="9"/>
@@ -9681,7 +9581,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="189" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A189" s="9" t="s">
         <v>643</v>
       </c>
@@ -9717,7 +9617,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="190" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A190" s="9" t="s">
         <v>644</v>
       </c>
@@ -9753,7 +9653,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="191" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
         <v>648</v>
       </c>
@@ -9779,7 +9679,7 @@
         <v>130.13</v>
       </c>
       <c r="I191" s="8">
-        <v>130.13999999999999</v>
+        <v>130.14</v>
       </c>
       <c r="J191" s="7"/>
       <c r="K191" s="7"/>
@@ -9789,7 +9689,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="192" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A192" s="9" t="s">
         <v>650</v>
       </c>
@@ -9825,7 +9725,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="193" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A193" s="9" t="s">
         <v>652</v>
       </c>
@@ -9839,13 +9739,13 @@
         <v>628</v>
       </c>
       <c r="E193" s="10">
-        <v>2215.1999999999998</v>
+        <v>2215.2</v>
       </c>
       <c r="F193" s="9" t="s">
         <v>653</v>
       </c>
       <c r="G193" s="10">
-        <v>2241.8000000000002</v>
+        <v>2241.8</v>
       </c>
       <c r="H193" s="10">
         <v>2224.4</v>
@@ -9861,7 +9761,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="194" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A194" s="7" t="s">
         <v>655</v>
       </c>
@@ -9897,7 +9797,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="195" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
         <v>657</v>
       </c>
@@ -9933,7 +9833,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="196" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A196" s="7" t="s">
         <v>658</v>
       </c>
@@ -9959,7 +9859,7 @@
         <v>278</v>
       </c>
       <c r="I196" s="8">
-        <v>289.60000000000002</v>
+        <v>289.6</v>
       </c>
       <c r="J196" s="7"/>
       <c r="K196" s="7"/>
@@ -9969,7 +9869,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="197" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
         <v>660</v>
       </c>
@@ -10005,7 +9905,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="198" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A198" s="7" t="s">
         <v>663</v>
       </c>
@@ -10041,7 +9941,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="199" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
         <v>665</v>
       </c>
@@ -10064,7 +9964,7 @@
         <v>162.4</v>
       </c>
       <c r="H199" s="8">
-        <v>160.69999999999999</v>
+        <v>160.7</v>
       </c>
       <c r="I199" s="8">
         <v>160.78</v>
@@ -10077,7 +9977,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="200" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A200" s="7" t="s">
         <v>666</v>
       </c>
@@ -10113,7 +10013,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="201" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A201" s="9" t="s">
         <v>668</v>
       </c>
@@ -10149,7 +10049,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="202" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A202" s="7" t="s">
         <v>671</v>
       </c>
@@ -10185,7 +10085,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="203" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" s="9" t="s">
         <v>672</v>
       </c>
@@ -10221,7 +10121,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="204" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A204" s="7" t="s">
         <v>674</v>
       </c>
@@ -10257,7 +10157,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="205" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A205" s="7" t="s">
         <v>678</v>
       </c>
@@ -10293,7 +10193,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="206" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A206" s="7" t="s">
         <v>681</v>
       </c>
@@ -10329,7 +10229,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="207" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" s="7" t="s">
         <v>683</v>
       </c>
@@ -10365,7 +10265,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="208" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A208" s="7" t="s">
         <v>687</v>
       </c>
@@ -10401,7 +10301,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="209" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A209" s="7" t="s">
         <v>690</v>
       </c>
@@ -10437,7 +10337,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="210" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A210" s="7" t="s">
         <v>693</v>
       </c>
@@ -10451,19 +10351,19 @@
         <v>676</v>
       </c>
       <c r="E210" s="8">
-        <v>1216.4000000000001</v>
+        <v>1216.4</v>
       </c>
       <c r="F210" s="7" t="s">
         <v>694</v>
       </c>
       <c r="G210" s="8">
-        <v>1228.4000000000001</v>
+        <v>1228.4</v>
       </c>
       <c r="H210" s="8">
         <v>1220.3</v>
       </c>
       <c r="I210" s="8">
-        <v>1220.9000000000001</v>
+        <v>1220.9</v>
       </c>
       <c r="J210" s="7"/>
       <c r="K210" s="7"/>
@@ -10473,7 +10373,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="211" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A211" s="9" t="s">
         <v>696</v>
       </c>
@@ -10509,7 +10409,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="212" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A212" s="7" t="s">
         <v>699</v>
       </c>
@@ -10532,10 +10432,10 @@
         <v>1205.8</v>
       </c>
       <c r="H212" s="8">
-        <v>1201.0999999999999</v>
+        <v>1201.1</v>
       </c>
       <c r="I212" s="8">
-        <v>1201.0999999999999</v>
+        <v>1201.1</v>
       </c>
       <c r="J212" s="7"/>
       <c r="K212" s="7"/>
@@ -10545,7 +10445,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="213" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A213" s="7" t="s">
         <v>702</v>
       </c>
@@ -10568,7 +10468,7 @@
         <v>151.28</v>
       </c>
       <c r="H213" s="8">
-        <v>150.66999999999999</v>
+        <v>150.67</v>
       </c>
       <c r="I213" s="8">
         <v>150.75</v>
@@ -10581,7 +10481,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="214" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A214" s="9" t="s">
         <v>706</v>
       </c>
@@ -10617,7 +10517,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="215" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A215" s="7" t="s">
         <v>709</v>
       </c>
@@ -10653,7 +10553,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="216" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A216" s="7" t="s">
         <v>712</v>
       </c>
@@ -10689,7 +10589,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="217" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A217" s="7" t="s">
         <v>714</v>
       </c>
@@ -10725,7 +10625,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="218" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A218" s="7" t="s">
         <v>716</v>
       </c>
@@ -10761,7 +10661,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="219" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A219" s="7" t="s">
         <v>717</v>
       </c>
@@ -10797,7 +10697,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="220" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A220" s="7" t="s">
         <v>719</v>
       </c>
@@ -10811,13 +10711,13 @@
         <v>679</v>
       </c>
       <c r="E220" s="8">
-        <v>2343.3000000000002</v>
+        <v>2343.3</v>
       </c>
       <c r="F220" s="7" t="s">
         <v>710</v>
       </c>
       <c r="G220" s="8">
-        <v>2349.3000000000002</v>
+        <v>2349.3</v>
       </c>
       <c r="H220" s="8">
         <v>2330.6</v>
@@ -10833,7 +10733,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="221" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A221" s="7" t="s">
         <v>721</v>
       </c>
@@ -10869,7 +10769,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="222" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A222" s="7" t="s">
         <v>723</v>
       </c>
@@ -10905,7 +10805,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="223" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A223" s="7" t="s">
         <v>725</v>
       </c>
@@ -10941,7 +10841,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="224" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A224" s="7" t="s">
         <v>728</v>
       </c>
@@ -10977,7 +10877,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="225" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A225" s="7" t="s">
         <v>729</v>
       </c>
@@ -11013,7 +10913,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="226" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A226" s="7" t="s">
         <v>730</v>
       </c>
@@ -11049,7 +10949,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="227" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A227" s="7" t="s">
         <v>731</v>
       </c>
@@ -11085,7 +10985,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="228" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A228" s="7" t="s">
         <v>732</v>
       </c>
@@ -11121,7 +11021,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="229" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A229" s="7" t="s">
         <v>734</v>
       </c>
@@ -11157,7 +11057,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="230" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A230" s="7" t="s">
         <v>735</v>
       </c>
@@ -11177,10 +11077,10 @@
         <v>711</v>
       </c>
       <c r="G230" s="8">
-        <v>536.20000000000005</v>
+        <v>536.2</v>
       </c>
       <c r="H230" s="8">
-        <v>532.04999999999995</v>
+        <v>532.05</v>
       </c>
       <c r="I230" s="8">
         <v>533.25</v>
@@ -11193,7 +11093,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="231" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A231" s="7" t="s">
         <v>737</v>
       </c>
@@ -11229,7 +11129,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="232" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A232" s="7" t="s">
         <v>741</v>
       </c>
@@ -11265,7 +11165,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="233" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A233" s="7" t="s">
         <v>744</v>
       </c>
@@ -11291,7 +11191,7 @@
         <v>1274</v>
       </c>
       <c r="I233" s="8">
-        <v>1276.5999999999999</v>
+        <v>1276.6</v>
       </c>
       <c r="J233" s="7"/>
       <c r="K233" s="7"/>
@@ -11301,7 +11201,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="234" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A234" s="7" t="s">
         <v>748</v>
       </c>
@@ -11324,7 +11224,7 @@
         <v>1280</v>
       </c>
       <c r="H234" s="8">
-        <v>1275.0999999999999</v>
+        <v>1275.1</v>
       </c>
       <c r="I234" s="8">
         <v>1276</v>
@@ -11337,7 +11237,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="235" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A235" s="7" t="s">
         <v>750</v>
       </c>
@@ -11373,7 +11273,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="236" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A236" s="7" t="s">
         <v>753</v>
       </c>
@@ -11409,7 +11309,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="237" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A237" s="7" t="s">
         <v>755</v>
       </c>
@@ -11445,7 +11345,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="238" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A238" s="7" t="s">
         <v>758</v>
       </c>
@@ -11481,7 +11381,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="239" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A239" s="7" t="s">
         <v>760</v>
       </c>
@@ -11517,7 +11417,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="240" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A240" s="7" t="s">
         <v>762</v>
       </c>
@@ -11553,7 +11453,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="241" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A241" s="7" t="s">
         <v>764</v>
       </c>
@@ -11589,7 +11489,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="242" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A242" s="7" t="s">
         <v>766</v>
       </c>
@@ -11609,10 +11509,10 @@
         <v>761</v>
       </c>
       <c r="G242" s="8">
-        <v>2091.1999999999998</v>
+        <v>2091.2</v>
       </c>
       <c r="H242" s="8">
-        <v>2075.1999999999998</v>
+        <v>2075.2</v>
       </c>
       <c r="I242" s="8">
         <v>2078.4</v>
@@ -11625,7 +11525,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="243" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A243" s="7" t="s">
         <v>767</v>
       </c>
@@ -11661,7 +11561,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="244" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A244" s="7" t="s">
         <v>768</v>
       </c>
@@ -11697,7 +11597,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="245" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A245" s="7" t="s">
         <v>771</v>
       </c>
@@ -11717,7 +11617,7 @@
         <v>770</v>
       </c>
       <c r="G245" s="8">
-        <v>526.04999999999995</v>
+        <v>526.05</v>
       </c>
       <c r="H245" s="8">
         <v>523.85</v>
@@ -11733,7 +11633,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="246" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A246" s="7" t="s">
         <v>773</v>
       </c>
@@ -11747,19 +11647,19 @@
         <v>739</v>
       </c>
       <c r="E246" s="8">
-        <v>611.45000000000005</v>
+        <v>611.45</v>
       </c>
       <c r="F246" s="7" t="s">
         <v>770</v>
       </c>
       <c r="G246" s="8">
-        <v>609.04999999999995</v>
+        <v>609.05</v>
       </c>
       <c r="H246" s="8">
         <v>606.75</v>
       </c>
       <c r="I246" s="8">
-        <v>606.79999999999995</v>
+        <v>606.8</v>
       </c>
       <c r="J246" s="7"/>
       <c r="K246" s="7"/>
@@ -11769,7 +11669,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="247" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A247" s="7" t="s">
         <v>774</v>
       </c>
@@ -11805,7 +11705,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="248" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A248" s="7" t="s">
         <v>777</v>
       </c>
@@ -11819,19 +11719,19 @@
         <v>739</v>
       </c>
       <c r="E248" s="8">
-        <v>1240.9000000000001</v>
+        <v>1240.9</v>
       </c>
       <c r="F248" s="7" t="s">
         <v>778</v>
       </c>
       <c r="G248" s="8">
-        <v>1242.5999999999999</v>
+        <v>1242.6</v>
       </c>
       <c r="H248" s="8">
         <v>1235</v>
       </c>
       <c r="I248" s="8">
-        <v>1235.5999999999999</v>
+        <v>1235.6</v>
       </c>
       <c r="J248" s="7"/>
       <c r="K248" s="7"/>
@@ -11841,7 +11741,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="249" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A249" s="7" t="s">
         <v>780</v>
       </c>
@@ -11861,10 +11761,10 @@
         <v>782</v>
       </c>
       <c r="G249" s="8">
-        <v>1202.9000000000001</v>
+        <v>1202.9</v>
       </c>
       <c r="H249" s="8">
-        <v>1183.4000000000001</v>
+        <v>1183.4</v>
       </c>
       <c r="I249" s="8">
         <v>1188.3</v>
@@ -11877,7 +11777,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="250" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A250" s="7" t="s">
         <v>784</v>
       </c>
@@ -11913,7 +11813,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="251" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A251" s="7" t="s">
         <v>787</v>
       </c>
@@ -11939,7 +11839,7 @@
         <v>2185.4</v>
       </c>
       <c r="I251" s="8">
-        <v>2192.8000000000002</v>
+        <v>2192.8</v>
       </c>
       <c r="J251" s="7"/>
       <c r="K251" s="7"/>
@@ -11949,7 +11849,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="252" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A252" s="7" t="s">
         <v>789</v>
       </c>
@@ -11972,10 +11872,10 @@
         <v>4728.8</v>
       </c>
       <c r="H252" s="8">
-        <v>4704.8999999999996</v>
+        <v>4704.9</v>
       </c>
       <c r="I252" s="8">
-        <v>4710.3999999999996</v>
+        <v>4710.4</v>
       </c>
       <c r="J252" s="7"/>
       <c r="K252" s="7"/>
@@ -11985,7 +11885,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="253" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A253" s="7" t="s">
         <v>792</v>
       </c>
@@ -12011,7 +11911,7 @@
         <v>70.02</v>
       </c>
       <c r="I253" s="8">
-        <v>70.099999999999994</v>
+        <v>70.1</v>
       </c>
       <c r="J253" s="7"/>
       <c r="K253" s="7"/>
@@ -12021,7 +11921,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="254" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A254" s="7" t="s">
         <v>795</v>
       </c>
@@ -12057,7 +11957,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="255" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A255" s="7" t="s">
         <v>797</v>
       </c>
@@ -12093,7 +11993,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="256" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A256" s="7" t="s">
         <v>798</v>
       </c>
@@ -12113,7 +12013,7 @@
         <v>782</v>
       </c>
       <c r="G256" s="8">
-        <v>1253.9000000000001</v>
+        <v>1253.9</v>
       </c>
       <c r="H256" s="8">
         <v>1215.3</v>
@@ -12129,7 +12029,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="257" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A257" s="7" t="s">
         <v>799</v>
       </c>
@@ -12165,7 +12065,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="258" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A258" s="7" t="s">
         <v>800</v>
       </c>
@@ -12201,7 +12101,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="259" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A259" s="7" t="s">
         <v>802</v>
       </c>
@@ -12237,7 +12137,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="260" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A260" s="7" t="s">
         <v>806</v>
       </c>
@@ -12273,7 +12173,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="261" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A261" s="9" t="s">
         <v>808</v>
       </c>
@@ -12309,7 +12209,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="262" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A262" s="9" t="s">
         <v>812</v>
       </c>
@@ -12335,7 +12235,7 @@
         <v>1220.3</v>
       </c>
       <c r="I262" s="10">
-        <v>1233.0999999999999</v>
+        <v>1233.1</v>
       </c>
       <c r="J262" s="9"/>
       <c r="K262" s="9"/>
@@ -12345,7 +12245,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="263" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A263" s="9" t="s">
         <v>814</v>
       </c>
@@ -12359,7 +12259,7 @@
         <v>815</v>
       </c>
       <c r="E263" s="10">
-        <v>1283.5999999999999</v>
+        <v>1283.6</v>
       </c>
       <c r="F263" s="9" t="s">
         <v>810</v>
@@ -12368,7 +12268,7 @@
         <v>1327.9</v>
       </c>
       <c r="H263" s="10">
-        <v>1276.0999999999999</v>
+        <v>1276.1</v>
       </c>
       <c r="I263" s="10">
         <v>1324.6</v>
@@ -12381,7 +12281,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="264" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A264" s="9" t="s">
         <v>816</v>
       </c>
@@ -12417,7 +12317,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="265" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A265" s="9" t="s">
         <v>818</v>
       </c>
@@ -12431,7 +12331,7 @@
         <v>819</v>
       </c>
       <c r="E265" s="10">
-        <v>2094.1999999999998</v>
+        <v>2094.2</v>
       </c>
       <c r="F265" s="9" t="s">
         <v>810</v>
@@ -12453,7 +12353,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="266" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A266" s="9" t="s">
         <v>820</v>
       </c>
@@ -12467,7 +12367,7 @@
         <v>822</v>
       </c>
       <c r="E266" s="10">
-        <v>2276.6999999999998</v>
+        <v>2276.7</v>
       </c>
       <c r="F266" s="9" t="s">
         <v>810</v>
@@ -12479,7 +12379,7 @@
         <v>2370.1</v>
       </c>
       <c r="I266" s="10">
-        <v>2457.6999999999998</v>
+        <v>2457.7</v>
       </c>
       <c r="J266" s="9"/>
       <c r="K266" s="9"/>
@@ -12489,7 +12389,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="267" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A267" s="9" t="s">
         <v>824</v>
       </c>
@@ -12525,7 +12425,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="268" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A268" s="9" t="s">
         <v>826</v>
       </c>
@@ -12561,7 +12461,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="269" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A269" s="9" t="s">
         <v>827</v>
       </c>
@@ -12597,7 +12497,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="270" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A270" s="7" t="s">
         <v>830</v>
       </c>
@@ -12611,19 +12511,19 @@
         <v>831</v>
       </c>
       <c r="E270" s="8">
-        <v>4355.8999999999996</v>
+        <v>4355.9</v>
       </c>
       <c r="F270" s="7" t="s">
         <v>832</v>
       </c>
       <c r="G270" s="8">
-        <v>4344.8999999999996</v>
+        <v>4344.9</v>
       </c>
       <c r="H270" s="8">
         <v>4335</v>
       </c>
       <c r="I270" s="8">
-        <v>4339.8999999999996</v>
+        <v>4339.9</v>
       </c>
       <c r="J270" s="7"/>
       <c r="K270" s="7"/>
@@ -12633,7 +12533,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="271" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A271" s="9" t="s">
         <v>834</v>
       </c>
@@ -12669,7 +12569,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="272" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A272" s="7" t="s">
         <v>838</v>
       </c>
@@ -12705,7 +12605,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="273" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A273" s="9" t="s">
         <v>839</v>
       </c>
@@ -12741,7 +12641,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="274" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A274" s="9" t="s">
         <v>841</v>
       </c>
@@ -12755,7 +12655,7 @@
         <v>819</v>
       </c>
       <c r="E274" s="10">
-        <v>2094.1999999999998</v>
+        <v>2094.2</v>
       </c>
       <c r="F274" s="9" t="s">
         <v>842</v>
@@ -12764,7 +12664,7 @@
         <v>2126.1</v>
       </c>
       <c r="H274" s="10">
-        <v>2118.3000000000002</v>
+        <v>2118.3</v>
       </c>
       <c r="I274" s="10">
         <v>2126.1</v>
@@ -12777,7 +12677,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="275" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A275" s="9" t="s">
         <v>844</v>
       </c>
@@ -12813,7 +12713,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="276" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A276" s="7" t="s">
         <v>846</v>
       </c>
@@ -12833,7 +12733,7 @@
         <v>848</v>
       </c>
       <c r="G276" s="8">
-        <v>2190.3000000000002</v>
+        <v>2190.3</v>
       </c>
       <c r="H276" s="8">
         <v>2180.9</v>
@@ -12849,7 +12749,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="277" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A277" s="9" t="s">
         <v>850</v>
       </c>
@@ -12886,39 +12786,363 @@
       </c>
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A278" s="20" t="s">
+      <c r="A278" s="17" t="s">
         <v>851</v>
       </c>
-      <c r="B278" s="20" t="s">
+      <c r="B278" s="17" t="s">
         <v>515</v>
       </c>
-      <c r="C278" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="D278" s="20" t="s">
+      <c r="C278" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D278" s="17" t="s">
         <v>852</v>
       </c>
-      <c r="E278" s="21">
+      <c r="E278" s="18">
         <v>409.65</v>
       </c>
-      <c r="F278" s="20" t="s">
+      <c r="F278" s="17" t="s">
         <v>810</v>
       </c>
-      <c r="G278" s="21">
+      <c r="G278" s="18">
         <v>422.45</v>
       </c>
-      <c r="H278" s="21">
+      <c r="H278" s="18">
         <v>412.2</v>
       </c>
-      <c r="I278" s="21">
+      <c r="I278" s="18">
         <v>421.75</v>
       </c>
-      <c r="J278" s="20"/>
-      <c r="K278" s="20"/>
-      <c r="L278" s="20"/>
-      <c r="M278" s="20"/>
-      <c r="N278" s="20" t="s">
+      <c r="J278" s="17"/>
+      <c r="K278" s="17"/>
+      <c r="L278" s="17"/>
+      <c r="M278" s="17"/>
+      <c r="N278" s="17" t="s">
         <v>823</v>
+      </c>
+    </row>
+    <row r="279" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A279" s="19" t="s">
+        <v>853</v>
+      </c>
+      <c r="B279" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="C279" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D279" s="19" t="s">
+        <v>854</v>
+      </c>
+      <c r="E279" s="20">
+        <v>397.4</v>
+      </c>
+      <c r="F279" s="19" t="s">
+        <v>855</v>
+      </c>
+      <c r="G279" s="20">
+        <v>391.9</v>
+      </c>
+      <c r="H279" s="20">
+        <v>382.65</v>
+      </c>
+      <c r="I279" s="20">
+        <v>384.1</v>
+      </c>
+      <c r="J279" s="19"/>
+      <c r="K279" s="19"/>
+      <c r="L279" s="19"/>
+      <c r="M279" s="19"/>
+      <c r="N279" s="19" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="280" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A280" s="19" t="s">
+        <v>857</v>
+      </c>
+      <c r="B280" s="19" t="s">
+        <v>858</v>
+      </c>
+      <c r="C280" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D280" s="19" t="s">
+        <v>859</v>
+      </c>
+      <c r="E280" s="20">
+        <v>1226</v>
+      </c>
+      <c r="F280" s="19" t="s">
+        <v>855</v>
+      </c>
+      <c r="G280" s="20">
+        <v>1202</v>
+      </c>
+      <c r="H280" s="20">
+        <v>1171.1</v>
+      </c>
+      <c r="I280" s="20">
+        <v>1180</v>
+      </c>
+      <c r="J280" s="19"/>
+      <c r="K280" s="19"/>
+      <c r="L280" s="19"/>
+      <c r="M280" s="19"/>
+      <c r="N280" s="19" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="281" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A281" s="19" t="s">
+        <v>860</v>
+      </c>
+      <c r="B281" s="19" t="s">
+        <v>861</v>
+      </c>
+      <c r="C281" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D281" s="19" t="s">
+        <v>862</v>
+      </c>
+      <c r="E281" s="20">
+        <v>576.35</v>
+      </c>
+      <c r="F281" s="19" t="s">
+        <v>855</v>
+      </c>
+      <c r="G281" s="20">
+        <v>570</v>
+      </c>
+      <c r="H281" s="20">
+        <v>558.8</v>
+      </c>
+      <c r="I281" s="20">
+        <v>561.75</v>
+      </c>
+      <c r="J281" s="19"/>
+      <c r="K281" s="19"/>
+      <c r="L281" s="19"/>
+      <c r="M281" s="19"/>
+      <c r="N281" s="19" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="282" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A282" s="19" t="s">
+        <v>864</v>
+      </c>
+      <c r="B282" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="C282" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D282" s="19" t="s">
+        <v>847</v>
+      </c>
+      <c r="E282" s="20">
+        <v>2204.9</v>
+      </c>
+      <c r="F282" s="19" t="s">
+        <v>865</v>
+      </c>
+      <c r="G282" s="20">
+        <v>2136</v>
+      </c>
+      <c r="H282" s="20">
+        <v>2121.7</v>
+      </c>
+      <c r="I282" s="20">
+        <v>2124</v>
+      </c>
+      <c r="J282" s="19"/>
+      <c r="K282" s="19"/>
+      <c r="L282" s="19"/>
+      <c r="M282" s="19"/>
+      <c r="N282" s="19" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="283" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A283" s="19" t="s">
+        <v>867</v>
+      </c>
+      <c r="B283" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="C283" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D283" s="19" t="s">
+        <v>856</v>
+      </c>
+      <c r="E283" s="20">
+        <v>7611</v>
+      </c>
+      <c r="F283" s="19" t="s">
+        <v>868</v>
+      </c>
+      <c r="G283" s="20">
+        <v>7673</v>
+      </c>
+      <c r="H283" s="20">
+        <v>7305.5</v>
+      </c>
+      <c r="I283" s="20">
+        <v>7312.5</v>
+      </c>
+      <c r="J283" s="19"/>
+      <c r="K283" s="19"/>
+      <c r="L283" s="19"/>
+      <c r="M283" s="19"/>
+      <c r="N283" s="19" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="284" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A284" s="19" t="s">
+        <v>870</v>
+      </c>
+      <c r="B284" s="19" t="s">
+        <v>718</v>
+      </c>
+      <c r="C284" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D284" s="19" t="s">
+        <v>862</v>
+      </c>
+      <c r="E284" s="20">
+        <v>1351.3</v>
+      </c>
+      <c r="F284" s="19" t="s">
+        <v>869</v>
+      </c>
+      <c r="G284" s="20">
+        <v>1321.5</v>
+      </c>
+      <c r="H284" s="20">
+        <v>1316.4</v>
+      </c>
+      <c r="I284" s="20">
+        <v>1318.3</v>
+      </c>
+      <c r="J284" s="19"/>
+      <c r="K284" s="19"/>
+      <c r="L284" s="19"/>
+      <c r="M284" s="19"/>
+      <c r="N284" s="19" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="285" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A285" s="19" t="s">
+        <v>872</v>
+      </c>
+      <c r="B285" s="19" t="s">
+        <v>873</v>
+      </c>
+      <c r="C285" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D285" s="19" t="s">
+        <v>855</v>
+      </c>
+      <c r="E285" s="20">
+        <v>173.54</v>
+      </c>
+      <c r="F285" s="19" t="s">
+        <v>874</v>
+      </c>
+      <c r="G285" s="20">
+        <v>176</v>
+      </c>
+      <c r="H285" s="20">
+        <v>173.76</v>
+      </c>
+      <c r="I285" s="20">
+        <v>173.9</v>
+      </c>
+      <c r="J285" s="19"/>
+      <c r="K285" s="19"/>
+      <c r="L285" s="19"/>
+      <c r="M285" s="19"/>
+      <c r="N285" s="19" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="286" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A286" s="19" t="s">
+        <v>876</v>
+      </c>
+      <c r="B286" s="19" t="s">
+        <v>877</v>
+      </c>
+      <c r="C286" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D286" s="19" t="s">
+        <v>842</v>
+      </c>
+      <c r="E286" s="20">
+        <v>2714</v>
+      </c>
+      <c r="F286" s="19" t="s">
+        <v>878</v>
+      </c>
+      <c r="G286" s="20">
+        <v>2682.4</v>
+      </c>
+      <c r="H286" s="20">
+        <v>2669.4</v>
+      </c>
+      <c r="I286" s="20">
+        <v>2669.4</v>
+      </c>
+      <c r="J286" s="19"/>
+      <c r="K286" s="19"/>
+      <c r="L286" s="19"/>
+      <c r="M286" s="19"/>
+      <c r="N286" s="19" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="287" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A287" s="19" t="s">
+        <v>880</v>
+      </c>
+      <c r="B287" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="C287" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D287" s="19" t="s">
+        <v>855</v>
+      </c>
+      <c r="E287" s="20">
+        <v>774.95</v>
+      </c>
+      <c r="F287" s="19" t="s">
+        <v>878</v>
+      </c>
+      <c r="G287" s="20">
+        <v>783.9</v>
+      </c>
+      <c r="H287" s="20">
+        <v>772</v>
+      </c>
+      <c r="I287" s="20">
+        <v>774.7</v>
+      </c>
+      <c r="J287" s="19"/>
+      <c r="K287" s="19"/>
+      <c r="L287" s="19"/>
+      <c r="M287" s="19"/>
+      <c r="N287" s="19" t="s">
+        <v>879</v>
       </c>
     </row>
   </sheetData>

--- a/pattern_signals.xlsx
+++ b/pattern_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1600" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="797">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -2396,6 +2396,15 @@
   </si>
   <si>
     <t>2026-03-06 12:59</t>
+  </si>
+  <si>
+    <t>NSE:SUNPHARMA-EQ_BULL_1772683200_1773041400</t>
+  </si>
+  <si>
+    <t>2026-03-09 13:00</t>
+  </si>
+  <si>
+    <t>2026-03-09 15:01</t>
   </si>
 </sst>
 </file>
@@ -2859,7 +2868,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N256"/>
+  <dimension ref="A1:N257"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -11756,6 +11765,42 @@
         <v>793</v>
       </c>
     </row>
+    <row r="257" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A257" s="11" t="s">
+        <v>794</v>
+      </c>
+      <c r="B257" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C257" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D257" s="11" t="s">
+        <v>753</v>
+      </c>
+      <c r="E257" s="12">
+        <v>1785</v>
+      </c>
+      <c r="F257" s="11" t="s">
+        <v>795</v>
+      </c>
+      <c r="G257" s="12">
+        <v>1805.8</v>
+      </c>
+      <c r="H257" s="12">
+        <v>1796.4</v>
+      </c>
+      <c r="I257" s="12">
+        <v>1804.1</v>
+      </c>
+      <c r="J257" s="11"/>
+      <c r="K257" s="11"/>
+      <c r="L257" s="11"/>
+      <c r="M257" s="11"/>
+      <c r="N257" s="11" t="s">
+        <v>796</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pattern_signals.xlsx
+++ b/pattern_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1786" uniqueCount="881">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1996" uniqueCount="955">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -2657,6 +2657,228 @@
   </si>
   <si>
     <t>NSE:MARICO-EQ_BEAR_1773027900_1773049500</t>
+  </si>
+  <si>
+    <t>NSE:AUROPHARMA-EQ_BULL_1773036000_1773114300</t>
+  </si>
+  <si>
+    <t>2026-03-09 11:30</t>
+  </si>
+  <si>
+    <t>2026-03-10 09:15</t>
+  </si>
+  <si>
+    <t>2026-03-10 09:30</t>
+  </si>
+  <si>
+    <t>NSE:BSE-EQ_BULL_1773044100_1773114300</t>
+  </si>
+  <si>
+    <t>2026-03-09 13:45</t>
+  </si>
+  <si>
+    <t>NSE:GLENMARK-EQ_BULL_1773045900_1773114300</t>
+  </si>
+  <si>
+    <t>2026-03-09 14:15</t>
+  </si>
+  <si>
+    <t>NSE:HINDALCO-EQ_BEAR_1773029700_1773114300</t>
+  </si>
+  <si>
+    <t>NSE:HINDALCO-EQ</t>
+  </si>
+  <si>
+    <t>NSE:TORNTPHARM-EQ_BULL_1773046800_1773114300</t>
+  </si>
+  <si>
+    <t>2026-03-09 14:30</t>
+  </si>
+  <si>
+    <t>2026-03-10 09:31</t>
+  </si>
+  <si>
+    <t>NSE:BLUESTARCO-EQ_BEAR_1773028800_1773115200</t>
+  </si>
+  <si>
+    <t>2026-03-10 09:45</t>
+  </si>
+  <si>
+    <t>NSE:AMBER-EQ_BEAR_1773028800_1773116100</t>
+  </si>
+  <si>
+    <t>2026-03-10 10:00</t>
+  </si>
+  <si>
+    <t>NSE:BHARATFORG-EQ_BEAR_1773029700_1773116100</t>
+  </si>
+  <si>
+    <t>NSE:PAGEIND-EQ_BEAR_1773027900_1773116100</t>
+  </si>
+  <si>
+    <t>NSE:PAGEIND-EQ</t>
+  </si>
+  <si>
+    <t>NSE:POLYCAB-EQ_BEAR_1773028800_1773116100</t>
+  </si>
+  <si>
+    <t>NSE:HFCL-EQ_BULL_1773117000_1773132300</t>
+  </si>
+  <si>
+    <t>2026-03-10 14:15</t>
+  </si>
+  <si>
+    <t>2026-03-10 14:30</t>
+  </si>
+  <si>
+    <t>NSE:VBL-EQ_BEAR_1773027900_1773132300</t>
+  </si>
+  <si>
+    <t>2026-03-10 14:31</t>
+  </si>
+  <si>
+    <t>NSE:ALKEM-EQ_BULL_1773117000_1773133200</t>
+  </si>
+  <si>
+    <t>NSE:ALKEM-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:00</t>
+  </si>
+  <si>
+    <t>NSE:COALINDIA-EQ_BULL_1773127800_1773134100</t>
+  </si>
+  <si>
+    <t>2026-03-10 13:00</t>
+  </si>
+  <si>
+    <t>2026-03-10 14:45</t>
+  </si>
+  <si>
+    <t>NSE:IRFC-EQ_BULL_1773126000_1773134100</t>
+  </si>
+  <si>
+    <t>2026-03-10 12:30</t>
+  </si>
+  <si>
+    <t>NSE:OFSS-EQ_BULL_1773121500_1773134100</t>
+  </si>
+  <si>
+    <t>2026-03-10 11:15</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:01</t>
+  </si>
+  <si>
+    <t>NSE:NCC-EQ_BULL_1773123300_1773135000</t>
+  </si>
+  <si>
+    <t>2026-03-10 11:45</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:15</t>
+  </si>
+  <si>
+    <t>NSE:SRF-EQ_BULL_1773121500_1773135000</t>
+  </si>
+  <si>
+    <t>NSE:SRF-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:16</t>
+  </si>
+  <si>
+    <t>NSE:UNITDSPR-EQ_BULL_1773116100_1773135000</t>
+  </si>
+  <si>
+    <t>NSE:VEDL-EQ_BULL_1773126000_1773135000</t>
+  </si>
+  <si>
+    <t>NSE:ASTRAL-EQ_BULL_1773123300_1773135900</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:30</t>
+  </si>
+  <si>
+    <t>NSE:CGPOWER-EQ_BULL_1773117000_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:CGPOWER-EQ</t>
+  </si>
+  <si>
+    <t>NSE:CDSL-EQ_BULL_1773120600_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:CDSL-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-10 11:00</t>
+  </si>
+  <si>
+    <t>NSE:CHOLAFIN-EQ_BULL_1773127800_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:COLPAL-EQ_BULL_1773131400_1773135900</t>
+  </si>
+  <si>
+    <t>2026-03-10 14:00</t>
+  </si>
+  <si>
+    <t>NSE:DLF-EQ_BULL_1773122400_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:DLF-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-10 11:30</t>
+  </si>
+  <si>
+    <t>NSE:DELHIVERY-EQ_BULL_1773121500_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:NYKAA-EQ_BULL_1773126900_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:NYKAA-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-10 12:45</t>
+  </si>
+  <si>
+    <t>NSE:GMRAIRPORT-EQ_BULL_1773130500_1773135900</t>
+  </si>
+  <si>
+    <t>2026-03-10 13:45</t>
+  </si>
+  <si>
+    <t>NSE:IREDA-EQ_BULL_1773133200_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:LAURUSLABS-EQ_BULL_1773121500_1773135900</t>
+  </si>
+  <si>
+    <t>2026-03-10 15:31</t>
+  </si>
+  <si>
+    <t>NSE:LUPIN-EQ_BULL_1773117000_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:LUPIN-EQ</t>
+  </si>
+  <si>
+    <t>NSE:NBCC-EQ_BULL_1773132300_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:NBCC-EQ</t>
+  </si>
+  <si>
+    <t>NSE:OBEROIRLTY-EQ_BULL_1773122400_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:OBEROIRLTY-EQ</t>
+  </si>
+  <si>
+    <t>NSE:PNBHOUSING-EQ_BULL_1773127800_1773135900</t>
   </si>
 </sst>
 </file>
@@ -3132,7 +3354,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N287"/>
+  <dimension ref="A1:N322"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -13145,6 +13367,1266 @@
         <v>879</v>
       </c>
     </row>
+    <row r="288" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A288" s="17" t="s">
+        <v>881</v>
+      </c>
+      <c r="B288" s="17" t="s">
+        <v>333</v>
+      </c>
+      <c r="C288" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D288" s="17" t="s">
+        <v>882</v>
+      </c>
+      <c r="E288" s="18">
+        <v>1230.9</v>
+      </c>
+      <c r="F288" s="17" t="s">
+        <v>883</v>
+      </c>
+      <c r="G288" s="18">
+        <v>1270</v>
+      </c>
+      <c r="H288" s="18">
+        <v>1249</v>
+      </c>
+      <c r="I288" s="18">
+        <v>1269</v>
+      </c>
+      <c r="J288" s="17"/>
+      <c r="K288" s="17"/>
+      <c r="L288" s="17"/>
+      <c r="M288" s="17"/>
+      <c r="N288" s="17" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="289" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A289" s="17" t="s">
+        <v>885</v>
+      </c>
+      <c r="B289" s="17" t="s">
+        <v>602</v>
+      </c>
+      <c r="C289" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D289" s="17" t="s">
+        <v>886</v>
+      </c>
+      <c r="E289" s="18">
+        <v>2744.9</v>
+      </c>
+      <c r="F289" s="17" t="s">
+        <v>883</v>
+      </c>
+      <c r="G289" s="18">
+        <v>2832</v>
+      </c>
+      <c r="H289" s="18">
+        <v>2805.3</v>
+      </c>
+      <c r="I289" s="18">
+        <v>2828</v>
+      </c>
+      <c r="J289" s="17"/>
+      <c r="K289" s="17"/>
+      <c r="L289" s="17"/>
+      <c r="M289" s="17"/>
+      <c r="N289" s="17" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="290" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A290" s="17" t="s">
+        <v>887</v>
+      </c>
+      <c r="B290" s="17" t="s">
+        <v>477</v>
+      </c>
+      <c r="C290" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D290" s="17" t="s">
+        <v>888</v>
+      </c>
+      <c r="E290" s="18">
+        <v>2105.8</v>
+      </c>
+      <c r="F290" s="17" t="s">
+        <v>883</v>
+      </c>
+      <c r="G290" s="18">
+        <v>2177.8</v>
+      </c>
+      <c r="H290" s="18">
+        <v>2130.4</v>
+      </c>
+      <c r="I290" s="18">
+        <v>2173.8</v>
+      </c>
+      <c r="J290" s="17"/>
+      <c r="K290" s="17"/>
+      <c r="L290" s="17"/>
+      <c r="M290" s="17"/>
+      <c r="N290" s="17" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="291" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A291" s="19" t="s">
+        <v>889</v>
+      </c>
+      <c r="B291" s="19" t="s">
+        <v>890</v>
+      </c>
+      <c r="C291" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D291" s="19" t="s">
+        <v>865</v>
+      </c>
+      <c r="E291" s="20">
+        <v>942.1</v>
+      </c>
+      <c r="F291" s="19" t="s">
+        <v>883</v>
+      </c>
+      <c r="G291" s="20">
+        <v>957.75</v>
+      </c>
+      <c r="H291" s="20">
+        <v>938.1</v>
+      </c>
+      <c r="I291" s="20">
+        <v>938.4</v>
+      </c>
+      <c r="J291" s="19"/>
+      <c r="K291" s="19"/>
+      <c r="L291" s="19"/>
+      <c r="M291" s="19"/>
+      <c r="N291" s="19" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="292" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A292" s="17" t="s">
+        <v>891</v>
+      </c>
+      <c r="B292" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="C292" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D292" s="17" t="s">
+        <v>892</v>
+      </c>
+      <c r="E292" s="18">
+        <v>4360</v>
+      </c>
+      <c r="F292" s="17" t="s">
+        <v>883</v>
+      </c>
+      <c r="G292" s="18">
+        <v>4432</v>
+      </c>
+      <c r="H292" s="18">
+        <v>4389</v>
+      </c>
+      <c r="I292" s="18">
+        <v>4428.5</v>
+      </c>
+      <c r="J292" s="17"/>
+      <c r="K292" s="17"/>
+      <c r="L292" s="17"/>
+      <c r="M292" s="17"/>
+      <c r="N292" s="17" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="293" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A293" s="19" t="s">
+        <v>894</v>
+      </c>
+      <c r="B293" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C293" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D293" s="19" t="s">
+        <v>856</v>
+      </c>
+      <c r="E293" s="20">
+        <v>1894.6</v>
+      </c>
+      <c r="F293" s="19" t="s">
+        <v>884</v>
+      </c>
+      <c r="G293" s="20">
+        <v>1902</v>
+      </c>
+      <c r="H293" s="20">
+        <v>1882.4</v>
+      </c>
+      <c r="I293" s="20">
+        <v>1891</v>
+      </c>
+      <c r="J293" s="19"/>
+      <c r="K293" s="19"/>
+      <c r="L293" s="19"/>
+      <c r="M293" s="19"/>
+      <c r="N293" s="19" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="294" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A294" s="19" t="s">
+        <v>896</v>
+      </c>
+      <c r="B294" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="C294" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D294" s="19" t="s">
+        <v>856</v>
+      </c>
+      <c r="E294" s="20">
+        <v>7611</v>
+      </c>
+      <c r="F294" s="19" t="s">
+        <v>895</v>
+      </c>
+      <c r="G294" s="20">
+        <v>7292</v>
+      </c>
+      <c r="H294" s="20">
+        <v>7221</v>
+      </c>
+      <c r="I294" s="20">
+        <v>7231</v>
+      </c>
+      <c r="J294" s="19"/>
+      <c r="K294" s="19"/>
+      <c r="L294" s="19"/>
+      <c r="M294" s="19"/>
+      <c r="N294" s="19" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="295" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A295" s="19" t="s">
+        <v>898</v>
+      </c>
+      <c r="B295" s="19" t="s">
+        <v>785</v>
+      </c>
+      <c r="C295" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D295" s="19" t="s">
+        <v>865</v>
+      </c>
+      <c r="E295" s="20">
+        <v>1845.5</v>
+      </c>
+      <c r="F295" s="19" t="s">
+        <v>895</v>
+      </c>
+      <c r="G295" s="20">
+        <v>1849.7</v>
+      </c>
+      <c r="H295" s="20">
+        <v>1841.2</v>
+      </c>
+      <c r="I295" s="20">
+        <v>1841.7</v>
+      </c>
+      <c r="J295" s="19"/>
+      <c r="K295" s="19"/>
+      <c r="L295" s="19"/>
+      <c r="M295" s="19"/>
+      <c r="N295" s="19" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="296" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A296" s="19" t="s">
+        <v>899</v>
+      </c>
+      <c r="B296" s="19" t="s">
+        <v>900</v>
+      </c>
+      <c r="C296" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D296" s="19" t="s">
+        <v>855</v>
+      </c>
+      <c r="E296" s="20">
+        <v>30915</v>
+      </c>
+      <c r="F296" s="19" t="s">
+        <v>895</v>
+      </c>
+      <c r="G296" s="20">
+        <v>31255</v>
+      </c>
+      <c r="H296" s="20">
+        <v>30955</v>
+      </c>
+      <c r="I296" s="20">
+        <v>30985</v>
+      </c>
+      <c r="J296" s="19"/>
+      <c r="K296" s="19"/>
+      <c r="L296" s="19"/>
+      <c r="M296" s="19"/>
+      <c r="N296" s="19" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="297" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A297" s="19" t="s">
+        <v>901</v>
+      </c>
+      <c r="B297" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="C297" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D297" s="19" t="s">
+        <v>856</v>
+      </c>
+      <c r="E297" s="20">
+        <v>8232</v>
+      </c>
+      <c r="F297" s="19" t="s">
+        <v>895</v>
+      </c>
+      <c r="G297" s="20">
+        <v>8213</v>
+      </c>
+      <c r="H297" s="20">
+        <v>8161.5</v>
+      </c>
+      <c r="I297" s="20">
+        <v>8165.5</v>
+      </c>
+      <c r="J297" s="19"/>
+      <c r="K297" s="19"/>
+      <c r="L297" s="19"/>
+      <c r="M297" s="19"/>
+      <c r="N297" s="19" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="298" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A298" s="17" t="s">
+        <v>902</v>
+      </c>
+      <c r="B298" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C298" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D298" s="17" t="s">
+        <v>897</v>
+      </c>
+      <c r="E298" s="18">
+        <v>69.25</v>
+      </c>
+      <c r="F298" s="17" t="s">
+        <v>903</v>
+      </c>
+      <c r="G298" s="18">
+        <v>70.26</v>
+      </c>
+      <c r="H298" s="18">
+        <v>69.42</v>
+      </c>
+      <c r="I298" s="18">
+        <v>69.73</v>
+      </c>
+      <c r="J298" s="17"/>
+      <c r="K298" s="17"/>
+      <c r="L298" s="17"/>
+      <c r="M298" s="17"/>
+      <c r="N298" s="17" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="299" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A299" s="19" t="s">
+        <v>905</v>
+      </c>
+      <c r="B299" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="C299" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D299" s="19" t="s">
+        <v>855</v>
+      </c>
+      <c r="E299" s="20">
+        <v>438.1</v>
+      </c>
+      <c r="F299" s="19" t="s">
+        <v>903</v>
+      </c>
+      <c r="G299" s="20">
+        <v>437.1</v>
+      </c>
+      <c r="H299" s="20">
+        <v>435.05</v>
+      </c>
+      <c r="I299" s="20">
+        <v>435.6</v>
+      </c>
+      <c r="J299" s="19"/>
+      <c r="K299" s="19"/>
+      <c r="L299" s="19"/>
+      <c r="M299" s="19"/>
+      <c r="N299" s="19" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="300" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A300" s="17" t="s">
+        <v>907</v>
+      </c>
+      <c r="B300" s="17" t="s">
+        <v>908</v>
+      </c>
+      <c r="C300" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D300" s="17" t="s">
+        <v>897</v>
+      </c>
+      <c r="E300" s="18">
+        <v>5571.5</v>
+      </c>
+      <c r="F300" s="17" t="s">
+        <v>904</v>
+      </c>
+      <c r="G300" s="18">
+        <v>5664.5</v>
+      </c>
+      <c r="H300" s="18">
+        <v>5624</v>
+      </c>
+      <c r="I300" s="18">
+        <v>5638.5</v>
+      </c>
+      <c r="J300" s="17"/>
+      <c r="K300" s="17"/>
+      <c r="L300" s="17"/>
+      <c r="M300" s="17"/>
+      <c r="N300" s="17" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="301" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A301" s="17" t="s">
+        <v>910</v>
+      </c>
+      <c r="B301" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C301" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D301" s="17" t="s">
+        <v>911</v>
+      </c>
+      <c r="E301" s="18">
+        <v>442.2</v>
+      </c>
+      <c r="F301" s="17" t="s">
+        <v>912</v>
+      </c>
+      <c r="G301" s="18">
+        <v>444.8</v>
+      </c>
+      <c r="H301" s="18">
+        <v>441.6</v>
+      </c>
+      <c r="I301" s="18">
+        <v>443.15</v>
+      </c>
+      <c r="J301" s="17"/>
+      <c r="K301" s="17"/>
+      <c r="L301" s="17"/>
+      <c r="M301" s="17"/>
+      <c r="N301" s="17" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="302" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A302" s="17" t="s">
+        <v>913</v>
+      </c>
+      <c r="B302" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C302" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D302" s="17" t="s">
+        <v>914</v>
+      </c>
+      <c r="E302" s="18">
+        <v>99.19</v>
+      </c>
+      <c r="F302" s="17" t="s">
+        <v>912</v>
+      </c>
+      <c r="G302" s="18">
+        <v>101.05</v>
+      </c>
+      <c r="H302" s="18">
+        <v>99.93</v>
+      </c>
+      <c r="I302" s="18">
+        <v>101</v>
+      </c>
+      <c r="J302" s="17"/>
+      <c r="K302" s="17"/>
+      <c r="L302" s="17"/>
+      <c r="M302" s="17"/>
+      <c r="N302" s="17" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="303" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A303" s="17" t="s">
+        <v>915</v>
+      </c>
+      <c r="B303" s="17" t="s">
+        <v>645</v>
+      </c>
+      <c r="C303" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D303" s="17" t="s">
+        <v>916</v>
+      </c>
+      <c r="E303" s="18">
+        <v>6776.5</v>
+      </c>
+      <c r="F303" s="17" t="s">
+        <v>912</v>
+      </c>
+      <c r="G303" s="18">
+        <v>6825.5</v>
+      </c>
+      <c r="H303" s="18">
+        <v>6798.5</v>
+      </c>
+      <c r="I303" s="18">
+        <v>6824.5</v>
+      </c>
+      <c r="J303" s="17"/>
+      <c r="K303" s="17"/>
+      <c r="L303" s="17"/>
+      <c r="M303" s="17"/>
+      <c r="N303" s="17" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="304" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A304" s="17" t="s">
+        <v>918</v>
+      </c>
+      <c r="B304" s="17" t="s">
+        <v>597</v>
+      </c>
+      <c r="C304" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D304" s="17" t="s">
+        <v>919</v>
+      </c>
+      <c r="E304" s="18">
+        <v>144.4</v>
+      </c>
+      <c r="F304" s="17" t="s">
+        <v>909</v>
+      </c>
+      <c r="G304" s="18">
+        <v>145.4</v>
+      </c>
+      <c r="H304" s="18">
+        <v>144.4</v>
+      </c>
+      <c r="I304" s="18">
+        <v>144.83</v>
+      </c>
+      <c r="J304" s="17"/>
+      <c r="K304" s="17"/>
+      <c r="L304" s="17"/>
+      <c r="M304" s="17"/>
+      <c r="N304" s="17" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="305" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A305" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="B305" s="17" t="s">
+        <v>922</v>
+      </c>
+      <c r="C305" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D305" s="17" t="s">
+        <v>916</v>
+      </c>
+      <c r="E305" s="18">
+        <v>2586.4</v>
+      </c>
+      <c r="F305" s="17" t="s">
+        <v>909</v>
+      </c>
+      <c r="G305" s="18">
+        <v>2601.5</v>
+      </c>
+      <c r="H305" s="18">
+        <v>2589</v>
+      </c>
+      <c r="I305" s="18">
+        <v>2596.1</v>
+      </c>
+      <c r="J305" s="17"/>
+      <c r="K305" s="17"/>
+      <c r="L305" s="17"/>
+      <c r="M305" s="17"/>
+      <c r="N305" s="17" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="306" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A306" s="17" t="s">
+        <v>924</v>
+      </c>
+      <c r="B306" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="C306" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D306" s="17" t="s">
+        <v>895</v>
+      </c>
+      <c r="E306" s="18">
+        <v>1356.7</v>
+      </c>
+      <c r="F306" s="17" t="s">
+        <v>909</v>
+      </c>
+      <c r="G306" s="18">
+        <v>1408.4</v>
+      </c>
+      <c r="H306" s="18">
+        <v>1401.8</v>
+      </c>
+      <c r="I306" s="18">
+        <v>1406.2</v>
+      </c>
+      <c r="J306" s="17"/>
+      <c r="K306" s="17"/>
+      <c r="L306" s="17"/>
+      <c r="M306" s="17"/>
+      <c r="N306" s="17" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="307" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A307" s="17" t="s">
+        <v>925</v>
+      </c>
+      <c r="B307" s="17" t="s">
+        <v>499</v>
+      </c>
+      <c r="C307" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D307" s="17" t="s">
+        <v>914</v>
+      </c>
+      <c r="E307" s="18">
+        <v>717.5</v>
+      </c>
+      <c r="F307" s="17" t="s">
+        <v>909</v>
+      </c>
+      <c r="G307" s="18">
+        <v>723.7</v>
+      </c>
+      <c r="H307" s="18">
+        <v>718.15</v>
+      </c>
+      <c r="I307" s="18">
+        <v>722.15</v>
+      </c>
+      <c r="J307" s="17"/>
+      <c r="K307" s="17"/>
+      <c r="L307" s="17"/>
+      <c r="M307" s="17"/>
+      <c r="N307" s="17" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="308" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A308" s="17" t="s">
+        <v>926</v>
+      </c>
+      <c r="B308" s="17" t="s">
+        <v>490</v>
+      </c>
+      <c r="C308" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D308" s="17" t="s">
+        <v>919</v>
+      </c>
+      <c r="E308" s="18">
+        <v>1659.3</v>
+      </c>
+      <c r="F308" s="17" t="s">
+        <v>920</v>
+      </c>
+      <c r="G308" s="18">
+        <v>1668</v>
+      </c>
+      <c r="H308" s="18">
+        <v>1658</v>
+      </c>
+      <c r="I308" s="18">
+        <v>1665</v>
+      </c>
+      <c r="J308" s="17"/>
+      <c r="K308" s="17"/>
+      <c r="L308" s="17"/>
+      <c r="M308" s="17"/>
+      <c r="N308" s="17" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="309" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A309" s="17" t="s">
+        <v>928</v>
+      </c>
+      <c r="B309" s="17" t="s">
+        <v>929</v>
+      </c>
+      <c r="C309" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D309" s="17" t="s">
+        <v>897</v>
+      </c>
+      <c r="E309" s="18">
+        <v>713</v>
+      </c>
+      <c r="F309" s="17" t="s">
+        <v>920</v>
+      </c>
+      <c r="G309" s="18">
+        <v>731.95</v>
+      </c>
+      <c r="H309" s="18">
+        <v>725.95</v>
+      </c>
+      <c r="I309" s="18">
+        <v>730</v>
+      </c>
+      <c r="J309" s="17"/>
+      <c r="K309" s="17"/>
+      <c r="L309" s="17"/>
+      <c r="M309" s="17"/>
+      <c r="N309" s="17" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="310" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A310" s="17" t="s">
+        <v>930</v>
+      </c>
+      <c r="B310" s="17" t="s">
+        <v>931</v>
+      </c>
+      <c r="C310" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D310" s="17" t="s">
+        <v>932</v>
+      </c>
+      <c r="E310" s="18">
+        <v>1239.6</v>
+      </c>
+      <c r="F310" s="17" t="s">
+        <v>920</v>
+      </c>
+      <c r="G310" s="18">
+        <v>1254</v>
+      </c>
+      <c r="H310" s="18">
+        <v>1247.1</v>
+      </c>
+      <c r="I310" s="18">
+        <v>1253.5</v>
+      </c>
+      <c r="J310" s="17"/>
+      <c r="K310" s="17"/>
+      <c r="L310" s="17"/>
+      <c r="M310" s="17"/>
+      <c r="N310" s="17" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="311" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A311" s="17" t="s">
+        <v>933</v>
+      </c>
+      <c r="B311" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C311" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D311" s="17" t="s">
+        <v>911</v>
+      </c>
+      <c r="E311" s="18">
+        <v>1628</v>
+      </c>
+      <c r="F311" s="17" t="s">
+        <v>920</v>
+      </c>
+      <c r="G311" s="18">
+        <v>1631</v>
+      </c>
+      <c r="H311" s="18">
+        <v>1619</v>
+      </c>
+      <c r="I311" s="18">
+        <v>1631</v>
+      </c>
+      <c r="J311" s="17"/>
+      <c r="K311" s="17"/>
+      <c r="L311" s="17"/>
+      <c r="M311" s="17"/>
+      <c r="N311" s="17" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="312" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A312" s="17" t="s">
+        <v>934</v>
+      </c>
+      <c r="B312" s="17" t="s">
+        <v>788</v>
+      </c>
+      <c r="C312" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D312" s="17" t="s">
+        <v>935</v>
+      </c>
+      <c r="E312" s="18">
+        <v>2199</v>
+      </c>
+      <c r="F312" s="17" t="s">
+        <v>920</v>
+      </c>
+      <c r="G312" s="18">
+        <v>2210.7</v>
+      </c>
+      <c r="H312" s="18">
+        <v>2191.4</v>
+      </c>
+      <c r="I312" s="18">
+        <v>2210.4</v>
+      </c>
+      <c r="J312" s="17"/>
+      <c r="K312" s="17"/>
+      <c r="L312" s="17"/>
+      <c r="M312" s="17"/>
+      <c r="N312" s="17" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="313" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A313" s="17" t="s">
+        <v>936</v>
+      </c>
+      <c r="B313" s="17" t="s">
+        <v>937</v>
+      </c>
+      <c r="C313" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D313" s="17" t="s">
+        <v>938</v>
+      </c>
+      <c r="E313" s="18">
+        <v>582.5</v>
+      </c>
+      <c r="F313" s="17" t="s">
+        <v>920</v>
+      </c>
+      <c r="G313" s="18">
+        <v>587</v>
+      </c>
+      <c r="H313" s="18">
+        <v>583.05</v>
+      </c>
+      <c r="I313" s="18">
+        <v>585.3</v>
+      </c>
+      <c r="J313" s="17"/>
+      <c r="K313" s="17"/>
+      <c r="L313" s="17"/>
+      <c r="M313" s="17"/>
+      <c r="N313" s="17" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="314" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A314" s="17" t="s">
+        <v>939</v>
+      </c>
+      <c r="B314" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="C314" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D314" s="17" t="s">
+        <v>916</v>
+      </c>
+      <c r="E314" s="18">
+        <v>423</v>
+      </c>
+      <c r="F314" s="17" t="s">
+        <v>920</v>
+      </c>
+      <c r="G314" s="18">
+        <v>427.7</v>
+      </c>
+      <c r="H314" s="18">
+        <v>424.15</v>
+      </c>
+      <c r="I314" s="18">
+        <v>426.5</v>
+      </c>
+      <c r="J314" s="17"/>
+      <c r="K314" s="17"/>
+      <c r="L314" s="17"/>
+      <c r="M314" s="17"/>
+      <c r="N314" s="17" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="315" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A315" s="17" t="s">
+        <v>940</v>
+      </c>
+      <c r="B315" s="17" t="s">
+        <v>941</v>
+      </c>
+      <c r="C315" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D315" s="17" t="s">
+        <v>942</v>
+      </c>
+      <c r="E315" s="18">
+        <v>255.45</v>
+      </c>
+      <c r="F315" s="17" t="s">
+        <v>920</v>
+      </c>
+      <c r="G315" s="18">
+        <v>258.4</v>
+      </c>
+      <c r="H315" s="18">
+        <v>256.15</v>
+      </c>
+      <c r="I315" s="18">
+        <v>257.05</v>
+      </c>
+      <c r="J315" s="17"/>
+      <c r="K315" s="17"/>
+      <c r="L315" s="17"/>
+      <c r="M315" s="17"/>
+      <c r="N315" s="17" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="316" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A316" s="17" t="s">
+        <v>943</v>
+      </c>
+      <c r="B316" s="17" t="s">
+        <v>763</v>
+      </c>
+      <c r="C316" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D316" s="17" t="s">
+        <v>944</v>
+      </c>
+      <c r="E316" s="18">
+        <v>95.3</v>
+      </c>
+      <c r="F316" s="17" t="s">
+        <v>920</v>
+      </c>
+      <c r="G316" s="18">
+        <v>97</v>
+      </c>
+      <c r="H316" s="18">
+        <v>95.27</v>
+      </c>
+      <c r="I316" s="18">
+        <v>96.35</v>
+      </c>
+      <c r="J316" s="17"/>
+      <c r="K316" s="17"/>
+      <c r="L316" s="17"/>
+      <c r="M316" s="17"/>
+      <c r="N316" s="17" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="317" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A317" s="17" t="s">
+        <v>945</v>
+      </c>
+      <c r="B317" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C317" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D317" s="17" t="s">
+        <v>904</v>
+      </c>
+      <c r="E317" s="18">
+        <v>116.69</v>
+      </c>
+      <c r="F317" s="17" t="s">
+        <v>920</v>
+      </c>
+      <c r="G317" s="18">
+        <v>117.5</v>
+      </c>
+      <c r="H317" s="18">
+        <v>116.55</v>
+      </c>
+      <c r="I317" s="18">
+        <v>117.31</v>
+      </c>
+      <c r="J317" s="17"/>
+      <c r="K317" s="17"/>
+      <c r="L317" s="17"/>
+      <c r="M317" s="17"/>
+      <c r="N317" s="17" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="318" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A318" s="17" t="s">
+        <v>946</v>
+      </c>
+      <c r="B318" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="C318" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D318" s="17" t="s">
+        <v>916</v>
+      </c>
+      <c r="E318" s="18">
+        <v>1040.3</v>
+      </c>
+      <c r="F318" s="17" t="s">
+        <v>920</v>
+      </c>
+      <c r="G318" s="18">
+        <v>1041.9</v>
+      </c>
+      <c r="H318" s="18">
+        <v>1036.1</v>
+      </c>
+      <c r="I318" s="18">
+        <v>1041.9</v>
+      </c>
+      <c r="J318" s="17"/>
+      <c r="K318" s="17"/>
+      <c r="L318" s="17"/>
+      <c r="M318" s="17"/>
+      <c r="N318" s="17" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="319" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A319" s="17" t="s">
+        <v>948</v>
+      </c>
+      <c r="B319" s="17" t="s">
+        <v>949</v>
+      </c>
+      <c r="C319" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D319" s="17" t="s">
+        <v>897</v>
+      </c>
+      <c r="E319" s="18">
+        <v>2341.1</v>
+      </c>
+      <c r="F319" s="17" t="s">
+        <v>920</v>
+      </c>
+      <c r="G319" s="18">
+        <v>2346.3</v>
+      </c>
+      <c r="H319" s="18">
+        <v>2332.8</v>
+      </c>
+      <c r="I319" s="18">
+        <v>2345</v>
+      </c>
+      <c r="J319" s="17"/>
+      <c r="K319" s="17"/>
+      <c r="L319" s="17"/>
+      <c r="M319" s="17"/>
+      <c r="N319" s="17" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="320" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A320" s="17" t="s">
+        <v>950</v>
+      </c>
+      <c r="B320" s="17" t="s">
+        <v>951</v>
+      </c>
+      <c r="C320" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D320" s="17" t="s">
+        <v>903</v>
+      </c>
+      <c r="E320" s="18">
+        <v>86.6</v>
+      </c>
+      <c r="F320" s="17" t="s">
+        <v>920</v>
+      </c>
+      <c r="G320" s="18">
+        <v>87.5</v>
+      </c>
+      <c r="H320" s="18">
+        <v>86.77</v>
+      </c>
+      <c r="I320" s="18">
+        <v>87.2</v>
+      </c>
+      <c r="J320" s="17"/>
+      <c r="K320" s="17"/>
+      <c r="L320" s="17"/>
+      <c r="M320" s="17"/>
+      <c r="N320" s="17" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="321" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A321" s="17" t="s">
+        <v>952</v>
+      </c>
+      <c r="B321" s="17" t="s">
+        <v>953</v>
+      </c>
+      <c r="C321" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D321" s="17" t="s">
+        <v>938</v>
+      </c>
+      <c r="E321" s="18">
+        <v>1485.9</v>
+      </c>
+      <c r="F321" s="17" t="s">
+        <v>920</v>
+      </c>
+      <c r="G321" s="18">
+        <v>1506</v>
+      </c>
+      <c r="H321" s="18">
+        <v>1489</v>
+      </c>
+      <c r="I321" s="18">
+        <v>1506</v>
+      </c>
+      <c r="J321" s="17"/>
+      <c r="K321" s="17"/>
+      <c r="L321" s="17"/>
+      <c r="M321" s="17"/>
+      <c r="N321" s="17" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="322" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A322" s="17" t="s">
+        <v>954</v>
+      </c>
+      <c r="B322" s="17" t="s">
+        <v>599</v>
+      </c>
+      <c r="C322" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D322" s="17" t="s">
+        <v>911</v>
+      </c>
+      <c r="E322" s="18">
+        <v>781</v>
+      </c>
+      <c r="F322" s="17" t="s">
+        <v>920</v>
+      </c>
+      <c r="G322" s="18">
+        <v>797</v>
+      </c>
+      <c r="H322" s="18">
+        <v>788.95</v>
+      </c>
+      <c r="I322" s="18">
+        <v>797</v>
+      </c>
+      <c r="J322" s="17"/>
+      <c r="K322" s="17"/>
+      <c r="L322" s="17"/>
+      <c r="M322" s="17"/>
+      <c r="N322" s="17" t="s">
+        <v>947</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pattern_signals.xlsx
+++ b/pattern_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1996" uniqueCount="955">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2230" uniqueCount="1033">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -2879,6 +2879,240 @@
   </si>
   <si>
     <t>NSE:PNBHOUSING-EQ_BULL_1773127800_1773135900</t>
+  </si>
+  <si>
+    <t>NSE:ADANIENSOL-EQ_BULL_1773118800_1773200700</t>
+  </si>
+  <si>
+    <t>2026-03-10 10:30</t>
+  </si>
+  <si>
+    <t>2026-03-11 09:15</t>
+  </si>
+  <si>
+    <t>2026-03-11 09:30</t>
+  </si>
+  <si>
+    <t>NSE:ANGELONE-EQ_BULL_1773128700_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:ANGELONE-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-10 13:15</t>
+  </si>
+  <si>
+    <t>NSE:COALINDIA-EQ_BULL_1773127800_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:CAMS-EQ_BULL_1773116100_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:CAMS-EQ</t>
+  </si>
+  <si>
+    <t>NSE:CYIENT-EQ_BULL_1773126900_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:CYIENT-EQ</t>
+  </si>
+  <si>
+    <t>NSE:HAVELLS-EQ_BULL_1773118800_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:HEROMOTOCO-EQ_BULL_1773117900_1773200700</t>
+  </si>
+  <si>
+    <t>2026-03-10 10:15</t>
+  </si>
+  <si>
+    <t>NSE:HINDALCO-EQ_BULL_1773131400_1773200700</t>
+  </si>
+  <si>
+    <t>2026-03-11 09:31</t>
+  </si>
+  <si>
+    <t>NSE:HUDCO-EQ_BULL_1773125100_1773200700</t>
+  </si>
+  <si>
+    <t>2026-03-10 12:15</t>
+  </si>
+  <si>
+    <t>NSE:IRFC-EQ_BULL_1773126000_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:INDIGO-EQ_BULL_1773130500_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:INDIGO-EQ</t>
+  </si>
+  <si>
+    <t>NSE:JINDALSTEL-EQ_BULL_1773123300_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:JSWENERGY-EQ_BULL_1773117900_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:MUTHOOTFIN-EQ_BEAR_1773129600_1773200700</t>
+  </si>
+  <si>
+    <t>2026-03-10 13:30</t>
+  </si>
+  <si>
+    <t>NSE:POLICYBZR-EQ_BULL_1773119700_1773200700</t>
+  </si>
+  <si>
+    <t>2026-03-10 10:45</t>
+  </si>
+  <si>
+    <t>NSE:SAMMAANCAP-EQ_BULL_1773134100_1773200700</t>
+  </si>
+  <si>
+    <t>2026-03-11 09:32</t>
+  </si>
+  <si>
+    <t>NSE:MOTHERSON-EQ_BULL_1773132300_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:SIEMENS-EQ_BULL_1773116100_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:SIEMENS-EQ</t>
+  </si>
+  <si>
+    <t>NSE:SUZLON-EQ_BULL_1773120600_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:SUZLON-EQ</t>
+  </si>
+  <si>
+    <t>NSE:TATAPOWER-EQ_BULL_1773116100_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:INFY-EQ_BEAR_1773115200_1773201600</t>
+  </si>
+  <si>
+    <t>2026-03-11 09:45</t>
+  </si>
+  <si>
+    <t>NSE:KAYNES-EQ_BULL_1773119700_1773201600</t>
+  </si>
+  <si>
+    <t>NSE:UNOMINDA-EQ_BEAR_1773126900_1773202500</t>
+  </si>
+  <si>
+    <t>2026-03-11 10:02</t>
+  </si>
+  <si>
+    <t>NSE:HFCL-EQ_BULL_1773117000_1773207000</t>
+  </si>
+  <si>
+    <t>2026-03-11 11:00</t>
+  </si>
+  <si>
+    <t>2026-03-11 11:15</t>
+  </si>
+  <si>
+    <t>NSE:POWERINDIA-EQ_BEAR_1773130500_1773210600</t>
+  </si>
+  <si>
+    <t>2026-03-11 12:00</t>
+  </si>
+  <si>
+    <t>2026-03-11 12:15</t>
+  </si>
+  <si>
+    <t>NSE:COLPAL-EQ_BEAR_1773200700_1773214200</t>
+  </si>
+  <si>
+    <t>2026-03-11 13:00</t>
+  </si>
+  <si>
+    <t>2026-03-11 13:15</t>
+  </si>
+  <si>
+    <t>NSE:APLAPOLLO-EQ_BEAR_1773126000_1773215100</t>
+  </si>
+  <si>
+    <t>2026-03-11 13:30</t>
+  </si>
+  <si>
+    <t>NSE:MFSL-EQ_BULL_1773130500_1773216900</t>
+  </si>
+  <si>
+    <t>2026-03-11 13:45</t>
+  </si>
+  <si>
+    <t>2026-03-11 14:01</t>
+  </si>
+  <si>
+    <t>NSE:ALKEM-EQ_BULL_1773117000_1773218700</t>
+  </si>
+  <si>
+    <t>2026-03-11 14:15</t>
+  </si>
+  <si>
+    <t>2026-03-11 14:30</t>
+  </si>
+  <si>
+    <t>NSE:ASTRAL-EQ_BULL_1773123300_1773218700</t>
+  </si>
+  <si>
+    <t>NSE:BANDHANBNK-EQ_BULL_1773126900_1773218700</t>
+  </si>
+  <si>
+    <t>NSE:NYKAA-EQ_BEAR_1773214200_1773219600</t>
+  </si>
+  <si>
+    <t>2026-03-11 14:45</t>
+  </si>
+  <si>
+    <t>NSE:EXIDEIND-EQ_BEAR_1773207900_1773220500</t>
+  </si>
+  <si>
+    <t>2026-03-11 15:00</t>
+  </si>
+  <si>
+    <t>NSE:MARICO-EQ_BEAR_1773203400_1773221400</t>
+  </si>
+  <si>
+    <t>2026-03-11 10:00</t>
+  </si>
+  <si>
+    <t>2026-03-11 15:16</t>
+  </si>
+  <si>
+    <t>NSE:PATANJALI-EQ_BEAR_1773207900_1773221400</t>
+  </si>
+  <si>
+    <t>NSE:RBLBANK-EQ_BEAR_1773209700_1773221400</t>
+  </si>
+  <si>
+    <t>NSE:RBLBANK-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-11 11:45</t>
+  </si>
+  <si>
+    <t>NSE:MOTHERSON-EQ_BEAR_1773210600_1773221400</t>
+  </si>
+  <si>
+    <t>NSE:INDHOTEL-EQ_BEAR_1773207900_1773221400</t>
+  </si>
+  <si>
+    <t>NSE:INDHOTEL-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-11 15:17</t>
+  </si>
+  <si>
+    <t>NSE:PAGEIND-EQ_BULL_1773201600_1773222300</t>
+  </si>
+  <si>
+    <t>2026-03-11 15:15</t>
+  </si>
+  <si>
+    <t>2026-03-11 15:31</t>
   </si>
 </sst>
 </file>
@@ -3354,7 +3588,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N322"/>
+  <dimension ref="A1:N361"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -14627,6 +14861,1410 @@
         <v>947</v>
       </c>
     </row>
+    <row r="323" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A323" s="17" t="s">
+        <v>955</v>
+      </c>
+      <c r="B323" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="C323" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D323" s="17" t="s">
+        <v>956</v>
+      </c>
+      <c r="E323" s="18">
+        <v>1002.1</v>
+      </c>
+      <c r="F323" s="17" t="s">
+        <v>957</v>
+      </c>
+      <c r="G323" s="18">
+        <v>1031.6</v>
+      </c>
+      <c r="H323" s="18">
+        <v>1010</v>
+      </c>
+      <c r="I323" s="18">
+        <v>1027.8</v>
+      </c>
+      <c r="J323" s="17"/>
+      <c r="K323" s="17"/>
+      <c r="L323" s="17"/>
+      <c r="M323" s="17"/>
+      <c r="N323" s="17" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="324" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A324" s="17" t="s">
+        <v>959</v>
+      </c>
+      <c r="B324" s="17" t="s">
+        <v>960</v>
+      </c>
+      <c r="C324" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D324" s="17" t="s">
+        <v>961</v>
+      </c>
+      <c r="E324" s="18">
+        <v>224.07</v>
+      </c>
+      <c r="F324" s="17" t="s">
+        <v>957</v>
+      </c>
+      <c r="G324" s="18">
+        <v>227.7</v>
+      </c>
+      <c r="H324" s="18">
+        <v>224.61</v>
+      </c>
+      <c r="I324" s="18">
+        <v>226.09</v>
+      </c>
+      <c r="J324" s="17"/>
+      <c r="K324" s="17"/>
+      <c r="L324" s="17"/>
+      <c r="M324" s="17"/>
+      <c r="N324" s="17" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="325" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A325" s="17" t="s">
+        <v>962</v>
+      </c>
+      <c r="B325" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C325" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D325" s="17" t="s">
+        <v>911</v>
+      </c>
+      <c r="E325" s="18">
+        <v>442.2</v>
+      </c>
+      <c r="F325" s="17" t="s">
+        <v>957</v>
+      </c>
+      <c r="G325" s="18">
+        <v>451.8</v>
+      </c>
+      <c r="H325" s="18">
+        <v>445.15</v>
+      </c>
+      <c r="I325" s="18">
+        <v>447.1</v>
+      </c>
+      <c r="J325" s="17"/>
+      <c r="K325" s="17"/>
+      <c r="L325" s="17"/>
+      <c r="M325" s="17"/>
+      <c r="N325" s="17" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="326" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A326" s="17" t="s">
+        <v>963</v>
+      </c>
+      <c r="B326" s="17" t="s">
+        <v>964</v>
+      </c>
+      <c r="C326" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D326" s="17" t="s">
+        <v>895</v>
+      </c>
+      <c r="E326" s="18">
+        <v>662.15</v>
+      </c>
+      <c r="F326" s="17" t="s">
+        <v>957</v>
+      </c>
+      <c r="G326" s="18">
+        <v>680.5</v>
+      </c>
+      <c r="H326" s="18">
+        <v>671.9</v>
+      </c>
+      <c r="I326" s="18">
+        <v>674.1</v>
+      </c>
+      <c r="J326" s="17"/>
+      <c r="K326" s="17"/>
+      <c r="L326" s="17"/>
+      <c r="M326" s="17"/>
+      <c r="N326" s="17" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="327" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A327" s="17" t="s">
+        <v>965</v>
+      </c>
+      <c r="B327" s="17" t="s">
+        <v>966</v>
+      </c>
+      <c r="C327" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D327" s="17" t="s">
+        <v>942</v>
+      </c>
+      <c r="E327" s="18">
+        <v>888.55</v>
+      </c>
+      <c r="F327" s="17" t="s">
+        <v>957</v>
+      </c>
+      <c r="G327" s="18">
+        <v>928</v>
+      </c>
+      <c r="H327" s="18">
+        <v>900</v>
+      </c>
+      <c r="I327" s="18">
+        <v>924.65</v>
+      </c>
+      <c r="J327" s="17"/>
+      <c r="K327" s="17"/>
+      <c r="L327" s="17"/>
+      <c r="M327" s="17"/>
+      <c r="N327" s="17" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="328" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A328" s="17" t="s">
+        <v>967</v>
+      </c>
+      <c r="B328" s="17" t="s">
+        <v>718</v>
+      </c>
+      <c r="C328" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D328" s="17" t="s">
+        <v>956</v>
+      </c>
+      <c r="E328" s="18">
+        <v>1365.3</v>
+      </c>
+      <c r="F328" s="17" t="s">
+        <v>957</v>
+      </c>
+      <c r="G328" s="18">
+        <v>1404.6</v>
+      </c>
+      <c r="H328" s="18">
+        <v>1359.8</v>
+      </c>
+      <c r="I328" s="18">
+        <v>1397.4</v>
+      </c>
+      <c r="J328" s="17"/>
+      <c r="K328" s="17"/>
+      <c r="L328" s="17"/>
+      <c r="M328" s="17"/>
+      <c r="N328" s="17" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="329" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A329" s="17" t="s">
+        <v>968</v>
+      </c>
+      <c r="B329" s="17" t="s">
+        <v>525</v>
+      </c>
+      <c r="C329" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D329" s="17" t="s">
+        <v>969</v>
+      </c>
+      <c r="E329" s="18">
+        <v>5594.5</v>
+      </c>
+      <c r="F329" s="17" t="s">
+        <v>957</v>
+      </c>
+      <c r="G329" s="18">
+        <v>5766</v>
+      </c>
+      <c r="H329" s="18">
+        <v>5700.5</v>
+      </c>
+      <c r="I329" s="18">
+        <v>5750</v>
+      </c>
+      <c r="J329" s="17"/>
+      <c r="K329" s="17"/>
+      <c r="L329" s="17"/>
+      <c r="M329" s="17"/>
+      <c r="N329" s="17" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="330" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A330" s="17" t="s">
+        <v>970</v>
+      </c>
+      <c r="B330" s="17" t="s">
+        <v>890</v>
+      </c>
+      <c r="C330" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D330" s="17" t="s">
+        <v>935</v>
+      </c>
+      <c r="E330" s="18">
+        <v>954.1</v>
+      </c>
+      <c r="F330" s="17" t="s">
+        <v>957</v>
+      </c>
+      <c r="G330" s="18">
+        <v>972.9</v>
+      </c>
+      <c r="H330" s="18">
+        <v>957</v>
+      </c>
+      <c r="I330" s="18">
+        <v>972.8</v>
+      </c>
+      <c r="J330" s="17"/>
+      <c r="K330" s="17"/>
+      <c r="L330" s="17"/>
+      <c r="M330" s="17"/>
+      <c r="N330" s="17" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="331" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A331" s="17" t="s">
+        <v>972</v>
+      </c>
+      <c r="B331" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="C331" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D331" s="17" t="s">
+        <v>973</v>
+      </c>
+      <c r="E331" s="18">
+        <v>177.26</v>
+      </c>
+      <c r="F331" s="17" t="s">
+        <v>957</v>
+      </c>
+      <c r="G331" s="18">
+        <v>182.1</v>
+      </c>
+      <c r="H331" s="18">
+        <v>179.09</v>
+      </c>
+      <c r="I331" s="18">
+        <v>181.31</v>
+      </c>
+      <c r="J331" s="17"/>
+      <c r="K331" s="17"/>
+      <c r="L331" s="17"/>
+      <c r="M331" s="17"/>
+      <c r="N331" s="17" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="332" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A332" s="17" t="s">
+        <v>974</v>
+      </c>
+      <c r="B332" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C332" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D332" s="17" t="s">
+        <v>914</v>
+      </c>
+      <c r="E332" s="18">
+        <v>99.19</v>
+      </c>
+      <c r="F332" s="17" t="s">
+        <v>957</v>
+      </c>
+      <c r="G332" s="18">
+        <v>101.79</v>
+      </c>
+      <c r="H332" s="18">
+        <v>100.44</v>
+      </c>
+      <c r="I332" s="18">
+        <v>101.21</v>
+      </c>
+      <c r="J332" s="17"/>
+      <c r="K332" s="17"/>
+      <c r="L332" s="17"/>
+      <c r="M332" s="17"/>
+      <c r="N332" s="17" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="333" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A333" s="17" t="s">
+        <v>975</v>
+      </c>
+      <c r="B333" s="17" t="s">
+        <v>976</v>
+      </c>
+      <c r="C333" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D333" s="17" t="s">
+        <v>944</v>
+      </c>
+      <c r="E333" s="18">
+        <v>4409.7</v>
+      </c>
+      <c r="F333" s="17" t="s">
+        <v>957</v>
+      </c>
+      <c r="G333" s="18">
+        <v>4502.9</v>
+      </c>
+      <c r="H333" s="18">
+        <v>4366</v>
+      </c>
+      <c r="I333" s="18">
+        <v>4498.7</v>
+      </c>
+      <c r="J333" s="17"/>
+      <c r="K333" s="17"/>
+      <c r="L333" s="17"/>
+      <c r="M333" s="17"/>
+      <c r="N333" s="17" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="334" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A334" s="17" t="s">
+        <v>977</v>
+      </c>
+      <c r="B334" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="C334" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D334" s="17" t="s">
+        <v>919</v>
+      </c>
+      <c r="E334" s="18">
+        <v>1186.8</v>
+      </c>
+      <c r="F334" s="17" t="s">
+        <v>957</v>
+      </c>
+      <c r="G334" s="18">
+        <v>1201.5</v>
+      </c>
+      <c r="H334" s="18">
+        <v>1186.1</v>
+      </c>
+      <c r="I334" s="18">
+        <v>1199</v>
+      </c>
+      <c r="J334" s="17"/>
+      <c r="K334" s="17"/>
+      <c r="L334" s="17"/>
+      <c r="M334" s="17"/>
+      <c r="N334" s="17" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="335" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A335" s="17" t="s">
+        <v>978</v>
+      </c>
+      <c r="B335" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="C335" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D335" s="17" t="s">
+        <v>969</v>
+      </c>
+      <c r="E335" s="18">
+        <v>487.8</v>
+      </c>
+      <c r="F335" s="17" t="s">
+        <v>957</v>
+      </c>
+      <c r="G335" s="18">
+        <v>498.5</v>
+      </c>
+      <c r="H335" s="18">
+        <v>488.8</v>
+      </c>
+      <c r="I335" s="18">
+        <v>497.6</v>
+      </c>
+      <c r="J335" s="17"/>
+      <c r="K335" s="17"/>
+      <c r="L335" s="17"/>
+      <c r="M335" s="17"/>
+      <c r="N335" s="17" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="336" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A336" s="19" t="s">
+        <v>979</v>
+      </c>
+      <c r="B336" s="19" t="s">
+        <v>664</v>
+      </c>
+      <c r="C336" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D336" s="19" t="s">
+        <v>980</v>
+      </c>
+      <c r="E336" s="20">
+        <v>3274.6</v>
+      </c>
+      <c r="F336" s="19" t="s">
+        <v>957</v>
+      </c>
+      <c r="G336" s="20">
+        <v>3302.4</v>
+      </c>
+      <c r="H336" s="20">
+        <v>3260.6</v>
+      </c>
+      <c r="I336" s="20">
+        <v>3265</v>
+      </c>
+      <c r="J336" s="19"/>
+      <c r="K336" s="19"/>
+      <c r="L336" s="19"/>
+      <c r="M336" s="19"/>
+      <c r="N336" s="19" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="337" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A337" s="17" t="s">
+        <v>981</v>
+      </c>
+      <c r="B337" s="17" t="s">
+        <v>458</v>
+      </c>
+      <c r="C337" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D337" s="17" t="s">
+        <v>982</v>
+      </c>
+      <c r="E337" s="18">
+        <v>1461.9</v>
+      </c>
+      <c r="F337" s="17" t="s">
+        <v>957</v>
+      </c>
+      <c r="G337" s="18">
+        <v>1488.6</v>
+      </c>
+      <c r="H337" s="18">
+        <v>1449.1</v>
+      </c>
+      <c r="I337" s="18">
+        <v>1480.4</v>
+      </c>
+      <c r="J337" s="17"/>
+      <c r="K337" s="17"/>
+      <c r="L337" s="17"/>
+      <c r="M337" s="17"/>
+      <c r="N337" s="17" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="338" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A338" s="17" t="s">
+        <v>983</v>
+      </c>
+      <c r="B338" s="17" t="s">
+        <v>552</v>
+      </c>
+      <c r="C338" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D338" s="17" t="s">
+        <v>912</v>
+      </c>
+      <c r="E338" s="18">
+        <v>145.18</v>
+      </c>
+      <c r="F338" s="17" t="s">
+        <v>957</v>
+      </c>
+      <c r="G338" s="18">
+        <v>149.2</v>
+      </c>
+      <c r="H338" s="18">
+        <v>144.85</v>
+      </c>
+      <c r="I338" s="18">
+        <v>148.35</v>
+      </c>
+      <c r="J338" s="17"/>
+      <c r="K338" s="17"/>
+      <c r="L338" s="17"/>
+      <c r="M338" s="17"/>
+      <c r="N338" s="17" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="339" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A339" s="17" t="s">
+        <v>985</v>
+      </c>
+      <c r="B339" s="17" t="s">
+        <v>641</v>
+      </c>
+      <c r="C339" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D339" s="17" t="s">
+        <v>903</v>
+      </c>
+      <c r="E339" s="18">
+        <v>122.98</v>
+      </c>
+      <c r="F339" s="17" t="s">
+        <v>957</v>
+      </c>
+      <c r="G339" s="18">
+        <v>125.98</v>
+      </c>
+      <c r="H339" s="18">
+        <v>122.85</v>
+      </c>
+      <c r="I339" s="18">
+        <v>125.66</v>
+      </c>
+      <c r="J339" s="17"/>
+      <c r="K339" s="17"/>
+      <c r="L339" s="17"/>
+      <c r="M339" s="17"/>
+      <c r="N339" s="17" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="340" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A340" s="17" t="s">
+        <v>986</v>
+      </c>
+      <c r="B340" s="17" t="s">
+        <v>987</v>
+      </c>
+      <c r="C340" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D340" s="17" t="s">
+        <v>895</v>
+      </c>
+      <c r="E340" s="18">
+        <v>3303.7</v>
+      </c>
+      <c r="F340" s="17" t="s">
+        <v>957</v>
+      </c>
+      <c r="G340" s="18">
+        <v>3344.6</v>
+      </c>
+      <c r="H340" s="18">
+        <v>3284</v>
+      </c>
+      <c r="I340" s="18">
+        <v>3334.1</v>
+      </c>
+      <c r="J340" s="17"/>
+      <c r="K340" s="17"/>
+      <c r="L340" s="17"/>
+      <c r="M340" s="17"/>
+      <c r="N340" s="17" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="341" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A341" s="17" t="s">
+        <v>988</v>
+      </c>
+      <c r="B341" s="17" t="s">
+        <v>989</v>
+      </c>
+      <c r="C341" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D341" s="17" t="s">
+        <v>932</v>
+      </c>
+      <c r="E341" s="18">
+        <v>40.67</v>
+      </c>
+      <c r="F341" s="17" t="s">
+        <v>957</v>
+      </c>
+      <c r="G341" s="18">
+        <v>42.06</v>
+      </c>
+      <c r="H341" s="18">
+        <v>41.49</v>
+      </c>
+      <c r="I341" s="18">
+        <v>41.75</v>
+      </c>
+      <c r="J341" s="17"/>
+      <c r="K341" s="17"/>
+      <c r="L341" s="17"/>
+      <c r="M341" s="17"/>
+      <c r="N341" s="17" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="342" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A342" s="17" t="s">
+        <v>990</v>
+      </c>
+      <c r="B342" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="C342" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D342" s="17" t="s">
+        <v>895</v>
+      </c>
+      <c r="E342" s="18">
+        <v>377.9</v>
+      </c>
+      <c r="F342" s="17" t="s">
+        <v>957</v>
+      </c>
+      <c r="G342" s="18">
+        <v>390.35</v>
+      </c>
+      <c r="H342" s="18">
+        <v>382.35</v>
+      </c>
+      <c r="I342" s="18">
+        <v>389</v>
+      </c>
+      <c r="J342" s="17"/>
+      <c r="K342" s="17"/>
+      <c r="L342" s="17"/>
+      <c r="M342" s="17"/>
+      <c r="N342" s="17" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="343" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A343" s="19" t="s">
+        <v>991</v>
+      </c>
+      <c r="B343" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="C343" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D343" s="19" t="s">
+        <v>884</v>
+      </c>
+      <c r="E343" s="20">
+        <v>1298.5</v>
+      </c>
+      <c r="F343" s="19" t="s">
+        <v>958</v>
+      </c>
+      <c r="G343" s="20">
+        <v>1293.8</v>
+      </c>
+      <c r="H343" s="20">
+        <v>1286.1</v>
+      </c>
+      <c r="I343" s="20">
+        <v>1287.2</v>
+      </c>
+      <c r="J343" s="19"/>
+      <c r="K343" s="19"/>
+      <c r="L343" s="19"/>
+      <c r="M343" s="19"/>
+      <c r="N343" s="19" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="344" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A344" s="17" t="s">
+        <v>993</v>
+      </c>
+      <c r="B344" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="C344" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D344" s="17" t="s">
+        <v>982</v>
+      </c>
+      <c r="E344" s="18">
+        <v>3765.9</v>
+      </c>
+      <c r="F344" s="17" t="s">
+        <v>958</v>
+      </c>
+      <c r="G344" s="18">
+        <v>3866</v>
+      </c>
+      <c r="H344" s="18">
+        <v>3789</v>
+      </c>
+      <c r="I344" s="18">
+        <v>3861.9</v>
+      </c>
+      <c r="J344" s="17"/>
+      <c r="K344" s="17"/>
+      <c r="L344" s="17"/>
+      <c r="M344" s="17"/>
+      <c r="N344" s="17" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="345" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A345" s="19" t="s">
+        <v>994</v>
+      </c>
+      <c r="B345" s="19" t="s">
+        <v>562</v>
+      </c>
+      <c r="C345" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D345" s="19" t="s">
+        <v>942</v>
+      </c>
+      <c r="E345" s="20">
+        <v>1103.6</v>
+      </c>
+      <c r="F345" s="19" t="s">
+        <v>992</v>
+      </c>
+      <c r="G345" s="20">
+        <v>1114.4</v>
+      </c>
+      <c r="H345" s="20">
+        <v>1103</v>
+      </c>
+      <c r="I345" s="20">
+        <v>1103.7</v>
+      </c>
+      <c r="J345" s="19"/>
+      <c r="K345" s="19"/>
+      <c r="L345" s="19"/>
+      <c r="M345" s="19"/>
+      <c r="N345" s="19" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="346" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A346" s="17" t="s">
+        <v>996</v>
+      </c>
+      <c r="B346" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C346" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D346" s="17" t="s">
+        <v>897</v>
+      </c>
+      <c r="E346" s="18">
+        <v>69.25</v>
+      </c>
+      <c r="F346" s="17" t="s">
+        <v>997</v>
+      </c>
+      <c r="G346" s="18">
+        <v>71.65</v>
+      </c>
+      <c r="H346" s="18">
+        <v>70.62</v>
+      </c>
+      <c r="I346" s="18">
+        <v>71.13</v>
+      </c>
+      <c r="J346" s="17"/>
+      <c r="K346" s="17"/>
+      <c r="L346" s="17"/>
+      <c r="M346" s="17"/>
+      <c r="N346" s="17" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="347" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A347" s="19" t="s">
+        <v>999</v>
+      </c>
+      <c r="B347" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="C347" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D347" s="19" t="s">
+        <v>944</v>
+      </c>
+      <c r="E347" s="20">
+        <v>25275</v>
+      </c>
+      <c r="F347" s="19" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G347" s="20">
+        <v>25165</v>
+      </c>
+      <c r="H347" s="20">
+        <v>24935</v>
+      </c>
+      <c r="I347" s="20">
+        <v>24940</v>
+      </c>
+      <c r="J347" s="19"/>
+      <c r="K347" s="19"/>
+      <c r="L347" s="19"/>
+      <c r="M347" s="19"/>
+      <c r="N347" s="19" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="348" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A348" s="19" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B348" s="19" t="s">
+        <v>788</v>
+      </c>
+      <c r="C348" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D348" s="19" t="s">
+        <v>957</v>
+      </c>
+      <c r="E348" s="20">
+        <v>2144</v>
+      </c>
+      <c r="F348" s="19" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G348" s="20">
+        <v>2078.5</v>
+      </c>
+      <c r="H348" s="20">
+        <v>2066</v>
+      </c>
+      <c r="I348" s="20">
+        <v>2069</v>
+      </c>
+      <c r="J348" s="19"/>
+      <c r="K348" s="19"/>
+      <c r="L348" s="19"/>
+      <c r="M348" s="19"/>
+      <c r="N348" s="19" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="349" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A349" s="19" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B349" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="C349" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D349" s="19" t="s">
+        <v>914</v>
+      </c>
+      <c r="E349" s="20">
+        <v>2122.7</v>
+      </c>
+      <c r="F349" s="19" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G349" s="20">
+        <v>2100.6</v>
+      </c>
+      <c r="H349" s="20">
+        <v>2064</v>
+      </c>
+      <c r="I349" s="20">
+        <v>2067</v>
+      </c>
+      <c r="J349" s="19"/>
+      <c r="K349" s="19"/>
+      <c r="L349" s="19"/>
+      <c r="M349" s="19"/>
+      <c r="N349" s="19" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="350" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A350" s="17" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B350" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="C350" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D350" s="17" t="s">
+        <v>944</v>
+      </c>
+      <c r="E350" s="18">
+        <v>1737</v>
+      </c>
+      <c r="F350" s="17" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G350" s="18">
+        <v>1741.4</v>
+      </c>
+      <c r="H350" s="18">
+        <v>1723.9</v>
+      </c>
+      <c r="I350" s="18">
+        <v>1739.4</v>
+      </c>
+      <c r="J350" s="17"/>
+      <c r="K350" s="17"/>
+      <c r="L350" s="17"/>
+      <c r="M350" s="17"/>
+      <c r="N350" s="17" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="351" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A351" s="17" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B351" s="17" t="s">
+        <v>908</v>
+      </c>
+      <c r="C351" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D351" s="17" t="s">
+        <v>897</v>
+      </c>
+      <c r="E351" s="18">
+        <v>5571.5</v>
+      </c>
+      <c r="F351" s="17" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G351" s="18">
+        <v>5645.5</v>
+      </c>
+      <c r="H351" s="18">
+        <v>5600</v>
+      </c>
+      <c r="I351" s="18">
+        <v>5644.5</v>
+      </c>
+      <c r="J351" s="17"/>
+      <c r="K351" s="17"/>
+      <c r="L351" s="17"/>
+      <c r="M351" s="17"/>
+      <c r="N351" s="17" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="352" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A352" s="17" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B352" s="17" t="s">
+        <v>490</v>
+      </c>
+      <c r="C352" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D352" s="17" t="s">
+        <v>919</v>
+      </c>
+      <c r="E352" s="18">
+        <v>1659.3</v>
+      </c>
+      <c r="F352" s="17" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G352" s="18">
+        <v>1740.6</v>
+      </c>
+      <c r="H352" s="18">
+        <v>1720</v>
+      </c>
+      <c r="I352" s="18">
+        <v>1739.5</v>
+      </c>
+      <c r="J352" s="17"/>
+      <c r="K352" s="17"/>
+      <c r="L352" s="17"/>
+      <c r="M352" s="17"/>
+      <c r="N352" s="17" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="353" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A353" s="17" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B353" s="17" t="s">
+        <v>873</v>
+      </c>
+      <c r="C353" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D353" s="17" t="s">
+        <v>942</v>
+      </c>
+      <c r="E353" s="18">
+        <v>181.1</v>
+      </c>
+      <c r="F353" s="17" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G353" s="18">
+        <v>184.31</v>
+      </c>
+      <c r="H353" s="18">
+        <v>183.1</v>
+      </c>
+      <c r="I353" s="18">
+        <v>184.27</v>
+      </c>
+      <c r="J353" s="17"/>
+      <c r="K353" s="17"/>
+      <c r="L353" s="17"/>
+      <c r="M353" s="17"/>
+      <c r="N353" s="17" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="354" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A354" s="19" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B354" s="19" t="s">
+        <v>941</v>
+      </c>
+      <c r="C354" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D354" s="19" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E354" s="20">
+        <v>253.95</v>
+      </c>
+      <c r="F354" s="19" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G354" s="20">
+        <v>254</v>
+      </c>
+      <c r="H354" s="20">
+        <v>252.6</v>
+      </c>
+      <c r="I354" s="20">
+        <v>252.95</v>
+      </c>
+      <c r="J354" s="19"/>
+      <c r="K354" s="19"/>
+      <c r="L354" s="19"/>
+      <c r="M354" s="19"/>
+      <c r="N354" s="19" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="355" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A355" s="19" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B355" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C355" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D355" s="19" t="s">
+        <v>998</v>
+      </c>
+      <c r="E355" s="20">
+        <v>314.6</v>
+      </c>
+      <c r="F355" s="19" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G355" s="20">
+        <v>312.95</v>
+      </c>
+      <c r="H355" s="20">
+        <v>311.6</v>
+      </c>
+      <c r="I355" s="20">
+        <v>311.75</v>
+      </c>
+      <c r="J355" s="19"/>
+      <c r="K355" s="19"/>
+      <c r="L355" s="19"/>
+      <c r="M355" s="19"/>
+      <c r="N355" s="19" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="356" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A356" s="19" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B356" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="C356" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D356" s="19" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E356" s="20">
+        <v>778</v>
+      </c>
+      <c r="F356" s="19" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G356" s="20">
+        <v>766.05</v>
+      </c>
+      <c r="H356" s="20">
+        <v>760.2</v>
+      </c>
+      <c r="I356" s="20">
+        <v>760.4</v>
+      </c>
+      <c r="J356" s="19"/>
+      <c r="K356" s="19"/>
+      <c r="L356" s="19"/>
+      <c r="M356" s="19"/>
+      <c r="N356" s="19" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="357" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A357" s="19" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B357" s="19" t="s">
+        <v>453</v>
+      </c>
+      <c r="C357" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D357" s="19" t="s">
+        <v>998</v>
+      </c>
+      <c r="E357" s="20">
+        <v>496.2</v>
+      </c>
+      <c r="F357" s="19" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G357" s="20">
+        <v>499.4</v>
+      </c>
+      <c r="H357" s="20">
+        <v>494.2</v>
+      </c>
+      <c r="I357" s="20">
+        <v>494.75</v>
+      </c>
+      <c r="J357" s="19"/>
+      <c r="K357" s="19"/>
+      <c r="L357" s="19"/>
+      <c r="M357" s="19"/>
+      <c r="N357" s="19" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="358" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A358" s="19" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B358" s="19" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C358" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D358" s="19" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E358" s="20">
+        <v>301.2</v>
+      </c>
+      <c r="F358" s="19" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G358" s="20">
+        <v>299.95</v>
+      </c>
+      <c r="H358" s="20">
+        <v>297.15</v>
+      </c>
+      <c r="I358" s="20">
+        <v>297.45</v>
+      </c>
+      <c r="J358" s="19"/>
+      <c r="K358" s="19"/>
+      <c r="L358" s="19"/>
+      <c r="M358" s="19"/>
+      <c r="N358" s="19" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="359" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A359" s="19" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B359" s="19" t="s">
+        <v>641</v>
+      </c>
+      <c r="C359" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D359" s="19" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E359" s="20">
+        <v>122.47</v>
+      </c>
+      <c r="F359" s="19" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G359" s="20">
+        <v>121.74</v>
+      </c>
+      <c r="H359" s="20">
+        <v>121.01</v>
+      </c>
+      <c r="I359" s="20">
+        <v>121.01</v>
+      </c>
+      <c r="J359" s="19"/>
+      <c r="K359" s="19"/>
+      <c r="L359" s="19"/>
+      <c r="M359" s="19"/>
+      <c r="N359" s="19" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="360" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A360" s="19" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B360" s="19" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C360" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D360" s="19" t="s">
+        <v>998</v>
+      </c>
+      <c r="E360" s="20">
+        <v>622.3</v>
+      </c>
+      <c r="F360" s="19" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G360" s="20">
+        <v>626.75</v>
+      </c>
+      <c r="H360" s="20">
+        <v>623.05</v>
+      </c>
+      <c r="I360" s="20">
+        <v>624.1</v>
+      </c>
+      <c r="J360" s="19"/>
+      <c r="K360" s="19"/>
+      <c r="L360" s="19"/>
+      <c r="M360" s="19"/>
+      <c r="N360" s="19" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="361" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A361" s="17" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B361" s="17" t="s">
+        <v>900</v>
+      </c>
+      <c r="C361" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D361" s="17" t="s">
+        <v>958</v>
+      </c>
+      <c r="E361" s="18">
+        <v>31650</v>
+      </c>
+      <c r="F361" s="17" t="s">
+        <v>1031</v>
+      </c>
+      <c r="G361" s="18">
+        <v>31745</v>
+      </c>
+      <c r="H361" s="18">
+        <v>31480</v>
+      </c>
+      <c r="I361" s="18">
+        <v>31745</v>
+      </c>
+      <c r="J361" s="17"/>
+      <c r="K361" s="17"/>
+      <c r="L361" s="17"/>
+      <c r="M361" s="17"/>
+      <c r="N361" s="17" t="s">
+        <v>1032</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pattern_signals.xlsx
+++ b/pattern_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2230" uniqueCount="1033">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2608" uniqueCount="1183">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -3113,6 +3113,456 @@
   </si>
   <si>
     <t>2026-03-11 15:31</t>
+  </si>
+  <si>
+    <t>NSE:HDFCAMC-EQ_BEAR_1773202500_1773287100</t>
+  </si>
+  <si>
+    <t>2026-03-12 09:15</t>
+  </si>
+  <si>
+    <t>2026-03-12 09:30</t>
+  </si>
+  <si>
+    <t>NSE:INDIANB-EQ_BEAR_1773208800_1773287100</t>
+  </si>
+  <si>
+    <t>2026-03-11 11:30</t>
+  </si>
+  <si>
+    <t>NSE:MCX-EQ_BEAR_1773216000_1773287100</t>
+  </si>
+  <si>
+    <t>NSE:MCX-EQ</t>
+  </si>
+  <si>
+    <t>NSE:PIIND-EQ_BEAR_1773202500_1773287100</t>
+  </si>
+  <si>
+    <t>2026-03-12 09:31</t>
+  </si>
+  <si>
+    <t>NSE:SBILIFE-EQ_BEAR_1773204300_1773287100</t>
+  </si>
+  <si>
+    <t>2026-03-11 10:15</t>
+  </si>
+  <si>
+    <t>NSE:SHRIRAMFIN-EQ_BEAR_1773221400_1773287100</t>
+  </si>
+  <si>
+    <t>NSE:OIL-EQ_BULL_1773214200_1773288000</t>
+  </si>
+  <si>
+    <t>2026-03-12 09:46</t>
+  </si>
+  <si>
+    <t>NSE:NTPC-EQ_BULL_1773201600_1773291600</t>
+  </si>
+  <si>
+    <t>2026-03-12 10:30</t>
+  </si>
+  <si>
+    <t>2026-03-12 10:47</t>
+  </si>
+  <si>
+    <t>NSE:APOLLOHOSP-EQ_BEAR_1773206100_1773294300</t>
+  </si>
+  <si>
+    <t>2026-03-11 10:45</t>
+  </si>
+  <si>
+    <t>2026-03-12 11:15</t>
+  </si>
+  <si>
+    <t>2026-03-12 11:30</t>
+  </si>
+  <si>
+    <t>NSE:NATIONALUM-EQ_BULL_1773200700_1773302400</t>
+  </si>
+  <si>
+    <t>NSE:NATIONALUM-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-12 13:30</t>
+  </si>
+  <si>
+    <t>2026-03-12 13:47</t>
+  </si>
+  <si>
+    <t>NSE:KFINTECH-EQ_BEAR_1773221400_1773304200</t>
+  </si>
+  <si>
+    <t>2026-03-12 14:00</t>
+  </si>
+  <si>
+    <t>2026-03-12 14:17</t>
+  </si>
+  <si>
+    <t>NSE:BDL-EQ_BEAR_1773288900_1773305100</t>
+  </si>
+  <si>
+    <t>2026-03-12 09:45</t>
+  </si>
+  <si>
+    <t>2026-03-12 14:15</t>
+  </si>
+  <si>
+    <t>2026-03-12 14:30</t>
+  </si>
+  <si>
+    <t>NSE:NUVAMA-EQ_BEAR_1773217800_1773306900</t>
+  </si>
+  <si>
+    <t>2026-03-11 14:00</t>
+  </si>
+  <si>
+    <t>2026-03-12 14:45</t>
+  </si>
+  <si>
+    <t>2026-03-12 15:02</t>
+  </si>
+  <si>
+    <t>NSE:VOLTAS-EQ_BEAR_1773287100_1773306900</t>
+  </si>
+  <si>
+    <t>2026-03-12 15:03</t>
+  </si>
+  <si>
+    <t>NSE:DALBHARAT-EQ_BULL_1773301500_1773307800</t>
+  </si>
+  <si>
+    <t>NSE:DALBHARAT-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-12 13:15</t>
+  </si>
+  <si>
+    <t>2026-03-12 15:00</t>
+  </si>
+  <si>
+    <t>2026-03-12 15:16</t>
+  </si>
+  <si>
+    <t>NSE:KAYNES-EQ_BEAR_1773218700_1773307800</t>
+  </si>
+  <si>
+    <t>2026-03-12 15:17</t>
+  </si>
+  <si>
+    <t>NSE:TVSMOTOR-EQ_BEAR_1773206100_1773307800</t>
+  </si>
+  <si>
+    <t>2026-03-12 15:18</t>
+  </si>
+  <si>
+    <t>NSE:ADANIENSOL-EQ_BULL_1773295200_1773308700</t>
+  </si>
+  <si>
+    <t>2026-03-12 15:15</t>
+  </si>
+  <si>
+    <t>2026-03-12 15:30</t>
+  </si>
+  <si>
+    <t>NSE:ANGELONE-EQ_BEAR_1773208800_1773308700</t>
+  </si>
+  <si>
+    <t>NSE:UNITDSPR-EQ_BEAR_1773287100_1773308700</t>
+  </si>
+  <si>
+    <t>2026-03-12 15:34</t>
+  </si>
+  <si>
+    <t>NSE:ADANIGREEN-EQ_BULL_1773299700_1773373500</t>
+  </si>
+  <si>
+    <t>NSE:ADANIGREEN-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-12 12:45</t>
+  </si>
+  <si>
+    <t>2026-03-13 09:15</t>
+  </si>
+  <si>
+    <t>2026-03-13 09:30</t>
+  </si>
+  <si>
+    <t>NSE:DMART-EQ_BULL_1773296100_1773373500</t>
+  </si>
+  <si>
+    <t>2026-03-12 11:45</t>
+  </si>
+  <si>
+    <t>NSE:BDL-EQ_BEAR_1773288900_1773373500</t>
+  </si>
+  <si>
+    <t>NSE:HAVELLS-EQ_BEAR_1773288000_1773373500</t>
+  </si>
+  <si>
+    <t>NSE:IREDA-EQ_BULL_1773299700_1773373500</t>
+  </si>
+  <si>
+    <t>2026-03-13 09:31</t>
+  </si>
+  <si>
+    <t>NSE:NHPC-EQ_BULL_1773293400_1773373500</t>
+  </si>
+  <si>
+    <t>NSE:NHPC-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-12 11:00</t>
+  </si>
+  <si>
+    <t>NSE:PAGEIND-EQ_BEAR_1773287100_1773373500</t>
+  </si>
+  <si>
+    <t>NSE:VEDL-EQ_BEAR_1773287100_1773373500</t>
+  </si>
+  <si>
+    <t>2026-03-13 09:32</t>
+  </si>
+  <si>
+    <t>NSE:HUDCO-EQ_BEAR_1773306900_1773374400</t>
+  </si>
+  <si>
+    <t>2026-03-13 09:46</t>
+  </si>
+  <si>
+    <t>NSE:ADANIENT-EQ_BEAR_1773306000_1773375300</t>
+  </si>
+  <si>
+    <t>2026-03-13 09:45</t>
+  </si>
+  <si>
+    <t>2026-03-13 10:00</t>
+  </si>
+  <si>
+    <t>NSE:PPLPHARMA-EQ_BEAR_1773288000_1773375300</t>
+  </si>
+  <si>
+    <t>2026-03-13 10:01</t>
+  </si>
+  <si>
+    <t>NSE:UNITDSPR-EQ_BEAR_1773287100_1773382500</t>
+  </si>
+  <si>
+    <t>2026-03-13 11:45</t>
+  </si>
+  <si>
+    <t>2026-03-13 12:03</t>
+  </si>
+  <si>
+    <t>NSE:BLUESTARCO-EQ_BEAR_1773374400_1773384300</t>
+  </si>
+  <si>
+    <t>2026-03-13 12:15</t>
+  </si>
+  <si>
+    <t>2026-03-13 12:30</t>
+  </si>
+  <si>
+    <t>NSE:HINDALCO-EQ_BEAR_1773374400_1773384300</t>
+  </si>
+  <si>
+    <t>NSE:ALKEM-EQ_BEAR_1773287100_1773386100</t>
+  </si>
+  <si>
+    <t>2026-03-13 12:45</t>
+  </si>
+  <si>
+    <t>2026-03-13 13:00</t>
+  </si>
+  <si>
+    <t>NSE:BLUESTARCO-EQ_BEAR_1773374400_1773632700</t>
+  </si>
+  <si>
+    <t>2026-03-16 09:15</t>
+  </si>
+  <si>
+    <t>2026-03-16 09:30</t>
+  </si>
+  <si>
+    <t>NSE:NBCC-EQ_BEAR_1773373500_1773632700</t>
+  </si>
+  <si>
+    <t>2026-03-16 09:32</t>
+  </si>
+  <si>
+    <t>NSE:NCC-EQ_BEAR_1773384300_1773632700</t>
+  </si>
+  <si>
+    <t>NSE:TORNTPHARM-EQ_BEAR_1773379800_1773632700</t>
+  </si>
+  <si>
+    <t>2026-03-13 11:00</t>
+  </si>
+  <si>
+    <t>2026-03-16 09:33</t>
+  </si>
+  <si>
+    <t>NSE:HFCL-EQ_BEAR_1773393300_1773634500</t>
+  </si>
+  <si>
+    <t>2026-03-13 14:45</t>
+  </si>
+  <si>
+    <t>2026-03-16 09:45</t>
+  </si>
+  <si>
+    <t>2026-03-16 10:01</t>
+  </si>
+  <si>
+    <t>NSE:NATIONALUM-EQ_BEAR_1773376200_1773634500</t>
+  </si>
+  <si>
+    <t>2026-03-16 10:02</t>
+  </si>
+  <si>
+    <t>NSE:CUMMINSIND-EQ_BEAR_1773375300_1773635400</t>
+  </si>
+  <si>
+    <t>2026-03-16 10:00</t>
+  </si>
+  <si>
+    <t>2026-03-16 10:15</t>
+  </si>
+  <si>
+    <t>NSE:IEX-EQ_BEAR_1773378900_1773635400</t>
+  </si>
+  <si>
+    <t>2026-03-13 10:45</t>
+  </si>
+  <si>
+    <t>2026-03-16 10:16</t>
+  </si>
+  <si>
+    <t>NSE:LAURUSLABS-EQ_BEAR_1773373500_1773635400</t>
+  </si>
+  <si>
+    <t>NSE:LUPIN-EQ_BEAR_1773378000_1773635400</t>
+  </si>
+  <si>
+    <t>2026-03-13 10:30</t>
+  </si>
+  <si>
+    <t>NSE:SIEMENS-EQ_BEAR_1773378900_1773635400</t>
+  </si>
+  <si>
+    <t>2026-03-16 10:17</t>
+  </si>
+  <si>
+    <t>NSE:SUZLON-EQ_BEAR_1773379800_1773635400</t>
+  </si>
+  <si>
+    <t>NSE:ASTRAL-EQ_BEAR_1773374400_1773636300</t>
+  </si>
+  <si>
+    <t>2026-03-16 10:30</t>
+  </si>
+  <si>
+    <t>NSE:DALBHARAT-EQ_BEAR_1773375300_1773636300</t>
+  </si>
+  <si>
+    <t>2026-03-16 10:31</t>
+  </si>
+  <si>
+    <t>NSE:DIXON-EQ_BEAR_1773382500_1773636300</t>
+  </si>
+  <si>
+    <t>NSE:JINDALSTEL-EQ_BEAR_1773377100_1773636300</t>
+  </si>
+  <si>
+    <t>2026-03-13 10:15</t>
+  </si>
+  <si>
+    <t>NSE:JIOFIN-EQ_BEAR_1773378900_1773636300</t>
+  </si>
+  <si>
+    <t>NSE:JIOFIN-EQ</t>
+  </si>
+  <si>
+    <t>NSE:LTM-EQ_BEAR_1773373500_1773636300</t>
+  </si>
+  <si>
+    <t>NSE:LTM-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-16 10:32</t>
+  </si>
+  <si>
+    <t>NSE:RECLTD-EQ_BEAR_1773379800_1773636300</t>
+  </si>
+  <si>
+    <t>NSE:UPL-EQ_BEAR_1773373500_1773636300</t>
+  </si>
+  <si>
+    <t>2026-03-16 10:33</t>
+  </si>
+  <si>
+    <t>NSE:WIPRO-EQ_BEAR_1773379800_1773636300</t>
+  </si>
+  <si>
+    <t>NSE:WIPRO-EQ</t>
+  </si>
+  <si>
+    <t>NSE:GLENMARK-EQ_BEAR_1773378000_1773637200</t>
+  </si>
+  <si>
+    <t>2026-03-16 10:46</t>
+  </si>
+  <si>
+    <t>NSE:MAZDOCK-EQ_BEAR_1773373500_1773637200</t>
+  </si>
+  <si>
+    <t>2026-03-16 10:47</t>
+  </si>
+  <si>
+    <t>NSE:TECHM-EQ_BEAR_1773374400_1773638100</t>
+  </si>
+  <si>
+    <t>NSE:TECHM-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-16 10:45</t>
+  </si>
+  <si>
+    <t>2026-03-16 11:03</t>
+  </si>
+  <si>
+    <t>NSE:SRF-EQ_BEAR_1773378000_1773644400</t>
+  </si>
+  <si>
+    <t>2026-03-16 12:30</t>
+  </si>
+  <si>
+    <t>2026-03-16 12:47</t>
+  </si>
+  <si>
+    <t>NSE:SAIL-EQ_BEAR_1773373500_1773646200</t>
+  </si>
+  <si>
+    <t>2026-03-16 13:00</t>
+  </si>
+  <si>
+    <t>2026-03-16 13:17</t>
+  </si>
+  <si>
+    <t>NSE:ABB-EQ_BEAR_1773635400_1773653400</t>
+  </si>
+  <si>
+    <t>2026-03-16 15:00</t>
+  </si>
+  <si>
+    <t>2026-03-16 15:15</t>
+  </si>
+  <si>
+    <t>NSE:PETRONET-EQ_BEAR_1773377100_1773654300</t>
+  </si>
+  <si>
+    <t>2026-03-16 15:32</t>
   </si>
 </sst>
 </file>
@@ -3588,7 +4038,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N361"/>
+  <dimension ref="A1:N424"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -16265,6 +16715,2274 @@
         <v>1032</v>
       </c>
     </row>
+    <row r="362" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A362" s="19" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B362" s="19" t="s">
+        <v>684</v>
+      </c>
+      <c r="C362" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D362" s="19" t="s">
+        <v>992</v>
+      </c>
+      <c r="E362" s="20">
+        <v>2492.4</v>
+      </c>
+      <c r="F362" s="19" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G362" s="20">
+        <v>2440</v>
+      </c>
+      <c r="H362" s="20">
+        <v>2408.4</v>
+      </c>
+      <c r="I362" s="20">
+        <v>2423.5</v>
+      </c>
+      <c r="J362" s="19"/>
+      <c r="K362" s="19"/>
+      <c r="L362" s="19"/>
+      <c r="M362" s="19"/>
+      <c r="N362" s="19" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="363" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A363" s="19" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B363" s="19" t="s">
+        <v>796</v>
+      </c>
+      <c r="C363" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D363" s="19" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E363" s="20">
+        <v>924.2</v>
+      </c>
+      <c r="F363" s="19" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G363" s="20">
+        <v>910</v>
+      </c>
+      <c r="H363" s="20">
+        <v>890</v>
+      </c>
+      <c r="I363" s="20">
+        <v>898.4</v>
+      </c>
+      <c r="J363" s="19"/>
+      <c r="K363" s="19"/>
+      <c r="L363" s="19"/>
+      <c r="M363" s="19"/>
+      <c r="N363" s="19" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="364" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A364" s="19" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B364" s="19" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C364" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D364" s="19" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E364" s="20">
+        <v>2547.5</v>
+      </c>
+      <c r="F364" s="19" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G364" s="20">
+        <v>2529.7</v>
+      </c>
+      <c r="H364" s="20">
+        <v>2481</v>
+      </c>
+      <c r="I364" s="20">
+        <v>2496</v>
+      </c>
+      <c r="J364" s="19"/>
+      <c r="K364" s="19"/>
+      <c r="L364" s="19"/>
+      <c r="M364" s="19"/>
+      <c r="N364" s="19" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="365" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A365" s="19" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B365" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="C365" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D365" s="19" t="s">
+        <v>992</v>
+      </c>
+      <c r="E365" s="20">
+        <v>3045.4</v>
+      </c>
+      <c r="F365" s="19" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G365" s="20">
+        <v>2997.2</v>
+      </c>
+      <c r="H365" s="20">
+        <v>2962.7</v>
+      </c>
+      <c r="I365" s="20">
+        <v>2967.9</v>
+      </c>
+      <c r="J365" s="19"/>
+      <c r="K365" s="19"/>
+      <c r="L365" s="19"/>
+      <c r="M365" s="19"/>
+      <c r="N365" s="19" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="366" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A366" s="19" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B366" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="C366" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D366" s="19" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E366" s="20">
+        <v>1940.4</v>
+      </c>
+      <c r="F366" s="19" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G366" s="20">
+        <v>1929</v>
+      </c>
+      <c r="H366" s="20">
+        <v>1910</v>
+      </c>
+      <c r="I366" s="20">
+        <v>1913.2</v>
+      </c>
+      <c r="J366" s="19"/>
+      <c r="K366" s="19"/>
+      <c r="L366" s="19"/>
+      <c r="M366" s="19"/>
+      <c r="N366" s="19" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="367" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A367" s="19" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B367" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C367" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D367" s="19" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E367" s="20">
+        <v>1029.8</v>
+      </c>
+      <c r="F367" s="19" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G367" s="20">
+        <v>1023</v>
+      </c>
+      <c r="H367" s="20">
+        <v>1008.1</v>
+      </c>
+      <c r="I367" s="20">
+        <v>1014.7</v>
+      </c>
+      <c r="J367" s="19"/>
+      <c r="K367" s="19"/>
+      <c r="L367" s="19"/>
+      <c r="M367" s="19"/>
+      <c r="N367" s="19" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="368" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A368" s="17" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B368" s="17" t="s">
+        <v>446</v>
+      </c>
+      <c r="C368" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D368" s="17" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E368" s="18">
+        <v>482.25</v>
+      </c>
+      <c r="F368" s="17" t="s">
+        <v>1035</v>
+      </c>
+      <c r="G368" s="18">
+        <v>486</v>
+      </c>
+      <c r="H368" s="18">
+        <v>480.75</v>
+      </c>
+      <c r="I368" s="18">
+        <v>485.9</v>
+      </c>
+      <c r="J368" s="17"/>
+      <c r="K368" s="17"/>
+      <c r="L368" s="17"/>
+      <c r="M368" s="17"/>
+      <c r="N368" s="17" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="369" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A369" s="17" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B369" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="C369" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D369" s="17" t="s">
+        <v>958</v>
+      </c>
+      <c r="E369" s="18">
+        <v>383.2</v>
+      </c>
+      <c r="F369" s="17" t="s">
+        <v>1048</v>
+      </c>
+      <c r="G369" s="18">
+        <v>387.5</v>
+      </c>
+      <c r="H369" s="18">
+        <v>383.4</v>
+      </c>
+      <c r="I369" s="18">
+        <v>387.45</v>
+      </c>
+      <c r="J369" s="17"/>
+      <c r="K369" s="17"/>
+      <c r="L369" s="17"/>
+      <c r="M369" s="17"/>
+      <c r="N369" s="17" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="370" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A370" s="19" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B370" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="C370" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D370" s="19" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E370" s="20">
+        <v>7731.5</v>
+      </c>
+      <c r="F370" s="19" t="s">
+        <v>1052</v>
+      </c>
+      <c r="G370" s="20">
+        <v>7609</v>
+      </c>
+      <c r="H370" s="20">
+        <v>7549.5</v>
+      </c>
+      <c r="I370" s="20">
+        <v>7557</v>
+      </c>
+      <c r="J370" s="19"/>
+      <c r="K370" s="19"/>
+      <c r="L370" s="19"/>
+      <c r="M370" s="19"/>
+      <c r="N370" s="19" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="371" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A371" s="17" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B371" s="17" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C371" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D371" s="17" t="s">
+        <v>957</v>
+      </c>
+      <c r="E371" s="18">
+        <v>400.55</v>
+      </c>
+      <c r="F371" s="17" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G371" s="18">
+        <v>408.95</v>
+      </c>
+      <c r="H371" s="18">
+        <v>401.65</v>
+      </c>
+      <c r="I371" s="18">
+        <v>407</v>
+      </c>
+      <c r="J371" s="17"/>
+      <c r="K371" s="17"/>
+      <c r="L371" s="17"/>
+      <c r="M371" s="17"/>
+      <c r="N371" s="17" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="372" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A372" s="19" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B372" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="C372" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D372" s="19" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E372" s="20">
+        <v>925.15</v>
+      </c>
+      <c r="F372" s="19" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G372" s="20">
+        <v>918.75</v>
+      </c>
+      <c r="H372" s="20">
+        <v>911.5</v>
+      </c>
+      <c r="I372" s="20">
+        <v>915</v>
+      </c>
+      <c r="J372" s="19"/>
+      <c r="K372" s="19"/>
+      <c r="L372" s="19"/>
+      <c r="M372" s="19"/>
+      <c r="N372" s="19" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="373" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A373" s="19" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B373" s="19" t="s">
+        <v>436</v>
+      </c>
+      <c r="C373" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D373" s="19" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E373" s="20">
+        <v>1339.2</v>
+      </c>
+      <c r="F373" s="19" t="s">
+        <v>1063</v>
+      </c>
+      <c r="G373" s="20">
+        <v>1344</v>
+      </c>
+      <c r="H373" s="20">
+        <v>1339.2</v>
+      </c>
+      <c r="I373" s="20">
+        <v>1340.6</v>
+      </c>
+      <c r="J373" s="19"/>
+      <c r="K373" s="19"/>
+      <c r="L373" s="19"/>
+      <c r="M373" s="19"/>
+      <c r="N373" s="19" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="374" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A374" s="19" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B374" s="19" t="s">
+        <v>858</v>
+      </c>
+      <c r="C374" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D374" s="19" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E374" s="20">
+        <v>1220</v>
+      </c>
+      <c r="F374" s="19" t="s">
+        <v>1067</v>
+      </c>
+      <c r="G374" s="20">
+        <v>1191.2</v>
+      </c>
+      <c r="H374" s="20">
+        <v>1184</v>
+      </c>
+      <c r="I374" s="20">
+        <v>1188.7</v>
+      </c>
+      <c r="J374" s="19"/>
+      <c r="K374" s="19"/>
+      <c r="L374" s="19"/>
+      <c r="M374" s="19"/>
+      <c r="N374" s="19" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="375" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A375" s="19" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B375" s="19" t="s">
+        <v>669</v>
+      </c>
+      <c r="C375" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D375" s="19" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E375" s="20">
+        <v>1433.6</v>
+      </c>
+      <c r="F375" s="19" t="s">
+        <v>1067</v>
+      </c>
+      <c r="G375" s="20">
+        <v>1458.5</v>
+      </c>
+      <c r="H375" s="20">
+        <v>1450.2</v>
+      </c>
+      <c r="I375" s="20">
+        <v>1455.8</v>
+      </c>
+      <c r="J375" s="19"/>
+      <c r="K375" s="19"/>
+      <c r="L375" s="19"/>
+      <c r="M375" s="19"/>
+      <c r="N375" s="19" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="376" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A376" s="17" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B376" s="17" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C376" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D376" s="17" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E376" s="18">
+        <v>1890.1</v>
+      </c>
+      <c r="F376" s="17" t="s">
+        <v>1074</v>
+      </c>
+      <c r="G376" s="18">
+        <v>1897.5</v>
+      </c>
+      <c r="H376" s="18">
+        <v>1883.9</v>
+      </c>
+      <c r="I376" s="18">
+        <v>1896.7</v>
+      </c>
+      <c r="J376" s="17"/>
+      <c r="K376" s="17"/>
+      <c r="L376" s="17"/>
+      <c r="M376" s="17"/>
+      <c r="N376" s="17" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="377" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A377" s="19" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B377" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="C377" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D377" s="19" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E377" s="20">
+        <v>3763.4</v>
+      </c>
+      <c r="F377" s="19" t="s">
+        <v>1074</v>
+      </c>
+      <c r="G377" s="20">
+        <v>3713.7</v>
+      </c>
+      <c r="H377" s="20">
+        <v>3694.6</v>
+      </c>
+      <c r="I377" s="20">
+        <v>3700.8</v>
+      </c>
+      <c r="J377" s="19"/>
+      <c r="K377" s="19"/>
+      <c r="L377" s="19"/>
+      <c r="M377" s="19"/>
+      <c r="N377" s="19" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="378" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A378" s="19" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B378" s="19" t="s">
+        <v>651</v>
+      </c>
+      <c r="C378" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D378" s="19" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E378" s="20">
+        <v>3681.7</v>
+      </c>
+      <c r="F378" s="19" t="s">
+        <v>1074</v>
+      </c>
+      <c r="G378" s="20">
+        <v>3433.9</v>
+      </c>
+      <c r="H378" s="20">
+        <v>3419</v>
+      </c>
+      <c r="I378" s="20">
+        <v>3426.1</v>
+      </c>
+      <c r="J378" s="19"/>
+      <c r="K378" s="19"/>
+      <c r="L378" s="19"/>
+      <c r="M378" s="19"/>
+      <c r="N378" s="19" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="379" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A379" s="17" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B379" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="C379" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D379" s="17" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E379" s="18">
+        <v>1004.4</v>
+      </c>
+      <c r="F379" s="17" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G379" s="18">
+        <v>1019</v>
+      </c>
+      <c r="H379" s="18">
+        <v>1002.7</v>
+      </c>
+      <c r="I379" s="18">
+        <v>1011.9</v>
+      </c>
+      <c r="J379" s="17"/>
+      <c r="K379" s="17"/>
+      <c r="L379" s="17"/>
+      <c r="M379" s="17"/>
+      <c r="N379" s="17" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="380" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A380" s="19" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B380" s="19" t="s">
+        <v>960</v>
+      </c>
+      <c r="C380" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D380" s="19" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E380" s="20">
+        <v>221.33</v>
+      </c>
+      <c r="F380" s="19" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G380" s="20">
+        <v>213.77</v>
+      </c>
+      <c r="H380" s="20">
+        <v>212.36</v>
+      </c>
+      <c r="I380" s="20">
+        <v>212.8</v>
+      </c>
+      <c r="J380" s="19"/>
+      <c r="K380" s="19"/>
+      <c r="L380" s="19"/>
+      <c r="M380" s="19"/>
+      <c r="N380" s="19" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="381" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A381" s="19" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B381" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="C381" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D381" s="19" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E381" s="20">
+        <v>1352</v>
+      </c>
+      <c r="F381" s="19" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G381" s="20">
+        <v>1366</v>
+      </c>
+      <c r="H381" s="20">
+        <v>1356.1</v>
+      </c>
+      <c r="I381" s="20">
+        <v>1356.7</v>
+      </c>
+      <c r="J381" s="19"/>
+      <c r="K381" s="19"/>
+      <c r="L381" s="19"/>
+      <c r="M381" s="19"/>
+      <c r="N381" s="19" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="382" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A382" s="17" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B382" s="17" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C382" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D382" s="17" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E382" s="18">
+        <v>869.1</v>
+      </c>
+      <c r="F382" s="17" t="s">
+        <v>1089</v>
+      </c>
+      <c r="G382" s="18">
+        <v>878.75</v>
+      </c>
+      <c r="H382" s="18">
+        <v>865.25</v>
+      </c>
+      <c r="I382" s="18">
+        <v>872.9</v>
+      </c>
+      <c r="J382" s="17"/>
+      <c r="K382" s="17"/>
+      <c r="L382" s="17"/>
+      <c r="M382" s="17"/>
+      <c r="N382" s="17" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="383" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A383" s="17" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B383" s="17" t="s">
+        <v>713</v>
+      </c>
+      <c r="C383" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D383" s="17" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E383" s="18">
+        <v>3944.4</v>
+      </c>
+      <c r="F383" s="17" t="s">
+        <v>1089</v>
+      </c>
+      <c r="G383" s="18">
+        <v>4025</v>
+      </c>
+      <c r="H383" s="18">
+        <v>3945</v>
+      </c>
+      <c r="I383" s="18">
+        <v>4023</v>
+      </c>
+      <c r="J383" s="17"/>
+      <c r="K383" s="17"/>
+      <c r="L383" s="17"/>
+      <c r="M383" s="17"/>
+      <c r="N383" s="17" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="384" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A384" s="19" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B384" s="19" t="s">
+        <v>436</v>
+      </c>
+      <c r="C384" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D384" s="19" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E384" s="20">
+        <v>1339.2</v>
+      </c>
+      <c r="F384" s="19" t="s">
+        <v>1089</v>
+      </c>
+      <c r="G384" s="20">
+        <v>1350.9</v>
+      </c>
+      <c r="H384" s="20">
+        <v>1325</v>
+      </c>
+      <c r="I384" s="20">
+        <v>1330.5</v>
+      </c>
+      <c r="J384" s="19"/>
+      <c r="K384" s="19"/>
+      <c r="L384" s="19"/>
+      <c r="M384" s="19"/>
+      <c r="N384" s="19" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="385" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A385" s="19" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B385" s="19" t="s">
+        <v>718</v>
+      </c>
+      <c r="C385" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D385" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E385" s="20">
+        <v>1343.9</v>
+      </c>
+      <c r="F385" s="19" t="s">
+        <v>1089</v>
+      </c>
+      <c r="G385" s="20">
+        <v>1353.2</v>
+      </c>
+      <c r="H385" s="20">
+        <v>1320.2</v>
+      </c>
+      <c r="I385" s="20">
+        <v>1323.9</v>
+      </c>
+      <c r="J385" s="19"/>
+      <c r="K385" s="19"/>
+      <c r="L385" s="19"/>
+      <c r="M385" s="19"/>
+      <c r="N385" s="19" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="386" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A386" s="17" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B386" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C386" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D386" s="17" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E386" s="18">
+        <v>117.6</v>
+      </c>
+      <c r="F386" s="17" t="s">
+        <v>1089</v>
+      </c>
+      <c r="G386" s="18">
+        <v>118.85</v>
+      </c>
+      <c r="H386" s="18">
+        <v>116.42</v>
+      </c>
+      <c r="I386" s="18">
+        <v>118.4</v>
+      </c>
+      <c r="J386" s="17"/>
+      <c r="K386" s="17"/>
+      <c r="L386" s="17"/>
+      <c r="M386" s="17"/>
+      <c r="N386" s="17" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="387" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A387" s="17" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B387" s="17" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C387" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D387" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E387" s="18">
+        <v>75.26</v>
+      </c>
+      <c r="F387" s="17" t="s">
+        <v>1089</v>
+      </c>
+      <c r="G387" s="18">
+        <v>76.48</v>
+      </c>
+      <c r="H387" s="18">
+        <v>75.2</v>
+      </c>
+      <c r="I387" s="18">
+        <v>75.94</v>
+      </c>
+      <c r="J387" s="17"/>
+      <c r="K387" s="17"/>
+      <c r="L387" s="17"/>
+      <c r="M387" s="17"/>
+      <c r="N387" s="17" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="388" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A388" s="19" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B388" s="19" t="s">
+        <v>900</v>
+      </c>
+      <c r="C388" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D388" s="19" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E388" s="20">
+        <v>31080</v>
+      </c>
+      <c r="F388" s="19" t="s">
+        <v>1089</v>
+      </c>
+      <c r="G388" s="20">
+        <v>30845</v>
+      </c>
+      <c r="H388" s="20">
+        <v>30270</v>
+      </c>
+      <c r="I388" s="20">
+        <v>30675</v>
+      </c>
+      <c r="J388" s="19"/>
+      <c r="K388" s="19"/>
+      <c r="L388" s="19"/>
+      <c r="M388" s="19"/>
+      <c r="N388" s="19" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="389" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A389" s="19" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B389" s="19" t="s">
+        <v>499</v>
+      </c>
+      <c r="C389" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D389" s="19" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E389" s="20">
+        <v>710.65</v>
+      </c>
+      <c r="F389" s="19" t="s">
+        <v>1089</v>
+      </c>
+      <c r="G389" s="20">
+        <v>715.5</v>
+      </c>
+      <c r="H389" s="20">
+        <v>702.1</v>
+      </c>
+      <c r="I389" s="20">
+        <v>705.65</v>
+      </c>
+      <c r="J389" s="19"/>
+      <c r="K389" s="19"/>
+      <c r="L389" s="19"/>
+      <c r="M389" s="19"/>
+      <c r="N389" s="19" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="390" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A390" s="19" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B390" s="19" t="s">
+        <v>316</v>
+      </c>
+      <c r="C390" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D390" s="19" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E390" s="20">
+        <v>177.2</v>
+      </c>
+      <c r="F390" s="19" t="s">
+        <v>1090</v>
+      </c>
+      <c r="G390" s="20">
+        <v>176.16</v>
+      </c>
+      <c r="H390" s="20">
+        <v>174.75</v>
+      </c>
+      <c r="I390" s="20">
+        <v>174.78</v>
+      </c>
+      <c r="J390" s="19"/>
+      <c r="K390" s="19"/>
+      <c r="L390" s="19"/>
+      <c r="M390" s="19"/>
+      <c r="N390" s="19" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="391" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A391" s="19" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B391" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="C391" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D391" s="19" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E391" s="20">
+        <v>2002.4</v>
+      </c>
+      <c r="F391" s="19" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G391" s="20">
+        <v>1988.5</v>
+      </c>
+      <c r="H391" s="20">
+        <v>1970.2</v>
+      </c>
+      <c r="I391" s="20">
+        <v>1970.2</v>
+      </c>
+      <c r="J391" s="19"/>
+      <c r="K391" s="19"/>
+      <c r="L391" s="19"/>
+      <c r="M391" s="19"/>
+      <c r="N391" s="19" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="392" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A392" s="19" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B392" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="C392" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D392" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E392" s="20">
+        <v>149.6</v>
+      </c>
+      <c r="F392" s="19" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G392" s="20">
+        <v>143.42</v>
+      </c>
+      <c r="H392" s="20">
+        <v>142</v>
+      </c>
+      <c r="I392" s="20">
+        <v>142</v>
+      </c>
+      <c r="J392" s="19"/>
+      <c r="K392" s="19"/>
+      <c r="L392" s="19"/>
+      <c r="M392" s="19"/>
+      <c r="N392" s="19" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="393" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A393" s="19" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B393" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="C393" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D393" s="19" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E393" s="20">
+        <v>1352</v>
+      </c>
+      <c r="F393" s="19" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G393" s="20">
+        <v>1360.6</v>
+      </c>
+      <c r="H393" s="20">
+        <v>1341.7</v>
+      </c>
+      <c r="I393" s="20">
+        <v>1341.8</v>
+      </c>
+      <c r="J393" s="19"/>
+      <c r="K393" s="19"/>
+      <c r="L393" s="19"/>
+      <c r="M393" s="19"/>
+      <c r="N393" s="19" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="394" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A394" s="19" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B394" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C394" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D394" s="19" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E394" s="20">
+        <v>1874.4</v>
+      </c>
+      <c r="F394" s="19" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G394" s="20">
+        <v>1869.2</v>
+      </c>
+      <c r="H394" s="20">
+        <v>1846.6</v>
+      </c>
+      <c r="I394" s="20">
+        <v>1848.8</v>
+      </c>
+      <c r="J394" s="19"/>
+      <c r="K394" s="19"/>
+      <c r="L394" s="19"/>
+      <c r="M394" s="19"/>
+      <c r="N394" s="19" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="395" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A395" s="19" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B395" s="19" t="s">
+        <v>890</v>
+      </c>
+      <c r="C395" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D395" s="19" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E395" s="20">
+        <v>934.1</v>
+      </c>
+      <c r="F395" s="19" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G395" s="20">
+        <v>917.5</v>
+      </c>
+      <c r="H395" s="20">
+        <v>911.25</v>
+      </c>
+      <c r="I395" s="20">
+        <v>912.55</v>
+      </c>
+      <c r="J395" s="19"/>
+      <c r="K395" s="19"/>
+      <c r="L395" s="19"/>
+      <c r="M395" s="19"/>
+      <c r="N395" s="19" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="396" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A396" s="19" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B396" s="19" t="s">
+        <v>908</v>
+      </c>
+      <c r="C396" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D396" s="19" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E396" s="20">
+        <v>5457</v>
+      </c>
+      <c r="F396" s="19" t="s">
+        <v>1118</v>
+      </c>
+      <c r="G396" s="20">
+        <v>5406</v>
+      </c>
+      <c r="H396" s="20">
+        <v>5381.5</v>
+      </c>
+      <c r="I396" s="20">
+        <v>5390</v>
+      </c>
+      <c r="J396" s="19"/>
+      <c r="K396" s="19"/>
+      <c r="L396" s="19"/>
+      <c r="M396" s="19"/>
+      <c r="N396" s="19" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="397" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A397" s="19" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B397" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C397" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D397" s="19" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E397" s="20">
+        <v>1874.4</v>
+      </c>
+      <c r="F397" s="19" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G397" s="20">
+        <v>1833.2</v>
+      </c>
+      <c r="H397" s="20">
+        <v>1801.6</v>
+      </c>
+      <c r="I397" s="20">
+        <v>1802.3</v>
+      </c>
+      <c r="J397" s="19"/>
+      <c r="K397" s="19"/>
+      <c r="L397" s="19"/>
+      <c r="M397" s="19"/>
+      <c r="N397" s="19" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="398" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A398" s="19" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B398" s="19" t="s">
+        <v>951</v>
+      </c>
+      <c r="C398" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D398" s="19" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E398" s="20">
+        <v>86.19</v>
+      </c>
+      <c r="F398" s="19" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G398" s="20">
+        <v>83.2</v>
+      </c>
+      <c r="H398" s="20">
+        <v>81.47</v>
+      </c>
+      <c r="I398" s="20">
+        <v>81.7</v>
+      </c>
+      <c r="J398" s="19"/>
+      <c r="K398" s="19"/>
+      <c r="L398" s="19"/>
+      <c r="M398" s="19"/>
+      <c r="N398" s="19" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="399" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A399" s="19" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B399" s="19" t="s">
+        <v>597</v>
+      </c>
+      <c r="C399" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D399" s="19" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E399" s="20">
+        <v>145.83</v>
+      </c>
+      <c r="F399" s="19" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G399" s="20">
+        <v>144.75</v>
+      </c>
+      <c r="H399" s="20">
+        <v>140.61</v>
+      </c>
+      <c r="I399" s="20">
+        <v>141.37</v>
+      </c>
+      <c r="J399" s="19"/>
+      <c r="K399" s="19"/>
+      <c r="L399" s="19"/>
+      <c r="M399" s="19"/>
+      <c r="N399" s="19" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="400" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A400" s="19" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B400" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="C400" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D400" s="19" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E400" s="20">
+        <v>4387.8</v>
+      </c>
+      <c r="F400" s="19" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G400" s="20">
+        <v>4443.9</v>
+      </c>
+      <c r="H400" s="20">
+        <v>4355</v>
+      </c>
+      <c r="I400" s="20">
+        <v>4357</v>
+      </c>
+      <c r="J400" s="19"/>
+      <c r="K400" s="19"/>
+      <c r="L400" s="19"/>
+      <c r="M400" s="19"/>
+      <c r="N400" s="19" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="401" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A401" s="19" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B401" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C401" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D401" s="19" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E401" s="20">
+        <v>72</v>
+      </c>
+      <c r="F401" s="19" t="s">
+        <v>1131</v>
+      </c>
+      <c r="G401" s="20">
+        <v>71.82</v>
+      </c>
+      <c r="H401" s="20">
+        <v>70.94</v>
+      </c>
+      <c r="I401" s="20">
+        <v>71</v>
+      </c>
+      <c r="J401" s="19"/>
+      <c r="K401" s="19"/>
+      <c r="L401" s="19"/>
+      <c r="M401" s="19"/>
+      <c r="N401" s="19" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="402" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A402" s="19" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B402" s="19" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C402" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D402" s="19" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E402" s="20">
+        <v>383.85</v>
+      </c>
+      <c r="F402" s="19" t="s">
+        <v>1131</v>
+      </c>
+      <c r="G402" s="20">
+        <v>383.75</v>
+      </c>
+      <c r="H402" s="20">
+        <v>379.6</v>
+      </c>
+      <c r="I402" s="20">
+        <v>379.8</v>
+      </c>
+      <c r="J402" s="19"/>
+      <c r="K402" s="19"/>
+      <c r="L402" s="19"/>
+      <c r="M402" s="19"/>
+      <c r="N402" s="19" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="403" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A403" s="19" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B403" s="19" t="s">
+        <v>790</v>
+      </c>
+      <c r="C403" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D403" s="19" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E403" s="20">
+        <v>4677.5</v>
+      </c>
+      <c r="F403" s="19" t="s">
+        <v>1136</v>
+      </c>
+      <c r="G403" s="20">
+        <v>4665</v>
+      </c>
+      <c r="H403" s="20">
+        <v>4615.3</v>
+      </c>
+      <c r="I403" s="20">
+        <v>4624</v>
+      </c>
+      <c r="J403" s="19"/>
+      <c r="K403" s="19"/>
+      <c r="L403" s="19"/>
+      <c r="M403" s="19"/>
+      <c r="N403" s="19" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="404" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A404" s="19" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B404" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C404" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D404" s="19" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E404" s="20">
+        <v>122.47</v>
+      </c>
+      <c r="F404" s="19" t="s">
+        <v>1136</v>
+      </c>
+      <c r="G404" s="20">
+        <v>120.09</v>
+      </c>
+      <c r="H404" s="20">
+        <v>118.44</v>
+      </c>
+      <c r="I404" s="20">
+        <v>118.7</v>
+      </c>
+      <c r="J404" s="19"/>
+      <c r="K404" s="19"/>
+      <c r="L404" s="19"/>
+      <c r="M404" s="19"/>
+      <c r="N404" s="19" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="405" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A405" s="19" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B405" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="C405" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D405" s="19" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E405" s="20">
+        <v>1022.8</v>
+      </c>
+      <c r="F405" s="19" t="s">
+        <v>1136</v>
+      </c>
+      <c r="G405" s="20">
+        <v>1006.6</v>
+      </c>
+      <c r="H405" s="20">
+        <v>995.9</v>
+      </c>
+      <c r="I405" s="20">
+        <v>996.9</v>
+      </c>
+      <c r="J405" s="19"/>
+      <c r="K405" s="19"/>
+      <c r="L405" s="19"/>
+      <c r="M405" s="19"/>
+      <c r="N405" s="19" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="406" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A406" s="19" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B406" s="19" t="s">
+        <v>949</v>
+      </c>
+      <c r="C406" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D406" s="19" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E406" s="20">
+        <v>2342.9</v>
+      </c>
+      <c r="F406" s="19" t="s">
+        <v>1136</v>
+      </c>
+      <c r="G406" s="20">
+        <v>2309.6</v>
+      </c>
+      <c r="H406" s="20">
+        <v>2281.4</v>
+      </c>
+      <c r="I406" s="20">
+        <v>2282.8</v>
+      </c>
+      <c r="J406" s="19"/>
+      <c r="K406" s="19"/>
+      <c r="L406" s="19"/>
+      <c r="M406" s="19"/>
+      <c r="N406" s="19" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="407" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A407" s="19" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B407" s="19" t="s">
+        <v>987</v>
+      </c>
+      <c r="C407" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D407" s="19" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E407" s="20">
+        <v>3279</v>
+      </c>
+      <c r="F407" s="19" t="s">
+        <v>1136</v>
+      </c>
+      <c r="G407" s="20">
+        <v>3201.1</v>
+      </c>
+      <c r="H407" s="20">
+        <v>3150</v>
+      </c>
+      <c r="I407" s="20">
+        <v>3154.8</v>
+      </c>
+      <c r="J407" s="19"/>
+      <c r="K407" s="19"/>
+      <c r="L407" s="19"/>
+      <c r="M407" s="19"/>
+      <c r="N407" s="19" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="408" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A408" s="19" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B408" s="19" t="s">
+        <v>989</v>
+      </c>
+      <c r="C408" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D408" s="19" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E408" s="20">
+        <v>41.08</v>
+      </c>
+      <c r="F408" s="19" t="s">
+        <v>1136</v>
+      </c>
+      <c r="G408" s="20">
+        <v>41.66</v>
+      </c>
+      <c r="H408" s="20">
+        <v>41.1</v>
+      </c>
+      <c r="I408" s="20">
+        <v>41.15</v>
+      </c>
+      <c r="J408" s="19"/>
+      <c r="K408" s="19"/>
+      <c r="L408" s="19"/>
+      <c r="M408" s="19"/>
+      <c r="N408" s="19" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="409" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A409" s="19" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B409" s="19" t="s">
+        <v>490</v>
+      </c>
+      <c r="C409" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D409" s="19" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E409" s="20">
+        <v>1667.2</v>
+      </c>
+      <c r="F409" s="19" t="s">
+        <v>1137</v>
+      </c>
+      <c r="G409" s="20">
+        <v>1617.9</v>
+      </c>
+      <c r="H409" s="20">
+        <v>1601.7</v>
+      </c>
+      <c r="I409" s="20">
+        <v>1602.4</v>
+      </c>
+      <c r="J409" s="19"/>
+      <c r="K409" s="19"/>
+      <c r="L409" s="19"/>
+      <c r="M409" s="19"/>
+      <c r="N409" s="19" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="410" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A410" s="19" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B410" s="19" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C410" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D410" s="19" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E410" s="20">
+        <v>1853</v>
+      </c>
+      <c r="F410" s="19" t="s">
+        <v>1137</v>
+      </c>
+      <c r="G410" s="20">
+        <v>1840.1</v>
+      </c>
+      <c r="H410" s="20">
+        <v>1824.1</v>
+      </c>
+      <c r="I410" s="20">
+        <v>1825.1</v>
+      </c>
+      <c r="J410" s="19"/>
+      <c r="K410" s="19"/>
+      <c r="L410" s="19"/>
+      <c r="M410" s="19"/>
+      <c r="N410" s="19" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="411" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A411" s="19" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B411" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="C411" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D411" s="19" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E411" s="20">
+        <v>10506</v>
+      </c>
+      <c r="F411" s="19" t="s">
+        <v>1137</v>
+      </c>
+      <c r="G411" s="20">
+        <v>10210</v>
+      </c>
+      <c r="H411" s="20">
+        <v>10061</v>
+      </c>
+      <c r="I411" s="20">
+        <v>10061</v>
+      </c>
+      <c r="J411" s="19"/>
+      <c r="K411" s="19"/>
+      <c r="L411" s="19"/>
+      <c r="M411" s="19"/>
+      <c r="N411" s="19" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="412" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A412" s="19" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B412" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="C412" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D412" s="19" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E412" s="20">
+        <v>1169.8</v>
+      </c>
+      <c r="F412" s="19" t="s">
+        <v>1137</v>
+      </c>
+      <c r="G412" s="20">
+        <v>1143.5</v>
+      </c>
+      <c r="H412" s="20">
+        <v>1134.8</v>
+      </c>
+      <c r="I412" s="20">
+        <v>1135</v>
+      </c>
+      <c r="J412" s="19"/>
+      <c r="K412" s="19"/>
+      <c r="L412" s="19"/>
+      <c r="M412" s="19"/>
+      <c r="N412" s="19" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="413" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A413" s="19" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B413" s="19" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C413" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D413" s="19" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E413" s="20">
+        <v>238.6</v>
+      </c>
+      <c r="F413" s="19" t="s">
+        <v>1137</v>
+      </c>
+      <c r="G413" s="20">
+        <v>234.75</v>
+      </c>
+      <c r="H413" s="20">
+        <v>231.85</v>
+      </c>
+      <c r="I413" s="20">
+        <v>232</v>
+      </c>
+      <c r="J413" s="19"/>
+      <c r="K413" s="19"/>
+      <c r="L413" s="19"/>
+      <c r="M413" s="19"/>
+      <c r="N413" s="19" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="414" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A414" s="19" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B414" s="19" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C414" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D414" s="19" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E414" s="20">
+        <v>4237.3</v>
+      </c>
+      <c r="F414" s="19" t="s">
+        <v>1137</v>
+      </c>
+      <c r="G414" s="20">
+        <v>4214.5</v>
+      </c>
+      <c r="H414" s="20">
+        <v>4166</v>
+      </c>
+      <c r="I414" s="20">
+        <v>4167</v>
+      </c>
+      <c r="J414" s="19"/>
+      <c r="K414" s="19"/>
+      <c r="L414" s="19"/>
+      <c r="M414" s="19"/>
+      <c r="N414" s="19" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="415" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A415" s="19" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B415" s="19" t="s">
+        <v>675</v>
+      </c>
+      <c r="C415" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D415" s="19" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E415" s="20">
+        <v>335.2</v>
+      </c>
+      <c r="F415" s="19" t="s">
+        <v>1137</v>
+      </c>
+      <c r="G415" s="20">
+        <v>331.15</v>
+      </c>
+      <c r="H415" s="20">
+        <v>327.8</v>
+      </c>
+      <c r="I415" s="20">
+        <v>327.8</v>
+      </c>
+      <c r="J415" s="19"/>
+      <c r="K415" s="19"/>
+      <c r="L415" s="19"/>
+      <c r="M415" s="19"/>
+      <c r="N415" s="19" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="416" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A416" s="19" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B416" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C416" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D416" s="19" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E416" s="20">
+        <v>626.3</v>
+      </c>
+      <c r="F416" s="19" t="s">
+        <v>1137</v>
+      </c>
+      <c r="G416" s="20">
+        <v>611.15</v>
+      </c>
+      <c r="H416" s="20">
+        <v>607.6</v>
+      </c>
+      <c r="I416" s="20">
+        <v>607.95</v>
+      </c>
+      <c r="J416" s="19"/>
+      <c r="K416" s="19"/>
+      <c r="L416" s="19"/>
+      <c r="M416" s="19"/>
+      <c r="N416" s="19" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="417" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A417" s="19" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B417" s="19" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C417" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D417" s="19" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E417" s="20">
+        <v>199.97</v>
+      </c>
+      <c r="F417" s="19" t="s">
+        <v>1137</v>
+      </c>
+      <c r="G417" s="20">
+        <v>196.45</v>
+      </c>
+      <c r="H417" s="20">
+        <v>194.26</v>
+      </c>
+      <c r="I417" s="20">
+        <v>194.26</v>
+      </c>
+      <c r="J417" s="19"/>
+      <c r="K417" s="19"/>
+      <c r="L417" s="19"/>
+      <c r="M417" s="19"/>
+      <c r="N417" s="19" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="418" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A418" s="19" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B418" s="19" t="s">
+        <v>477</v>
+      </c>
+      <c r="C418" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D418" s="19" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E418" s="20">
+        <v>2168</v>
+      </c>
+      <c r="F418" s="19" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G418" s="20">
+        <v>2184.5</v>
+      </c>
+      <c r="H418" s="20">
+        <v>2161.1</v>
+      </c>
+      <c r="I418" s="20">
+        <v>2161.6</v>
+      </c>
+      <c r="J418" s="19"/>
+      <c r="K418" s="19"/>
+      <c r="L418" s="19"/>
+      <c r="M418" s="19"/>
+      <c r="N418" s="19" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="419" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A419" s="19" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B419" s="19" t="s">
+        <v>821</v>
+      </c>
+      <c r="C419" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D419" s="19" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E419" s="20">
+        <v>2404.6</v>
+      </c>
+      <c r="F419" s="19" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G419" s="20">
+        <v>2292.9</v>
+      </c>
+      <c r="H419" s="20">
+        <v>2273</v>
+      </c>
+      <c r="I419" s="20">
+        <v>2275.2</v>
+      </c>
+      <c r="J419" s="19"/>
+      <c r="K419" s="19"/>
+      <c r="L419" s="19"/>
+      <c r="M419" s="19"/>
+      <c r="N419" s="19" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="420" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A420" s="19" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B420" s="19" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C420" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D420" s="19" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E420" s="20">
+        <v>1324.7</v>
+      </c>
+      <c r="F420" s="19" t="s">
+        <v>1170</v>
+      </c>
+      <c r="G420" s="20">
+        <v>1323</v>
+      </c>
+      <c r="H420" s="20">
+        <v>1315.9</v>
+      </c>
+      <c r="I420" s="20">
+        <v>1320.9</v>
+      </c>
+      <c r="J420" s="19"/>
+      <c r="K420" s="19"/>
+      <c r="L420" s="19"/>
+      <c r="M420" s="19"/>
+      <c r="N420" s="19" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="421" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A421" s="19" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B421" s="19" t="s">
+        <v>922</v>
+      </c>
+      <c r="C421" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D421" s="19" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E421" s="20">
+        <v>2523.1</v>
+      </c>
+      <c r="F421" s="19" t="s">
+        <v>1173</v>
+      </c>
+      <c r="G421" s="20">
+        <v>2483.8</v>
+      </c>
+      <c r="H421" s="20">
+        <v>2460</v>
+      </c>
+      <c r="I421" s="20">
+        <v>2461.1</v>
+      </c>
+      <c r="J421" s="19"/>
+      <c r="K421" s="19"/>
+      <c r="L421" s="19"/>
+      <c r="M421" s="19"/>
+      <c r="N421" s="19" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="422" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A422" s="19" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B422" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="C422" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D422" s="19" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E422" s="20">
+        <v>150.63</v>
+      </c>
+      <c r="F422" s="19" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G422" s="20">
+        <v>144.78</v>
+      </c>
+      <c r="H422" s="20">
+        <v>143.66</v>
+      </c>
+      <c r="I422" s="20">
+        <v>143.78</v>
+      </c>
+      <c r="J422" s="19"/>
+      <c r="K422" s="19"/>
+      <c r="L422" s="19"/>
+      <c r="M422" s="19"/>
+      <c r="N422" s="19" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="423" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A423" s="19" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B423" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C423" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D423" s="19" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E423" s="20">
+        <v>6260</v>
+      </c>
+      <c r="F423" s="19" t="s">
+        <v>1179</v>
+      </c>
+      <c r="G423" s="20">
+        <v>6247.5</v>
+      </c>
+      <c r="H423" s="20">
+        <v>6202.5</v>
+      </c>
+      <c r="I423" s="20">
+        <v>6219</v>
+      </c>
+      <c r="J423" s="19"/>
+      <c r="K423" s="19"/>
+      <c r="L423" s="19"/>
+      <c r="M423" s="19"/>
+      <c r="N423" s="19" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="424" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A424" s="19" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B424" s="19" t="s">
+        <v>513</v>
+      </c>
+      <c r="C424" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D424" s="19" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E424" s="20">
+        <v>289.6</v>
+      </c>
+      <c r="F424" s="19" t="s">
+        <v>1180</v>
+      </c>
+      <c r="G424" s="20">
+        <v>283.75</v>
+      </c>
+      <c r="H424" s="20">
+        <v>282.25</v>
+      </c>
+      <c r="I424" s="20">
+        <v>282.7</v>
+      </c>
+      <c r="J424" s="19"/>
+      <c r="K424" s="19"/>
+      <c r="L424" s="19"/>
+      <c r="M424" s="19"/>
+      <c r="N424" s="19" t="s">
+        <v>1182</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pattern_signals.xlsx
+++ b/pattern_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2608" uniqueCount="1183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2704" uniqueCount="1222">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -3563,6 +3563,123 @@
   </si>
   <si>
     <t>2026-03-16 15:32</t>
+  </si>
+  <si>
+    <t>NSE:ABCAPITAL-EQ_BULL_1773725400_1773729000</t>
+  </si>
+  <si>
+    <t>2026-03-17 11:00</t>
+  </si>
+  <si>
+    <t>2026-03-17 11:45</t>
+  </si>
+  <si>
+    <t>2026-03-17 12:00</t>
+  </si>
+  <si>
+    <t>FIRST RUN (notified)</t>
+  </si>
+  <si>
+    <t>2026-03-17 17:57</t>
+  </si>
+  <si>
+    <t>NSE:ASIANPAINT-EQ_BULL_1773721800_1773730800</t>
+  </si>
+  <si>
+    <t>2026-03-17 10:00</t>
+  </si>
+  <si>
+    <t>2026-03-17 12:15</t>
+  </si>
+  <si>
+    <t>2026-03-17 12:30</t>
+  </si>
+  <si>
+    <t>NSE:AUROPHARMA-EQ_BEAR_1773638100_1773722700</t>
+  </si>
+  <si>
+    <t>2026-03-17 10:15</t>
+  </si>
+  <si>
+    <t>NSE:CHOLAFIN-EQ_BEAR_1773727200_1773733500</t>
+  </si>
+  <si>
+    <t>2026-03-17 11:30</t>
+  </si>
+  <si>
+    <t>2026-03-17 13:00</t>
+  </si>
+  <si>
+    <t>2026-03-17 13:15</t>
+  </si>
+  <si>
+    <t>2026-03-17 17:58</t>
+  </si>
+  <si>
+    <t>NSE:CROMPTON-EQ_BULL_1773720900_1773732600</t>
+  </si>
+  <si>
+    <t>NSE:CROMPTON-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-17 09:45</t>
+  </si>
+  <si>
+    <t>2026-03-17 12:45</t>
+  </si>
+  <si>
+    <t>NSE:DIXON-EQ_BEAR_1773726300_1773739800</t>
+  </si>
+  <si>
+    <t>2026-03-17 11:15</t>
+  </si>
+  <si>
+    <t>2026-03-17 14:45</t>
+  </si>
+  <si>
+    <t>2026-03-17 15:00</t>
+  </si>
+  <si>
+    <t>NSE:IIFL-EQ_BEAR_1773632700_1773719100</t>
+  </si>
+  <si>
+    <t>2026-03-17 09:15</t>
+  </si>
+  <si>
+    <t>NSE:ITC-EQ_BULL_1773729000_1773736200</t>
+  </si>
+  <si>
+    <t>2026-03-17 13:45</t>
+  </si>
+  <si>
+    <t>2026-03-17 14:00</t>
+  </si>
+  <si>
+    <t>NSE:JSWENERGY-EQ_BULL_1773722700_1773732600</t>
+  </si>
+  <si>
+    <t>NSE:POLICYBZR-EQ_BULL_1773650700_1773729900</t>
+  </si>
+  <si>
+    <t>2026-03-16 14:15</t>
+  </si>
+  <si>
+    <t>NSE:PERSISTENT-EQ_BEAR_1773720000_1773739800</t>
+  </si>
+  <si>
+    <t>NSE:PERSISTENT-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-17 09:30</t>
+  </si>
+  <si>
+    <t>NSE:TORNTPOWER-EQ_BEAR_1773728100_1773739800</t>
+  </si>
+  <si>
+    <t>NSE:TORNTPOWER-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-17 17:59</t>
   </si>
 </sst>
 </file>
@@ -4038,7 +4155,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N424"/>
+  <dimension ref="A1:U436"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -4052,6 +4169,10 @@
     <col min="10" max="12" width="18" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
     <col min="14" max="14" width="22" customWidth="1"/>
+    <col min="15" max="18" width="18" customWidth="1"/>
+    <col min="19" max="19" width="14" customWidth="1"/>
+    <col min="20" max="20" width="16" customWidth="1"/>
+    <col min="21" max="21" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -18983,6 +19104,786 @@
         <v>1182</v>
       </c>
     </row>
+    <row r="425" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A425" s="17" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B425" s="17" t="s">
+        <v>432</v>
+      </c>
+      <c r="C425" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D425" s="17" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E425" s="18">
+        <v>321.6</v>
+      </c>
+      <c r="F425" s="17" t="s">
+        <v>1185</v>
+      </c>
+      <c r="G425" s="18">
+        <v>316.1</v>
+      </c>
+      <c r="H425" s="18">
+        <v>315.9</v>
+      </c>
+      <c r="I425" s="18">
+        <v>314.8</v>
+      </c>
+      <c r="J425" s="18">
+        <v>316.93</v>
+      </c>
+      <c r="K425" s="17" t="s">
+        <v>1186</v>
+      </c>
+      <c r="L425" s="18">
+        <v>315.8</v>
+      </c>
+      <c r="M425" s="18">
+        <v>317.1</v>
+      </c>
+      <c r="N425" s="18">
+        <v>316.67</v>
+      </c>
+      <c r="O425" s="18">
+        <v>317.1</v>
+      </c>
+      <c r="P425" s="18">
+        <v>314.8</v>
+      </c>
+      <c r="Q425" s="18">
+        <v>319.4</v>
+      </c>
+      <c r="R425" s="18">
+        <v>321.7</v>
+      </c>
+      <c r="S425" s="17">
+        <v>10</v>
+      </c>
+      <c r="T425" s="17" t="s">
+        <v>1187</v>
+      </c>
+      <c r="U425" s="17" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="426" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A426" s="17" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B426" s="17" t="s">
+        <v>549</v>
+      </c>
+      <c r="C426" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D426" s="17" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E426" s="18">
+        <v>2253.6</v>
+      </c>
+      <c r="F426" s="17" t="s">
+        <v>1191</v>
+      </c>
+      <c r="G426" s="18">
+        <v>2225</v>
+      </c>
+      <c r="H426" s="18">
+        <v>2222.8</v>
+      </c>
+      <c r="I426" s="18">
+        <v>2218.2</v>
+      </c>
+      <c r="J426" s="18">
+        <v>2224.1</v>
+      </c>
+      <c r="K426" s="17" t="s">
+        <v>1192</v>
+      </c>
+      <c r="L426" s="18">
+        <v>2222.8</v>
+      </c>
+      <c r="M426" s="18">
+        <v>2225.7</v>
+      </c>
+      <c r="N426" s="18">
+        <v>2223.32</v>
+      </c>
+      <c r="O426" s="18">
+        <v>2225.7</v>
+      </c>
+      <c r="P426" s="18">
+        <v>2218.2</v>
+      </c>
+      <c r="Q426" s="18">
+        <v>2233.2</v>
+      </c>
+      <c r="R426" s="18">
+        <v>2240.7</v>
+      </c>
+      <c r="S426" s="17">
+        <v>10</v>
+      </c>
+      <c r="T426" s="17" t="s">
+        <v>1187</v>
+      </c>
+      <c r="U426" s="17" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="427" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A427" s="19" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B427" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="C427" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D427" s="19" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E427" s="20">
+        <v>1274.2</v>
+      </c>
+      <c r="F427" s="19" t="s">
+        <v>1190</v>
+      </c>
+      <c r="G427" s="20">
+        <v>1289.3</v>
+      </c>
+      <c r="H427" s="20">
+        <v>1293.3</v>
+      </c>
+      <c r="I427" s="20">
+        <v>1295</v>
+      </c>
+      <c r="J427" s="20">
+        <v>1289</v>
+      </c>
+      <c r="K427" s="19" t="s">
+        <v>1194</v>
+      </c>
+      <c r="L427" s="20">
+        <v>1294</v>
+      </c>
+      <c r="M427" s="20">
+        <v>1282.8</v>
+      </c>
+      <c r="N427" s="20">
+        <v>1290</v>
+      </c>
+      <c r="O427" s="20">
+        <v>1282.8</v>
+      </c>
+      <c r="P427" s="20">
+        <v>1295</v>
+      </c>
+      <c r="Q427" s="20">
+        <v>1270.6</v>
+      </c>
+      <c r="R427" s="20">
+        <v>1258.4</v>
+      </c>
+      <c r="S427" s="19">
+        <v>23</v>
+      </c>
+      <c r="T427" s="19" t="s">
+        <v>1187</v>
+      </c>
+      <c r="U427" s="19" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="428" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A428" s="19" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B428" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C428" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D428" s="19" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E428" s="20">
+        <v>1525</v>
+      </c>
+      <c r="F428" s="19" t="s">
+        <v>1197</v>
+      </c>
+      <c r="G428" s="20">
+        <v>1529</v>
+      </c>
+      <c r="H428" s="20">
+        <v>1533</v>
+      </c>
+      <c r="I428" s="20">
+        <v>1534.1</v>
+      </c>
+      <c r="J428" s="20">
+        <v>1532.46</v>
+      </c>
+      <c r="K428" s="19" t="s">
+        <v>1198</v>
+      </c>
+      <c r="L428" s="20">
+        <v>1532.8</v>
+      </c>
+      <c r="M428" s="20">
+        <v>1528.8</v>
+      </c>
+      <c r="N428" s="20">
+        <v>1532.79</v>
+      </c>
+      <c r="O428" s="20">
+        <v>1528.8</v>
+      </c>
+      <c r="P428" s="20">
+        <v>1534.1</v>
+      </c>
+      <c r="Q428" s="20">
+        <v>1523.5</v>
+      </c>
+      <c r="R428" s="20">
+        <v>1518.2</v>
+      </c>
+      <c r="S428" s="19">
+        <v>10</v>
+      </c>
+      <c r="T428" s="19" t="s">
+        <v>1187</v>
+      </c>
+      <c r="U428" s="19" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="429" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A429" s="17" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B429" s="17" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C429" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D429" s="17" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E429" s="18">
+        <v>250.25</v>
+      </c>
+      <c r="F429" s="17" t="s">
+        <v>1203</v>
+      </c>
+      <c r="G429" s="18">
+        <v>246.55</v>
+      </c>
+      <c r="H429" s="18">
+        <v>246.3</v>
+      </c>
+      <c r="I429" s="18">
+        <v>246.1</v>
+      </c>
+      <c r="J429" s="18">
+        <v>246.56</v>
+      </c>
+      <c r="K429" s="17" t="s">
+        <v>1197</v>
+      </c>
+      <c r="L429" s="18">
+        <v>246.6</v>
+      </c>
+      <c r="M429" s="18">
+        <v>247.75</v>
+      </c>
+      <c r="N429" s="18">
+        <v>246.55</v>
+      </c>
+      <c r="O429" s="18">
+        <v>247.75</v>
+      </c>
+      <c r="P429" s="18">
+        <v>246.1</v>
+      </c>
+      <c r="Q429" s="18">
+        <v>249.4</v>
+      </c>
+      <c r="R429" s="18">
+        <v>251.05</v>
+      </c>
+      <c r="S429" s="17">
+        <v>13</v>
+      </c>
+      <c r="T429" s="17" t="s">
+        <v>1187</v>
+      </c>
+      <c r="U429" s="17" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="430" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A430" s="19" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B430" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="C430" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D430" s="19" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E430" s="20">
+        <v>10250</v>
+      </c>
+      <c r="F430" s="19" t="s">
+        <v>1206</v>
+      </c>
+      <c r="G430" s="20">
+        <v>10314</v>
+      </c>
+      <c r="H430" s="20">
+        <v>10347</v>
+      </c>
+      <c r="I430" s="20">
+        <v>10347</v>
+      </c>
+      <c r="J430" s="20">
+        <v>10312.44</v>
+      </c>
+      <c r="K430" s="19" t="s">
+        <v>1207</v>
+      </c>
+      <c r="L430" s="20">
+        <v>10346</v>
+      </c>
+      <c r="M430" s="20">
+        <v>10297</v>
+      </c>
+      <c r="N430" s="20">
+        <v>10319.16</v>
+      </c>
+      <c r="O430" s="20">
+        <v>10297</v>
+      </c>
+      <c r="P430" s="20">
+        <v>10347</v>
+      </c>
+      <c r="Q430" s="20">
+        <v>10247</v>
+      </c>
+      <c r="R430" s="20">
+        <v>10197</v>
+      </c>
+      <c r="S430" s="19">
+        <v>15</v>
+      </c>
+      <c r="T430" s="19" t="s">
+        <v>1187</v>
+      </c>
+      <c r="U430" s="19" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="431" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A431" s="19" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B431" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C431" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D431" s="19" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E431" s="20">
+        <v>465.55</v>
+      </c>
+      <c r="F431" s="19" t="s">
+        <v>1180</v>
+      </c>
+      <c r="G431" s="20">
+        <v>475.15</v>
+      </c>
+      <c r="H431" s="20">
+        <v>478.25</v>
+      </c>
+      <c r="I431" s="20">
+        <v>479</v>
+      </c>
+      <c r="J431" s="20">
+        <v>474.42</v>
+      </c>
+      <c r="K431" s="19" t="s">
+        <v>1209</v>
+      </c>
+      <c r="L431" s="20">
+        <v>475</v>
+      </c>
+      <c r="M431" s="20">
+        <v>464.15</v>
+      </c>
+      <c r="N431" s="20">
+        <v>474.54</v>
+      </c>
+      <c r="O431" s="20">
+        <v>464.15</v>
+      </c>
+      <c r="P431" s="20">
+        <v>479</v>
+      </c>
+      <c r="Q431" s="20">
+        <v>449.3</v>
+      </c>
+      <c r="R431" s="20">
+        <v>434.45</v>
+      </c>
+      <c r="S431" s="19">
+        <v>25</v>
+      </c>
+      <c r="T431" s="19" t="s">
+        <v>1187</v>
+      </c>
+      <c r="U431" s="19" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="432" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A432" s="17" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B432" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="C432" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D432" s="17" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E432" s="18">
+        <v>306.75</v>
+      </c>
+      <c r="F432" s="17" t="s">
+        <v>1211</v>
+      </c>
+      <c r="G432" s="18">
+        <v>305.95</v>
+      </c>
+      <c r="H432" s="18">
+        <v>305.7</v>
+      </c>
+      <c r="I432" s="18">
+        <v>305.6</v>
+      </c>
+      <c r="J432" s="18">
+        <v>305.93</v>
+      </c>
+      <c r="K432" s="17" t="s">
+        <v>1212</v>
+      </c>
+      <c r="L432" s="18">
+        <v>305.7</v>
+      </c>
+      <c r="M432" s="18">
+        <v>306.25</v>
+      </c>
+      <c r="N432" s="18">
+        <v>305.88</v>
+      </c>
+      <c r="O432" s="18">
+        <v>306.25</v>
+      </c>
+      <c r="P432" s="18">
+        <v>305.6</v>
+      </c>
+      <c r="Q432" s="18">
+        <v>306.9</v>
+      </c>
+      <c r="R432" s="18">
+        <v>307.55</v>
+      </c>
+      <c r="S432" s="17">
+        <v>10</v>
+      </c>
+      <c r="T432" s="17" t="s">
+        <v>1187</v>
+      </c>
+      <c r="U432" s="17" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="433" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A433" s="17" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B433" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="C433" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D433" s="17" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E433" s="18">
+        <v>509.8</v>
+      </c>
+      <c r="F433" s="17" t="s">
+        <v>1203</v>
+      </c>
+      <c r="G433" s="18">
+        <v>505.65</v>
+      </c>
+      <c r="H433" s="18">
+        <v>505</v>
+      </c>
+      <c r="I433" s="18">
+        <v>504.05</v>
+      </c>
+      <c r="J433" s="18">
+        <v>505.54</v>
+      </c>
+      <c r="K433" s="17" t="s">
+        <v>1197</v>
+      </c>
+      <c r="L433" s="18">
+        <v>505.1</v>
+      </c>
+      <c r="M433" s="18">
+        <v>507.6</v>
+      </c>
+      <c r="N433" s="18">
+        <v>505.45</v>
+      </c>
+      <c r="O433" s="18">
+        <v>507.6</v>
+      </c>
+      <c r="P433" s="18">
+        <v>504.05</v>
+      </c>
+      <c r="Q433" s="18">
+        <v>511.15</v>
+      </c>
+      <c r="R433" s="18">
+        <v>514.7</v>
+      </c>
+      <c r="S433" s="17">
+        <v>11</v>
+      </c>
+      <c r="T433" s="17" t="s">
+        <v>1187</v>
+      </c>
+      <c r="U433" s="17" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="434" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A434" s="17" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B434" s="17" t="s">
+        <v>458</v>
+      </c>
+      <c r="C434" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D434" s="17" t="s">
+        <v>1215</v>
+      </c>
+      <c r="E434" s="18">
+        <v>1469.4</v>
+      </c>
+      <c r="F434" s="17" t="s">
+        <v>1186</v>
+      </c>
+      <c r="G434" s="18">
+        <v>1484.9</v>
+      </c>
+      <c r="H434" s="18">
+        <v>1481.7</v>
+      </c>
+      <c r="I434" s="18">
+        <v>1480.5</v>
+      </c>
+      <c r="J434" s="18">
+        <v>1481.83</v>
+      </c>
+      <c r="K434" s="17" t="s">
+        <v>1191</v>
+      </c>
+      <c r="L434" s="18">
+        <v>1481.9</v>
+      </c>
+      <c r="M434" s="18">
+        <v>1485.5</v>
+      </c>
+      <c r="N434" s="18">
+        <v>1481.49</v>
+      </c>
+      <c r="O434" s="18">
+        <v>1485.5</v>
+      </c>
+      <c r="P434" s="18">
+        <v>1480.5</v>
+      </c>
+      <c r="Q434" s="18">
+        <v>1490.5</v>
+      </c>
+      <c r="R434" s="18">
+        <v>1495.5</v>
+      </c>
+      <c r="S434" s="17">
+        <v>17</v>
+      </c>
+      <c r="T434" s="17" t="s">
+        <v>1187</v>
+      </c>
+      <c r="U434" s="17" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="435" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A435" s="19" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B435" s="19" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C435" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D435" s="19" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E435" s="20">
+        <v>4549.9</v>
+      </c>
+      <c r="F435" s="19" t="s">
+        <v>1206</v>
+      </c>
+      <c r="G435" s="20">
+        <v>4539.9</v>
+      </c>
+      <c r="H435" s="20">
+        <v>4544</v>
+      </c>
+      <c r="I435" s="20">
+        <v>4546.5</v>
+      </c>
+      <c r="J435" s="20">
+        <v>4542.93</v>
+      </c>
+      <c r="K435" s="19" t="s">
+        <v>1207</v>
+      </c>
+      <c r="L435" s="20">
+        <v>4544</v>
+      </c>
+      <c r="M435" s="20">
+        <v>4534.3</v>
+      </c>
+      <c r="N435" s="20">
+        <v>4543.3</v>
+      </c>
+      <c r="O435" s="20">
+        <v>4534.3</v>
+      </c>
+      <c r="P435" s="20">
+        <v>4546.5</v>
+      </c>
+      <c r="Q435" s="20">
+        <v>4522.1</v>
+      </c>
+      <c r="R435" s="20">
+        <v>4509.9</v>
+      </c>
+      <c r="S435" s="19">
+        <v>22</v>
+      </c>
+      <c r="T435" s="19" t="s">
+        <v>1187</v>
+      </c>
+      <c r="U435" s="19" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="436" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A436" s="19" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B436" s="19" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C436" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D436" s="19" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E436" s="20">
+        <v>1445.5</v>
+      </c>
+      <c r="F436" s="19" t="s">
+        <v>1206</v>
+      </c>
+      <c r="G436" s="20">
+        <v>1449</v>
+      </c>
+      <c r="H436" s="20">
+        <v>1450.6</v>
+      </c>
+      <c r="I436" s="20">
+        <v>1453.2</v>
+      </c>
+      <c r="J436" s="20">
+        <v>1448.92</v>
+      </c>
+      <c r="K436" s="19" t="s">
+        <v>1207</v>
+      </c>
+      <c r="L436" s="20">
+        <v>1451.7</v>
+      </c>
+      <c r="M436" s="20">
+        <v>1444.6</v>
+      </c>
+      <c r="N436" s="20">
+        <v>1449.48</v>
+      </c>
+      <c r="O436" s="20">
+        <v>1444.6</v>
+      </c>
+      <c r="P436" s="20">
+        <v>1453.2</v>
+      </c>
+      <c r="Q436" s="20">
+        <v>1436</v>
+      </c>
+      <c r="R436" s="20">
+        <v>1427.4</v>
+      </c>
+      <c r="S436" s="19">
+        <v>13</v>
+      </c>
+      <c r="T436" s="19" t="s">
+        <v>1187</v>
+      </c>
+      <c r="U436" s="19" t="s">
+        <v>1221</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pattern_signals.xlsx
+++ b/pattern_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2704" uniqueCount="1222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2712" uniqueCount="1227">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -3680,6 +3680,21 @@
   </si>
   <si>
     <t>2026-03-17 17:59</t>
+  </si>
+  <si>
+    <t>NSE:GRASIM-EQ_BULL_1773723600_1773805500</t>
+  </si>
+  <si>
+    <t>2026-03-17 10:30</t>
+  </si>
+  <si>
+    <t>2026-03-17 15:15</t>
+  </si>
+  <si>
+    <t>2026-03-18 09:15</t>
+  </si>
+  <si>
+    <t>2026-03-18 09:50</t>
   </si>
 </sst>
 </file>
@@ -4155,7 +4170,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:U436"/>
+  <dimension ref="A1:U437"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -19884,6 +19899,71 @@
         <v>1221</v>
       </c>
     </row>
+    <row r="437" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A437" s="17" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B437" s="17" t="s">
+        <v>877</v>
+      </c>
+      <c r="C437" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D437" s="17" t="s">
+        <v>1223</v>
+      </c>
+      <c r="E437" s="18">
+        <v>2677.2</v>
+      </c>
+      <c r="F437" s="17" t="s">
+        <v>1224</v>
+      </c>
+      <c r="G437" s="18">
+        <v>2682.7</v>
+      </c>
+      <c r="H437" s="18">
+        <v>2677</v>
+      </c>
+      <c r="I437" s="18">
+        <v>2677</v>
+      </c>
+      <c r="J437" s="18">
+        <v>2680.26</v>
+      </c>
+      <c r="K437" s="17" t="s">
+        <v>1225</v>
+      </c>
+      <c r="L437" s="18">
+        <v>2699</v>
+      </c>
+      <c r="M437" s="18">
+        <v>2711.4</v>
+      </c>
+      <c r="N437" s="18">
+        <v>2681.55</v>
+      </c>
+      <c r="O437" s="18">
+        <v>2711.4</v>
+      </c>
+      <c r="P437" s="18">
+        <v>2677</v>
+      </c>
+      <c r="Q437" s="18">
+        <v>2745.8</v>
+      </c>
+      <c r="R437" s="18">
+        <v>2780.2</v>
+      </c>
+      <c r="S437" s="17">
+        <v>20</v>
+      </c>
+      <c r="T437" s="17" t="s">
+        <v>1187</v>
+      </c>
+      <c r="U437" s="17" t="s">
+        <v>1226</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pattern_signals.xlsx
+++ b/pattern_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1624" uniqueCount="810">
   <si>
     <t>Pattern ID</t>
   </si>
@@ -2405,6 +2405,45 @@
   </si>
   <si>
     <t>2026-03-09 15:01</t>
+  </si>
+  <si>
+    <t>NSE:TORNTPHARM-EQ_BULL_1773046800_1773114300</t>
+  </si>
+  <si>
+    <t>2026-03-09 14:30</t>
+  </si>
+  <si>
+    <t>2026-03-10 09:15</t>
+  </si>
+  <si>
+    <t>2026-03-10 11:47</t>
+  </si>
+  <si>
+    <t>NSE:GLENMARK-EQ_BULL_1773045900_1773120600</t>
+  </si>
+  <si>
+    <t>2026-03-09 14:15</t>
+  </si>
+  <si>
+    <t>2026-03-10 11:00</t>
+  </si>
+  <si>
+    <t>2026-03-10 12:15</t>
+  </si>
+  <si>
+    <t>NSE:CYIENT-EQ_BULL_1773126900_1773200700</t>
+  </si>
+  <si>
+    <t>NSE:CYIENT-EQ</t>
+  </si>
+  <si>
+    <t>2026-03-10 12:45</t>
+  </si>
+  <si>
+    <t>2026-03-11 09:15</t>
+  </si>
+  <si>
+    <t>2026-03-11 11:30</t>
   </si>
 </sst>
 </file>
@@ -2868,7 +2907,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N257"/>
+  <dimension ref="A1:N260"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -11801,6 +11840,114 @@
         <v>796</v>
       </c>
     </row>
+    <row r="258" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A258" s="11" t="s">
+        <v>797</v>
+      </c>
+      <c r="B258" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="C258" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D258" s="11" t="s">
+        <v>798</v>
+      </c>
+      <c r="E258" s="12">
+        <v>4360</v>
+      </c>
+      <c r="F258" s="11" t="s">
+        <v>799</v>
+      </c>
+      <c r="G258" s="12">
+        <v>4432</v>
+      </c>
+      <c r="H258" s="12">
+        <v>4389</v>
+      </c>
+      <c r="I258" s="12">
+        <v>4428.5</v>
+      </c>
+      <c r="J258" s="11"/>
+      <c r="K258" s="11"/>
+      <c r="L258" s="11"/>
+      <c r="M258" s="11"/>
+      <c r="N258" s="11" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="259" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A259" s="11" t="s">
+        <v>801</v>
+      </c>
+      <c r="B259" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="C259" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D259" s="11" t="s">
+        <v>802</v>
+      </c>
+      <c r="E259" s="12">
+        <v>2105.8</v>
+      </c>
+      <c r="F259" s="11" t="s">
+        <v>803</v>
+      </c>
+      <c r="G259" s="12">
+        <v>2198.6</v>
+      </c>
+      <c r="H259" s="12">
+        <v>2175.3</v>
+      </c>
+      <c r="I259" s="12">
+        <v>2191.6</v>
+      </c>
+      <c r="J259" s="11"/>
+      <c r="K259" s="11"/>
+      <c r="L259" s="11"/>
+      <c r="M259" s="11"/>
+      <c r="N259" s="11" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="260" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A260" s="11" t="s">
+        <v>805</v>
+      </c>
+      <c r="B260" s="11" t="s">
+        <v>806</v>
+      </c>
+      <c r="C260" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D260" s="11" t="s">
+        <v>807</v>
+      </c>
+      <c r="E260" s="12">
+        <v>888.55</v>
+      </c>
+      <c r="F260" s="11" t="s">
+        <v>808</v>
+      </c>
+      <c r="G260" s="12">
+        <v>928</v>
+      </c>
+      <c r="H260" s="12">
+        <v>900</v>
+      </c>
+      <c r="I260" s="12">
+        <v>924.65</v>
+      </c>
+      <c r="J260" s="11"/>
+      <c r="K260" s="11"/>
+      <c r="L260" s="11"/>
+      <c r="M260" s="11"/>
+      <c r="N260" s="11" t="s">
+        <v>809</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
